--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI16"/>
+  <dimension ref="A1:AI26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,68 +603,68 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8918399134670087</v>
+        <v>1.37713506060395</v>
       </c>
       <c r="D2" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4146522417229446</v>
+        <v>0.08359037233672091</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2835630784532303</v>
+        <v>0.2850805651294578</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.810812230634564</v>
+        <v>1.248342443837526</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.073837351569227</v>
+        <v>0.08329848985772981</v>
       </c>
       <c r="I2" t="n">
-        <v>1.073886284574249</v>
+        <v>-0.08329576708676574</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.21822742662512</v>
+        <v>0.3577501779234991</v>
       </c>
       <c r="K2" t="n">
-        <v>0.154224863342322</v>
+        <v>0.8893678011647782</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5779604926390248</v>
+        <v>1.849279955539432</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.873154902621778</v>
+        <v>0.3592647761527498</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.434982714052587</v>
+        <v>3.079310452785065</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7491051177680702</v>
+        <v>0.6951676880997961</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6810148768734923</v>
+        <v>4.214702469337768</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.300833750895663</v>
+        <v>-1.380170982282029</v>
       </c>
       <c r="R2" t="n">
-        <v>-2.678637133400926</v>
+        <v>1.588146069813711</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.269498205480952</v>
+        <v>0.7982875000831346</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8013182701104554</v>
+        <v>-0.4633540167947378</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -673,107 +673,107 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4932177052508289</v>
+        <v>1.49461309572772</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.9100212713517273</v>
+        <v>1.231546204023025</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.132211386953151</v>
+        <v>1.414825099284884</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6043327666503044</v>
+        <v>-0.491889002337783</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1.108078608409123</v>
+        <v>1.26388223424452</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8422089578672457</v>
+        <v>0.01969879131520835</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.443289510510791</v>
+        <v>1.38161754853354</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.269927750938855</v>
+        <v>1.587728308100283</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.434789898782155</v>
+        <v>1.979371650634541</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.8090238902893245</v>
+        <v>2.057627221086355</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.1858797637867726</v>
+        <v>0.7181822513192559</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C3" t="n">
-        <v>1.597034424150377</v>
+        <v>1.37713506060395</v>
       </c>
       <c r="D3" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4157521150431646</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1903066245323431</v>
+        <v>-0.5678849002445744</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.869966905106654</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5452691277075311</v>
+        <v>-0.4309841063320289</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5452969523340327</v>
+        <v>0.4310073669847965</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4789792244272392</v>
+        <v>-0.1271660080914603</v>
       </c>
       <c r="K3" t="n">
-        <v>1.357186034324523</v>
+        <v>0.6888742726677447</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3301248380041233</v>
+        <v>-1.238210168647272</v>
       </c>
       <c r="M3" t="n">
         <v>0.7700713357442589</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3058530112157789</v>
+        <v>-0.9118181719443772</v>
       </c>
       <c r="O3" t="n">
-        <v>1.706158652207303</v>
+        <v>1.211678810198304</v>
       </c>
       <c r="P3" t="n">
-        <v>1.050397355323173</v>
+        <v>-0.9994355172774767</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.904039512581734</v>
+        <v>-0.1107752801001733</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7638811328290654</v>
+        <v>1.103284342175684</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5268440273970857</v>
+        <v>-1.072724661002653</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3121053595335355</v>
+        <v>-0.01517534387602885</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -782,107 +782,107 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.224201137925904</v>
+        <v>-0.6660179834180622</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.410129093411008</v>
+        <v>-0.2852932695516225</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.993814492722347</v>
+        <v>-0.2934200502236396</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.5986559046118181</v>
+        <v>0.3922323513804653</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.411785146322436</v>
+        <v>-0.2797711952719986</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.645640875674063</v>
+        <v>1.433360127425415</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.8921519072992897</v>
+        <v>-0.7452893830435103</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.9022555148124438</v>
+        <v>-0.6134669264764532</v>
       </c>
       <c r="AF3" t="n">
-        <v>-2.122592165704877</v>
+        <v>-0.519051440935859</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1.728931513975355</v>
+        <v>-0.3815092424945759</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.283931335996497</v>
+        <v>-0.6482356727190127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C4" t="n">
-        <v>1.339221377233877</v>
+        <v>1.597034424150377</v>
       </c>
       <c r="D4" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4146522417229446</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.09401519725900095</v>
+        <v>-0.1887891378561156</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.398981295740146</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8547223841423679</v>
+        <v>-1.259550511304418</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8547504681941092</v>
+        <v>1.259606860766758</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7214373174347188</v>
+        <v>-1.21822742662512</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.717048069296657</v>
+        <v>2.626978381472402</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.419827234775901</v>
+        <v>-1.78306136703316</v>
       </c>
       <c r="M4" t="n">
-        <v>1.591684454927278</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.65658516201982</v>
+        <v>-2.298546892729021</v>
       </c>
       <c r="O4" t="n">
-        <v>2.068450813679242</v>
+        <v>0.09787520567308552</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.755684538236939</v>
+        <v>-1.676079378135944</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999459593089504</v>
+        <v>-0.1107752801001733</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4244779234824463</v>
+        <v>-1.321024296014451</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2251846759667669</v>
+        <v>-0.1962144594129164</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.299588913698293</v>
+        <v>-1.530226518054245</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -891,107 +891,107 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1371968681964333</v>
+        <v>-0.248235798813542</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07697843419222514</v>
+        <v>-0.07339576348902506</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.09682031532781767</v>
+        <v>-0.3943439502089759</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.5926747454746231</v>
+        <v>-0.8805298268276671</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01834574143529453</v>
+        <v>-0.5381917775653837</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.2202771008883722</v>
+        <v>-1.024755030406695</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.1926522599588997</v>
+        <v>-0.3649086634728636</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.2570233689241815</v>
+        <v>0.05663865645132861</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.06047289497370743</v>
+        <v>-0.209642011981749</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.2992762486648831</v>
+        <v>-0.4212614023404438</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.8399994474895361</v>
+        <v>0.4102364739929419</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6112786565284644</v>
+        <v>-0.874937731578419</v>
       </c>
       <c r="D5" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4157521150431646</v>
+        <v>-1.411137469842276</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0007587433381137274</v>
+        <v>-1.705172187409951</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8365115089431081</v>
+        <v>-0.810812230634564</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5166978723636554</v>
+        <v>-0.8166960534743479</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5167245559967235</v>
+        <v>0.8167347175384682</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3696241010989402</v>
+        <v>0.7214373174347188</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1130998413203891</v>
+        <v>0.4883807441707113</v>
       </c>
       <c r="L5" t="n">
-        <v>2.394131153925321</v>
+        <v>0.2147263603817656</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.489364742009042</v>
+        <v>2.207894294314541</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8450094825587373</v>
+        <v>0.7216431713192469</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.412491440463311</v>
+        <v>0.6290738478312667</v>
       </c>
       <c r="P5" t="n">
-        <v>2.423586367065355</v>
+        <v>0.3936547844899549</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7619342651498524</v>
+        <v>1.356963500547597</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.902858369180083</v>
+        <v>2.751814216144976</v>
       </c>
       <c r="S5" t="n">
-        <v>0.102136128435901</v>
+        <v>1.214067980324422</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3177831012299182</v>
+        <v>-0.3599503843232972</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1000,107 +1000,107 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06439475024434588</v>
+        <v>-0.2153038453222748</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.02592700599265186</v>
+        <v>-1.505299228796994</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.2935681647769423</v>
+        <v>-1.287210710922481</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.311884984092761</v>
+        <v>-0.3801611210577399</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.1949593674594895</v>
+        <v>-0.6856781321136279</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8286887001068362</v>
+        <v>1.031492566512993</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.268336569534327</v>
+        <v>-0.9908263431704764</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.4312890917822899</v>
+        <v>-1.220341267097778</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.3196051672913867</v>
+        <v>-1.626855342335622</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.02994269153963446</v>
+        <v>-0.112518633485026</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.6915670560254653</v>
+        <v>1.177123068544223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7477679166607292</v>
+        <v>-0.874937731578419</v>
       </c>
       <c r="D6" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4157521150431646</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F6" t="n">
-        <v>1.043272089906375</v>
+        <v>0.0007587433381137274</v>
       </c>
       <c r="G6" t="n">
-        <v>2.48383524852078</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H6" t="n">
-        <v>1.397576235676002</v>
+        <v>1.326148097316313</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.397625998602981</v>
+        <v>-1.326195007759708</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8545402871139001</v>
+        <v>-1.09699838012138</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.514086898314456</v>
+        <v>0.08739368717664438</v>
       </c>
       <c r="L6" t="n">
-        <v>2.75736528618258</v>
+        <v>4.028684749082988</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.543397539966588</v>
+        <v>-4.570413938945361</v>
       </c>
       <c r="N6" t="n">
-        <v>3.451693947822787</v>
+        <v>1.221962100234958</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.772286330050807</v>
+        <v>-3.182337607653933</v>
       </c>
       <c r="P6" t="n">
-        <v>4.851543750145735</v>
+        <v>1.468324445853402</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.632997469123034</v>
+        <v>-3.998299618032106</v>
       </c>
       <c r="R6" t="n">
-        <v>-6.169641572394721</v>
+        <v>-5.97569688133951</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5099851341415469</v>
+        <v>0.4797097537360951</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.04564642919183598</v>
+        <v>0.2073183912164612</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1109,107 +1109,107 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8579068055738028</v>
+        <v>-1.015564932989378</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.752497315098807</v>
+        <v>0.01539523552852866</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.820342070770335</v>
+        <v>-0.1333224315583821</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1253364572702831</v>
+        <v>0.0006033990119951412</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.357634665959755</v>
+        <v>-0.4522798162849485</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.9524870271204698</v>
+        <v>-1.357920888305204</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.438603071349568</v>
+        <v>-0.0168693473966234</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.336671537752975</v>
+        <v>-0.287451976597784</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.977436376004106</v>
+        <v>-0.1161313697065667</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.025360848224572</v>
+        <v>-1.023806330836888</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.417912536648558</v>
+        <v>0.7984313243851581</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7477679166607292</v>
+        <v>-0.3593116377454187</v>
       </c>
       <c r="D7" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08249049901650093</v>
+        <v>-0.2485713703697228</v>
       </c>
       <c r="F7" t="n">
         <v>0.1903066245323431</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01284963915427201</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.43812085720364</v>
+        <v>-2.145259426964558</v>
       </c>
       <c r="I7" t="n">
-        <v>1.438184337874939</v>
+        <v>2.145351147223337</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3696241010989402</v>
+        <v>0.7214373174347188</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.416307776551107</v>
+        <v>1.290354858158845</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7595775587676545</v>
+        <v>-3.054380829933568</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.105574581396306</v>
+        <v>3.440313973089069</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.758752563554639</v>
+        <v>-3.98683770765464</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.276631879911333</v>
+        <v>2.839545616812086</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5616071367219981</v>
+        <v>-3.905023860963833</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1901125114865394</v>
+        <v>2.904039512581734</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.175565777723043</v>
+        <v>3.624565325893424</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1208308363061085</v>
+        <v>1.555120347225045</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6623174778209597</v>
+        <v>0.3912298595322262</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1218,107 +1218,107 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1273031985113343</v>
+        <v>-0.3022981762194435</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.05450943459587675</v>
+        <v>0.2917936209072263</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06897820055755884</v>
+        <v>0.1333140762726866</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5763765380341489</v>
+        <v>0.7515615792202713</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2273510979158995</v>
+        <v>0.2501238607021111</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.8695091216852507</v>
+        <v>0.2432485566662109</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.1918233796270364</v>
+        <v>0.2091617979387357</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.7639113608425089</v>
+        <v>-0.05397655999473026</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.1051291630014064</v>
+        <v>0.0729270589869757</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.2776370358799312</v>
+        <v>0.1266563645613566</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.296318168869189</v>
+        <v>0.2246834016652738</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C8" t="n">
-        <v>1.339221377233877</v>
+        <v>0.6112786565284644</v>
       </c>
       <c r="D8" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E8" t="n">
-        <v>1.744399085868939</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4746284463236872</v>
+        <v>0.09553268393522843</v>
       </c>
       <c r="G8" t="n">
-        <v>2.072004313626362</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04044160684191658</v>
+        <v>2.240428268320329</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.04043717258080222</v>
+        <v>-2.240511690553596</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1514118173922085</v>
+        <v>1.206353503449679</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6343830154126764</v>
+        <v>-3.454658649604279</v>
       </c>
       <c r="L8" t="n">
-        <v>2.067220434893788</v>
+        <v>0.2147263603817656</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3801870311119669</v>
+        <v>-0.4623483430302688</v>
       </c>
       <c r="N8" t="n">
-        <v>1.374113884096997</v>
+        <v>0.298999327258029</v>
       </c>
       <c r="O8" t="n">
-        <v>1.03298064947228</v>
+        <v>-0.9743137586830593</v>
       </c>
       <c r="P8" t="n">
-        <v>1.157864321459517</v>
+        <v>0.5926676847424448</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9523436204771309</v>
+        <v>-1.419839597975212</v>
       </c>
       <c r="R8" t="n">
-        <v>0.599028145432136</v>
+        <v>-0.9331349139040293</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.502551779089928</v>
+        <v>0.5919267827501704</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.165225628954651</v>
+        <v>-0.149258804740747</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1327,107 +1327,107 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7683013280166845</v>
+        <v>2.34952371115793</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6082449542815018</v>
+        <v>2.145503277417505</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5596150832883047</v>
+        <v>2.709312569597958</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5024336238479286</v>
+        <v>-0.2811838371119872</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9433335201752329</v>
+        <v>2.88956253831906</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.40794465178834</v>
+        <v>0.3142883307752303</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.9857227237430525</v>
+        <v>2.777874002843401</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.6668527900325151</v>
+        <v>2.667341788851361</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.6822362447846618</v>
+        <v>2.946345625532425</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.6333264196170865</v>
+        <v>2.719845121714518</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.6906275910973984</v>
+        <v>-1.466299051671496</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.5109663712257129</v>
+        <v>-1.056923411754772</v>
       </c>
       <c r="D9" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7468139844293883</v>
+        <v>-1.078975727135832</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.378337019050345</v>
+        <v>-0.5678849002445744</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.222643165528982</v>
+        <v>-0.810812230634564</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8595529364901612</v>
+        <v>2.097571991600951</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8595933120444317</v>
+        <v>-2.097649708867051</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7214373174347188</v>
+        <v>-0.00593696158772055</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7145804268114895</v>
+        <v>1.089861329661812</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.05769923881117887</v>
+        <v>-1.419827234775901</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9754746155400137</v>
+        <v>0.3592647761527498</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4777515212869103</v>
+        <v>-0.22416521485018</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2154585555999435</v>
+        <v>-0.3917087963160216</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3227916564190099</v>
+        <v>-0.8004226170249864</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9041475939638333</v>
+        <v>-1.142159288122931</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.157356149683186</v>
+        <v>1.297229033230895</v>
       </c>
       <c r="S9" t="n">
-        <v>1.63883830878714</v>
+        <v>-2.54537417277618</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.511841637234328</v>
+        <v>-2.020025598270832</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1436,107 +1436,107 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2050733370106578</v>
+        <v>-0.7709126192920759</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1711041634371105</v>
+        <v>-0.8115391557951772</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.002749390350811867</v>
+        <v>-0.1676518761862107</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.3220947216883759</v>
+        <v>0.1049807978364387</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.004742059571283061</v>
+        <v>-0.4386950912662314</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.5208941901044097</v>
+        <v>0.1333134676393106</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.05677993537613624</v>
+        <v>-0.5596352592562346</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.07418573382958295</v>
+        <v>-0.9549237522145571</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.02333840485530008</v>
+        <v>-0.5016306745404301</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.1357236145246998</v>
+        <v>-0.3506737336568958</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.6478197900074567</v>
+        <v>-1.838676842815548</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C10" t="n">
-        <v>1.013163700251244</v>
+        <v>-0.7763621548162278</v>
       </c>
       <c r="D10" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9128948557826102</v>
+        <v>2.408722571281827</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2835630784532303</v>
+        <v>1.896237555280407</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1.248342443837526</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5166978723636554</v>
+        <v>1.440433118691816</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5167245559967235</v>
+        <v>-1.440484593108944</v>
       </c>
       <c r="J10" t="n">
-        <v>1.266968026701548</v>
+        <v>-0.1271660080914607</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.215814248054073</v>
+        <v>0.2878872156736779</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3301248380041233</v>
+        <v>0.03310929425313586</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.105574581396306</v>
+        <v>0.9754746155400137</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6936425659560193</v>
+        <v>1.014067020183224</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.533663480955614</v>
+        <v>-0.5655111170221552</v>
       </c>
       <c r="P10" t="n">
-        <v>0.453358654565702</v>
+        <v>1.229508965550414</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.737188523520676</v>
+        <v>-2.808241147236616</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.902858369180083</v>
+        <v>-0.3513008407383969</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.353129694999717</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2628713979938229</v>
+        <v>0.5891941717414209</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1545,107 +1545,107 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.566380594291326</v>
+        <v>0.5814224118633787</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.072427870351774</v>
+        <v>1.05278528477952</v>
       </c>
       <c r="Z10" t="n">
-        <v>-1.712055916468547</v>
+        <v>1.089368622597979</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.6893538978107264</v>
+        <v>-0.1342042048407136</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.340265789375291</v>
+        <v>0.9855961649518545</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.2504148496684337</v>
+        <v>-1.259031979692709</v>
       </c>
       <c r="AD10" t="n">
-        <v>-2.353769343414925</v>
+        <v>1.260601020080599</v>
       </c>
       <c r="AE10" t="n">
-        <v>-2.56506783291362</v>
+        <v>1.05212472842119</v>
       </c>
       <c r="AF10" t="n">
-        <v>-2.245036594766701</v>
+        <v>1.353338173699583</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-2.045940823497894</v>
+        <v>0.6163504878899595</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.02247444157545526</v>
+        <v>-1.429507595617219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6112786565284644</v>
+        <v>1.005580963577229</v>
       </c>
       <c r="D11" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E11" t="n">
-        <v>1.744399085868939</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F11" t="n">
-        <v>2.085785436474636</v>
+        <v>-0.4731109596474597</v>
       </c>
       <c r="G11" t="n">
-        <v>1.248342443837526</v>
+        <v>0.42468057404869</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1738428082371496</v>
+        <v>0.7690086181107414</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1738557999490154</v>
+        <v>-0.7690332791821821</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1877805313433304</v>
+        <v>-0.2483950545952001</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.61680130504814</v>
+        <v>1.156692505827489</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3301248380041233</v>
+        <v>-1.056593102518642</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9754746155400137</v>
+        <v>-0.05154178343875964</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6839479095516249</v>
+        <v>0.589138614802757</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3500109666974757</v>
+        <v>-0.3868129562961306</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6921741348686902</v>
+        <v>0.6324702647929431</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.356963500547597</v>
+        <v>-1.697519907827493</v>
       </c>
       <c r="R11" t="n">
-        <v>1.297229033230895</v>
+        <v>-0.7391902228488186</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2480750770005946</v>
+        <v>0.6995240286504462</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3320864105621214</v>
+        <v>-1.013729794052257</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1654,107 +1654,107 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.9584212836373204</v>
+        <v>-0.7110123800706889</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.009212275318014239</v>
+        <v>-0.3348022897736097</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.64803460794662</v>
+        <v>-0.764734113763639</v>
       </c>
       <c r="AA11" t="n">
-        <v>-1.289618497388059</v>
+        <v>-0.2713957558521023</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.5250348352143922</v>
+        <v>-0.832702892199803</v>
       </c>
       <c r="AC11" t="n">
-        <v>-1.185777439329283</v>
+        <v>0.5687725118244784</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.145900422751489</v>
+        <v>-0.9132037932230525</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.136840388875925</v>
+        <v>-0.2460159160142223</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.7460471477817401</v>
+        <v>-0.6666220487050644</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.8392152531009947</v>
+        <v>-1.018677019889034</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.698157774976528</v>
+        <v>-1.706635943035382</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>697ha3El</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.056923411754772</v>
+        <v>0.8918399134670087</v>
       </c>
       <c r="D12" t="n">
-        <v>2.393718654096563</v>
+        <v>-0.5056960363928432</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5818329863963865</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8537242087121459</v>
+        <v>-0.2835630784532303</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8365115089431081</v>
+        <v>-0.810812230634564</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3118685326087335</v>
+        <v>-1.073837351569227</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3118749377852377</v>
+        <v>1.073886284574249</v>
       </c>
       <c r="J12" t="n">
-        <v>2.903560154502037</v>
+        <v>-0.8545402871139001</v>
       </c>
       <c r="K12" t="n">
-        <v>2.760640733803758</v>
+        <v>0.154224863342322</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.872763763804937</v>
+        <v>0.5779604926390248</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3592647761527498</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8775497521556299</v>
+        <v>-1.434982714052587</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.091813919160445</v>
+        <v>-0.7491051177680702</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1635813362170178</v>
+        <v>-0.6810148768734923</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.221496519509297</v>
+        <v>-1.300833750895663</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.3513008407383969</v>
+        <v>-2.678637133400926</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.616235901390139</v>
+        <v>-2.269498205480952</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9711662178089645</v>
+        <v>-0.8215542497984099</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1763,107 +1763,107 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.07663496150480353</v>
+        <v>-0.4852296526093979</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.409800751059402</v>
+        <v>-0.9598319781204386</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.2346691372621008</v>
+        <v>-1.154949645709614</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.9136767431912179</v>
+        <v>0.5348248936958526</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8947189859077489</v>
+        <v>-1.145474683753708</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.5315881218224262</v>
+        <v>0.898393140116064</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.9954614587313523</v>
+        <v>-1.495459238598651</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.679236937270401</v>
+        <v>-1.229946875027577</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2382916859409214</v>
+        <v>-1.437949824044835</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.1929139405145071</v>
+        <v>-0.7968701072846855</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.2339455726560332</v>
+        <v>-0.1885623253177652</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>fmqtFMjD</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C13" t="n">
-        <v>1.63494810752045</v>
+        <v>1.597034424150377</v>
       </c>
       <c r="D13" t="n">
-        <v>2.393718654096563</v>
+        <v>-0.5056960363928432</v>
       </c>
       <c r="E13" t="n">
         <v>0.4157521150431646</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5694023869208018</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01284963915427201</v>
+        <v>-2.869966905106654</v>
       </c>
       <c r="H13" t="n">
-        <v>1.669003161442819</v>
+        <v>-0.5452691277075311</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.669063763807416</v>
+        <v>0.5452969523340327</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.73331124061016</v>
+        <v>0.4789792244272389</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.915073955308523</v>
+        <v>1.357186034324523</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2147263603817656</v>
+        <v>-0.3301248380041233</v>
       </c>
       <c r="M13" t="n">
-        <v>3.440313973089069</v>
+        <v>0.7700713357442589</v>
       </c>
       <c r="N13" t="n">
-        <v>1.434426302925192</v>
+        <v>0.3058530112157789</v>
       </c>
       <c r="O13" t="n">
-        <v>1.451574971172967</v>
+        <v>1.706158652207303</v>
       </c>
       <c r="P13" t="n">
-        <v>0.03543156403547253</v>
+        <v>1.050397355323173</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.428016124263538</v>
+        <v>2.904039512581734</v>
       </c>
       <c r="R13" t="n">
-        <v>5.079150508807505</v>
+        <v>0.7638811328290654</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.286354170896134</v>
+        <v>0.5268440273970857</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.251248975902584</v>
+        <v>0.3219032664487058</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1872,107 +1872,107 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01946609249702566</v>
+        <v>-1.148747991091731</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.7714120596359753</v>
+        <v>-1.361083440614614</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.06899296595429134</v>
+        <v>-2.03897579280563</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.02626367025341976</v>
+        <v>-0.5075376405367464</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.4099971026400017</v>
+        <v>-1.480819983151036</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.509036197265181</v>
+        <v>-1.73139405329007</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.9425219603635665</v>
+        <v>-0.9232725961231154</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.002125204403756</v>
+        <v>-0.8960997224702029</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1062217580317536</v>
+        <v>-2.037846633053485</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.1149901643125172</v>
+        <v>-1.800032113753688</v>
       </c>
       <c r="AI13" t="n">
-        <v>-1.164323460044918</v>
+        <v>1.243100103729532</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>8WpYGrM0</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8994226501410234</v>
+        <v>1.339221377233877</v>
       </c>
       <c r="D14" t="n">
-        <v>2.393718654096563</v>
+        <v>-0.5056960363928432</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.08249049901650093</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1903066245323431</v>
+        <v>-0.09401519725900095</v>
       </c>
       <c r="G14" t="n">
         <v>-0.398981295740146</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.973831894901305</v>
+        <v>0.8547223841423679</v>
       </c>
       <c r="I14" t="n">
-        <v>1.973916769199483</v>
+        <v>-0.8547504681941092</v>
       </c>
       <c r="J14" t="n">
         <v>0.7214373174347188</v>
       </c>
       <c r="K14" t="n">
-        <v>0.08739368717664438</v>
+        <v>-1.717048069296657</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3301248380041233</v>
+        <v>-1.419827234775901</v>
       </c>
       <c r="M14" t="n">
-        <v>2.824104133701805</v>
+        <v>1.591684454927278</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.855341996794555</v>
+        <v>-1.65658516201982</v>
       </c>
       <c r="O14" t="n">
-        <v>4.484547863495486</v>
+        <v>2.068450813679242</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.994500018539928</v>
+        <v>-1.755684538236939</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.666027818422636</v>
+        <v>0.9999459593089504</v>
       </c>
       <c r="R14" t="n">
-        <v>5.079150508807505</v>
+        <v>0.4244779234824463</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.241284315154525</v>
+        <v>0.2251846759667669</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7769769588486537</v>
+        <v>0.3082528125228759</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1981,107 +1981,107 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.007655069013491917</v>
+        <v>-0.1235196449045225</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.06833362283931665</v>
+        <v>0.06308095410829709</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.04715218145994972</v>
+        <v>-0.1024010186404272</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.4340628507515836</v>
+        <v>-0.6179474067113954</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.06727013847007454</v>
+        <v>0.03319754325239105</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.389960093165063</v>
+        <v>0.3190361853522751</v>
       </c>
       <c r="AD14" t="n">
-        <v>-1.231317180307368</v>
+        <v>-0.2111890382898018</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.1316614231249538</v>
+        <v>0.2922638835833277</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.01589503549431402</v>
+        <v>-0.06223090253785078</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0006542446958196771</v>
+        <v>-0.3106830012088025</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0762867368325241</v>
+        <v>-0.7618095157383372</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>nHdPI4il</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.9962615183626544</v>
+        <v>0.6112786565284644</v>
       </c>
       <c r="D15" t="n">
-        <v>2.393718654096563</v>
+        <v>-0.5056960363928432</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08359037233672091</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3798545057265725</v>
+        <v>0.0007587433381137274</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01284963915427201</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H15" t="n">
-        <v>1.626146278427006</v>
+        <v>-0.5166978723636554</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.626205169301453</v>
+        <v>0.5167245559967235</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.00593696158772055</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.516554540799623</v>
+        <v>-0.1130998413203891</v>
       </c>
       <c r="L15" t="n">
-        <v>1.849279955539432</v>
+        <v>2.394131153925321</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3592647761527498</v>
+        <v>-1.489364742009042</v>
       </c>
       <c r="N15" t="n">
-        <v>1.777110500812665</v>
+        <v>0.8450094825587373</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.596085441209226</v>
+        <v>-1.412491440463311</v>
       </c>
       <c r="P15" t="n">
-        <v>1.11010122539892</v>
+        <v>2.423586367065355</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.188358088827596</v>
+        <v>0.7619342651498524</v>
       </c>
       <c r="R15" t="n">
-        <v>-3.066526515511348</v>
+        <v>-1.902858369180083</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.133767980400661</v>
+        <v>0.102136128435901</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5548544149366031</v>
+        <v>0.3320785342904702</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2090,149 +2090,1239 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.007655069013491917</v>
+        <v>0.05218468900235684</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.4410945860044058</v>
+        <v>-0.08089311104841712</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.0833673659496012</v>
+        <v>-0.3006193782736553</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.4642756166093543</v>
+        <v>1.101203659697189</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.5381502340637936</v>
+        <v>-0.1958733244943854</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.2434524395904746</v>
+        <v>0.9021320755954827</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.5861339983204222</v>
+        <v>-0.2789160966792822</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.5765295797458112</v>
+        <v>-0.3655131836626123</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.0939910387720447</v>
+        <v>-0.2709141508462061</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.0006542446958196771</v>
+        <v>-0.03504218091221024</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.06131758470958937</v>
+        <v>-0.6801437109594263</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>tYjCfe2E</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C16" t="n">
+        <v>0.7477679166607292</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.08249049901650093</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1903066245323431</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.01284963915427201</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.43812085720364</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.438184337874939</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.73331124061016</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-1.416307776551107</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.7595775587676545</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-2.105574581396306</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.758752563554639</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-1.276631879911333</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.5616071367219981</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.1901125114865394</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-1.175565777723043</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.1208308363061085</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.5737531787251923</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.04600003343898125</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.07370005387843509</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.07743160144746188</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.5072766934815244</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.2237575850286848</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.7284520931899188</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.1653494441788407</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.7161835233724485</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.1005559837151037</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.2499924355970209</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2.351885360824546</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>pjyqwZx3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.339221377233877</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.744399085868939</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4746284463236872</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.072004313626362</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.04044160684191658</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.04043717258080222</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.07867438948996455</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.6343830154126764</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.067220434893788</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.3801870311119669</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.374113884096997</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.03298064947228</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.157864321459517</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.9523436204771309</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.599028145432136</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-1.502551779089928</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.077883027107298</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.8268405746626207</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.6814063327289538</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.5650552085630076</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.4944855014509028</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9554632784679403</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.3132497375865005</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.009706478899454</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.7772859919888203</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.7430080797058065</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.6351380803152383</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.7306018624284001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>tIUiyD7F</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.5109663712257129</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.7468139844293883</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.378337019050345</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.222643165528982</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.8595529364901612</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8595933120444317</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5395937476791089</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.7145804268114895</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.05769923881117887</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.9754746155400137</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.4777515212869103</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.2154585555999435</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.3227916564190099</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.9041475939638333</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.157356149683186</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.63883830878714</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.527090099165605</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.1616875673890296</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.1493175891296886</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.003009525476421387</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.2954992123815934</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.03124499867783427</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.634731422111817</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.06908880830439977</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.08774967980292016</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.05956835317488387</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.1394140344653798</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.676342401929966</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>CntkHiGq</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7477679166607292</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.4157521150431646</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.043272089906375</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.48383524852078</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.397576235676002</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1.397625998602981</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.73331124061016</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.514086898314456</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.75736528618258</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-3.543397539966588</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.451693947822787</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-3.772286330050807</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.851543750145735</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-4.632997469123034</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-6.169641572394721</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.5099851341415469</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.1216901911667917</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.8679871191728845</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.736116552981189</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.820295671967088</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.1084062407104038</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.366155411233027</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.9069674350207338</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.435909210270993</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.336361966177125</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.957515071869511</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.024130708244346</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-0.3937058763779737</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>t4kJMDhM</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.013163700251244</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.9128948557826102</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.2835630784532303</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.5166978723636554</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5167245559967235</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5395937476791089</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-1.215814248054073</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.3301248380041233</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-2.105574581396306</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.6936425659560193</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-1.533663480955614</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.453358654565702</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1.737188523520676</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-1.902858369180083</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.1667021210409293</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-1.671704907469842</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-2.094600667610797</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-1.773311689315108</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.7123625690587683</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-2.433821754947603</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.1176232919667358</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-2.388853587280236</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-2.583946430335986</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-2.319784908599028</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-2.131469101395831</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-0.04038318167252452</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Kl1AOZN9</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C21" t="n">
         <v>0.6112786565284644</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D21" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.744399085868939</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.085785436474636</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.248342443837526</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.1738428082371496</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1738557999490154</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.3696241010989402</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-1.61680130504814</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.3301248380041233</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.9754746155400137</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.6839479095516249</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.3500109666974757</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.6921741348686902</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.356963500547597</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.297229033230895</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.4416794557715791</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.3631883487735664</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.9171874163941814</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.05756108005260286</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.6286728206214888</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-1.366409678442931</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.5334320777420994</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-1.095024926707563</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.128360279780143</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.144124010030556</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.7371131837915595</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.826473307300301</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.715892944784188</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>697ha3El</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.056923411754772</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5818329863963865</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.8537242087121459</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8365115089431081</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3118685326087335</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.3118749377852377</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.176185875479598</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.760640733803758</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-2.872763763804937</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.3592647761527498</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.8775497521556299</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-1.091813919160445</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.1635813362170178</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.221496519509297</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-0.3513008407383969</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-1.616235901390139</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.049432029168562</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.06472897360612198</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.312068950091571</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.2436832174554022</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.7888265455249338</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9446841245896824</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-0.5355479644245309</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.045357375500735</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.6830191737012737</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.2394022657511447</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.1848800081345542</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.104778429583655</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>634r8bcJ</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.63494810752045</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.4157521150431646</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.5694023869208018</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.01284963915427201</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.669003161442819</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.669063763807416</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.3696241010989402</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.915073955308523</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2147263603817656</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.440313973089069</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.434426302925192</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.451574971172967</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.03543156403547253</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.428016124263538</v>
+      </c>
+      <c r="R23" t="n">
+        <v>5.079150508807505</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-2.286354170896134</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.9803288596577738</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.03882003430873411</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.7844860215671735</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.07021105979703625</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.03454537681271449</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.4188874119794689</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-1.641901940194646</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.015493570671055</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.999183739193184</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.1226622159594722</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.115258558490021</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>-1.376949399600211</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>tOTmlbNp</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8994226501410234</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.08249049901650093</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.1903066245323431</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.398981295740146</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.973831894901305</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.973916769199483</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.00593696158772055</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.08739368717664438</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.3301248380041233</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2.824104133701805</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.855341996794555</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.484547863495486</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.994500018539928</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.666027818422636</v>
+      </c>
+      <c r="R24" t="n">
+        <v>5.079150508807505</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-1.241284315154525</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.8445784734106215</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.007655069013491917</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.0795785394428087</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-0.04095773553290011</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.5222647922784536</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.0957817898045909</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.112534542569239</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>-1.092184090734201</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>-0.2241158146079971</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.02071442016070084</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.0006542446958196771</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.03228290695655738</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.9962615183626544</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.393718654096563</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.08359037233672091</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.3798545057265725</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.01284963915427201</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.626146278427006</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.626205169301453</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.00593696158772055</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.516554540799623</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.849279955539432</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.3592647761527498</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.777110500812665</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.596085441209226</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.11010122539892</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-5.188358088827596</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-3.066526515511348</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-4.133767980400661</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.3888156072405329</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.007655069013491917</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>-0.4589867689793425</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-0.08007658382283023</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.481401746359389</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-0.5274518592164055</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>-0.3309333602506461</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-0.5434929403810099</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>-0.5932449303772731</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.09732975704283472</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.0006542446958196771</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>-0.2639739339115436</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>tYjCfe2E</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2.218427650214686</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.6112786565284644</v>
+      </c>
+      <c r="D26" t="n">
         <v>0.4607755271036255</v>
       </c>
-      <c r="E16" t="n">
-        <v>0.08359037233672091</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.5694023869208018</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-1.6344741004234</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.7738391704585348</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.7738761230325046</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.5395937476791089</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.9896145654132948</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-1.419827234775901</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2.207894294314541</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0.2687141605755519</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.348762330755255</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.468324445853402</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.070998583024891</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.315438661270752</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-0.4416794557715791</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.067807370948323</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.908644591515666</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>-1.129717865306354</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>-1.654377349841564</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>-0.2224146925236383</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>-1.081801336540609</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>-0.9551652402949236</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>-0.6511272072930019</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>-0.8713356554409183</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>-1.914196643874994</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>-1.163595778269236</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.535176641364186</v>
+      <c r="E26" t="n">
+        <v>-0.9128948557826102</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.5678849002445744</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.660173378731944</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.506147005982728</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.506201104684754</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.1877805313433304</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.67694936359725</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.7595775587676545</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.873154902621778</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.5626377034994592</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.7265842536765708</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.969836954489678</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.427422436582059</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-0.9719238521150715</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.006806279587785195</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.06589882089744376</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-1.010630043583902</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.03107533278114179</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.005716133768708311</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.9269956944558219</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.116068931327023</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.696969638974388</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.2511596952520777</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.124120663019018</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.009049474412908</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.6968083398830358</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.842603019557411</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.871640253804628</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.854561294668261</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.225187768770108</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>-1.551538948421115</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,68 +603,68 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C2" t="n">
-        <v>1.37713506060395</v>
+        <v>0.8918399134670087</v>
       </c>
       <c r="D2" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08359037233672091</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2850805651294578</v>
+        <v>-0.2835630784532303</v>
       </c>
       <c r="G2" t="n">
-        <v>1.248342443837526</v>
+        <v>-0.810812230634564</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08329848985772981</v>
+        <v>-1.073837351569227</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08329576708676574</v>
+        <v>1.073886284574249</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3577501779234991</v>
+        <v>-1.21822742662512</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8893678011647782</v>
+        <v>0.154224863342322</v>
       </c>
       <c r="L2" t="n">
-        <v>1.849279955539432</v>
+        <v>0.5779604926390248</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3592647761527498</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N2" t="n">
-        <v>3.079310452785065</v>
+        <v>-1.434982714052587</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6951676880997961</v>
+        <v>-0.7491051177680702</v>
       </c>
       <c r="P2" t="n">
-        <v>4.214702469337768</v>
+        <v>-0.6810148768734923</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.380170982282029</v>
+        <v>-1.300833750895663</v>
       </c>
       <c r="R2" t="n">
-        <v>1.588146069813711</v>
+        <v>-2.678637133400926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7982875000831346</v>
+        <v>-2.269498205480952</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4633540167947378</v>
+        <v>-0.8215542497984099</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -673,107 +673,107 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.49461309572772</v>
+        <v>-0.4852296526093979</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.231546204023025</v>
+        <v>-0.9598319781204386</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.414825099284884</v>
+        <v>-1.154949645709614</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.491889002337783</v>
+        <v>0.5348248936958526</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.26388223424452</v>
+        <v>-1.145474683753708</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.01969879131520835</v>
+        <v>0.898393140116064</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38161754853354</v>
+        <v>-1.495459238598651</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.587728308100283</v>
+        <v>-1.229946875027577</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.979371650634541</v>
+        <v>-1.437949824044835</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.057627221086355</v>
+        <v>-0.7968701072846855</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7181822513192559</v>
+        <v>-0.1885623253177652</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>fmqtFMjD</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C3" t="n">
-        <v>1.37713506060395</v>
+        <v>1.597034424150377</v>
       </c>
       <c r="D3" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4146522417229446</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5678849002445744</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8365115089431081</v>
+        <v>-2.869966905106654</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4309841063320289</v>
+        <v>-0.5452691277075311</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4310073669847965</v>
+        <v>0.5452969523340327</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1271660080914603</v>
+        <v>0.4789792244272389</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6888742726677447</v>
+        <v>1.357186034324523</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.238210168647272</v>
+        <v>-0.3301248380041233</v>
       </c>
       <c r="M3" t="n">
         <v>0.7700713357442589</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9118181719443772</v>
+        <v>0.3058530112157789</v>
       </c>
       <c r="O3" t="n">
-        <v>1.211678810198304</v>
+        <v>1.706158652207303</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9994355172774767</v>
+        <v>1.050397355323173</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1107752801001733</v>
+        <v>2.904039512581734</v>
       </c>
       <c r="R3" t="n">
-        <v>1.103284342175684</v>
+        <v>0.7638811328290654</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.072724661002653</v>
+        <v>0.5268440273970857</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.01517534387602885</v>
+        <v>0.3219032664487058</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -782,107 +782,107 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6660179834180622</v>
+        <v>-1.148747991091731</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.2852932695516225</v>
+        <v>-1.361083440614614</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.2934200502236396</v>
+        <v>-2.03897579280563</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.3922323513804653</v>
+        <v>-0.5075376405367464</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.2797711952719986</v>
+        <v>-1.480819983151036</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.433360127425415</v>
+        <v>-1.73139405329007</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.7452893830435103</v>
+        <v>-0.9232725961231154</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.6134669264764532</v>
+        <v>-0.8960997224702029</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.519051440935859</v>
+        <v>-2.037846633053485</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.3815092424945759</v>
+        <v>-1.800032113753688</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.6482356727190127</v>
+        <v>1.243100103729532</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>8WpYGrM0</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C4" t="n">
-        <v>1.597034424150377</v>
+        <v>1.339221377233877</v>
       </c>
       <c r="D4" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5807331130761665</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1887891378561156</v>
+        <v>-0.09401519725900095</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01284963915427201</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.259550511304418</v>
+        <v>0.8547223841423679</v>
       </c>
       <c r="I4" t="n">
-        <v>1.259606860766758</v>
+        <v>-0.8547504681941092</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.21822742662512</v>
+        <v>0.7214373174347188</v>
       </c>
       <c r="K4" t="n">
-        <v>2.626978381472402</v>
+        <v>-1.717048069296657</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.78306136703316</v>
+        <v>-1.419827234775901</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.873154902621778</v>
+        <v>1.591684454927278</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.298546892729021</v>
+        <v>-1.65658516201982</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09787520567308552</v>
+        <v>2.068450813679242</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.676079378135944</v>
+        <v>-1.755684538236939</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1107752801001733</v>
+        <v>0.9999459593089504</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.321024296014451</v>
+        <v>0.4244779234824463</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1962144594129164</v>
+        <v>0.2251846759667669</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.530226518054245</v>
+        <v>0.3082528125228759</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -891,107 +891,107 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.248235798813542</v>
+        <v>-0.1235196449045225</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.07339576348902506</v>
+        <v>0.06308095410829709</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.3943439502089759</v>
+        <v>-0.1024010186404272</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.8805298268276671</v>
+        <v>-0.6179474067113954</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.5381917775653837</v>
+        <v>0.03319754325239105</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.024755030406695</v>
+        <v>0.3190361853522751</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.3649086634728636</v>
+        <v>-0.2111890382898018</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.05663865645132861</v>
+        <v>0.2922638835833277</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.209642011981749</v>
+        <v>-0.06223090253785078</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.4212614023404438</v>
+        <v>-0.3106830012088025</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.4102364739929419</v>
+        <v>-0.7618095157383372</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>nHdPI4il</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.874937731578419</v>
+        <v>0.6112786565284644</v>
       </c>
       <c r="D5" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.411137469842276</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.705172187409951</v>
+        <v>0.0007587433381137274</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.810812230634564</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8166960534743479</v>
+        <v>-0.5166978723636554</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8167347175384682</v>
+        <v>0.5167245559967235</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7214373174347188</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4883807441707113</v>
+        <v>-0.1130998413203891</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2147263603817656</v>
+        <v>2.394131153925321</v>
       </c>
       <c r="M5" t="n">
-        <v>2.207894294314541</v>
+        <v>-1.489364742009042</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7216431713192469</v>
+        <v>0.8450094825587373</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6290738478312667</v>
+        <v>-1.412491440463311</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3936547844899549</v>
+        <v>2.423586367065355</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.356963500547597</v>
+        <v>0.7619342651498524</v>
       </c>
       <c r="R5" t="n">
-        <v>2.751814216144976</v>
+        <v>-1.902858369180083</v>
       </c>
       <c r="S5" t="n">
-        <v>1.214067980324422</v>
+        <v>0.102136128435901</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3599503843232972</v>
+        <v>0.3320785342904702</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1000,107 +1000,107 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2153038453222748</v>
+        <v>0.05218468900235684</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.505299228796994</v>
+        <v>-0.08089311104841712</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.287210710922481</v>
+        <v>-0.3006193782736553</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.3801611210577399</v>
+        <v>1.101203659697189</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.6856781321136279</v>
+        <v>-0.1958733244943854</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.031492566512993</v>
+        <v>0.9021320755954827</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.9908263431704764</v>
+        <v>-0.2789160966792822</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.220341267097778</v>
+        <v>-0.3655131836626123</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1.626855342335622</v>
+        <v>-0.2709141508462061</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.112518633485026</v>
+        <v>-0.03504218091221024</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.177123068544223</v>
+        <v>-0.6801437109594263</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>CntkHiGq</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.874937731578419</v>
+        <v>0.7477679166607292</v>
       </c>
       <c r="D6" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5807331130761665</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0007587433381137274</v>
+        <v>1.043272089906375</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8365115089431081</v>
+        <v>2.48383524852078</v>
       </c>
       <c r="H6" t="n">
-        <v>1.326148097316313</v>
+        <v>1.397576235676002</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.326195007759708</v>
+        <v>-1.397625998602981</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.09699838012138</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08739368717664438</v>
+        <v>-0.514086898314456</v>
       </c>
       <c r="L6" t="n">
-        <v>4.028684749082988</v>
+        <v>2.75736528618258</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.570413938945361</v>
+        <v>-3.543397539966588</v>
       </c>
       <c r="N6" t="n">
-        <v>1.221962100234958</v>
+        <v>3.451693947822787</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.182337607653933</v>
+        <v>-3.772286330050807</v>
       </c>
       <c r="P6" t="n">
-        <v>1.468324445853402</v>
+        <v>4.851543750145735</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.998299618032106</v>
+        <v>-4.632997469123034</v>
       </c>
       <c r="R6" t="n">
-        <v>-5.97569688133951</v>
+        <v>-6.169641572394721</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4797097537360951</v>
+        <v>-0.5099851341415469</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2073183912164612</v>
+        <v>0.1216901911667917</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1109,107 +1109,107 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.015564932989378</v>
+        <v>0.8679871191728845</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01539523552852866</v>
+        <v>1.736116552981189</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.1333224315583821</v>
+        <v>1.820295671967088</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0006033990119951412</v>
+        <v>0.1084062407104038</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.4522798162849485</v>
+        <v>1.366155411233027</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.357920888305204</v>
+        <v>-0.9069674350207338</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.0168693473966234</v>
+        <v>1.435909210270993</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.287451976597784</v>
+        <v>1.336361966177125</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.1161313697065667</v>
+        <v>1.957515071869511</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-1.023806330836888</v>
+        <v>1.024130708244346</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.7984313243851581</v>
+        <v>-0.3937058763779737</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.3593116377454187</v>
+        <v>0.7477679166607292</v>
       </c>
       <c r="D7" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2485713703697228</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F7" t="n">
         <v>0.1903066245323431</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8365115089431081</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.145259426964558</v>
+        <v>-1.43812085720364</v>
       </c>
       <c r="I7" t="n">
-        <v>2.145351147223337</v>
+        <v>1.438184337874939</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7214373174347188</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K7" t="n">
-        <v>1.290354858158845</v>
+        <v>-1.416307776551107</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.054380829933568</v>
+        <v>0.7595775587676545</v>
       </c>
       <c r="M7" t="n">
-        <v>3.440313973089069</v>
+        <v>-2.105574581396306</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.98683770765464</v>
+        <v>-0.758752563554639</v>
       </c>
       <c r="O7" t="n">
-        <v>2.839545616812086</v>
+        <v>-1.276631879911333</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.905023860963833</v>
+        <v>-0.5616071367219981</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.904039512581734</v>
+        <v>-0.1901125114865394</v>
       </c>
       <c r="R7" t="n">
-        <v>3.624565325893424</v>
+        <v>-1.175565777723043</v>
       </c>
       <c r="S7" t="n">
-        <v>1.555120347225045</v>
+        <v>-0.1208308363061085</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3912298595322262</v>
+        <v>0.5737531787251923</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1218,107 +1218,107 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3022981762194435</v>
+        <v>-0.04600003343898125</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2917936209072263</v>
+        <v>-0.07370005387843509</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1333140762726866</v>
+        <v>0.07743160144746188</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.7515615792202713</v>
+        <v>0.5072766934815244</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2501238607021111</v>
+        <v>0.2237575850286848</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2432485566662109</v>
+        <v>0.7284520931899188</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.2091617979387357</v>
+        <v>-0.1653494441788407</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.05397655999473026</v>
+        <v>-0.7161835233724485</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0729270589869757</v>
+        <v>-0.1005559837151037</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1266563645613566</v>
+        <v>0.2499924355970209</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.2246834016652738</v>
+        <v>2.351885360824546</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6112786565284644</v>
+        <v>1.339221377233877</v>
       </c>
       <c r="D8" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.08249049901650093</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09553268393522843</v>
+        <v>0.4746284463236872</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2.072004313626362</v>
       </c>
       <c r="H8" t="n">
-        <v>2.240428268320329</v>
+        <v>0.04044160684191658</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.240511690553596</v>
+        <v>-0.04043717258080222</v>
       </c>
       <c r="J8" t="n">
-        <v>1.206353503449679</v>
+        <v>0.2122753221190111</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.454658649604279</v>
+        <v>-0.6343830154126764</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2147263603817656</v>
+        <v>2.067220434893788</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4623483430302688</v>
+        <v>-0.3801870311119669</v>
       </c>
       <c r="N8" t="n">
-        <v>0.298999327258029</v>
+        <v>1.374113884096997</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9743137586830593</v>
+        <v>1.03298064947228</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5926676847424448</v>
+        <v>1.157864321459517</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.419839597975212</v>
+        <v>0.9523436204771309</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.9331349139040293</v>
+        <v>0.599028145432136</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5919267827501704</v>
+        <v>-1.502551779089928</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.149258804740747</v>
+        <v>2.077883027107298</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1327,107 +1327,107 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.34952371115793</v>
+        <v>0.8268405746626207</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.145503277417505</v>
+        <v>0.6814063327289538</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.709312569597958</v>
+        <v>0.5650552085630076</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.2811838371119872</v>
+        <v>0.4944855014509028</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.88956253831906</v>
+        <v>0.9554632784679403</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.3142883307752303</v>
+        <v>0.3132497375865005</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.777874002843401</v>
+        <v>1.009706478899454</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.667341788851361</v>
+        <v>0.7772859919888203</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.946345625532425</v>
+        <v>0.7430080797058065</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.719845121714518</v>
+        <v>0.6351380803152383</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.466299051671496</v>
+        <v>0.7306018624284001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.056923411754772</v>
+        <v>-0.5109663712257129</v>
       </c>
       <c r="D9" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.078975727135832</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5678849002445744</v>
+        <v>-0.378337019050345</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.810812230634564</v>
+        <v>-1.222643165528982</v>
       </c>
       <c r="H9" t="n">
-        <v>2.097571991600951</v>
+        <v>-0.8595529364901612</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.097649708867051</v>
+        <v>0.8595933120444317</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.00593696158772055</v>
+        <v>0.5395937476791089</v>
       </c>
       <c r="K9" t="n">
-        <v>1.089861329661812</v>
+        <v>-0.7145804268114895</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.419827234775901</v>
+        <v>-0.05769923881117887</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3592647761527498</v>
+        <v>0.9754746155400137</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.22416521485018</v>
+        <v>-0.4777515212869103</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3917087963160216</v>
+        <v>-0.2154585555999435</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8004226170249864</v>
+        <v>-0.3227916564190099</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.142159288122931</v>
+        <v>-0.9041475939638333</v>
       </c>
       <c r="R9" t="n">
-        <v>1.297229033230895</v>
+        <v>-0.157356149683186</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.54537417277618</v>
+        <v>1.63883830878714</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.020025598270832</v>
+        <v>1.527090099165605</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1436,107 +1436,107 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7709126192920759</v>
+        <v>0.1616875673890296</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.8115391557951772</v>
+        <v>0.1493175891296886</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.1676518761862107</v>
+        <v>0.003009525476421387</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1049807978364387</v>
+        <v>0.2954992123815934</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.4386950912662314</v>
+        <v>0.03124499867783427</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1333134676393106</v>
+        <v>0.634731422111817</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.5596352592562346</v>
+        <v>-0.06908880830439977</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.9549237522145571</v>
+        <v>0.08774967980292016</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.5016306745404301</v>
+        <v>-0.05956835317488387</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.3506737336568958</v>
+        <v>0.1394140344653798</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.838676842815548</v>
+        <v>0.676342401929966</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>t4kJMDhM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.7763621548162278</v>
+        <v>1.013163700251244</v>
       </c>
       <c r="D10" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E10" t="n">
-        <v>2.408722571281827</v>
+        <v>-0.9128948557826102</v>
       </c>
       <c r="F10" t="n">
-        <v>1.896237555280407</v>
+        <v>-0.2835630784532303</v>
       </c>
       <c r="G10" t="n">
-        <v>1.248342443837526</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.440433118691816</v>
+        <v>-0.5166978723636554</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.440484593108944</v>
+        <v>0.5167245559967235</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1271660080914607</v>
+        <v>0.5395937476791089</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2878872156736779</v>
+        <v>-1.215814248054073</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03310929425313586</v>
+        <v>-0.3301248380041233</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9754746155400137</v>
+        <v>-2.105574581396306</v>
       </c>
       <c r="N10" t="n">
-        <v>1.014067020183224</v>
+        <v>-0.6936425659560193</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5655111170221552</v>
+        <v>-1.533663480955614</v>
       </c>
       <c r="P10" t="n">
-        <v>1.229508965550414</v>
+        <v>0.453358654565702</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.808241147236616</v>
+        <v>-1.737188523520676</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.3513008407383969</v>
+        <v>-1.902858369180083</v>
       </c>
       <c r="S10" t="n">
-        <v>1.353129694999717</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5891941717414209</v>
+        <v>-0.2704089899712188</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1545,107 +1545,107 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5814224118633787</v>
+        <v>-1.671704907469842</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.05278528477952</v>
+        <v>-2.10927760018107</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.089368622597979</v>
+        <v>-1.770065631609299</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.1342042048407136</v>
+        <v>0.7455351125733261</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9855961649518545</v>
+        <v>-2.385839010615443</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.259031979692709</v>
+        <v>0.1176232919667358</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.260601020080599</v>
+        <v>-2.34043190534757</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05212472842119</v>
+        <v>-2.61019839289719</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.353338173699583</v>
+        <v>-2.323822529418945</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.6163504878899595</v>
+        <v>-2.131469101395831</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.429507595617219</v>
+        <v>0.04378381995675121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>Kl1AOZN9</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C11" t="n">
-        <v>1.005580963577229</v>
+        <v>0.6112786565284644</v>
       </c>
       <c r="D11" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5807331130761665</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4731109596474597</v>
+        <v>2.085785436474636</v>
       </c>
       <c r="G11" t="n">
-        <v>0.42468057404869</v>
+        <v>1.248342443837526</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7690086181107414</v>
+        <v>-0.1738428082371496</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7690332791821821</v>
+        <v>0.1738557999490154</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2483950545952001</v>
+        <v>-0.3696241010989402</v>
       </c>
       <c r="K11" t="n">
-        <v>1.156692505827489</v>
+        <v>-1.61680130504814</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.056593102518642</v>
+        <v>-0.3301248380041233</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.05154178343875964</v>
+        <v>0.9754746155400137</v>
       </c>
       <c r="N11" t="n">
-        <v>0.589138614802757</v>
+        <v>0.6839479095516249</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3868129562961306</v>
+        <v>0.3500109666974757</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6324702647929431</v>
+        <v>0.6921741348686902</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.697519907827493</v>
+        <v>1.356963500547597</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.7391902228488186</v>
+        <v>1.297229033230895</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6995240286504462</v>
+        <v>-0.4416794557715791</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.013729794052257</v>
+        <v>0.3631883487735664</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1654,107 +1654,107 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7110123800706889</v>
+        <v>0.9171874163941814</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.3348022897736097</v>
+        <v>-0.05756108005260286</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.764734113763639</v>
+        <v>0.6286728206214888</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.2713957558521023</v>
+        <v>-1.366409678442931</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.832702892199803</v>
+        <v>0.5334320777420994</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.5687725118244784</v>
+        <v>-1.095024926707563</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.9132037932230525</v>
+        <v>1.128360279780143</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.2460159160142223</v>
+        <v>1.144124010030556</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.6666220487050644</v>
+        <v>0.7371131837915595</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-1.018677019889034</v>
+        <v>0.826473307300301</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.706635943035382</v>
+        <v>0.715892944784188</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8918399134670087</v>
+        <v>-1.056923411754772</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5056960363928432</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4146522417229446</v>
+        <v>0.5818329863963865</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2835630784532303</v>
+        <v>0.8537242087121459</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.810812230634564</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.073837351569227</v>
+        <v>0.3118685326087335</v>
       </c>
       <c r="I12" t="n">
-        <v>1.073886284574249</v>
+        <v>-0.3118749377852377</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8545402871139001</v>
+        <v>2.903560154502037</v>
       </c>
       <c r="K12" t="n">
-        <v>0.154224863342322</v>
+        <v>2.760640733803758</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5779604926390248</v>
+        <v>-2.872763763804937</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.873154902621778</v>
+        <v>0.3592647761527498</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.434982714052587</v>
+        <v>-0.8775497521556299</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7491051177680702</v>
+        <v>-1.091813919160445</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6810148768734923</v>
+        <v>-0.1635813362170178</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.300833750895663</v>
+        <v>-1.221496519509297</v>
       </c>
       <c r="R12" t="n">
-        <v>-2.678637133400926</v>
+        <v>-0.3513008407383969</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.269498205480952</v>
+        <v>-1.616235901390139</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8215542497984099</v>
+        <v>1.053434750425517</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1763,107 +1763,107 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4852296526093979</v>
+        <v>0.05991079373100872</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.9598319781204386</v>
+        <v>1.29406309700919</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.154949645709614</v>
+        <v>0.2447468193419866</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.5348248936958526</v>
+        <v>0.7451506636132317</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.145474683753708</v>
+        <v>0.9763527358489066</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.898393140116064</v>
+        <v>-0.499560710435093</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.495459238598651</v>
+        <v>1.074600273609093</v>
       </c>
       <c r="AE12" t="n">
-        <v>-1.229946875027577</v>
+        <v>0.6755936272081654</v>
       </c>
       <c r="AF12" t="n">
-        <v>-1.437949824044835</v>
+        <v>0.2408692786653819</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.7968701072846855</v>
+        <v>0.1910799136348961</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.1885623253177652</v>
+        <v>0.002890526949230735</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C13" t="n">
-        <v>1.597034424150377</v>
+        <v>1.63494810752045</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.5056960363928432</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E13" t="n">
         <v>0.4157521150431646</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1903066245323431</v>
+        <v>0.5694023869208018</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.869966905106654</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5452691277075311</v>
+        <v>1.669003161442819</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5452969523340327</v>
+        <v>-1.669063763807416</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4789792244272389</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K13" t="n">
-        <v>1.357186034324523</v>
+        <v>-0.915073955308523</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3301248380041233</v>
+        <v>0.2147263603817656</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7700713357442589</v>
+        <v>3.440313973089069</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3058530112157789</v>
+        <v>1.434426302925192</v>
       </c>
       <c r="O13" t="n">
-        <v>1.706158652207303</v>
+        <v>1.451574971172967</v>
       </c>
       <c r="P13" t="n">
-        <v>1.050397355323173</v>
+        <v>0.03543156403547253</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.904039512581734</v>
+        <v>2.428016124263538</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7638811328290654</v>
+        <v>5.079150508807505</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5268440273970857</v>
+        <v>-2.286354170896134</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3219032664487058</v>
+        <v>-0.9524311054425986</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1872,107 +1872,107 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.148747991091731</v>
+        <v>0.02657495670796622</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.361083440614614</v>
+        <v>0.7828977142974622</v>
       </c>
       <c r="Z13" t="n">
-        <v>-2.03897579280563</v>
+        <v>0.06882975864562792</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.5075376405367464</v>
+        <v>-0.1493426881623891</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.480819983151036</v>
+        <v>0.382827652602573</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.73139405329007</v>
+        <v>-1.680070239880412</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.9232725961231154</v>
+        <v>0.9980870837017969</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.8960997224702029</v>
+        <v>1.054510652486297</v>
       </c>
       <c r="AF13" t="n">
-        <v>-2.037846633053485</v>
+        <v>0.1275403438381962</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-1.800032113753688</v>
+        <v>0.1133797992474932</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.243100103729532</v>
+        <v>-1.326558912229255</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C14" t="n">
-        <v>1.339221377233877</v>
+        <v>0.8994226501410234</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5056960363928432</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4146522417229446</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.09401519725900095</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G14" t="n">
         <v>-0.398981295740146</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8547223841423679</v>
+        <v>-1.973831894901305</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8547504681941092</v>
+        <v>1.973916769199483</v>
       </c>
       <c r="J14" t="n">
         <v>0.7214373174347188</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.717048069296657</v>
+        <v>0.08739368717664438</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.419827234775901</v>
+        <v>-0.3301248380041233</v>
       </c>
       <c r="M14" t="n">
-        <v>1.591684454927278</v>
+        <v>2.824104133701805</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.65658516201982</v>
+        <v>-1.855341996794555</v>
       </c>
       <c r="O14" t="n">
-        <v>2.068450813679242</v>
+        <v>4.484547863495486</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.755684538236939</v>
+        <v>-1.994500018539928</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9999459593089504</v>
+        <v>2.666027818422636</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4244779234824463</v>
+        <v>5.079150508807505</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2251846759667669</v>
+        <v>-1.241284315154525</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3082528125228759</v>
+        <v>0.8445784734106215</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1981,107 +1981,107 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1235196449045225</v>
+        <v>-0.007655069013491917</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.06308095410829709</v>
+        <v>0.0795785394428087</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.1024010186404272</v>
+        <v>-0.04095773553290011</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.6179474067113954</v>
+        <v>0.5222647922784536</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.03319754325239105</v>
+        <v>0.0957817898045909</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.3190361853522751</v>
+        <v>2.112534542569239</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.2111890382898018</v>
+        <v>-1.092184090734201</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.2922638835833277</v>
+        <v>-0.2241158146079971</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.06223090253785078</v>
+        <v>-0.02071442016070084</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.3106830012088025</v>
+        <v>0.0006542446958196771</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.7618095157383372</v>
+        <v>0.03228290695655738</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6112786565284644</v>
+        <v>-0.9962615183626544</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5056960363928432</v>
+        <v>2.393718654096563</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4157521150431646</v>
+        <v>0.08359037233672091</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0007587433381137274</v>
+        <v>0.3798545057265725</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8365115089431081</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5166978723636554</v>
+        <v>1.626146278427006</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5167245559967235</v>
+        <v>-1.626205169301453</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.73331124061016</v>
+        <v>-0.00593696158772055</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1130998413203891</v>
+        <v>-1.516554540799623</v>
       </c>
       <c r="L15" t="n">
-        <v>2.394131153925321</v>
+        <v>1.849279955539432</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.489364742009042</v>
+        <v>0.3592647761527498</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8450094825587373</v>
+        <v>1.777110500812665</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.412491440463311</v>
+        <v>-1.596085441209226</v>
       </c>
       <c r="P15" t="n">
-        <v>2.423586367065355</v>
+        <v>1.11010122539892</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7619342651498524</v>
+        <v>-5.188358088827596</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.902858369180083</v>
+        <v>-3.066526515511348</v>
       </c>
       <c r="S15" t="n">
-        <v>0.102136128435901</v>
+        <v>-4.133767980400661</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3320785342904702</v>
+        <v>-0.4432970910158072</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2090,1238 +2090,148 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.05218468900235684</v>
+        <v>-0.007655069013491917</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.08089311104841712</v>
+        <v>-0.3945636444160281</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.3006193782736553</v>
+        <v>-0.07973101872575049</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.101203659697189</v>
+        <v>0.4765522616202459</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.1958733244943854</v>
+        <v>-0.5347292421067819</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9021320755954827</v>
+        <v>-0.3722758603694653</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.2789160966792822</v>
+        <v>-0.5259123885420567</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.3655131836626123</v>
+        <v>-0.5377674511062713</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.2709141508462061</v>
+        <v>-0.09296816969787731</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.03504218091221024</v>
+        <v>0.0006542446958196771</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.6801437109594263</v>
+        <v>-0.3298727277131648</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>tYjCfe2E</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.819875174399046</v>
+        <v>2.218427650214686</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7477679166607292</v>
+        <v>0.6112786565284644</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5056960363928432</v>
+        <v>0.4607755271036255</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.08249049901650093</v>
+        <v>-0.9128948557826102</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1903066245323431</v>
+        <v>-0.5678849002445744</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01284963915427201</v>
+        <v>1.660173378731944</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.43812085720364</v>
+        <v>1.506147005982728</v>
       </c>
       <c r="I16" t="n">
-        <v>1.438184337874939</v>
+        <v>-1.506201104684754</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.73331124061016</v>
+        <v>-0.1877805313433304</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.416307776551107</v>
+        <v>-1.67694936359725</v>
       </c>
       <c r="L16" t="n">
         <v>0.7595775587676545</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.105574581396306</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.758752563554639</v>
+        <v>0.5626377034994592</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.276631879911333</v>
+        <v>-0.7265842536765708</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5616071367219981</v>
+        <v>1.969836954489678</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1901125114865394</v>
+        <v>-2.427422436582059</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.175565777723043</v>
+        <v>-0.9719238521150715</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1208308363061085</v>
+        <v>0.006806279587785195</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.4890709511367117</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5737531787251923</v>
+        <v>-1.010630043583902</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.7649428322954317</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.04600003343898125</v>
+        <v>0.9269956944558219</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.07370005387843509</v>
+        <v>1.116068931327023</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.07743160144746188</v>
+        <v>1.696969638974388</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.5072766934815244</v>
+        <v>0.2511596952520777</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2237575850286848</v>
+        <v>1.124120663019018</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.7284520931899188</v>
+        <v>1.009049474412908</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.1653494441788407</v>
+        <v>0.6968083398830358</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.7161835233724485</v>
+        <v>0.842603019557411</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.1005559837151037</v>
+        <v>1.871640253804628</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.2499924355970209</v>
+        <v>1.225187768770108</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.351885360824546</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>pjyqwZx3</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.819875174399046</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.339221377233877</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-0.5056960363928432</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.744399085868939</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.4746284463236872</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2.072004313626362</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.04044160684191658</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-0.04043717258080222</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-0.07867438948996455</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-0.6343830154126764</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2.067220434893788</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-0.3801870311119669</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.374113884096997</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.03298064947228</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.157864321459517</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.9523436204771309</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.599028145432136</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-1.502551779089928</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.077883027107298</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.8268405746626207</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.6814063327289538</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0.5650552085630076</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.4944855014509028</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0.9554632784679403</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0.3132497375865005</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.009706478899454</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0.7772859919888203</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0.7430080797058065</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0.6351380803152383</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0.7306018624284001</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>tIUiyD7F</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.819875174399046</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.5109663712257129</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-0.5056960363928432</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-0.7468139844293883</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-0.378337019050345</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-1.222643165528982</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.8595529364901612</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.8595933120444317</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.5395937476791089</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-0.7145804268114895</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-0.05769923881117887</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.9754746155400137</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.4777515212869103</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-0.2154585555999435</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-0.3227916564190099</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-0.9041475939638333</v>
-      </c>
-      <c r="R18" t="n">
-        <v>-0.157356149683186</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.63883830878714</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.527090099165605</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.1616875673890296</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.1493175891296886</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0.003009525476421387</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.2954992123815934</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0.03124499867783427</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0.634731422111817</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>-0.06908880830439977</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0.08774967980292016</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>-0.05956835317488387</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0.1394140344653798</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0.676342401929966</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>CntkHiGq</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1.819875174399046</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.7477679166607292</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-0.5056960363928432</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.4157521150431646</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.043272089906375</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2.48383524852078</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.397576235676002</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-1.397625998602981</v>
-      </c>
-      <c r="J19" t="n">
-        <v>-0.73331124061016</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-0.514086898314456</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2.75736528618258</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-3.543397539966588</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.451693947822787</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-3.772286330050807</v>
-      </c>
-      <c r="P19" t="n">
-        <v>4.851543750145735</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-4.632997469123034</v>
-      </c>
-      <c r="R19" t="n">
-        <v>-6.169641572394721</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-0.5099851341415469</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.1216901911667917</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.8679871191728845</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.736116552981189</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.820295671967088</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.1084062407104038</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.366155411233027</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>-0.9069674350207338</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.435909210270993</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.336361966177125</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.957515071869511</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.024130708244346</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>-0.3937058763779737</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>t4kJMDhM</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.819875174399046</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.013163700251244</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-0.5056960363928432</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0.9128948557826102</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.2835630784532303</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-0.5166978723636554</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.5167245559967235</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.5395937476791089</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-1.215814248054073</v>
-      </c>
-      <c r="L20" t="n">
-        <v>-0.3301248380041233</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-2.105574581396306</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-0.6936425659560193</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-1.533663480955614</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.453358654565702</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-1.737188523520676</v>
-      </c>
-      <c r="R20" t="n">
-        <v>-1.902858369180083</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>-0.1667021210409293</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-1.671704907469842</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>-2.094600667610797</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>-1.773311689315108</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0.7123625690587683</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>-2.433821754947603</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0.1176232919667358</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>-2.388853587280236</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>-2.583946430335986</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>-2.319784908599028</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>-2.131469101395831</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>-0.04038318167252452</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Kl1AOZN9</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1.819875174399046</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.6112786565284644</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-0.5056960363928432</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1.744399085868939</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.085785436474636</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.248342443837526</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-0.1738428082371496</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.1738557999490154</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-0.3696241010989402</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-1.61680130504814</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-0.3301248380041233</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.9754746155400137</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.6839479095516249</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.3500109666974757</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.6921741348686902</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.356963500547597</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.297229033230895</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-0.4416794557715791</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.3631883487735664</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0.9171874163941814</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>-0.05756108005260286</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0.6286728206214888</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>-1.366409678442931</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0.5334320777420994</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>-1.095024926707563</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.128360279780143</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.144124010030556</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0.7371131837915595</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0.826473307300301</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0.715892944784188</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1.819875174399046</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-1.056923411754772</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.393718654096563</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.5818329863963865</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.8537242087121459</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.8365115089431081</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.3118685326087335</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.3118749377852377</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.176185875479598</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.760640733803758</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-2.872763763804937</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.3592647761527498</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-0.8775497521556299</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-1.091813919160445</v>
-      </c>
-      <c r="P22" t="n">
-        <v>-0.1635813362170178</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-1.221496519509297</v>
-      </c>
-      <c r="R22" t="n">
-        <v>-0.3513008407383969</v>
-      </c>
-      <c r="S22" t="n">
-        <v>-1.616235901390139</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.049432029168562</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.06472897360612198</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.312068950091571</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0.2436832174554022</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.7888265455249338</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0.9446841245896824</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>-0.5355479644245309</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.045357375500735</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0.6830191737012737</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0.2394022657511447</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0.1848800081345542</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0.104778429583655</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1.819875174399046</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1.63494810752045</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.393718654096563</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.4157521150431646</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.5694023869208018</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.01284963915427201</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.669003161442819</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-1.669063763807416</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-0.3696241010989402</v>
-      </c>
-      <c r="K23" t="n">
-        <v>-0.915073955308523</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.2147263603817656</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.440313973089069</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.434426302925192</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.451574971172967</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.03543156403547253</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.428016124263538</v>
-      </c>
-      <c r="R23" t="n">
-        <v>5.079150508807505</v>
-      </c>
-      <c r="S23" t="n">
-        <v>-2.286354170896134</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-0.9803288596577738</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.03882003430873411</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0.7844860215671735</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.07021105979703625</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>-0.03454537681271449</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0.4188874119794689</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>-1.641901940194646</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.015493570671055</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0.999183739193184</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0.1226622159594722</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0.115258558490021</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>-1.376949399600211</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>tOTmlbNp</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1.819875174399046</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.8994226501410234</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.393718654096563</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-0.08249049901650093</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.1903066245323431</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-0.398981295740146</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-1.973831894901305</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.973916769199483</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-0.00593696158772055</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.08739368717664438</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-0.3301248380041233</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.824104133701805</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-1.855341996794555</v>
-      </c>
-      <c r="O24" t="n">
-        <v>4.484547863495486</v>
-      </c>
-      <c r="P24" t="n">
-        <v>-1.994500018539928</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.666027818422636</v>
-      </c>
-      <c r="R24" t="n">
-        <v>5.079150508807505</v>
-      </c>
-      <c r="S24" t="n">
-        <v>-1.241284315154525</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.8445784734106215</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>-0.007655069013491917</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0.0795785394428087</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>-0.04095773553290011</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.5222647922784536</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0.0957817898045909</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.112534542569239</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>-1.092184090734201</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>-0.2241158146079971</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>-0.02071442016070084</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0.0006542446958196771</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0.03228290695655738</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>GINCsvmn</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1.819875174399046</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.9962615183626544</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.393718654096563</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.08359037233672091</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.3798545057265725</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.01284963915427201</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.626146278427006</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-1.626205169301453</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-0.00593696158772055</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-1.516554540799623</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.849279955539432</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.3592647761527498</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.777110500812665</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-1.596085441209226</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.11010122539892</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-5.188358088827596</v>
-      </c>
-      <c r="R25" t="n">
-        <v>-3.066526515511348</v>
-      </c>
-      <c r="S25" t="n">
-        <v>-4.133767980400661</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>-0.3888156072405329</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>-0.007655069013491917</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>-0.4589867689793425</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>-0.08007658382283023</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.481401746359389</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>-0.5274518592164055</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>-0.3309333602506461</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>-0.5434929403810099</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>-0.5932449303772731</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>-0.09732975704283472</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0.0006542446958196771</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>-0.2639739339115436</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>tYjCfe2E</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2.218427650214686</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.6112786565284644</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.4607755271036255</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0.9128948557826102</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.5678849002445744</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.660173378731944</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.506147005982728</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-1.506201104684754</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-0.1877805313433304</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-1.67694936359725</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.7595775587676545</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-0.873154902621778</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.5626377034994592</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-0.7265842536765708</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.969836954489678</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-2.427422436582059</v>
-      </c>
-      <c r="R26" t="n">
-        <v>-0.9719238521150715</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.006806279587785195</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-0.06589882089744376</v>
-      </c>
-      <c r="U26" t="n">
-        <v>-1.010630043583902</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0.03107533278114179</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.005716133768708311</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0.9269956944558219</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.116068931327023</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.696969638974388</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.2511596952520777</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.124120663019018</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.009049474412908</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.6968083398830358</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0.842603019557411</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.871640253804628</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.854561294668261</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.225187768770108</v>
-      </c>
-      <c r="AI26" t="n">
         <v>-1.551538948421115</v>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4633540167947378</v>
+        <v>-0.5416063509784073</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -673,40 +673,40 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.49461309572772</v>
+        <v>1.255220462537494</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.231546204023025</v>
+        <v>1.059602915079372</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.414825099284884</v>
+        <v>1.332319891816384</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.491889002337783</v>
+        <v>-0.5471868618974325</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.26388223424452</v>
+        <v>1.210367406173853</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.01969879131520835</v>
+        <v>-0.1238233223773065</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38161754853354</v>
+        <v>1.369389029045715</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.587728308100283</v>
+        <v>1.555477060127494</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.979371650634541</v>
+        <v>1.750080574461782</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.057627221086355</v>
+        <v>1.946707227365162</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7181822513192559</v>
+        <v>0.9539156255057242</v>
       </c>
     </row>
     <row r="3">
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.01517534387602885</v>
+        <v>0.02838722074170034</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -782,40 +782,40 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6660179834180622</v>
+        <v>-0.8037978970265566</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.2852932695516225</v>
+        <v>-0.3750180600127781</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.2934200502236396</v>
+        <v>-0.3439125163065386</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.3922323513804653</v>
+        <v>0.2913063964739597</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.2797711952719986</v>
+        <v>-0.3084351757379331</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.433360127425415</v>
+        <v>1.600800704184132</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.7452893830435103</v>
+        <v>-0.7773644435221762</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.6134669264764532</v>
+        <v>-0.6378336414714419</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.519051440935859</v>
+        <v>-0.48747034758404</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.3815092424945759</v>
+        <v>-0.3634155751863477</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.6482356727190127</v>
+        <v>-0.4551948050311057</v>
       </c>
     </row>
     <row r="4">
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.530226518054245</v>
+        <v>-1.567670313519776</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -891,40 +891,40 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.248235798813542</v>
+        <v>-0.113175472695782</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.07339576348902506</v>
+        <v>0.2329279256221052</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.3943439502089759</v>
+        <v>-0.4148051960563006</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.8805298268276671</v>
+        <v>-0.7608228117398796</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.5381917775653837</v>
+        <v>-0.5786073101389009</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.024755030406695</v>
+        <v>-1.083374848565313</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.3649086634728636</v>
+        <v>-0.385177185174809</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.05663865645132861</v>
+        <v>0.3019371399315472</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.209642011981749</v>
+        <v>0.0007718576270169641</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.4212614023404438</v>
+        <v>-0.4721098992421069</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.4102364739929419</v>
+        <v>0.3536601917360916</v>
       </c>
     </row>
     <row r="5">
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3599503843232972</v>
+        <v>-0.09561627516831558</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1000,40 +1000,40 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2153038453222748</v>
+        <v>-0.1115431141443193</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.505299228796994</v>
+        <v>-1.405164270377252</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.287210710922481</v>
+        <v>-1.230130880042962</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.3801611210577399</v>
+        <v>-0.3618885308007449</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.6856781321136279</v>
+        <v>-0.7196558696693568</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.031492566512993</v>
+        <v>0.8172660296615185</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.9908263431704764</v>
+        <v>-0.9412803980967652</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.220341267097778</v>
+        <v>-1.173554721412973</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1.626855342335622</v>
+        <v>-1.577959169520293</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.112518633485026</v>
+        <v>-0.1297942720436997</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.177123068544223</v>
+        <v>0.9861427318501043</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2073183912164612</v>
+        <v>0.2338299216196877</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1109,40 +1109,40 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.015564932989378</v>
+        <v>-1.021783105652138</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01539523552852866</v>
+        <v>-0.1857347444722231</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.1333224315583821</v>
+        <v>-0.1876312462570396</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0006033990119951412</v>
+        <v>-0.3269493534769882</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.4522798162849485</v>
+        <v>-0.4805127799629867</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.357920888305204</v>
+        <v>-1.032767035005459</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.0168693473966234</v>
+        <v>-0.1148520449544874</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.287451976597784</v>
+        <v>-0.2599894520820339</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.1161313697065667</v>
+        <v>-0.1086285653072785</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-1.023806330836888</v>
+        <v>-1.037548112725092</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.7984313243851581</v>
+        <v>0.8019350674185658</v>
       </c>
     </row>
     <row r="7">
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3912298595322262</v>
+        <v>0.4586292164549462</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1218,40 +1218,40 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3022981762194435</v>
+        <v>-0.2608334343293608</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2917936209072263</v>
+        <v>0.275740789899114</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1333140762726866</v>
+        <v>0.1252357667055335</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.7515615792202713</v>
+        <v>0.7814617263022781</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2501238607021111</v>
+        <v>0.2468280762429318</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2432485566662109</v>
+        <v>0.3151192053262135</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.2091617979387357</v>
+        <v>0.2319484717893988</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.05397655999473026</v>
+        <v>-0.02303076348748194</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0729270589869757</v>
+        <v>0.05312799316504201</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1266563645613566</v>
+        <v>0.1874029134030919</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.2246834016652738</v>
+        <v>0.1800832968632841</v>
       </c>
     </row>
     <row r="8">
@@ -1285,7 +1285,7 @@
         <v>-2.240511690553596</v>
       </c>
       <c r="J8" t="n">
-        <v>1.206353503449679</v>
+        <v>1.570040642960898</v>
       </c>
       <c r="K8" t="n">
         <v>-3.454658649604279</v>
@@ -1312,13 +1312,13 @@
         <v>-0.9331349139040293</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5919267827501704</v>
+        <v>0.5921260769281529</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.149258804740747</v>
+        <v>-0.2311793003959823</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1327,40 +1327,40 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.34952371115793</v>
+        <v>2.262945242009581</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.145503277417505</v>
+        <v>2.160426620442891</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.709312569597958</v>
+        <v>2.672245294169951</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.2811838371119872</v>
+        <v>-0.1900947432968207</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.88956253831906</v>
+        <v>2.758357508129675</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.3142883307752303</v>
+        <v>0.01561289723207803</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.777874002843401</v>
+        <v>2.747637839464633</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.667341788851361</v>
+        <v>2.636386026823984</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.946345625532425</v>
+        <v>2.882183143475709</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.719845121714518</v>
+        <v>2.631495264001797</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.466299051671496</v>
+        <v>-1.401479895061255</v>
       </c>
     </row>
     <row r="9">
@@ -1394,7 +1394,7 @@
         <v>-2.097649708867051</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.00593696158772055</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K9" t="n">
         <v>1.089861329661812</v>
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.020025598270832</v>
+        <v>-2.208274791931421</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1436,40 +1436,40 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7709126192920759</v>
+        <v>-0.8080882423021828</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.8115391557951772</v>
+        <v>-0.8312331756664083</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.1676518761862107</v>
+        <v>-0.1616646440544205</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1049807978364387</v>
+        <v>0.08911193033946781</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.4386950912662314</v>
+        <v>-0.4032765931189486</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1333134676393106</v>
+        <v>0.1324706093207676</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.5596352592562346</v>
+        <v>-0.5389503477016269</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.9549237522145571</v>
+        <v>-0.9090301003131893</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.5016306745404301</v>
+        <v>-0.5296200774067438</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.3506737336568958</v>
+        <v>-0.3668310631426355</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.838676842815548</v>
+        <v>-1.657062128315919</v>
       </c>
     </row>
     <row r="10">
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5891941717414209</v>
+        <v>0.3044840165341666</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1545,40 +1545,40 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5814224118633787</v>
+        <v>0.7252693069320967</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.05278528477952</v>
+        <v>1.054407515185459</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.089368622597979</v>
+        <v>1.091579663677143</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.1342042048407136</v>
+        <v>-0.2392449390196802</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9855961649518545</v>
+        <v>0.9879433727914823</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.259031979692709</v>
+        <v>-1.14844035140008</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.260601020080599</v>
+        <v>1.234340584111829</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.05212472842119</v>
+        <v>1.104817654336507</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.353338173699583</v>
+        <v>1.401928409610353</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.6163504878899595</v>
+        <v>0.67700757200586</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.429507595617219</v>
+        <v>-1.162221073169684</v>
       </c>
     </row>
     <row r="11">
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.013729794052257</v>
+        <v>-1.177574241048867</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1654,40 +1654,40 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7110123800706889</v>
+        <v>-0.8974114011752855</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.3348022897736097</v>
+        <v>-0.4503048964063766</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.764734113763639</v>
+        <v>-0.7705280112861475</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.2713957558521023</v>
+        <v>-0.3719506875490243</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.832702892199803</v>
+        <v>-0.8364651237807823</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.5687725118244784</v>
+        <v>0.5159307545235977</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.9132037932230525</v>
+        <v>-0.8957269770135142</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.2460159160142223</v>
+        <v>-0.2815181412055308</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.6666220487050644</v>
+        <v>-0.7352105556293964</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-1.018677019889034</v>
+        <v>-1.03540386499701</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.706635943035382</v>
+        <v>-1.700724965951256</v>
       </c>
     </row>
     <row r="12">
@@ -1721,7 +1721,7 @@
         <v>1.073886284574249</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8545402871139001</v>
+        <v>-1.21822742662512</v>
       </c>
       <c r="K12" t="n">
         <v>0.154224863342322</v>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8215542497984099</v>
+        <v>-0.5746995565220469</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1763,40 +1763,40 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4852296526093979</v>
+        <v>-0.6379041544319998</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.9598319781204386</v>
+        <v>-1.013951584492341</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.154949645709614</v>
+        <v>-1.150436710112458</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.5348248936958526</v>
+        <v>0.5167945151078079</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.145474683753708</v>
+        <v>-1.144351624427494</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.898393140116064</v>
+        <v>0.698593775434444</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.495459238598651</v>
+        <v>-1.457841635028116</v>
       </c>
       <c r="AE12" t="n">
-        <v>-1.229946875027577</v>
+        <v>-1.338393181063955</v>
       </c>
       <c r="AF12" t="n">
-        <v>-1.437949824044835</v>
+        <v>-1.489275975228819</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.7968701072846855</v>
+        <v>-0.9300830840524966</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.1885623253177652</v>
+        <v>-0.3607592654502234</v>
       </c>
     </row>
     <row r="13">
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3219032664487058</v>
+        <v>0.3426373832938708</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1872,40 +1872,40 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.148747991091731</v>
+        <v>-1.017832916233872</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.361083440614614</v>
+        <v>-1.293112303469993</v>
       </c>
       <c r="Z13" t="n">
-        <v>-2.03897579280563</v>
+        <v>-1.965945561393409</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.5075376405367464</v>
+        <v>-0.5077709881491326</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.480819983151036</v>
+        <v>-1.373631594465591</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.73139405329007</v>
+        <v>-1.602115831887972</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.9232725961231154</v>
+        <v>-0.8620050079562626</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.8960997224702029</v>
+        <v>-0.8270430204621729</v>
       </c>
       <c r="AF13" t="n">
-        <v>-2.037846633053485</v>
+        <v>-2.034855918799655</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-1.800032113753688</v>
+        <v>-1.704681067752572</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.243100103729532</v>
+        <v>1.326356977702323</v>
       </c>
     </row>
     <row r="14">
@@ -1972,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3082528125228759</v>
+        <v>0.4598017307625239</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1981,40 +1981,40 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1235196449045225</v>
+        <v>-0.1248939056402486</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.06308095410829709</v>
+        <v>0.1417841947503617</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.1024010186404272</v>
+        <v>-0.09966998893535683</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.6179474067113954</v>
+        <v>-0.667796608214376</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.03319754325239105</v>
+        <v>-0.01865705542761047</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.3190361853522751</v>
+        <v>0.176311225652666</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.2111890382898018</v>
+        <v>-0.2037200729720813</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.2922638835833277</v>
+        <v>0.2804022094170529</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.06223090253785078</v>
+        <v>0.03521587811355715</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.3106830012088025</v>
+        <v>-0.3149773080488661</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.7618095157383372</v>
+        <v>-1.111240053801304</v>
       </c>
     </row>
     <row r="15">
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3320785342904702</v>
+        <v>0.1967137790551501</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2090,40 +2090,40 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.05218468900235684</v>
+        <v>-0.009557134085341335</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.08089311104841712</v>
+        <v>-0.06523490693479181</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.3006193782736553</v>
+        <v>-0.2587095502556336</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.101203659697189</v>
+        <v>1.418684735144918</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.1958733244943854</v>
+        <v>-0.1053749606388236</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9021320755954827</v>
+        <v>0.903066809465341</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.2789160966792822</v>
+        <v>-0.2513821991097257</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.3655131836626123</v>
+        <v>-0.4785278957807249</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.2709141508462061</v>
+        <v>-0.4026730088889842</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.03504218091221024</v>
+        <v>0.008545033514437346</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.6801437109594263</v>
+        <v>-0.6737590263016837</v>
       </c>
     </row>
     <row r="16">
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5737531787251923</v>
+        <v>0.7353381006551266</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -2199,40 +2199,40 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.04600003343898125</v>
+        <v>-0.009017550057460712</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.07370005387843509</v>
+        <v>-0.01425754571295434</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.07743160144746188</v>
+        <v>0.0722202347974373</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.5072766934815244</v>
+        <v>0.6584010503112059</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.2237575850286848</v>
+        <v>0.234086530441603</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.7284520931899188</v>
+        <v>0.8121783655272882</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.1653494441788407</v>
+        <v>-0.1944272360231096</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.7161835233724485</v>
+        <v>-0.7347842240107532</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.1005559837151037</v>
+        <v>-0.09221436003096149</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.2499924355970209</v>
+        <v>0.2563046690309104</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.351885360824546</v>
+        <v>2.222555270959666</v>
       </c>
     </row>
     <row r="17">
@@ -2266,7 +2266,7 @@
         <v>-0.04043717258080222</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.07867438948996455</v>
+        <v>0.2122753221190111</v>
       </c>
       <c r="K17" t="n">
         <v>-0.6343830154126764</v>
@@ -2299,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.077883027107298</v>
+        <v>2.341801137847493</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2308,40 +2308,40 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.8268405746626207</v>
+        <v>0.6820597583111887</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.6814063327289538</v>
+        <v>0.4416178080490291</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.5650552085630076</v>
+        <v>0.573828395097944</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.4944855014509028</v>
+        <v>0.3644003076161629</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9554632784679403</v>
+        <v>0.9901223730267831</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.3132497375865005</v>
+        <v>0.5315504052341145</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.009706478899454</v>
+        <v>0.9798573019896782</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.7772859919888203</v>
+        <v>0.5755377558402982</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.7430080797058065</v>
+        <v>0.5581639371470225</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.6351380803152383</v>
+        <v>0.6763243868267584</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.7306018624284001</v>
+        <v>0.7249951130144805</v>
       </c>
     </row>
     <row r="18">
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.527090099165605</v>
+        <v>1.488864977551531</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2417,40 +2417,40 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1616875673890296</v>
+        <v>0.2085836806328085</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1493175891296886</v>
+        <v>0.1024764445697142</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.003009525476421387</v>
+        <v>0.008710352657019495</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.2954992123815934</v>
+        <v>0.3217462586255166</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.03124499867783427</v>
+        <v>0.001582938545225925</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.634731422111817</v>
+        <v>0.4758934309413642</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.06908880830439977</v>
+        <v>-0.03965602124728654</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.08774967980292016</v>
+        <v>-0.001694219430144185</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.05956835317488387</v>
+        <v>-0.05714867735855229</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.1394140344653798</v>
+        <v>0.1652335543412626</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.676342401929966</v>
+        <v>0.5569107191011068</v>
       </c>
     </row>
     <row r="19">
@@ -2517,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1216901911667917</v>
+        <v>0.001449715312912057</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2526,40 +2526,40 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.8679871191728845</v>
+        <v>0.9428367643749416</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.736116552981189</v>
+        <v>1.835958876723381</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.820295671967088</v>
+        <v>1.755820648660525</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.1084062407104038</v>
+        <v>0.2296048285218058</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.366155411233027</v>
+        <v>1.327845378853541</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.9069674350207338</v>
+        <v>-0.9498094040557764</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.435909210270993</v>
+        <v>1.398568151320271</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.336361966177125</v>
+        <v>1.34394277507612</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.957515071869511</v>
+        <v>2.029503867325254</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.024130708244346</v>
+        <v>0.971972773082738</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.3937058763779737</v>
+        <v>-0.4892205862695931</v>
       </c>
     </row>
     <row r="20">
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1667021210409293</v>
+        <v>-0.2576152993735751</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2635,40 +2635,40 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.671704907469842</v>
+        <v>-1.448145086274461</v>
       </c>
       <c r="Y20" t="n">
-        <v>-2.094600667610797</v>
+        <v>-2.009035815292868</v>
       </c>
       <c r="Z20" t="n">
-        <v>-1.773311689315108</v>
+        <v>-1.659213822345314</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.7123625690587683</v>
+        <v>0.6981803377979809</v>
       </c>
       <c r="AB20" t="n">
-        <v>-2.433821754947603</v>
+        <v>-2.265749336469369</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1176232919667358</v>
+        <v>0.3368069194581115</v>
       </c>
       <c r="AD20" t="n">
-        <v>-2.388853587280236</v>
+        <v>-2.32480648355423</v>
       </c>
       <c r="AE20" t="n">
-        <v>-2.583946430335986</v>
+        <v>-2.522382900164025</v>
       </c>
       <c r="AF20" t="n">
-        <v>-2.319784908599028</v>
+        <v>-2.154978853254192</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>-2.131469101395831</v>
+        <v>-2.001761515249359</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.04038318167252452</v>
+        <v>0.008803702827623163</v>
       </c>
     </row>
     <row r="21">
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3631883487735664</v>
+        <v>0.3359039788484133</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2744,585 +2744,40 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.9171874163941814</v>
+        <v>1.033966818981059</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.05756108005260286</v>
+        <v>0.06704922538875925</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.6286728206214888</v>
+        <v>0.641032417684855</v>
       </c>
       <c r="AA21" t="n">
-        <v>-1.366409678442931</v>
+        <v>-1.323808137890686</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.5334320777420994</v>
+        <v>0.5266908812034983</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.095024926707563</v>
+        <v>-1.108572354015064</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.128360279780143</v>
+        <v>1.105817413962446</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.144124010030556</v>
+        <v>1.223034519473982</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.7371131837915595</v>
+        <v>0.8198950481268974</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.826473307300301</v>
+        <v>0.8486972627845625</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.715892944784188</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>697ha3El</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1.819875174399046</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-1.056923411754772</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.393718654096563</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.5818329863963865</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.8537242087121459</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.8365115089431081</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.3118685326087335</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.3118749377852377</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.176185875479598</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.760640733803758</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-2.872763763804937</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.3592647761527498</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-0.8775497521556299</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-1.091813919160445</v>
-      </c>
-      <c r="P22" t="n">
-        <v>-0.1635813362170178</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-1.221496519509297</v>
-      </c>
-      <c r="R22" t="n">
-        <v>-0.3513008407383969</v>
-      </c>
-      <c r="S22" t="n">
-        <v>-1.616235901390139</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.049432029168562</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.06472897360612198</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.312068950091571</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0.2436832174554022</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.7888265455249338</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0.9446841245896824</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>-0.5355479644245309</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.045357375500735</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0.6830191737012737</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0.2394022657511447</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0.1848800081345542</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0.104778429583655</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>634r8bcJ</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1.819875174399046</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1.63494810752045</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.393718654096563</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.4157521150431646</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.5694023869208018</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.01284963915427201</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.669003161442819</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-1.669063763807416</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-0.3696241010989402</v>
-      </c>
-      <c r="K23" t="n">
-        <v>-0.915073955308523</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.2147263603817656</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.440313973089069</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.434426302925192</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.451574971172967</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.03543156403547253</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.428016124263538</v>
-      </c>
-      <c r="R23" t="n">
-        <v>5.079150508807505</v>
-      </c>
-      <c r="S23" t="n">
-        <v>-2.286354170896134</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-0.9803288596577738</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.03882003430873411</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0.7844860215671735</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.07021105979703625</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>-0.03454537681271449</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0.4188874119794689</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>-1.641901940194646</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.015493570671055</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0.999183739193184</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0.1226622159594722</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0.115258558490021</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>-1.376949399600211</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>tOTmlbNp</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1.819875174399046</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.8994226501410234</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.393718654096563</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-0.08249049901650093</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.1903066245323431</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-0.398981295740146</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-1.973831894901305</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.973916769199483</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-0.00593696158772055</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.08739368717664438</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-0.3301248380041233</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.824104133701805</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-1.855341996794555</v>
-      </c>
-      <c r="O24" t="n">
-        <v>4.484547863495486</v>
-      </c>
-      <c r="P24" t="n">
-        <v>-1.994500018539928</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.666027818422636</v>
-      </c>
-      <c r="R24" t="n">
-        <v>5.079150508807505</v>
-      </c>
-      <c r="S24" t="n">
-        <v>-1.241284315154525</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.8445784734106215</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>-0.007655069013491917</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0.0795785394428087</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>-0.04095773553290011</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.5222647922784536</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0.0957817898045909</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.112534542569239</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>-1.092184090734201</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>-0.2241158146079971</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>-0.02071442016070084</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0.0006542446958196771</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0.03228290695655738</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>GINCsvmn</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1.819875174399046</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.9962615183626544</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2.393718654096563</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.08359037233672091</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.3798545057265725</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.01284963915427201</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.626146278427006</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-1.626205169301453</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-0.00593696158772055</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-1.516554540799623</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.849279955539432</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.3592647761527498</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.777110500812665</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-1.596085441209226</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.11010122539892</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-5.188358088827596</v>
-      </c>
-      <c r="R25" t="n">
-        <v>-3.066526515511348</v>
-      </c>
-      <c r="S25" t="n">
-        <v>-4.133767980400661</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>-0.3888156072405329</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>-0.007655069013491917</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>-0.4589867689793425</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>-0.08007658382283023</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.481401746359389</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>-0.5274518592164055</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>-0.3309333602506461</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>-0.5434929403810099</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>-0.5932449303772731</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>-0.09732975704283472</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0.0006542446958196771</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>-0.2639739339115436</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>tYjCfe2E</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2.218427650214686</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.6112786565284644</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.4607755271036255</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0.9128948557826102</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.5678849002445744</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.660173378731944</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.506147005982728</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-1.506201104684754</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-0.1877805313433304</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-1.67694936359725</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.7595775587676545</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-0.873154902621778</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.5626377034994592</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-0.7265842536765708</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.969836954489678</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-2.427422436582059</v>
-      </c>
-      <c r="R26" t="n">
-        <v>-0.9719238521150715</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.006806279587785195</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-0.06589882089744376</v>
-      </c>
-      <c r="U26" t="n">
-        <v>-1.010630043583902</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0.03107533278114179</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.005716133768708311</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0.9269956944558219</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.116068931327023</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.696969638974388</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.2511596952520777</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.124120663019018</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.009049474412908</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.6968083398830358</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0.842603019557411</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.871640253804628</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.854561294668261</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.225187768770108</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>-1.551538948421115</v>
+        <v>0.7888225800518529</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -712,68 +712,68 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C3" t="n">
-        <v>1.37713506060395</v>
+        <v>1.597034424150377</v>
       </c>
       <c r="D3" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4146522417229446</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5678849002445744</v>
+        <v>-0.1887891378561156</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8365115089431081</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4309841063320289</v>
+        <v>-1.259550511304418</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4310073669847965</v>
+        <v>1.259606860766758</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1271660080914603</v>
+        <v>-1.21822742662512</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6888742726677447</v>
+        <v>2.626978381472402</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.238210168647272</v>
+        <v>-1.78306136703316</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7700713357442589</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9118181719443772</v>
+        <v>-2.298546892729021</v>
       </c>
       <c r="O3" t="n">
-        <v>1.211678810198304</v>
+        <v>0.09787520567308552</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9994355172774767</v>
+        <v>-1.676079378135944</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.1107752801001733</v>
       </c>
       <c r="R3" t="n">
-        <v>1.103284342175684</v>
+        <v>-1.321024296014451</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.072724661002653</v>
+        <v>-0.1962144594129164</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02838722074170034</v>
+        <v>-1.567670313519776</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -782,107 +782,107 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8037978970265566</v>
+        <v>-0.113175472695782</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.3750180600127781</v>
+        <v>0.2329279256221052</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.3439125163065386</v>
+        <v>-0.4148051960563006</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2913063964739597</v>
+        <v>-0.7608228117398796</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.3084351757379331</v>
+        <v>-0.5786073101389009</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.600800704184132</v>
+        <v>-1.083374848565313</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.7773644435221762</v>
+        <v>-0.385177185174809</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.6378336414714419</v>
+        <v>0.3019371399315472</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.48747034758404</v>
+        <v>0.0007718576270169641</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.3634155751863477</v>
+        <v>-0.4721098992421069</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.4551948050311057</v>
+        <v>0.3536601917360916</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C4" t="n">
-        <v>1.597034424150377</v>
+        <v>1.37713506060395</v>
       </c>
       <c r="D4" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5807331130761665</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1887891378561156</v>
+        <v>-0.5678849002445744</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01284963915427201</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.259550511304418</v>
+        <v>-0.4309841063320289</v>
       </c>
       <c r="I4" t="n">
-        <v>1.259606860766758</v>
+        <v>0.4310073669847965</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.21822742662512</v>
+        <v>-0.1271660080914603</v>
       </c>
       <c r="K4" t="n">
-        <v>2.626978381472402</v>
+        <v>0.6888742726677447</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.78306136703316</v>
+        <v>-1.238210168647272</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.873154902621778</v>
+        <v>0.7700713357442589</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.298546892729021</v>
+        <v>-0.9118181719443772</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09787520567308552</v>
+        <v>1.211678810198304</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.676079378135944</v>
+        <v>-0.9994355172774767</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.1107752801001733</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.321024296014451</v>
+        <v>1.103284342175684</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1962144594129164</v>
+        <v>-1.072724661002653</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.567670313519776</v>
+        <v>0.02838722074170034</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -891,40 +891,40 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.113175472695782</v>
+        <v>-0.8037978970265566</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2329279256221052</v>
+        <v>-0.3750180600127781</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.4148051960563006</v>
+        <v>-0.3439125163065386</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.7608228117398796</v>
+        <v>0.2913063964739597</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.5786073101389009</v>
+        <v>-0.3084351757379331</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.083374848565313</v>
+        <v>1.600800704184132</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.385177185174809</v>
+        <v>-0.7773644435221762</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3019371399315472</v>
+        <v>-0.6378336414714419</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0007718576270169641</v>
+        <v>-0.48747034758404</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.4721098992421069</v>
+        <v>-0.3634155751863477</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.3536601917360916</v>
+        <v>-0.4551948050311057</v>
       </c>
     </row>
     <row r="5">
@@ -1039,68 +1039,68 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.874937731578419</v>
+        <v>-0.7763621548162278</v>
       </c>
       <c r="D6" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5807331130761665</v>
+        <v>2.408722571281827</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0007587433381137274</v>
+        <v>1.896237555280407</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8365115089431081</v>
+        <v>1.248342443837526</v>
       </c>
       <c r="H6" t="n">
-        <v>1.326148097316313</v>
+        <v>1.440433118691816</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.326195007759708</v>
+        <v>-1.440484593108944</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.09699838012138</v>
+        <v>-0.1271660080914607</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08739368717664438</v>
+        <v>0.2878872156736779</v>
       </c>
       <c r="L6" t="n">
-        <v>4.028684749082988</v>
+        <v>0.03310929425313586</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.570413938945361</v>
+        <v>0.9754746155400137</v>
       </c>
       <c r="N6" t="n">
-        <v>1.221962100234958</v>
+        <v>1.014067020183224</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.182337607653933</v>
+        <v>-0.5655111170221552</v>
       </c>
       <c r="P6" t="n">
-        <v>1.468324445853402</v>
+        <v>1.229508965550414</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.998299618032106</v>
+        <v>-2.808241147236616</v>
       </c>
       <c r="R6" t="n">
-        <v>-5.97569688133951</v>
+        <v>-0.3513008407383969</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4797097537360951</v>
+        <v>1.353129694999717</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2338299216196877</v>
+        <v>0.3044840165341666</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1109,107 +1109,107 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.021783105652138</v>
+        <v>0.7252693069320967</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.1857347444722231</v>
+        <v>1.054407515185459</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.1876312462570396</v>
+        <v>1.091579663677143</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.3269493534769882</v>
+        <v>-0.2392449390196802</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.4805127799629867</v>
+        <v>0.9879433727914823</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.032767035005459</v>
+        <v>-1.14844035140008</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.1148520449544874</v>
+        <v>1.234340584111829</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.2599894520820339</v>
+        <v>1.104817654336507</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.1086285653072785</v>
+        <v>1.401928409610353</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-1.037548112725092</v>
+        <v>0.67700757200586</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.8019350674185658</v>
+        <v>-1.162221073169684</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.3593116377454187</v>
+        <v>-1.056923411754772</v>
       </c>
       <c r="D7" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2485713703697228</v>
+        <v>-1.078975727135832</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1903066245323431</v>
+        <v>-0.5678849002445744</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8365115089431081</v>
+        <v>-0.810812230634564</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.145259426964558</v>
+        <v>2.097571991600951</v>
       </c>
       <c r="I7" t="n">
-        <v>2.145351147223337</v>
+        <v>-2.097649708867051</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7214373174347188</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K7" t="n">
-        <v>1.290354858158845</v>
+        <v>1.089861329661812</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.054380829933568</v>
+        <v>-1.419827234775901</v>
       </c>
       <c r="M7" t="n">
-        <v>3.440313973089069</v>
+        <v>0.3592647761527498</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.98683770765464</v>
+        <v>-0.22416521485018</v>
       </c>
       <c r="O7" t="n">
-        <v>2.839545616812086</v>
+        <v>-0.3917087963160216</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.905023860963833</v>
+        <v>-0.8004226170249864</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.904039512581734</v>
+        <v>-1.142159288122931</v>
       </c>
       <c r="R7" t="n">
-        <v>3.624565325893424</v>
+        <v>1.297229033230895</v>
       </c>
       <c r="S7" t="n">
-        <v>1.555120347225045</v>
+        <v>-2.54537417277618</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4586292164549462</v>
+        <v>-2.208274791931421</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1218,40 +1218,40 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2608334343293608</v>
+        <v>-0.8080882423021828</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.275740789899114</v>
+        <v>-0.8312331756664083</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1252357667055335</v>
+        <v>-0.1616646440544205</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.7814617263022781</v>
+        <v>0.08911193033946781</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2468280762429318</v>
+        <v>-0.4032765931189486</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3151192053262135</v>
+        <v>0.1324706093207676</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.2319484717893988</v>
+        <v>-0.5389503477016269</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.02303076348748194</v>
+        <v>-0.9090301003131893</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.05312799316504201</v>
+        <v>-0.5296200774067438</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1874029134030919</v>
+        <v>-0.3668310631426355</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.1800832968632841</v>
+        <v>-1.657062128315919</v>
       </c>
     </row>
     <row r="8">
@@ -1279,46 +1279,46 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.240428268320329</v>
+        <v>2.054715108585138</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.240511690553596</v>
+        <v>-2.054791114361088</v>
       </c>
       <c r="J8" t="n">
         <v>1.570040642960898</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.454658649604279</v>
+        <v>-2.920009240278857</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2147263603817656</v>
+        <v>-0.05769923881117887</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4623483430302688</v>
+        <v>-0.565049982928146</v>
       </c>
       <c r="N8" t="n">
-        <v>0.298999327258029</v>
+        <v>-0.2036041629769318</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9743137586830593</v>
+        <v>-0.9645220786432772</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5926676847424448</v>
+        <v>-0.2630877863432628</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.419839597975212</v>
+        <v>-1.26116513520248</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.9331349139040293</v>
+        <v>-1.030107259431635</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5921260769281529</v>
+        <v>0.7205627706686657</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2311793003959823</v>
+        <v>-0.2174436884902342</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1327,107 +1327,107 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.262945242009581</v>
+        <v>2.26786622022417</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.160426620442891</v>
+        <v>2.14942611069094</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.672245294169951</v>
+        <v>2.603343886632926</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.1900947432968207</v>
+        <v>-0.1567179744319159</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.758357508129675</v>
+        <v>2.669658936588986</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01561289723207803</v>
+        <v>-0.1187679363106135</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.747637839464633</v>
+        <v>2.718194618948798</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.636386026823984</v>
+        <v>2.619875608547407</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.882183143475709</v>
+        <v>2.878302924337442</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.631495264001797</v>
+        <v>2.572407253538996</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.401479895061255</v>
+        <v>-1.358814887590141</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.056923411754772</v>
+        <v>-0.3593116377454187</v>
       </c>
       <c r="D9" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.078975727135832</v>
+        <v>-0.2485713703697228</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5678849002445744</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.810812230634564</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H9" t="n">
-        <v>2.097571991600951</v>
+        <v>-2.145259426964558</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.097649708867051</v>
+        <v>2.145351147223337</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.73331124061016</v>
+        <v>0.7214373174347188</v>
       </c>
       <c r="K9" t="n">
-        <v>1.089861329661812</v>
+        <v>1.290354858158845</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.419827234775901</v>
+        <v>-3.054380829933568</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3592647761527498</v>
+        <v>3.440313973089069</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.22416521485018</v>
+        <v>-3.98683770765464</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3917087963160216</v>
+        <v>2.839545616812086</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8004226170249864</v>
+        <v>-3.905023860963833</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.142159288122931</v>
+        <v>2.904039512581734</v>
       </c>
       <c r="R9" t="n">
-        <v>1.297229033230895</v>
+        <v>3.624565325893424</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.54537417277618</v>
+        <v>1.555120347225045</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.208274791931421</v>
+        <v>0.4586292164549462</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1436,107 +1436,107 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8080882423021828</v>
+        <v>-0.2608334343293608</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.8312331756664083</v>
+        <v>0.275740789899114</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.1616646440544205</v>
+        <v>0.1252357667055335</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.08911193033946781</v>
+        <v>0.7814617263022781</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.4032765931189486</v>
+        <v>0.2468280762429318</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1324706093207676</v>
+        <v>0.3151192053262135</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.5389503477016269</v>
+        <v>0.2319484717893988</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.9090301003131893</v>
+        <v>-0.02303076348748194</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.5296200774067438</v>
+        <v>0.05312799316504201</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.3668310631426355</v>
+        <v>0.1874029134030919</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.657062128315919</v>
+        <v>0.1800832968632841</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.7763621548162278</v>
+        <v>-0.874937731578419</v>
       </c>
       <c r="D10" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E10" t="n">
-        <v>2.408722571281827</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F10" t="n">
-        <v>1.896237555280407</v>
+        <v>0.0007587433381137274</v>
       </c>
       <c r="G10" t="n">
-        <v>1.248342443837526</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H10" t="n">
-        <v>1.440433118691816</v>
+        <v>1.326148097316313</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.440484593108944</v>
+        <v>-1.326195007759708</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1271660080914607</v>
+        <v>-1.09699838012138</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2878872156736779</v>
+        <v>0.08739368717664438</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03310929425313586</v>
+        <v>4.028684749082988</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9754746155400137</v>
+        <v>-4.570413938945361</v>
       </c>
       <c r="N10" t="n">
-        <v>1.014067020183224</v>
+        <v>1.221962100234958</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5655111170221552</v>
+        <v>-3.182337607653933</v>
       </c>
       <c r="P10" t="n">
-        <v>1.229508965550414</v>
+        <v>1.468324445853402</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.808241147236616</v>
+        <v>-3.998299618032106</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.3513008407383969</v>
+        <v>-5.97569688133951</v>
       </c>
       <c r="S10" t="n">
-        <v>1.353129694999717</v>
+        <v>0.4797097537360951</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3044840165341666</v>
+        <v>0.2338299216196877</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1545,40 +1545,40 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.7252693069320967</v>
+        <v>-1.021783105652138</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.054407515185459</v>
+        <v>-0.1857347444722231</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.091579663677143</v>
+        <v>-0.1876312462570396</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.2392449390196802</v>
+        <v>-0.3269493534769882</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9879433727914823</v>
+        <v>-0.4805127799629867</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.14844035140008</v>
+        <v>-1.032767035005459</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.234340584111829</v>
+        <v>-0.1148520449544874</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.104817654336507</v>
+        <v>-0.2599894520820339</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.401928409610353</v>
+        <v>-0.1086285653072785</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.67700757200586</v>
+        <v>-1.037548112725092</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.162221073169684</v>
+        <v>0.8019350674185658</v>
       </c>
     </row>
     <row r="11">
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.819875174399046</v>
+        <v>2.218427650214686</v>
       </c>
       <c r="C11" t="n">
         <v>1.005580963577229</v>
@@ -1606,37 +1606,37 @@
         <v>0.42468057404869</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7690086181107414</v>
+        <v>0.7904370596186481</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7690332791821821</v>
+        <v>-0.7904625764351639</v>
       </c>
       <c r="J11" t="n">
         <v>-0.2483950545952001</v>
       </c>
       <c r="K11" t="n">
-        <v>1.156692505827489</v>
+        <v>1.390601622407362</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.056593102518642</v>
+        <v>-0.9657845694543271</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.05154178343875964</v>
+        <v>-0.1542434233366368</v>
       </c>
       <c r="N11" t="n">
-        <v>0.589138614802757</v>
+        <v>0.6896593128497492</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3868129562961306</v>
+        <v>-0.1016302751374757</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6324702647929431</v>
+        <v>0.7319767149191881</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.697519907827493</v>
+        <v>-1.102490672429748</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.7391902228488186</v>
+        <v>-0.06038380415558071</v>
       </c>
       <c r="S11" t="n">
         <v>0.6995240286504462</v>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.177574241048867</v>
+        <v>-1.141836769153705</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1654,40 +1654,40 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8974114011752855</v>
+        <v>-0.9052139658651964</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.4503048964063766</v>
+        <v>-0.4445779755931722</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.7705280112861475</v>
+        <v>-0.7857918001107426</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.3719506875490243</v>
+        <v>-0.3207119253431235</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.8364651237807823</v>
+        <v>-0.8554579605316445</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.5159307545235977</v>
+        <v>0.4549105514078189</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.8957269770135142</v>
+        <v>-0.8908290477797393</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.2815181412055308</v>
+        <v>-0.2827393355743561</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.7352105556293964</v>
+        <v>-0.7402052555834663</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-1.03540386499701</v>
+        <v>-1.075745574446455</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.700724965951256</v>
+        <v>-1.683647858217679</v>
       </c>
     </row>
     <row r="12">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.819875174399046</v>
+        <v>2.218427650214686</v>
       </c>
       <c r="C13" t="n">
         <v>1.597034424150377</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3426373832938708</v>
+        <v>0.3289017713881228</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1872,40 +1872,40 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.017832916233872</v>
+        <v>-1.02275389444846</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.293112303469993</v>
+        <v>-1.282111793718041</v>
       </c>
       <c r="Z13" t="n">
-        <v>-1.965945561393409</v>
+        <v>-1.897044153856384</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.5077709881491326</v>
+        <v>-0.5411477570140375</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.373631594465591</v>
+        <v>-1.284933022924902</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.602115831887972</v>
+        <v>-1.467734998345281</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.8620050079562626</v>
+        <v>-0.8325617874404283</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.8270430204621729</v>
+        <v>-0.810532602185596</v>
       </c>
       <c r="AF13" t="n">
-        <v>-2.034855918799655</v>
+        <v>-2.030975699661388</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-1.704681067752572</v>
+        <v>-1.645593057289772</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.326356977702323</v>
+        <v>1.283691970231209</v>
       </c>
     </row>
     <row r="14">
@@ -2129,68 +2129,68 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7477679166607292</v>
+        <v>-0.5109663712257129</v>
       </c>
       <c r="D16" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.08249049901650093</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1903066245323431</v>
+        <v>-0.378337019050345</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01284963915427201</v>
+        <v>-1.222643165528982</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.43812085720364</v>
+        <v>-0.8595529364901612</v>
       </c>
       <c r="I16" t="n">
-        <v>1.438184337874939</v>
+        <v>0.8595933120444317</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.73331124061016</v>
+        <v>0.5395937476791089</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.416307776551107</v>
+        <v>-0.7145804268114895</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7595775587676545</v>
+        <v>-0.05769923881117887</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.105574581396306</v>
+        <v>0.9754746155400137</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.758752563554639</v>
+        <v>-0.4777515212869103</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.276631879911333</v>
+        <v>-0.2154585555999435</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5616071367219981</v>
+        <v>-0.3227916564190099</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1901125114865394</v>
+        <v>-0.9041475939638333</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.175565777723043</v>
+        <v>-0.157356149683186</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1208308363061085</v>
+        <v>1.63883830878714</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7353381006551266</v>
+        <v>1.488864977551531</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -2199,40 +2199,40 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.009017550057460712</v>
+        <v>0.2085836806328085</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.01425754571295434</v>
+        <v>0.1024764445697142</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0722202347974373</v>
+        <v>0.008710352657019495</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.6584010503112059</v>
+        <v>0.3217462586255166</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.234086530441603</v>
+        <v>0.001582938545225925</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.8121783655272882</v>
+        <v>0.4758934309413642</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.1944272360231096</v>
+        <v>-0.03965602124728654</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.7347842240107532</v>
+        <v>-0.001694219430144185</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.09221436003096149</v>
+        <v>-0.05714867735855229</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.2563046690309104</v>
+        <v>0.1652335543412626</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.222555270959666</v>
+        <v>0.5569107191011068</v>
       </c>
     </row>
     <row r="17">
@@ -2347,68 +2347,68 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.5109663712257129</v>
+        <v>0.7477679166607292</v>
       </c>
       <c r="D18" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7468139844293883</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.378337019050345</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.222643165528982</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8595529364901612</v>
+        <v>-1.43812085720364</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8595933120444317</v>
+        <v>1.438184337874939</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5395937476791089</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7145804268114895</v>
+        <v>-1.416307776551107</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.05769923881117887</v>
+        <v>0.7595775587676545</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9754746155400137</v>
+        <v>-2.105574581396306</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4777515212869103</v>
+        <v>-0.758752563554639</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2154585555999435</v>
+        <v>-1.276631879911333</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3227916564190099</v>
+        <v>-0.5616071367219981</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9041475939638333</v>
+        <v>-0.1901125114865394</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.157356149683186</v>
+        <v>-1.175565777723043</v>
       </c>
       <c r="S18" t="n">
-        <v>1.63883830878714</v>
+        <v>-0.1208308363061085</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.488864977551531</v>
+        <v>0.7353381006551266</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2417,40 +2417,40 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2085836806328085</v>
+        <v>-0.009017550057460712</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1024764445697142</v>
+        <v>-0.01425754571295434</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.008710352657019495</v>
+        <v>0.0722202347974373</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.3217462586255166</v>
+        <v>0.6584010503112059</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.001582938545225925</v>
+        <v>0.234086530441603</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.4758934309413642</v>
+        <v>0.8121783655272882</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.03965602124728654</v>
+        <v>-0.1944272360231096</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.001694219430144185</v>
+        <v>-0.7347842240107532</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.05714867735855229</v>
+        <v>-0.09221436003096149</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.1652335543412626</v>
+        <v>0.2563046690309104</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.5569107191011068</v>
+        <v>2.222555270959666</v>
       </c>
     </row>
     <row r="19">
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3359039788484133</v>
+        <v>0.3001665069532508</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2744,40 +2744,40 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.033966818981059</v>
+        <v>1.04176938367097</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.06704922538875925</v>
+        <v>0.06132230457555496</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.641032417684855</v>
+        <v>0.6562962065094501</v>
       </c>
       <c r="AA21" t="n">
-        <v>-1.323808137890686</v>
+        <v>-1.375046900096587</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.5266908812034983</v>
+        <v>0.5456837179543604</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.108572354015064</v>
+        <v>-1.047552150899285</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.105817413962446</v>
+        <v>1.100919484728671</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.223034519473982</v>
+        <v>1.224255713842808</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.8198950481268974</v>
+        <v>0.8248897480809674</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.8486972627845625</v>
+        <v>0.8890389722340076</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.7888225800518529</v>
+        <v>0.7717454723182761</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI21"/>
+  <dimension ref="A1:AI22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,68 +603,68 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C2" t="n">
-        <v>1.37713506060395</v>
+        <v>0.4292929763521113</v>
       </c>
       <c r="D2" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08359037233672091</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2850805651294578</v>
+        <v>0.9484981493092606</v>
       </c>
       <c r="G2" t="n">
-        <v>1.248342443837526</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08329848985772981</v>
+        <v>-0.9881235855376008</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08329576708676574</v>
+        <v>0.9881690955623221</v>
       </c>
       <c r="J2" t="n">
         <v>0.3577501779234991</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8893678011647782</v>
+        <v>-2.118035126290724</v>
       </c>
       <c r="L2" t="n">
-        <v>1.849279955539432</v>
+        <v>-1.601444300904531</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3592647761527498</v>
+        <v>-0.2569450632345141</v>
       </c>
       <c r="N2" t="n">
-        <v>3.079310452785065</v>
+        <v>-1.140274303869359</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6951676880997961</v>
+        <v>-0.3941567163259672</v>
       </c>
       <c r="P2" t="n">
-        <v>4.214702469337768</v>
+        <v>-0.8004226170249864</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.380170982282029</v>
+        <v>0.7619342651498524</v>
       </c>
       <c r="R2" t="n">
-        <v>1.588146069813711</v>
+        <v>1.297229033230895</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7982875000831346</v>
+        <v>0.6474266096172088</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5416063509784073</v>
+        <v>0.5462724293372833</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -673,107 +673,107 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.255220462537494</v>
+        <v>0.1066511979278359</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.059602915079372</v>
+        <v>-0.8331526317968772</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.332319891816384</v>
+        <v>-0.6336372330022989</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.5471868618974325</v>
+        <v>0.3486120289584462</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.210367406173853</v>
+        <v>-0.5414296529011389</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.1238233223773065</v>
+        <v>-0.442952323565686</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.369389029045715</v>
+        <v>-0.2472193017735524</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.555477060127494</v>
+        <v>-0.6870019890510012</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.750080574461782</v>
+        <v>-1.065683421149025</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.946707227365162</v>
+        <v>-0.4492109960068809</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.9539156255057242</v>
+        <v>0.1444242836986425</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C3" t="n">
-        <v>1.597034424150377</v>
+        <v>0.543034026462332</v>
       </c>
       <c r="D3" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5807331130761665</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1887891378561156</v>
+        <v>-0.09401519725900095</v>
       </c>
       <c r="G3" t="n">
         <v>0.01284963915427201</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.259550511304418</v>
+        <v>-2.530971374106877</v>
       </c>
       <c r="I3" t="n">
-        <v>1.259606860766758</v>
+        <v>2.531078497777009</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.21822742662512</v>
+        <v>-0.3696241010989402</v>
       </c>
       <c r="K3" t="n">
-        <v>2.626978381472402</v>
+        <v>0.6888742726677447</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.78306136703316</v>
+        <v>-1.96467843316179</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.873154902621778</v>
+        <v>-1.489364742009042</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.298546892729021</v>
+        <v>-1.77995147325931</v>
       </c>
       <c r="O3" t="n">
-        <v>0.09787520567308552</v>
+        <v>-0.8470219181658917</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.676079378135944</v>
+        <v>-1.516869057933951</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1107752801001733</v>
+        <v>0.8809401122294014</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.321024296014451</v>
+        <v>-1.030107259431635</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1962144594129164</v>
+        <v>-1.127974769863544</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.567670313519776</v>
+        <v>0.2893855975780284</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -782,107 +782,107 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.113175472695782</v>
+        <v>-0.6765144462536322</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2329279256221052</v>
+        <v>-0.9490931164833513</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.4148051960563006</v>
+        <v>-0.767921057283669</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.7608228117398796</v>
+        <v>0.6008512767753831</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.5786073101389009</v>
+        <v>-0.7304433951926332</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.083374848565313</v>
+        <v>0.7081901404543892</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.385177185174809</v>
+        <v>-0.8599738822835314</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3019371399315472</v>
+        <v>-0.91454244365921</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0007718576270169641</v>
+        <v>-1.080092554855749</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.4721098992421069</v>
+        <v>-0.7330268589555373</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.3536601917360916</v>
+        <v>-0.002599528194612392</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C4" t="n">
-        <v>1.37713506060395</v>
+        <v>0.8918399134670087</v>
       </c>
       <c r="D4" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4146522417229446</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5678849002445744</v>
+        <v>2.085785436474636</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8365115089431081</v>
+        <v>2.48383524852078</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4309841063320289</v>
+        <v>1.026149916205621</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4310073669847965</v>
+        <v>-1.026184846217963</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1271660080914603</v>
+        <v>-0.2483950545952004</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6888742726677447</v>
+        <v>-1.449723364633946</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.238210168647272</v>
+        <v>0.0331092942531361</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7700713357442589</v>
+        <v>-0.2569450632345141</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9118181719443772</v>
+        <v>-0.5485729221836555</v>
       </c>
       <c r="O4" t="n">
-        <v>1.211678810198304</v>
+        <v>0.5091257673439357</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9994355172774767</v>
+        <v>0.2742470443384608</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1107752801001733</v>
+        <v>1.436300731933963</v>
       </c>
       <c r="R4" t="n">
-        <v>1.103284342175684</v>
+        <v>-1.030107259431635</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.072724661002653</v>
+        <v>0.9567335749858984</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02838722074170034</v>
+        <v>-0.2959658758582872</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -891,107 +891,107 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8037978970265566</v>
+        <v>0.8590620789414448</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.3750180600127781</v>
+        <v>0.1099327462761978</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.3439125163065386</v>
+        <v>0.2874755704302207</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2913063964739597</v>
+        <v>-1.237145440448594</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.3084351757379331</v>
+        <v>0.2980835575905008</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.600800704184132</v>
+        <v>-1.248649160472326</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.7773644435221762</v>
+        <v>0.7198894457046625</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.6378336414714419</v>
+        <v>1.120354790730962</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.48747034758404</v>
+        <v>0.5441350196096062</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.3634155751863477</v>
+        <v>0.5454944250289068</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.4551948050311057</v>
+        <v>-0.247817072333241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.874937731578419</v>
+        <v>0.7174369699646703</v>
       </c>
       <c r="D5" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.411137469842276</v>
+        <v>-1.245056598489054</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.705172187409951</v>
+        <v>-2.273815830992639</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.810812230634564</v>
+        <v>-1.6344741004234</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8166960534743479</v>
+        <v>-0.1881284359090871</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8167347175384682</v>
+        <v>0.1881419981176697</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7214373174347188</v>
+        <v>-1.09699838012138</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4883807441707113</v>
+        <v>2.025497795981301</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2147263603817656</v>
+        <v>-1.056593102518642</v>
       </c>
       <c r="M5" t="n">
         <v>2.207894294314541</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7216431713192469</v>
+        <v>-0.4937434505216594</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6290738478312667</v>
+        <v>1.074595289641354</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3936547844899549</v>
+        <v>1.189706385499916</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.356963500547597</v>
+        <v>1.118951806388499</v>
       </c>
       <c r="R5" t="n">
-        <v>2.751814216144976</v>
+        <v>-0.157356149683186</v>
       </c>
       <c r="S5" t="n">
-        <v>1.214067980324422</v>
+        <v>-0.5672954165531842</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.09561627516831558</v>
+        <v>0.3939965312235278</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1000,107 +1000,107 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1115431141443193</v>
+        <v>-1.048458883983512</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.405164270377252</v>
+        <v>-1.241742425282456</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.230130880042962</v>
+        <v>-1.981208776784071</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.3618885308007449</v>
+        <v>0.9235090111862538</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.7196558696693568</v>
+        <v>-1.102715342354329</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8172660296615185</v>
+        <v>0.8807667299987877</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.9412803980967652</v>
+        <v>-1.43625005591049</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.173554721412973</v>
+        <v>-1.693603282165887</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1.577959169520293</v>
+        <v>-2.4460486213568</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.1297942720436997</v>
+        <v>-1.179331810227863</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.9861427318501043</v>
+        <v>0.563742812882979</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.908442391246966</v>
+        <v>2.284853062850626</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.7763621548162278</v>
+        <v>1.013163700251244</v>
       </c>
       <c r="D6" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E6" t="n">
-        <v>2.408722571281827</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F6" t="n">
-        <v>1.896237555280407</v>
+        <v>-0.1887891378561156</v>
       </c>
       <c r="G6" t="n">
-        <v>1.248342443837526</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H6" t="n">
-        <v>1.440433118691816</v>
+        <v>-0.2166996912529628</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.440484593108944</v>
+        <v>0.2167143944549789</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1271660080914607</v>
+        <v>-0.3696241010989402</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2878872156736779</v>
+        <v>-1.115567483805556</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03310929425313586</v>
+        <v>-0.6933589702613824</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9754746155400137</v>
+        <v>0.3592647761527498</v>
       </c>
       <c r="N6" t="n">
-        <v>1.014067020183224</v>
+        <v>-0.3132631063009232</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5655111170221552</v>
+        <v>0.1125627257327581</v>
       </c>
       <c r="P6" t="n">
-        <v>1.229508965550414</v>
+        <v>-0.1237787561665195</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.808241147236616</v>
+        <v>0.4049167239112055</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.3513008407383969</v>
+        <v>-0.2543284952107916</v>
       </c>
       <c r="S6" t="n">
-        <v>1.353129694999717</v>
+        <v>2.467028076186675</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3044840165341666</v>
+        <v>-0.6447471785188281</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1109,107 +1109,107 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7252693069320967</v>
+        <v>-0.5524900958308684</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.054407515185459</v>
+        <v>-1.131548916918645</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.091579663677143</v>
+        <v>-0.3765391428079359</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.2392449390196802</v>
+        <v>-1.013283831305479</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9879433727914823</v>
+        <v>-1.160219857250067</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.14844035140008</v>
+        <v>-0.2741785699582603</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.234340584111829</v>
+        <v>-0.9365648225360037</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.104817654336507</v>
+        <v>-0.6493193849327275</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.401928409610353</v>
+        <v>-0.3210022450247348</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.67700757200586</v>
+        <v>-0.6351178829756178</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.162221073169684</v>
+        <v>0.4366727243813309</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.056923411754772</v>
+        <v>1.339221377233877</v>
       </c>
       <c r="D7" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.078975727135832</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5678849002445744</v>
+        <v>0.2850805651294578</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.810812230634564</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H7" t="n">
-        <v>2.097571991600951</v>
+        <v>-0.5666975692154377</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.097649708867051</v>
+        <v>0.5667262495870146</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.73331124061016</v>
+        <v>0.3577501779234991</v>
       </c>
       <c r="K7" t="n">
-        <v>1.089861329661812</v>
+        <v>-2.21828189053924</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.419827234775901</v>
+        <v>0.3055348934460803</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3592647761527498</v>
+        <v>1.797087734723032</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.22416521485018</v>
+        <v>0.03056337224617514</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3917087963160216</v>
+        <v>2.265508374479858</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8004226170249864</v>
+        <v>-1.477066477883453</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.142159288122931</v>
+        <v>1.39663211624078</v>
       </c>
       <c r="R7" t="n">
-        <v>1.297229033230895</v>
+        <v>2.218466315743146</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.54537417277618</v>
+        <v>0.08247083545151267</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.208274791931421</v>
+        <v>1.993213631860892</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1218,107 +1218,107 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8080882423021828</v>
+        <v>0.2186230334351373</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.8312331756664083</v>
+        <v>0.536757255232435</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.1616646440544205</v>
+        <v>0.2651079108897363</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.08911193033946781</v>
+        <v>0.02419594453736944</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.4032765931189486</v>
+        <v>0.6860065880457429</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1324706093207676</v>
+        <v>0.2845845655775999</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.5389503477016269</v>
+        <v>0.6062256180071888</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.9090301003131893</v>
+        <v>0.4469138546127484</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.5296200774067438</v>
+        <v>0.3146898169970525</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.3668310631426355</v>
+        <v>0.05701702197165631</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.657062128315919</v>
+        <v>0.2206185939582957</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.908442391246966</v>
+        <v>2.284853062850626</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6112786565284644</v>
+        <v>0.8918399134670087</v>
       </c>
       <c r="D8" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.08249049901650093</v>
+        <v>0.08359037233672091</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09553268393522843</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H8" t="n">
-        <v>2.054715108585138</v>
+        <v>2.140428874616765</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.054791114361088</v>
+        <v>-2.140508303373015</v>
       </c>
       <c r="J8" t="n">
-        <v>1.570040642960898</v>
+        <v>-1.460685519632599</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.920009240278857</v>
+        <v>-1.783879245462334</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.05769923881117887</v>
+        <v>-1.056593102518642</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.565049982928146</v>
+        <v>-0.05154178343875964</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2036041629769318</v>
+        <v>-0.3932227524746673</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9645220786432772</v>
+        <v>0.2349587262300355</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2630877863432628</v>
+        <v>0.7916805849949352</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.26116513520248</v>
+        <v>-0.8248103625774671</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.030107259431635</v>
+        <v>-2.290747751290505</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7205627706686657</v>
+        <v>-0.5366019521221617</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2174436884902342</v>
+        <v>0.137072783087257</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1327,107 +1327,107 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.26786622022417</v>
+        <v>-0.3537472073069263</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.14942611069094</v>
+        <v>-0.05582895066634061</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.603343886632926</v>
+        <v>-0.6106806019560544</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.1567179744319159</v>
+        <v>0.961580492843477</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.669658936588986</v>
+        <v>-0.7169260769530903</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1187679363106135</v>
+        <v>0.1704604840228286</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.718194618948798</v>
+        <v>-0.736736007820901</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.619875608547407</v>
+        <v>-0.7371454405291623</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.878302924337442</v>
+        <v>-0.5574669140856525</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.572407253538996</v>
+        <v>-0.8968777540327075</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.358814887590141</v>
+        <v>-0.6354650410287542</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.3593116377454187</v>
+        <v>1.286142220515774</v>
       </c>
       <c r="D9" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2485713703697228</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1903066245323431</v>
+        <v>0.0007587433381137274</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8365115089431081</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.145259426964558</v>
+        <v>0.197583511233232</v>
       </c>
       <c r="I9" t="n">
-        <v>2.145351147223337</v>
+        <v>-0.2261577487733106</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7214373174347188</v>
+        <v>-0.2483950545952004</v>
       </c>
       <c r="K9" t="n">
-        <v>1.290354858158845</v>
+        <v>-1.115567483805556</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.054380829933568</v>
+        <v>-0.5117419041327529</v>
       </c>
       <c r="M9" t="n">
-        <v>3.440313973089069</v>
+        <v>-0.2569450632345141</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.98683770765464</v>
+        <v>-0.7084922145311433</v>
       </c>
       <c r="O9" t="n">
-        <v>2.839545616812086</v>
+        <v>-0.8715011182653473</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.905023860963833</v>
+        <v>-1.198448417529967</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.904039512581734</v>
+        <v>-1.023153441043382</v>
       </c>
       <c r="R9" t="n">
-        <v>3.624565325893424</v>
+        <v>-2.290747751290505</v>
       </c>
       <c r="S9" t="n">
-        <v>1.555120347225045</v>
+        <v>-1.594089035719624</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4586292164549462</v>
+        <v>0.9838898971029448</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1436,107 +1436,107 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2608334343293608</v>
+        <v>0.1571454104651572</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.275740789899114</v>
+        <v>-0.274121108503933</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.1252357667055335</v>
+        <v>0.09370843995819361</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7814617263022781</v>
+        <v>0.5243030347787914</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.2468280762429318</v>
+        <v>0.3100912757949237</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.3151192053262135</v>
+        <v>1.61149122349696</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2319484717893988</v>
+        <v>-0.009561499974817431</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.02303076348748194</v>
+        <v>-0.5495533614605043</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.05312799316504201</v>
+        <v>-0.2736652139666792</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.1874029134030919</v>
+        <v>0.5240879560837413</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.1800832968632841</v>
+        <v>0.8458655487425889</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.819875174399046</v>
+        <v>2.218427650214686</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.874937731578419</v>
+        <v>-0.5488800545957865</v>
       </c>
       <c r="D10" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5807331130761665</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0007587433381137274</v>
+        <v>-0.2835630784532303</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8365115089431081</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H10" t="n">
-        <v>1.326148097316313</v>
+        <v>-0.002415276173896646</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.326195007759708</v>
+        <v>0.04528001643112482</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.09699838012138</v>
+        <v>-0.3696241010989402</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08739368717664438</v>
+        <v>1.023030153496134</v>
       </c>
       <c r="L10" t="n">
-        <v>4.028684749082988</v>
+        <v>0.9411946248962842</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.570413938945361</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N10" t="n">
-        <v>1.221962100234958</v>
+        <v>0.8404403599202378</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.182337607653933</v>
+        <v>-1.405147680433473</v>
       </c>
       <c r="P10" t="n">
-        <v>1.468324445853402</v>
+        <v>2.304178626913861</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.998299618032106</v>
+        <v>-2.133874680452506</v>
       </c>
       <c r="R10" t="n">
-        <v>-5.97569688133951</v>
+        <v>-2.872581824456137</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4797097537360951</v>
+        <v>-0.1172808678323042</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2338299216196877</v>
+        <v>0.9135759987813451</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1545,53 +1545,53 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.021783105652138</v>
+        <v>0.1715822389684006</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.1857347444722231</v>
+        <v>0.595035103207857</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.1876312462570396</v>
+        <v>-0.1259556116081686</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.3269493534769882</v>
+        <v>0.1404526829372301</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.4805127799629867</v>
+        <v>-0.3076434998103389</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.032767035005459</v>
+        <v>-0.6385863001100867</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.1148520449544874</v>
+        <v>-0.1533233115415633</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.2599894520820339</v>
+        <v>0.1677587843900229</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.1086285653072785</v>
+        <v>0.1550823494835517</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-1.037548112725092</v>
+        <v>-0.1822812385858773</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.8019350674185658</v>
+        <v>1.095167294001493</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.218427650214686</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C11" t="n">
-        <v>1.005580963577229</v>
+        <v>0.7477679166607292</v>
       </c>
       <c r="D11" t="n">
         <v>-0.5056960363928432</v>
@@ -1600,52 +1600,52 @@
         <v>-0.5807331130761665</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4731109596474597</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G11" t="n">
-        <v>0.42468057404869</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7904370596186481</v>
+        <v>0.3261541602806716</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7904625764351639</v>
+        <v>-0.3261611359538926</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2483950545952001</v>
+        <v>0.7214373174347188</v>
       </c>
       <c r="K11" t="n">
-        <v>1.390601622407362</v>
+        <v>0.7557054488334223</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9657845694543271</v>
+        <v>0.0331092942531361</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1542434233366368</v>
+        <v>0.1538614963569951</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6896593128497492</v>
+        <v>1.274507010577705</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1016302751374757</v>
+        <v>-0.7613447178177976</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7319767149191881</v>
+        <v>1.866350246358383</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.102490672429748</v>
+        <v>-1.023153441043382</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.06038380415558071</v>
+        <v>-0.5452455317936075</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6995240286504462</v>
+        <v>-0.6799806668287885</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.141836769153705</v>
+        <v>0.3068593687952422</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1654,107 +1654,107 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9052139658651964</v>
+        <v>0.7817902685685049</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.4445779755931722</v>
+        <v>1.554171630430104</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.7857918001107426</v>
+        <v>1.886191184678708</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.3207119253431235</v>
+        <v>0.4475031604971795</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.8554579605316445</v>
+        <v>1.53296434076075</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4549105514078189</v>
+        <v>-0.791865344879914</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.8908290477797393</v>
+        <v>1.343500356181161</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.2827393355743561</v>
+        <v>0.9483540381020542</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.7402052555834663</v>
+        <v>1.997447899341295</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-1.075745574446455</v>
+        <v>1.036852592258035</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.683647858217679</v>
+        <v>0.3899977241566469</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8918399134670087</v>
+        <v>1.013163700251244</v>
       </c>
       <c r="D12" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4146522417229446</v>
+        <v>0.08359037233672091</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2835630784532303</v>
+        <v>0.2850805651294578</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.810812230634564</v>
+        <v>1.248342443837526</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.073837351569227</v>
+        <v>0.08329848985772981</v>
       </c>
       <c r="I12" t="n">
-        <v>1.073886284574249</v>
+        <v>-0.08329576708676574</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.21822742662512</v>
+        <v>-0.00593696158772055</v>
       </c>
       <c r="K12" t="n">
-        <v>0.154224863342322</v>
+        <v>0.8893678011647782</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5779604926390248</v>
+        <v>1.849279955539432</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.873154902621778</v>
+        <v>0.3592647761527498</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.434982714052587</v>
+        <v>3.079310452785065</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7491051177680702</v>
+        <v>0.6951676880997961</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6810148768734923</v>
+        <v>4.214702469337768</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.300833750895663</v>
+        <v>-1.380170982282029</v>
       </c>
       <c r="R12" t="n">
-        <v>-2.678637133400926</v>
+        <v>1.588146069813711</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.269498205480952</v>
+        <v>0.7982875000831346</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5746995565220469</v>
+        <v>-0.5017776204546213</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1763,107 +1763,107 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6379041544319998</v>
+        <v>1.227905381925339</v>
       </c>
       <c r="Y12" t="n">
-        <v>-1.013951584492341</v>
+        <v>1.112949556931529</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.150436710112458</v>
+        <v>1.374526804225985</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.5167945151078079</v>
+        <v>-0.4841113211168335</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.144351624427494</v>
+        <v>1.242614982777913</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.698593775434444</v>
+        <v>-0.09301959257525098</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.457841635028116</v>
+        <v>1.384994448107078</v>
       </c>
       <c r="AE12" t="n">
-        <v>-1.338393181063955</v>
+        <v>1.515915624379784</v>
       </c>
       <c r="AF12" t="n">
-        <v>-1.489275975228819</v>
+        <v>1.782164020621224</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.9300830840524966</v>
+        <v>1.986673560342574</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.3607592654502234</v>
+        <v>1.033756567089463</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.218427650214686</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C13" t="n">
-        <v>1.597034424150377</v>
+        <v>-0.5488800545957865</v>
       </c>
       <c r="D13" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4157521150431646</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1903066245323431</v>
+        <v>-0.1887891378561156</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.869966905106654</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5452691277075311</v>
+        <v>-1.259550511304418</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5452969523340327</v>
+        <v>1.259606860766758</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4789792244272389</v>
+        <v>-1.09699838012138</v>
       </c>
       <c r="K13" t="n">
-        <v>1.357186034324523</v>
+        <v>2.626978381472402</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3301248380041233</v>
+        <v>-1.78306136703316</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7700713357442589</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3058530112157789</v>
+        <v>-2.298546892729021</v>
       </c>
       <c r="O13" t="n">
-        <v>1.706158652207303</v>
+        <v>0.09787520567308552</v>
       </c>
       <c r="P13" t="n">
-        <v>1.050397355323173</v>
+        <v>-1.676079378135944</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.904039512581734</v>
+        <v>-0.1107752801001733</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7638811328290654</v>
+        <v>-1.321024296014451</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5268440273970857</v>
+        <v>-0.1962144594129164</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3289017713881228</v>
+        <v>-1.623870137228588</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1872,53 +1872,53 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.02275389444846</v>
+        <v>-0.2045399705252551</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.282111793718041</v>
+        <v>0.1463367184841673</v>
       </c>
       <c r="Z13" t="n">
-        <v>-1.897044153856384</v>
+        <v>-0.4128214941249725</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.5411477570140375</v>
+        <v>-0.8362586616820753</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.284933022924902</v>
+        <v>-0.5650364329540472</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.467734998345281</v>
+        <v>-1.087009924725866</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.8325617874404283</v>
+        <v>-0.3674542166242922</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.810532602185596</v>
+        <v>0.3018583124556456</v>
       </c>
       <c r="AF13" t="n">
-        <v>-2.030975699661388</v>
+        <v>-0.0502779134264426</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-1.645593057289772</v>
+        <v>-0.459584837625255</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.283691970231209</v>
+        <v>0.3227106019491588</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C14" t="n">
-        <v>1.339221377233877</v>
+        <v>0.7477679166607292</v>
       </c>
       <c r="D14" t="n">
         <v>-0.5056960363928432</v>
@@ -1927,52 +1927,52 @@
         <v>-0.4146522417229446</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.09401519725900095</v>
+        <v>-0.5678849002445744</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.398981295740146</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8547223841423679</v>
+        <v>-0.4309841063320289</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8547504681941092</v>
+        <v>0.4310073669847965</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7214373174347188</v>
+        <v>0.9638954104421987</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.717048069296657</v>
+        <v>0.6888742726677447</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.419827234775901</v>
+        <v>-1.238210168647272</v>
       </c>
       <c r="M14" t="n">
-        <v>1.591684454927278</v>
+        <v>0.7700713357442589</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.65658516201982</v>
+        <v>-0.9118181719443772</v>
       </c>
       <c r="O14" t="n">
-        <v>2.068450813679242</v>
+        <v>1.211678810198304</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.755684538236939</v>
+        <v>-0.9994355172774767</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9999459593089504</v>
+        <v>-0.1107752801001733</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4244779234824463</v>
+        <v>1.103284342175684</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2251846759667669</v>
+        <v>-1.072724661002653</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4598017307625239</v>
+        <v>-0.01956258426656824</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1981,107 +1981,107 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1248939056402486</v>
+        <v>-0.6343394208020771</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1417841947503617</v>
+        <v>-0.3379815751701792</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.09966998893535683</v>
+        <v>-0.3556690765831189</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.667796608214376</v>
+        <v>0.3934561822041817</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.01865705542761047</v>
+        <v>-0.2911470132533752</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.176311225652666</v>
+        <v>1.673480590037023</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.2037200729720813</v>
+        <v>-0.81654030991459</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.2804022094170529</v>
+        <v>-0.6284842553397906</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.03521587811355715</v>
+        <v>-0.5060466933800721</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.3149773080488661</v>
+        <v>-0.3612504523555711</v>
       </c>
       <c r="AI14" t="n">
-        <v>-1.111240053801304</v>
+        <v>-0.4894530484796624</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.819875174399046</v>
+        <v>2.218427650214686</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6112786565284644</v>
+        <v>0.7174369699646703</v>
       </c>
       <c r="D15" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4157521150431646</v>
+        <v>-1.411137469842276</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0007587433381137274</v>
+        <v>-1.705172187409951</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8365115089431081</v>
+        <v>-0.810812230634564</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5166978723636554</v>
+        <v>-0.8166960534743479</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5167245559967235</v>
+        <v>0.8167347175384682</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.73331124061016</v>
+        <v>-1.09699838012138</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1130998413203891</v>
+        <v>0.4883807441707113</v>
       </c>
       <c r="L15" t="n">
-        <v>2.394131153925321</v>
+        <v>0.2147263603817656</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.489364742009042</v>
+        <v>2.207894294314541</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8450094825587373</v>
+        <v>0.7216431713192469</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.412491440463311</v>
+        <v>0.6290738478312667</v>
       </c>
       <c r="P15" t="n">
-        <v>2.423586367065355</v>
+        <v>0.3936547844899549</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7619342651498524</v>
+        <v>1.356963500547597</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.902858369180083</v>
+        <v>2.751814216144976</v>
       </c>
       <c r="S15" t="n">
-        <v>0.102136128435901</v>
+        <v>1.214067980324422</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1967137790551501</v>
+        <v>-0.09095654158382248</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2090,107 +2090,107 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.009557134085341335</v>
+        <v>-0.2564937675438262</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.06523490693479181</v>
+        <v>-1.431539967288882</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.2587095502556336</v>
+        <v>-1.258194315102407</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.418684735144918</v>
+        <v>-0.4171497601466182</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.1053749606388236</v>
+        <v>-0.7166169625283227</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.903066809465341</v>
+        <v>0.8777511004900883</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.2513821991097257</v>
+        <v>-0.9631492753617833</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.4785278957807249</v>
+        <v>-1.165019489194087</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.4026730088889842</v>
+        <v>-1.613923290432531</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.008545033514437346</v>
+        <v>-0.1465778546102821</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.6737590263016837</v>
+        <v>0.9715228520786635</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.5109663712257129</v>
+        <v>0.8918399134670087</v>
       </c>
       <c r="D16" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7468139844293883</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.378337019050345</v>
+        <v>0.09553268393522843</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.222643165528982</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8595529364901612</v>
+        <v>2.054715108585138</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8595933120444317</v>
+        <v>-2.054791114361088</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5395937476791089</v>
+        <v>1.691269689464638</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7145804268114895</v>
+        <v>-2.920009240278857</v>
       </c>
       <c r="L16" t="n">
         <v>-0.05769923881117887</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9754746155400137</v>
+        <v>-0.565049982928146</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4777515212869103</v>
+        <v>-0.2036041629769318</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2154585555999435</v>
+        <v>-0.9645220786432772</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3227916564190099</v>
+        <v>-0.2630877863432628</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9041475939638333</v>
+        <v>-1.26116513520248</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.157356149683186</v>
+        <v>-1.030107259431635</v>
       </c>
       <c r="S16" t="n">
-        <v>1.63883830878714</v>
+        <v>0.7205627706686657</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.488864977551531</v>
+        <v>-0.1760013724459726</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -2199,50 +2199,50 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.2085836806328085</v>
+        <v>2.289939529538654</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1024764445697142</v>
+        <v>2.158682428869865</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.008710352657019495</v>
+        <v>2.599384978868622</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.3217462586255166</v>
+        <v>-0.1152627424258172</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.001582938545225925</v>
+        <v>2.66540765159332</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.4758934309413642</v>
+        <v>-0.04914510005192888</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.03965602124728654</v>
+        <v>2.683713197143029</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.001694219430144185</v>
+        <v>2.624501277353565</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.05714867735855229</v>
+        <v>2.906463643125794</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.1652335543412626</v>
+        <v>2.58206944392914</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.5569107191011068</v>
+        <v>-1.23827594594042</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.819875174399046</v>
+        <v>2.284853062850626</v>
       </c>
       <c r="C17" t="n">
         <v>1.339221377233877</v>
@@ -2251,55 +2251,55 @@
         <v>-0.5056960363928432</v>
       </c>
       <c r="E17" t="n">
-        <v>1.744399085868939</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4746284463236872</v>
+        <v>0.0007587433381137274</v>
       </c>
       <c r="G17" t="n">
-        <v>2.072004313626362</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H17" t="n">
-        <v>0.04044160684191658</v>
+        <v>1.326148097316313</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.04043717258080222</v>
+        <v>-1.326195007759708</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2122753221190111</v>
+        <v>-0.3696241010989402</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6343830154126764</v>
+        <v>0.08739368717664438</v>
       </c>
       <c r="L17" t="n">
-        <v>2.067220434893788</v>
+        <v>4.028684749082988</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3801870311119669</v>
+        <v>-4.570413938945361</v>
       </c>
       <c r="N17" t="n">
-        <v>1.374113884096997</v>
+        <v>1.221962100234958</v>
       </c>
       <c r="O17" t="n">
-        <v>1.03298064947228</v>
+        <v>-3.182337607653933</v>
       </c>
       <c r="P17" t="n">
-        <v>1.157864321459517</v>
+        <v>1.468324445853402</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9523436204771309</v>
+        <v>-3.998299618032106</v>
       </c>
       <c r="R17" t="n">
-        <v>0.599028145432136</v>
+        <v>-5.97569688133951</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.502551779089928</v>
+        <v>0.4797097537360951</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.341801137847493</v>
+        <v>0.2967193253906257</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2308,107 +2308,107 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6820597583111887</v>
+        <v>-0.9622830882963833</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.4416178080490291</v>
+        <v>-0.1632019012961676</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.573828395097944</v>
+        <v>-0.1850015418680325</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.3644003076161629</v>
+        <v>-0.2675757134908732</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9901223730267831</v>
+        <v>-0.4736744678230853</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.5315504052341145</v>
+        <v>-1.089275946228544</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.9798573019896782</v>
+        <v>-0.09526854832020075</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.5755377558402982</v>
+        <v>-0.2632227003818449</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.5581639371470225</v>
+        <v>-0.1246585803421917</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.6763243868267584</v>
+        <v>-1.028780569593295</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.7249951130144805</v>
+        <v>0.8246145880898825</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7477679166607292</v>
+        <v>0.4292929763521113</v>
       </c>
       <c r="D18" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.08249049901650093</v>
+        <v>-0.2485713703697228</v>
       </c>
       <c r="F18" t="n">
         <v>0.1903066245323431</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01284963915427201</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.43812085720364</v>
+        <v>-2.145259426964558</v>
       </c>
       <c r="I18" t="n">
-        <v>1.438184337874939</v>
+        <v>2.145351147223337</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.73331124061016</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.416307776551107</v>
+        <v>1.290354858158845</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7595775587676545</v>
+        <v>-3.054380829933568</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.105574581396306</v>
+        <v>3.440313973089069</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.758752563554639</v>
+        <v>-3.98683770765464</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.276631879911333</v>
+        <v>2.839545616812086</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5616071367219981</v>
+        <v>-3.905023860963833</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1901125114865394</v>
+        <v>2.904039512581734</v>
       </c>
       <c r="R18" t="n">
-        <v>-1.175565777723043</v>
+        <v>3.624565325893424</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1208308363061085</v>
+        <v>1.555120347225045</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7353381006551266</v>
+        <v>0.498701352944366</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2417,107 +2417,107 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.009017550057460712</v>
+        <v>-0.3316097312636615</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.01425754571295434</v>
+        <v>0.2204126950306438</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.0722202347974373</v>
+        <v>0.1145956977282886</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.6584010503112059</v>
+        <v>0.6767249232144826</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.234086530441603</v>
+        <v>0.1983886611229679</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.8121783655272882</v>
+        <v>0.2088018825733855</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.1944272360231096</v>
+        <v>0.1902971513876742</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.7347842240107532</v>
+        <v>-0.02245602805564015</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.09221436003096149</v>
+        <v>0.05141724993833285</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.2563046690309104</v>
+        <v>0.1327797280184845</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.222555270959666</v>
+        <v>0.2164596864464875</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7477679166607292</v>
+        <v>-0.7763621548162278</v>
       </c>
       <c r="D19" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4157521150431646</v>
+        <v>2.408722571281827</v>
       </c>
       <c r="F19" t="n">
-        <v>1.043272089906375</v>
+        <v>1.896237555280407</v>
       </c>
       <c r="G19" t="n">
-        <v>2.48383524852078</v>
+        <v>1.248342443837526</v>
       </c>
       <c r="H19" t="n">
-        <v>1.397576235676002</v>
+        <v>1.440433118691816</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.397625998602981</v>
+        <v>-1.440484593108944</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.73331124061016</v>
+        <v>-0.1271660080914603</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.514086898314456</v>
+        <v>0.2878872156736779</v>
       </c>
       <c r="L19" t="n">
-        <v>2.75736528618258</v>
+        <v>0.03310929425313586</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.543397539966588</v>
+        <v>0.9754746155400137</v>
       </c>
       <c r="N19" t="n">
-        <v>3.451693947822787</v>
+        <v>1.014067020183224</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.772286330050807</v>
+        <v>-0.5655111170221552</v>
       </c>
       <c r="P19" t="n">
-        <v>4.851543750145735</v>
+        <v>1.229508965550414</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.632997469123034</v>
+        <v>-2.808241147236616</v>
       </c>
       <c r="R19" t="n">
-        <v>-6.169641572394721</v>
+        <v>-0.3513008407383969</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5099851341415469</v>
+        <v>1.353129694999717</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.001449715312912057</v>
+        <v>0.4053156524954408</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2526,107 +2526,107 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.9428367643749416</v>
+        <v>0.6932887302597625</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.835958876723381</v>
+        <v>1.022666509077557</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.755820648660525</v>
+        <v>1.09310301909469</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.2296048285218058</v>
+        <v>-0.2744599650308314</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.327845378853541</v>
+        <v>0.995209960665916</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.9498094040557764</v>
+        <v>-1.17613184229455</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.398568151320271</v>
+        <v>1.253063346748597</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.34394277507612</v>
+        <v>1.128988068692581</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.029503867325254</v>
+        <v>1.376202722257614</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.971972773082738</v>
+        <v>0.6711407192803297</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.4892205862695931</v>
+        <v>-1.187472726961375</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C20" t="n">
-        <v>1.013163700251244</v>
+        <v>0.543034026462332</v>
       </c>
       <c r="D20" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9128948557826102</v>
+        <v>-1.078975727135832</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2835630784532303</v>
+        <v>-0.5678849002445744</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.810812230634564</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5166978723636554</v>
+        <v>2.097571991600951</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5167245559967235</v>
+        <v>-2.097649708867051</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5395937476791089</v>
+        <v>0.3577501779234991</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.215814248054073</v>
+        <v>1.089861329661812</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3301248380041233</v>
+        <v>-1.419827234775901</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.105574581396306</v>
+        <v>0.3592647761527498</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6936425659560193</v>
+        <v>-0.22416521485018</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.533663480955614</v>
+        <v>-0.3917087963160216</v>
       </c>
       <c r="P20" t="n">
-        <v>0.453358654565702</v>
+        <v>-0.8004226170249864</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.737188523520676</v>
+        <v>-1.142159288122931</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.902858369180083</v>
+        <v>1.297229033230895</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-2.54537417277618</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2576152993735751</v>
+        <v>-2.120867604656465</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2635,107 +2635,107 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.448145086274461</v>
+        <v>-0.7387752832416217</v>
       </c>
       <c r="Y20" t="n">
-        <v>-2.009035815292868</v>
+        <v>-0.8598828467207934</v>
       </c>
       <c r="Z20" t="n">
-        <v>-1.659213822345314</v>
+        <v>-0.1634692743743312</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.6981803377979809</v>
+        <v>0.003622268992228587</v>
       </c>
       <c r="AB20" t="n">
-        <v>-2.265749336469369</v>
+        <v>-0.3987828645088972</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.3368069194581115</v>
+        <v>0.1694565106070595</v>
       </c>
       <c r="AD20" t="n">
-        <v>-2.32480648355423</v>
+        <v>-0.5410321704987857</v>
       </c>
       <c r="AE20" t="n">
-        <v>-2.522382900164025</v>
+        <v>-0.8388314880010732</v>
       </c>
       <c r="AF20" t="n">
-        <v>-2.154978853254192</v>
+        <v>-0.5136170693458291</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>-2.001761515249359</v>
+        <v>-0.3713400853247025</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.008803702827623163</v>
+        <v>-1.675413360647825</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.819875174399046</v>
+        <v>2.284853062850626</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6112786565284644</v>
+        <v>1.286142220515774</v>
       </c>
       <c r="D21" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E21" t="n">
-        <v>1.744399085868939</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F21" t="n">
-        <v>2.085785436474636</v>
+        <v>-0.4731109596474597</v>
       </c>
       <c r="G21" t="n">
-        <v>1.248342443837526</v>
+        <v>0.42468057404869</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1738428082371496</v>
+        <v>0.7904370596186481</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1738557999490154</v>
+        <v>-0.7904625764351639</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3696241010989402</v>
+        <v>-0.2483950545952008</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.61680130504814</v>
+        <v>1.390601622407362</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3301248380041233</v>
+        <v>-0.9657845694543271</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9754746155400137</v>
+        <v>-0.1542434233366368</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6839479095516249</v>
+        <v>0.6896593128497492</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3500109666974757</v>
+        <v>-0.1016302751374757</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6921741348686902</v>
+        <v>0.7319767149191881</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.356963500547597</v>
+        <v>-1.102490672429748</v>
       </c>
       <c r="R21" t="n">
-        <v>1.297229033230895</v>
+        <v>-0.06038380415558071</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4416794557715791</v>
+        <v>0.6995240286504462</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3001665069532508</v>
+        <v>-1.017648603844671</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2744,40 +2744,149 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04176938367097</v>
+        <v>-0.8998373552523101</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.06132230457555496</v>
+        <v>-0.4499061905405299</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.6562962065094501</v>
+        <v>-0.8126509421581717</v>
       </c>
       <c r="AA21" t="n">
-        <v>-1.375046900096587</v>
+        <v>-0.3273851470715624</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.5456837179543604</v>
+        <v>-0.8750244112519121</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.047552150899285</v>
+        <v>0.588528862258957</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.100919484728671</v>
+        <v>-0.9382414213891003</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.224255713842808</v>
+        <v>-0.2717120078038754</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.8248897480809674</v>
+        <v>-0.7142850039650447</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.8890389722340076</v>
+        <v>-1.079650212702884</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.7717454723182761</v>
+        <v>-1.696537076210942</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>AeRSxQrK</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.8918399134670087</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.4146522417229446</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.2835630784532303</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.810812230634564</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.073837351569227</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.073886284574249</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.73331124061016</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.154224863342322</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.5779604926390248</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.873154902621778</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1.434982714052587</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.7491051177680702</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.6810148768734923</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.300833750895663</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-2.678637133400926</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-2.269498205480952</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.1604072633175469</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.6871542357414602</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.007935269842869309</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.005716133768708311</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.5067488174867379</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.9652684969024259</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-1.140872329406872</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.6087226979006948</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-1.113457414810803</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.742400770640682</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-1.424054881920683</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-1.327229436810696</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-1.473066010663299</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>-1.757610664975391</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>-0.8937778012825365</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>-0.3162826722544151</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -603,68 +603,68 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GdWtpsjm</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C2" t="n">
-        <v>1.37713506060395</v>
+        <v>0.4292929763521113</v>
       </c>
       <c r="D2" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08359037233672091</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2850805651294578</v>
+        <v>0.9484981493092606</v>
       </c>
       <c r="G2" t="n">
-        <v>1.248342443837526</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08329848985772981</v>
+        <v>-0.9881235855376008</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08329576708676574</v>
+        <v>0.9881690955623221</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3577501779234991</v>
+        <v>1.085124456945938</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8893678011647782</v>
+        <v>-2.118035126290724</v>
       </c>
       <c r="L2" t="n">
-        <v>1.849279955539432</v>
+        <v>-1.601444300904531</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3592647761527498</v>
+        <v>-0.2569450632345141</v>
       </c>
       <c r="N2" t="n">
-        <v>3.079310452785065</v>
+        <v>-1.140274303869359</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6951676880997961</v>
+        <v>-0.3941567163259672</v>
       </c>
       <c r="P2" t="n">
-        <v>4.214702469337768</v>
+        <v>-0.8004226170249864</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.380170982282029</v>
+        <v>0.7619342651498524</v>
       </c>
       <c r="R2" t="n">
-        <v>1.588146069813711</v>
+        <v>1.297229033230895</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7982875000831346</v>
+        <v>0.6474266096172088</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5416063509784073</v>
+        <v>0.5462724293372833</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -673,107 +673,107 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.255220462537494</v>
+        <v>0.1066511979278359</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.059602915079372</v>
+        <v>-0.8331526317968772</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.332319891816384</v>
+        <v>-0.6336372330022989</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.5471868618974325</v>
+        <v>0.3486120289584462</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.210367406173853</v>
+        <v>-0.5414296529011389</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.1238233223773065</v>
+        <v>-0.442952323565686</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.369389029045715</v>
+        <v>-0.2472193017735524</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.555477060127494</v>
+        <v>-0.6870019890510012</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.750080574461782</v>
+        <v>-1.065683421149025</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.946707227365162</v>
+        <v>-0.4492109960068809</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.9539156255057242</v>
+        <v>0.1444242836986425</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C3" t="n">
-        <v>1.597034424150377</v>
+        <v>0.543034026462332</v>
       </c>
       <c r="D3" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5807331130761665</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1887891378561156</v>
+        <v>-0.09401519725900095</v>
       </c>
       <c r="G3" t="n">
         <v>0.01284963915427201</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.259550511304418</v>
+        <v>-2.716684533842068</v>
       </c>
       <c r="I3" t="n">
-        <v>1.259606860766758</v>
+        <v>2.716799073969518</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.21822742662512</v>
+        <v>-0.00593696158772055</v>
       </c>
       <c r="K3" t="n">
-        <v>2.626978381472402</v>
+        <v>0.4883807441707113</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.78306136703316</v>
+        <v>-1.419827234775901</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.873154902621778</v>
+        <v>-1.078558182417533</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.298546892729021</v>
+        <v>-1.185965530254356</v>
       </c>
       <c r="O3" t="n">
-        <v>0.09787520567308552</v>
+        <v>-0.3721254362364578</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.676079378135944</v>
+        <v>-1.556671637984449</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1107752801001733</v>
+        <v>1.555306579013512</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.321024296014451</v>
+        <v>-0.2543284952107916</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1962144594129164</v>
+        <v>-1.127974769863544</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.567670313519776</v>
+        <v>0.2699885720929168</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -782,107 +782,107 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.113175472695782</v>
+        <v>-0.7098009423623417</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2329279256221052</v>
+        <v>-0.9408015268041218</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.4148051960563006</v>
+        <v>-0.7630155197223483</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.7608228117398796</v>
+        <v>0.6317905654815504</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.5786073101389009</v>
+        <v>-0.7222911753980188</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.083374848565313</v>
+        <v>0.7217827288118702</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.385177185174809</v>
+        <v>-0.8547255627276497</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3019371399315472</v>
+        <v>-0.9372286313951173</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0007718576270169641</v>
+        <v>-1.073477153457406</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.4721098992421069</v>
+        <v>-0.7061292891333459</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.3536601917360916</v>
+        <v>-0.04446111036586359</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C4" t="n">
-        <v>1.37713506060395</v>
+        <v>0.8918399134670087</v>
       </c>
       <c r="D4" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4146522417229446</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5678849002445744</v>
+        <v>2.085785436474636</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8365115089431081</v>
+        <v>2.48383524852078</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4309841063320289</v>
+        <v>1.026149916205621</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4310073669847965</v>
+        <v>-1.026184846217963</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1271660080914603</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6888742726677447</v>
+        <v>-1.449723364633946</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.238210168647272</v>
+        <v>0.0331092942531361</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7700713357442589</v>
+        <v>-0.2569450632345141</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9118181719443772</v>
+        <v>-0.5485729221836555</v>
       </c>
       <c r="O4" t="n">
-        <v>1.211678810198304</v>
+        <v>0.5091257673439357</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9994355172774767</v>
+        <v>0.2742470443384608</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1107752801001733</v>
+        <v>1.436300731933963</v>
       </c>
       <c r="R4" t="n">
-        <v>1.103284342175684</v>
+        <v>-1.030107259431635</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.072724661002653</v>
+        <v>0.9567335749858984</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02838722074170034</v>
+        <v>-0.2959658758582872</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -891,107 +891,107 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8037978970265566</v>
+        <v>0.8590620789414448</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.3750180600127781</v>
+        <v>0.1099327462761978</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.3439125163065386</v>
+        <v>0.2874755704302207</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.2913063964739597</v>
+        <v>-1.237145440448594</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.3084351757379331</v>
+        <v>0.2980835575905008</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.600800704184132</v>
+        <v>-1.248649160472326</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.7773644435221762</v>
+        <v>0.7198894457046625</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.6378336414714419</v>
+        <v>1.120354790730962</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.48747034758404</v>
+        <v>0.5441350196096062</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.3634155751863477</v>
+        <v>0.5454944250289068</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.4551948050311057</v>
+        <v>-0.247817072333241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.874937731578419</v>
+        <v>0.7174369699646703</v>
       </c>
       <c r="D5" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.411137469842276</v>
+        <v>-1.245056598489054</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.705172187409951</v>
+        <v>-2.273815830992639</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.810812230634564</v>
+        <v>-1.6344741004234</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8166960534743479</v>
+        <v>-0.1881284359090871</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8167347175384682</v>
+        <v>0.1881419981176697</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7214373174347188</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4883807441707113</v>
+        <v>2.025497795981301</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2147263603817656</v>
+        <v>-1.056593102518642</v>
       </c>
       <c r="M5" t="n">
         <v>2.207894294314541</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7216431713192469</v>
+        <v>-0.4937434505216594</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6290738478312667</v>
+        <v>1.074595289641354</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3936547844899549</v>
+        <v>1.189706385499916</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.356963500547597</v>
+        <v>1.118951806388499</v>
       </c>
       <c r="R5" t="n">
-        <v>2.751814216144976</v>
+        <v>-0.157356149683186</v>
       </c>
       <c r="S5" t="n">
-        <v>1.214067980324422</v>
+        <v>-0.5672954165531842</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.09561627516831558</v>
+        <v>0.3939965312235278</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1000,107 +1000,107 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1115431141443193</v>
+        <v>-1.048458883983512</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.405164270377252</v>
+        <v>-1.241742425282456</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.230130880042962</v>
+        <v>-1.981208776784071</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.3618885308007449</v>
+        <v>0.9235090111862538</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.7196558696693568</v>
+        <v>-1.102715342354329</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8172660296615185</v>
+        <v>0.8807667299987877</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.9412803980967652</v>
+        <v>-1.43625005591049</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.173554721412973</v>
+        <v>-1.693603282165887</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1.577959169520293</v>
+        <v>-2.4460486213568</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.1297942720436997</v>
+        <v>-1.179331810227863</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.9861427318501043</v>
+        <v>0.563742812882979</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.7763621548162278</v>
+        <v>1.339221377233877</v>
       </c>
       <c r="D6" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E6" t="n">
-        <v>2.408722571281827</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F6" t="n">
-        <v>1.896237555280407</v>
+        <v>0.2850805651294578</v>
       </c>
       <c r="G6" t="n">
-        <v>1.248342443837526</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H6" t="n">
-        <v>1.440433118691816</v>
+        <v>-0.5666975692154377</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.440484593108944</v>
+        <v>0.5667262495870146</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1271660080914607</v>
+        <v>-0.00593696158772055</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2878872156736779</v>
+        <v>-2.21828189053924</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03310929425313586</v>
+        <v>0.3055348934460803</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9754746155400137</v>
+        <v>1.797087734723032</v>
       </c>
       <c r="N6" t="n">
-        <v>1.014067020183224</v>
+        <v>0.03056337224617514</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5655111170221552</v>
+        <v>2.265508374479858</v>
       </c>
       <c r="P6" t="n">
-        <v>1.229508965550414</v>
+        <v>-1.477066477883453</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.808241147236616</v>
+        <v>1.39663211624078</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.3513008407383969</v>
+        <v>2.218466315743146</v>
       </c>
       <c r="S6" t="n">
-        <v>1.353129694999717</v>
+        <v>0.08247083545151267</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3044840165341666</v>
+        <v>1.993213631860892</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1109,107 +1109,107 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7252693069320967</v>
+        <v>0.2186230334351373</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.054407515185459</v>
+        <v>0.536757255232435</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.091579663677143</v>
+        <v>0.2651079108897363</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.2392449390196802</v>
+        <v>0.02419594453736944</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9879433727914823</v>
+        <v>0.6860065880457429</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.14844035140008</v>
+        <v>0.2845845655775999</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.234340584111829</v>
+        <v>0.6062256180071888</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.104817654336507</v>
+        <v>0.4469138546127484</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.401928409610353</v>
+        <v>0.3146898169970525</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.67700757200586</v>
+        <v>0.05701702197165631</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.162221073169684</v>
+        <v>0.2206185939582957</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.908442391246966</v>
+        <v>2.284853062850626</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.056923411754772</v>
+        <v>-0.6777865780540365</v>
       </c>
       <c r="D7" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.078975727135832</v>
+        <v>0.08359037233672091</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5678849002445744</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.810812230634564</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H7" t="n">
-        <v>2.097571991600951</v>
+        <v>0.08329848985772981</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.097649708867051</v>
+        <v>-0.08329576708676574</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.73331124061016</v>
+        <v>-1.460685519632599</v>
       </c>
       <c r="K7" t="n">
-        <v>1.089861329661812</v>
+        <v>-0.5809180744801336</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.419827234775901</v>
+        <v>-0.5117419041327529</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3592647761527498</v>
+        <v>-0.6677516228260235</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.22416521485018</v>
+        <v>-0.3315395968549221</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3917087963160216</v>
+        <v>-0.4626984766044422</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8004226170249864</v>
+        <v>-0.0441735960655237</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.142159288122931</v>
+        <v>-0.1107752801001733</v>
       </c>
       <c r="R7" t="n">
-        <v>1.297229033230895</v>
+        <v>-1.12707960495924</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.54537417277618</v>
+        <v>-0.6232322499309956</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.208274791931421</v>
+        <v>0.08750822233750201</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1218,107 +1218,107 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8080882423021828</v>
+        <v>-0.3958222019781681</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.8312331756664083</v>
+        <v>-0.07020532458698528</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.1616646440544205</v>
+        <v>-0.6190787424256108</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.08911193033946781</v>
+        <v>0.9209544445165551</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.4032765931189486</v>
+        <v>-0.7358585276797048</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1324706093207676</v>
+        <v>0.1460881638606688</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.5389503477016269</v>
+        <v>-0.730830695945405</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.9090301003131893</v>
+        <v>-0.7131867674298671</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.5296200774067438</v>
+        <v>-0.5586607471977286</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.3668310631426355</v>
+        <v>-0.9100429854655323</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.657062128315919</v>
+        <v>-0.6596065719069475</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1.908442391246966</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6112786565284644</v>
+        <v>1.286142220515774</v>
       </c>
       <c r="D8" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.08249049901650093</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09553268393522843</v>
+        <v>0.0007587433381137274</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H8" t="n">
-        <v>2.054715108585138</v>
+        <v>0.197583511233232</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.054791114361088</v>
+        <v>-0.2261577487733106</v>
       </c>
       <c r="J8" t="n">
-        <v>1.570040642960898</v>
+        <v>-0.2483950545952004</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.920009240278857</v>
+        <v>-1.115567483805556</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.05769923881117887</v>
+        <v>-0.5117419041327529</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.565049982928146</v>
+        <v>-0.2569450632345141</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2036041629769318</v>
+        <v>-0.7084922145311433</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9645220786432772</v>
+        <v>-0.8715011182653473</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2630877863432628</v>
+        <v>-1.198448417529967</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.26116513520248</v>
+        <v>-1.023153441043382</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.030107259431635</v>
+        <v>-2.290747751290505</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7205627706686657</v>
+        <v>-1.594089035719624</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2174436884902342</v>
+        <v>0.9838898971029448</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1327,107 +1327,107 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.26786622022417</v>
+        <v>0.1571454104651572</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.14942611069094</v>
+        <v>-0.274121108503933</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.603343886632926</v>
+        <v>0.09370843995819361</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.1567179744319159</v>
+        <v>0.5243030347787914</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.669658936588986</v>
+        <v>0.3100912757949237</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1187679363106135</v>
+        <v>1.61149122349696</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.718194618948798</v>
+        <v>-0.009561499974817431</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.619875608547407</v>
+        <v>-0.5495533614605043</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.878302924337442</v>
+        <v>-0.2736652139666792</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.572407253538996</v>
+        <v>0.524087956083741</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.358814887590141</v>
+        <v>0.8458655487425889</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.819875174399046</v>
+        <v>2.218427650214686</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.3593116377454187</v>
+        <v>-0.5488800545957865</v>
       </c>
       <c r="D9" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2485713703697228</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1903066245323431</v>
+        <v>-0.2835630784532303</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8365115089431081</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.145259426964558</v>
+        <v>-0.002415276173896646</v>
       </c>
       <c r="I9" t="n">
-        <v>2.145351147223337</v>
+        <v>0.04528001643112482</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7214373174347188</v>
+        <v>-0.00593696158772055</v>
       </c>
       <c r="K9" t="n">
-        <v>1.290354858158845</v>
+        <v>1.023030153496134</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.054380829933568</v>
+        <v>0.9411946248962842</v>
       </c>
       <c r="M9" t="n">
-        <v>3.440313973089069</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.98683770765464</v>
+        <v>0.8404403599202378</v>
       </c>
       <c r="O9" t="n">
-        <v>2.839545616812086</v>
+        <v>-1.405147680433473</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.905023860963833</v>
+        <v>2.304178626913861</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.904039512581734</v>
+        <v>-2.133874680452506</v>
       </c>
       <c r="R9" t="n">
-        <v>3.624565325893424</v>
+        <v>-2.872581824456137</v>
       </c>
       <c r="S9" t="n">
-        <v>1.555120347225045</v>
+        <v>-0.1172808678323042</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4586292164549462</v>
+        <v>0.9135759987813451</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1436,107 +1436,107 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2608334343293608</v>
+        <v>0.1715822389684006</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.275740789899114</v>
+        <v>0.595035103207857</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.1252357667055335</v>
+        <v>-0.1259556116081686</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7814617263022781</v>
+        <v>0.1404526829372301</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.2468280762429318</v>
+        <v>-0.3076434998103389</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.3151192053262135</v>
+        <v>-0.6385863001100867</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2319484717893988</v>
+        <v>-0.1533233115415633</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.02303076348748194</v>
+        <v>0.1677587843900229</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.05312799316504201</v>
+        <v>0.1550823494835517</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.1874029134030919</v>
+        <v>-0.1822812385858773</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.1800832968632841</v>
+        <v>1.095167294001493</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.819875174399046</v>
+        <v>2.284853062850626</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.874937731578419</v>
+        <v>1.013163700251244</v>
       </c>
       <c r="D10" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5807331130761665</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0007587433381137274</v>
+        <v>-0.1887891378561156</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8365115089431081</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H10" t="n">
-        <v>1.326148097316313</v>
+        <v>-0.2166996912529628</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.326195007759708</v>
+        <v>0.2167143944549789</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.09699838012138</v>
+        <v>-0.3696241010989402</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08739368717664438</v>
+        <v>-1.115567483805556</v>
       </c>
       <c r="L10" t="n">
-        <v>4.028684749082988</v>
+        <v>-0.6933589702613824</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.570413938945361</v>
+        <v>0.3592647761527498</v>
       </c>
       <c r="N10" t="n">
-        <v>1.221962100234958</v>
+        <v>-0.3132631063009232</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.182337607653933</v>
+        <v>0.1125627257327581</v>
       </c>
       <c r="P10" t="n">
-        <v>1.468324445853402</v>
+        <v>-0.1237787561665195</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.998299618032106</v>
+        <v>0.4049167239112055</v>
       </c>
       <c r="R10" t="n">
-        <v>-5.97569688133951</v>
+        <v>-0.2543284952107916</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4797097537360951</v>
+        <v>2.467028076186675</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2338299216196877</v>
+        <v>-0.6447471785188281</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1545,53 +1545,53 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.021783105652138</v>
+        <v>-0.5524900958308684</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.1857347444722231</v>
+        <v>-1.131548916918645</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.1876312462570396</v>
+        <v>-0.3765391428079359</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.3269493534769882</v>
+        <v>-1.013283831305482</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.4805127799629867</v>
+        <v>-1.160219857250067</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.032767035005459</v>
+        <v>-0.2741785699582603</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.1148520449544874</v>
+        <v>-0.9365648225360037</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.2599894520820339</v>
+        <v>-0.6493193849327275</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.1086285653072785</v>
+        <v>-0.3210022450247348</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-1.037548112725092</v>
+        <v>-0.6351178829756178</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.8019350674185658</v>
+        <v>0.4366727243813309</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>ERWFdKZh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.218427650214686</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C11" t="n">
-        <v>1.005580963577229</v>
+        <v>0.7477679166607292</v>
       </c>
       <c r="D11" t="n">
         <v>-0.5056960363928432</v>
@@ -1600,52 +1600,52 @@
         <v>-0.5807331130761665</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4731109596474597</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G11" t="n">
-        <v>0.42468057404869</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7904370596186481</v>
+        <v>0.3261541602806716</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7904625764351639</v>
+        <v>-0.3261611359538926</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2483950545952001</v>
+        <v>-0.00593696158772055</v>
       </c>
       <c r="K11" t="n">
-        <v>1.390601622407362</v>
+        <v>0.7557054488334223</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9657845694543271</v>
+        <v>0.0331092942531361</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1542434233366368</v>
+        <v>0.1538614963569951</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6896593128497492</v>
+        <v>1.274507010577705</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1016302751374757</v>
+        <v>-0.7613447178177976</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7319767149191881</v>
+        <v>1.866350246358383</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.102490672429748</v>
+        <v>-1.023153441043382</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.06038380415558071</v>
+        <v>-0.5452455317936075</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6995240286504462</v>
+        <v>-0.6799806668287885</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.141836769153705</v>
+        <v>0.3068593687952422</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1654,107 +1654,107 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9052139658651964</v>
+        <v>0.7817902685685049</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.4445779755931722</v>
+        <v>1.554171630430104</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.7857918001107426</v>
+        <v>1.886191184678708</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.3207119253431235</v>
+        <v>0.4475031604971795</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.8554579605316445</v>
+        <v>1.53296434076075</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4549105514078189</v>
+        <v>-0.791865344879914</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.8908290477797393</v>
+        <v>1.343500356181161</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.2827393355743561</v>
+        <v>0.9483540381020542</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.7402052555834663</v>
+        <v>1.997447899341295</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-1.075745574446455</v>
+        <v>1.036852592258035</v>
       </c>
       <c r="AI11" t="n">
-        <v>-1.683647858217679</v>
+        <v>0.3899977241566469</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8918399134670087</v>
+        <v>1.013163700251244</v>
       </c>
       <c r="D12" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4146522417229446</v>
+        <v>0.08359037233672091</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2835630784532303</v>
+        <v>0.2850805651294578</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.810812230634564</v>
+        <v>1.248342443837526</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.073837351569227</v>
+        <v>0.08329848985772981</v>
       </c>
       <c r="I12" t="n">
-        <v>1.073886284574249</v>
+        <v>-0.08329576708676574</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.21822742662512</v>
+        <v>0.7214373174347188</v>
       </c>
       <c r="K12" t="n">
-        <v>0.154224863342322</v>
+        <v>0.8893678011647782</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5779604926390248</v>
+        <v>1.849279955539432</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.873154902621778</v>
+        <v>0.3592647761527498</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.434982714052587</v>
+        <v>3.079310452785065</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7491051177680702</v>
+        <v>0.6951676880997961</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6810148768734923</v>
+        <v>4.214702469337768</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.300833750895663</v>
+        <v>-1.380170982282029</v>
       </c>
       <c r="R12" t="n">
-        <v>-2.678637133400926</v>
+        <v>1.588146069813711</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.269498205480952</v>
+        <v>0.7982875000831346</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5746995565220469</v>
+        <v>-0.5017776204546213</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1763,107 +1763,107 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6379041544319998</v>
+        <v>1.227905381925339</v>
       </c>
       <c r="Y12" t="n">
-        <v>-1.013951584492341</v>
+        <v>1.112949556931529</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.150436710112458</v>
+        <v>1.374526804225985</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.5167945151078079</v>
+        <v>-0.4841113211168335</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.144351624427494</v>
+        <v>1.242614982777913</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.698593775434444</v>
+        <v>-0.09301959257525098</v>
       </c>
       <c r="AD12" t="n">
-        <v>-1.457841635028116</v>
+        <v>1.384994448107078</v>
       </c>
       <c r="AE12" t="n">
-        <v>-1.338393181063955</v>
+        <v>1.515915624379784</v>
       </c>
       <c r="AF12" t="n">
-        <v>-1.489275975228819</v>
+        <v>1.782164020621224</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.9300830840524966</v>
+        <v>1.986673560342574</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.3607592654502234</v>
+        <v>1.033756567089463</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.218427650214686</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C13" t="n">
-        <v>1.597034424150377</v>
+        <v>-0.5488800545957865</v>
       </c>
       <c r="D13" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4157521150431646</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1903066245323431</v>
+        <v>-0.1887891378561156</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.869966905106654</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5452691277075311</v>
+        <v>-1.259550511304418</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5452969523340327</v>
+        <v>1.259606860766758</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4789792244272389</v>
+        <v>-0.8545402871138997</v>
       </c>
       <c r="K13" t="n">
-        <v>1.357186034324523</v>
+        <v>2.626978381472402</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3301248380041233</v>
+        <v>-1.78306136703316</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7700713357442589</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3058530112157789</v>
+        <v>-2.298546892729021</v>
       </c>
       <c r="O13" t="n">
-        <v>1.706158652207303</v>
+        <v>0.09787520567308552</v>
       </c>
       <c r="P13" t="n">
-        <v>1.050397355323173</v>
+        <v>-1.676079378135944</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.904039512581734</v>
+        <v>-0.1107752801001733</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7638811328290654</v>
+        <v>-1.321024296014451</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5268440273970857</v>
+        <v>-0.1962144594129164</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3289017713881228</v>
+        <v>-1.623870137228588</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1872,53 +1872,53 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.02275389444846</v>
+        <v>-0.2045399705252551</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.282111793718041</v>
+        <v>0.1463367184841673</v>
       </c>
       <c r="Z13" t="n">
-        <v>-1.897044153856384</v>
+        <v>-0.4128214941249725</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.5411477570140375</v>
+        <v>-0.8362586616820753</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.284933022924902</v>
+        <v>-0.5650364329540472</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.467734998345281</v>
+        <v>-1.087009924725866</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.8325617874404283</v>
+        <v>-0.3674542166242922</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.810532602185596</v>
+        <v>0.3018583124556456</v>
       </c>
       <c r="AF13" t="n">
-        <v>-2.030975699661388</v>
+        <v>-0.0502779134264426</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-1.645593057289772</v>
+        <v>-0.459584837625255</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.283691970231209</v>
+        <v>0.3227106019491588</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C14" t="n">
-        <v>1.339221377233877</v>
+        <v>0.7477679166607292</v>
       </c>
       <c r="D14" t="n">
         <v>-0.5056960363928432</v>
@@ -1927,52 +1927,52 @@
         <v>-0.4146522417229446</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.09401519725900095</v>
+        <v>-0.5678849002445744</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.398981295740146</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8547223841423679</v>
+        <v>-0.4309841063320289</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8547504681941092</v>
+        <v>0.4310073669847965</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7214373174347188</v>
+        <v>-0.00593696158772055</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.717048069296657</v>
+        <v>0.6888742726677447</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.419827234775901</v>
+        <v>-1.238210168647272</v>
       </c>
       <c r="M14" t="n">
-        <v>1.591684454927278</v>
+        <v>0.7700713357442589</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.65658516201982</v>
+        <v>-0.9118181719443772</v>
       </c>
       <c r="O14" t="n">
-        <v>2.068450813679242</v>
+        <v>1.211678810198304</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.755684538236939</v>
+        <v>-0.9994355172774767</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9999459593089504</v>
+        <v>-0.1107752801001733</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4244779234824463</v>
+        <v>1.103284342175684</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2251846759667669</v>
+        <v>-1.072724661002653</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4598017307625239</v>
+        <v>-0.01956258426656824</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1981,107 +1981,107 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1248939056402486</v>
+        <v>-0.6343394208020771</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1417841947503617</v>
+        <v>-0.3379815751701792</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.09966998893535683</v>
+        <v>-0.3556690765831189</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.667796608214376</v>
+        <v>0.3934561822041817</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.01865705542761047</v>
+        <v>-0.2911470132533752</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.176311225652666</v>
+        <v>1.673480590037023</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.2037200729720813</v>
+        <v>-0.81654030991459</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.2804022094170529</v>
+        <v>-0.6284842553397906</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.03521587811355715</v>
+        <v>-0.5060466933800721</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.3149773080488661</v>
+        <v>-0.3612504523555711</v>
       </c>
       <c r="AI14" t="n">
-        <v>-1.111240053801304</v>
+        <v>-0.4894530484796624</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.819875174399046</v>
+        <v>2.218427650214686</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6112786565284644</v>
+        <v>0.7174369699646703</v>
       </c>
       <c r="D15" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4157521150431646</v>
+        <v>-1.411137469842276</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0007587433381137274</v>
+        <v>-1.705172187409951</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8365115089431081</v>
+        <v>-0.810812230634564</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5166978723636554</v>
+        <v>-0.8166960534743479</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5167245559967235</v>
+        <v>0.8167347175384682</v>
       </c>
       <c r="J15" t="n">
         <v>-0.73331124061016</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1130998413203891</v>
+        <v>0.4883807441707113</v>
       </c>
       <c r="L15" t="n">
-        <v>2.394131153925321</v>
+        <v>0.2147263603817656</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.489364742009042</v>
+        <v>2.207894294314541</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8450094825587373</v>
+        <v>0.7216431713192469</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.412491440463311</v>
+        <v>0.6290738478312667</v>
       </c>
       <c r="P15" t="n">
-        <v>2.423586367065355</v>
+        <v>0.3936547844899549</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7619342651498524</v>
+        <v>1.356963500547597</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.902858369180083</v>
+        <v>2.751814216144976</v>
       </c>
       <c r="S15" t="n">
-        <v>0.102136128435901</v>
+        <v>1.214067980324422</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1967137790551501</v>
+        <v>-0.09095654158382248</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -2090,107 +2090,107 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.009557134085341335</v>
+        <v>-0.2564937675438262</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.06523490693479181</v>
+        <v>-1.431539967288882</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.2587095502556336</v>
+        <v>-1.258194315102407</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.418684735144918</v>
+        <v>-0.4171497601466182</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.1053749606388236</v>
+        <v>-0.7166169625283227</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.903066809465341</v>
+        <v>0.8777511004900883</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.2513821991097257</v>
+        <v>-0.9631492753617833</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.4785278957807249</v>
+        <v>-1.165019489194087</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.4026730088889842</v>
+        <v>-1.613923290432531</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.008545033514437346</v>
+        <v>-0.1465778546102821</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.6737590263016837</v>
+        <v>0.9715228520786635</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.5109663712257129</v>
+        <v>0.4292929763521113</v>
       </c>
       <c r="D16" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7468139844293883</v>
+        <v>-0.2485713703697228</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.378337019050345</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.222643165528982</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8595529364901612</v>
+        <v>-2.145259426964558</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8595933120444317</v>
+        <v>2.145351147223337</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5395937476791089</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7145804268114895</v>
+        <v>1.290354858158845</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.05769923881117887</v>
+        <v>-3.054380829933568</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9754746155400137</v>
+        <v>3.440313973089069</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4777515212869103</v>
+        <v>-3.98683770765464</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2154585555999435</v>
+        <v>2.839545616812086</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3227916564190099</v>
+        <v>-3.905023860963833</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9041475939638333</v>
+        <v>2.904039512581734</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.157356149683186</v>
+        <v>3.624565325893424</v>
       </c>
       <c r="S16" t="n">
-        <v>1.63883830878714</v>
+        <v>1.555120347225045</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.488864977551531</v>
+        <v>0.548265913694121</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -2199,107 +2199,107 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.2085836806328085</v>
+        <v>-0.2895347365924197</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1024764445697142</v>
+        <v>0.2347890689512885</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.008710352657019495</v>
+        <v>0.1229938381978449</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.3217462586255166</v>
+        <v>0.717350971541407</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.001582938545225925</v>
+        <v>0.2173211118495824</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.4758934309413642</v>
+        <v>0.2331742027355452</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.03965602124728654</v>
+        <v>0.1843918395121781</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.001694219430144185</v>
+        <v>-0.04641470115493537</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.05714867735855229</v>
+        <v>0.05261108305040895</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.1652335543412626</v>
+        <v>0.1459449594513093</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.5569107191011068</v>
+        <v>0.2406012173246807</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C17" t="n">
-        <v>1.339221377233877</v>
+        <v>0.8918399134670087</v>
       </c>
       <c r="D17" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E17" t="n">
-        <v>1.744399085868939</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4746284463236872</v>
+        <v>0.09553268393522843</v>
       </c>
       <c r="G17" t="n">
-        <v>2.072004313626362</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.04044160684191658</v>
+        <v>2.054715108585138</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.04043717258080222</v>
+        <v>-2.054791114361088</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2122753221190111</v>
+        <v>1.570040642960898</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6343830154126764</v>
+        <v>-2.920009240278857</v>
       </c>
       <c r="L17" t="n">
-        <v>2.067220434893788</v>
+        <v>-0.05769923881117887</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3801870311119669</v>
+        <v>-0.565049982928146</v>
       </c>
       <c r="N17" t="n">
-        <v>1.374113884096997</v>
+        <v>-0.2036041629769318</v>
       </c>
       <c r="O17" t="n">
-        <v>1.03298064947228</v>
+        <v>-0.9645220786432772</v>
       </c>
       <c r="P17" t="n">
-        <v>1.157864321459517</v>
+        <v>-0.2630877863432628</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9523436204771309</v>
+        <v>-1.26116513520248</v>
       </c>
       <c r="R17" t="n">
-        <v>0.599028145432136</v>
+        <v>-1.030107259431635</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.502551779089928</v>
+        <v>0.7205627706686657</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.341801137847493</v>
+        <v>-0.1760013724459726</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2308,107 +2308,107 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6820597583111887</v>
+        <v>2.289939529538654</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.4416178080490291</v>
+        <v>2.158682428869865</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.573828395097944</v>
+        <v>2.599384978868622</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.3644003076161629</v>
+        <v>-0.1152627424258172</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9901223730267831</v>
+        <v>2.66540765159332</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.5315504052341145</v>
+        <v>-0.04914510005192888</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.9798573019896782</v>
+        <v>2.683713197143029</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.5755377558402982</v>
+        <v>2.624501277353565</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.5581639371470225</v>
+        <v>2.906463643125794</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.6763243868267584</v>
+        <v>2.58206944392914</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.7249951130144805</v>
+        <v>-1.23827594594042</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7477679166607292</v>
+        <v>0.543034026462332</v>
       </c>
       <c r="D18" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.08249049901650093</v>
+        <v>-1.078975727135832</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1903066245323431</v>
+        <v>-0.5678849002445744</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01284963915427201</v>
+        <v>-0.810812230634564</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.43812085720364</v>
+        <v>2.097571991600951</v>
       </c>
       <c r="I18" t="n">
-        <v>1.438184337874939</v>
+        <v>-2.097649708867051</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.73331124061016</v>
+        <v>0.3577501779234991</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.416307776551107</v>
+        <v>1.089861329661812</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7595775587676545</v>
+        <v>-1.419827234775901</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.105574581396306</v>
+        <v>0.3592647761527498</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.758752563554639</v>
+        <v>-0.22416521485018</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.276631879911333</v>
+        <v>-0.3917087963160216</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5616071367219981</v>
+        <v>-0.8004226170249864</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1901125114865394</v>
+        <v>-1.142159288122931</v>
       </c>
       <c r="R18" t="n">
-        <v>-1.175565777723043</v>
+        <v>1.297229033230895</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1208308363061085</v>
+        <v>-2.54537417277618</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7353381006551266</v>
+        <v>-2.120867604656465</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2417,107 +2417,107 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.009017550057460712</v>
+        <v>-0.7387752832416217</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.01425754571295434</v>
+        <v>-0.8598828467207934</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.0722202347974373</v>
+        <v>-0.1634692743743312</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.6584010503112059</v>
+        <v>0.003622268992228587</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.234086530441603</v>
+        <v>-0.3987828645088972</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.8121783655272882</v>
+        <v>0.1694565106070595</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.1944272360231096</v>
+        <v>-0.5410321704987857</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.7347842240107532</v>
+        <v>-0.8388314880010732</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.09221436003096149</v>
+        <v>-0.5136170693458291</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.2563046690309104</v>
+        <v>-0.3713400853247025</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.222555270959666</v>
+        <v>-1.675413360647825</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7477679166607292</v>
+        <v>-0.6777865780540365</v>
       </c>
       <c r="D19" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4157521150431646</v>
+        <v>2.408722571281827</v>
       </c>
       <c r="F19" t="n">
-        <v>1.043272089906375</v>
+        <v>1.896237555280407</v>
       </c>
       <c r="G19" t="n">
-        <v>2.48383524852078</v>
+        <v>1.248342443837526</v>
       </c>
       <c r="H19" t="n">
-        <v>1.397576235676002</v>
+        <v>1.440433118691816</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.397625998602981</v>
+        <v>-1.440484593108944</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.73331124061016</v>
+        <v>-0.1271660080914603</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.514086898314456</v>
+        <v>0.2878872156736779</v>
       </c>
       <c r="L19" t="n">
-        <v>2.75736528618258</v>
+        <v>0.03310929425313586</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.543397539966588</v>
+        <v>0.9754746155400137</v>
       </c>
       <c r="N19" t="n">
-        <v>3.451693947822787</v>
+        <v>1.014067020183224</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.772286330050807</v>
+        <v>-0.5655111170221552</v>
       </c>
       <c r="P19" t="n">
-        <v>4.851543750145735</v>
+        <v>1.229508965550414</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.632997469123034</v>
+        <v>-2.808241147236616</v>
       </c>
       <c r="R19" t="n">
-        <v>-6.169641572394721</v>
+        <v>-0.3513008407383969</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5099851341415469</v>
+        <v>1.353129694999717</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.001449715312912057</v>
+        <v>0.4247126779805524</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2526,107 +2526,107 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.9428367643749416</v>
+        <v>0.7265752263684719</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.835958876723381</v>
+        <v>1.014374919398328</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.755820648660525</v>
+        <v>1.088197481533369</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.2296048285218058</v>
+        <v>-0.3053992537369987</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.327845378853541</v>
+        <v>0.9870577408713016</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.9498094040557764</v>
+        <v>-1.189724430652031</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.398568151320271</v>
+        <v>1.247815027192715</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.34394277507612</v>
+        <v>1.151674256428488</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.029503867325254</v>
+        <v>1.369587320859271</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.971972773082738</v>
+        <v>0.6442431494581385</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.4892205862695931</v>
+        <v>-1.145611144790124</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.819875174399046</v>
+        <v>2.284853062850626</v>
       </c>
       <c r="C20" t="n">
-        <v>1.013163700251244</v>
+        <v>1.339221377233877</v>
       </c>
       <c r="D20" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9128948557826102</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2835630784532303</v>
+        <v>0.0007587433381137274</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5166978723636554</v>
+        <v>1.326148097316313</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5167245559967235</v>
+        <v>-1.326195007759708</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5395937476791089</v>
+        <v>-1.09699838012138</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.215814248054073</v>
+        <v>0.08739368717664438</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3301248380041233</v>
+        <v>4.028684749082988</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.105574581396306</v>
+        <v>-4.570413938945361</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6936425659560193</v>
+        <v>1.221962100234958</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.533663480955614</v>
+        <v>-3.182337607653933</v>
       </c>
       <c r="P20" t="n">
-        <v>0.453358654565702</v>
+        <v>1.468324445853402</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.737188523520676</v>
+        <v>-3.998299618032106</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.902858369180083</v>
+        <v>-5.97569688133951</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.4797097537360951</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2576152993735751</v>
+        <v>0.2967193253906257</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2635,107 +2635,107 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.448145086274461</v>
+        <v>-0.9622830882963833</v>
       </c>
       <c r="Y20" t="n">
-        <v>-2.009035815292868</v>
+        <v>-0.1632019012961676</v>
       </c>
       <c r="Z20" t="n">
-        <v>-1.659213822345314</v>
+        <v>-0.1850015418680325</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.6981803377979809</v>
+        <v>-0.2675757134908732</v>
       </c>
       <c r="AB20" t="n">
-        <v>-2.265749336469369</v>
+        <v>-0.4736744678230853</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.3368069194581115</v>
+        <v>-1.089275946228544</v>
       </c>
       <c r="AD20" t="n">
-        <v>-2.32480648355423</v>
+        <v>-0.09526854832020075</v>
       </c>
       <c r="AE20" t="n">
-        <v>-2.522382900164025</v>
+        <v>-0.2632227003818449</v>
       </c>
       <c r="AF20" t="n">
-        <v>-2.154978853254192</v>
+        <v>-0.1246585803421917</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>-2.001761515249359</v>
+        <v>-1.028780569593295</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.008803702827623163</v>
+        <v>0.8246145880898825</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.819875174399046</v>
+        <v>2.284853062850626</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6112786565284644</v>
+        <v>1.286142220515774</v>
       </c>
       <c r="D21" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E21" t="n">
-        <v>1.744399085868939</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F21" t="n">
-        <v>2.085785436474636</v>
+        <v>-0.4731109596474597</v>
       </c>
       <c r="G21" t="n">
-        <v>1.248342443837526</v>
+        <v>0.42468057404869</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1738428082371496</v>
+        <v>0.7904370596186481</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1738557999490154</v>
+        <v>-0.7904625764351639</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3696241010989402</v>
+        <v>-0.49085314760268</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.61680130504814</v>
+        <v>1.390601622407362</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3301248380041233</v>
+        <v>-0.9657845694543271</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9754746155400137</v>
+        <v>-0.1542434233366368</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6839479095516249</v>
+        <v>0.6896593128497492</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3500109666974757</v>
+        <v>-0.1016302751374757</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6921741348686902</v>
+        <v>0.7319767149191881</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.356963500547597</v>
+        <v>-1.102490672429748</v>
       </c>
       <c r="R21" t="n">
-        <v>1.297229033230895</v>
+        <v>-0.06038380415558071</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4416794557715791</v>
+        <v>0.6995240286504462</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3001665069532508</v>
+        <v>-1.017648603844671</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2744,40 +2744,40 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04176938367097</v>
+        <v>-0.8998373552523101</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.06132230457555496</v>
+        <v>-0.4499061905405299</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.6562962065094501</v>
+        <v>-0.8126509421581717</v>
       </c>
       <c r="AA21" t="n">
-        <v>-1.375046900096587</v>
+        <v>-0.3273851470715624</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.5456837179543604</v>
+        <v>-0.8750244112519121</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.047552150899285</v>
+        <v>0.588528862258957</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.100919484728671</v>
+        <v>-0.9382414213891003</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.224255713842808</v>
+        <v>-0.2717120078038754</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.8248897480809674</v>
+        <v>-0.7142850039650447</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.8890389722340076</v>
+        <v>-1.079650212702884</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.7717454723182761</v>
+        <v>-1.696537076210942</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -712,68 +712,68 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C3" t="n">
-        <v>0.543034026462332</v>
+        <v>0.8918399134670087</v>
       </c>
       <c r="D3" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4157521150431646</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.09401519725900095</v>
+        <v>2.085785436474636</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01284963915427201</v>
+        <v>2.48383524852078</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.716684533842068</v>
+        <v>1.026149916205621</v>
       </c>
       <c r="I3" t="n">
-        <v>2.716799073969518</v>
+        <v>-1.026184846217963</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.00593696158772055</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4883807441707113</v>
+        <v>-1.449723364633946</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.419827234775901</v>
+        <v>0.0331092942531361</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.078558182417533</v>
+        <v>-0.2569450632345141</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.185965530254356</v>
+        <v>-0.5485729221836555</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3721254362364578</v>
+        <v>0.5091257673439357</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.556671637984449</v>
+        <v>0.2742470443384608</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.555306579013512</v>
+        <v>1.436300731933963</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2543284952107916</v>
+        <v>-1.030107259431635</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.127974769863544</v>
+        <v>0.9567335749858984</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2699885720929168</v>
+        <v>-0.2959658758582872</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -782,107 +782,107 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7098009423623417</v>
+        <v>0.8590620789414448</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.9408015268041218</v>
+        <v>0.1099327462761978</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.7630155197223483</v>
+        <v>0.2874755704302207</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6317905654815504</v>
+        <v>-1.237145440448594</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.7222911753980188</v>
+        <v>0.2980835575905008</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7217827288118702</v>
+        <v>-1.248649160472326</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.8547255627276497</v>
+        <v>0.7198894457046625</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.9372286313951173</v>
+        <v>1.120354790730962</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1.073477153457406</v>
+        <v>0.5441350196096062</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.7061292891333459</v>
+        <v>0.5454944250289068</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.04446111036586359</v>
+        <v>-0.247817072333241</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8918399134670087</v>
+        <v>0.543034026462332</v>
       </c>
       <c r="D4" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E4" t="n">
-        <v>1.744399085868939</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F4" t="n">
-        <v>2.085785436474636</v>
+        <v>-0.09401519725900095</v>
       </c>
       <c r="G4" t="n">
-        <v>2.48383524852078</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H4" t="n">
-        <v>1.026149916205621</v>
+        <v>-2.716684533842068</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.026184846217963</v>
+        <v>2.716799073969518</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.73331124061016</v>
+        <v>-0.00593696158772055</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.449723364633946</v>
+        <v>0.4883807441707113</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0331092942531361</v>
+        <v>-1.419827234775901</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2569450632345141</v>
+        <v>-1.078558182417533</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5485729221836555</v>
+        <v>-1.185965530254356</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5091257673439357</v>
+        <v>-0.3721254362364578</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2742470443384608</v>
+        <v>-1.556671637984449</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.436300731933963</v>
+        <v>1.555306579013512</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.030107259431635</v>
+        <v>-0.2543284952107916</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9567335749858984</v>
+        <v>-1.127974769863544</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2959658758582872</v>
+        <v>0.2699885720929168</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -891,40 +891,40 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8590620789414448</v>
+        <v>-0.7098009423623417</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1099327462761978</v>
+        <v>-0.9408015268041218</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2874755704302207</v>
+        <v>-0.7630155197223483</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.237145440448594</v>
+        <v>0.6317905654815504</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2980835575905008</v>
+        <v>-0.7222911753980188</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.248649160472326</v>
+        <v>0.7217827288118702</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.7198894457046625</v>
+        <v>-0.8547255627276497</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.120354790730962</v>
+        <v>-0.9372286313951173</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5441350196096062</v>
+        <v>-1.073477153457406</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.5454944250289068</v>
+        <v>-0.7061292891333459</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.247817072333241</v>
+        <v>-0.04446111036586359</v>
       </c>
     </row>
     <row r="5">
@@ -985,7 +985,7 @@
         <v>-0.157356149683186</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5672954165531842</v>
+        <v>-0.4203987994349035</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1039,68 +1039,68 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.819875174399046</v>
+        <v>2.284853062850626</v>
       </c>
       <c r="C6" t="n">
-        <v>1.339221377233877</v>
+        <v>1.013163700251244</v>
       </c>
       <c r="D6" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.08249049901650093</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2850805651294578</v>
+        <v>-0.1887891378561156</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8365115089431081</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5666975692154377</v>
+        <v>-0.2166996912529628</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5667262495870146</v>
+        <v>0.2167143944549789</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.00593696158772055</v>
+        <v>-0.4908531476026802</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.21828189053924</v>
+        <v>-1.115567483805556</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3055348934460803</v>
+        <v>-0.6933589702613824</v>
       </c>
       <c r="M6" t="n">
-        <v>1.797087734723032</v>
+        <v>0.3592647761527498</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03056337224617514</v>
+        <v>-0.3132631063009232</v>
       </c>
       <c r="O6" t="n">
-        <v>2.265508374479858</v>
+        <v>0.1125627257327581</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.477066477883453</v>
+        <v>-0.1237787561665195</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.39663211624078</v>
+        <v>0.4049167239112055</v>
       </c>
       <c r="R6" t="n">
-        <v>2.218466315743146</v>
+        <v>-0.2543284952107916</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08247083545151267</v>
+        <v>2.467028076186675</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.993213631860892</v>
+        <v>-0.6447471785188281</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1109,107 +1109,107 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2186230334351373</v>
+        <v>-0.5524900958308684</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.536757255232435</v>
+        <v>-1.131548916918645</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2651079108897363</v>
+        <v>-0.3765391428079359</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02419594453736944</v>
+        <v>-1.013283831305482</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6860065880457429</v>
+        <v>-1.160219857250067</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2845845655775999</v>
+        <v>-0.2741785699582603</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.6062256180071888</v>
+        <v>-0.9365648225360037</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.4469138546127484</v>
+        <v>-0.6493193849327275</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.3146898169970525</v>
+        <v>-0.3210022450247348</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.05701702197165631</v>
+        <v>-0.6351178829756178</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.2206185939582957</v>
+        <v>0.4366727243813309</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>lpob9cJb</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.284853062850626</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.6777865780540365</v>
+        <v>1.286142220515774</v>
       </c>
       <c r="D7" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08359037233672091</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1903066245323431</v>
+        <v>0.0007587433381137274</v>
       </c>
       <c r="G7" t="n">
         <v>-0.398981295740146</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08329848985772981</v>
+        <v>0.197583511233232</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08329576708676574</v>
+        <v>-0.2261577487733106</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.460685519632599</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5809180744801336</v>
+        <v>-1.115567483805556</v>
       </c>
       <c r="L7" t="n">
         <v>-0.5117419041327529</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6677516228260235</v>
+        <v>-0.2569450632345141</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3315395968549221</v>
+        <v>-0.7084922145311433</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4626984766044422</v>
+        <v>-0.8715011182653473</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0441735960655237</v>
+        <v>-1.198448417529967</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1107752801001733</v>
+        <v>-1.023153441043382</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.12707960495924</v>
+        <v>-2.290747751290505</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6232322499309956</v>
+        <v>-1.594089035719624</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08750822233750201</v>
+        <v>0.9838898971029448</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1218,107 +1218,107 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3958222019781681</v>
+        <v>0.1571454104651572</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.07020532458698528</v>
+        <v>-0.274121108503933</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.6190787424256108</v>
+        <v>0.09370843995819361</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9209544445165551</v>
+        <v>0.5243030347787914</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.7358585276797048</v>
+        <v>0.3100912757949237</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1460881638606688</v>
+        <v>1.61149122349696</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.730830695945405</v>
+        <v>-0.009561499974817431</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.7131867674298671</v>
+        <v>-0.5495533614605043</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.5586607471977286</v>
+        <v>-0.2736652139666792</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.9100429854655323</v>
+        <v>0.524087956083741</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.6596065719069475</v>
+        <v>0.8458655487425889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C8" t="n">
-        <v>1.286142220515774</v>
+        <v>1.339221377233877</v>
       </c>
       <c r="D8" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4157521150431646</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0007587433381137274</v>
+        <v>0.2850805651294578</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.398981295740146</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H8" t="n">
-        <v>0.197583511233232</v>
+        <v>-0.5666975692154377</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2261577487733106</v>
+        <v>0.5667262495870146</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2483950545952004</v>
+        <v>0.4789792244272389</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.115567483805556</v>
+        <v>-2.21828189053924</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5117419041327529</v>
+        <v>0.3055348934460803</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2569450632345141</v>
+        <v>1.797087734723032</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7084922145311433</v>
+        <v>0.03056337224617514</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8715011182653473</v>
+        <v>2.265508374479858</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.198448417529967</v>
+        <v>-1.477066477883453</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.023153441043382</v>
+        <v>1.39663211624078</v>
       </c>
       <c r="R8" t="n">
-        <v>-2.290747751290505</v>
+        <v>2.218466315743146</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.594089035719624</v>
+        <v>0.08247083545151267</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9838898971029448</v>
+        <v>1.993213631860892</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1327,40 +1327,40 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1571454104651572</v>
+        <v>0.2186230334351373</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.274121108503933</v>
+        <v>0.536757255232435</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.09370843995819361</v>
+        <v>0.2651079108897363</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5243030347787914</v>
+        <v>0.02419594453736944</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3100912757949237</v>
+        <v>0.6860065880457429</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.61149122349696</v>
+        <v>0.2845845655775999</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.009561499974817431</v>
+        <v>0.6062256180071888</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.5495533614605043</v>
+        <v>0.4469138546127484</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.2736652139666792</v>
+        <v>0.3146898169970525</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.524087956083741</v>
+        <v>0.05701702197165631</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.8458655487425889</v>
+        <v>0.2206185939582957</v>
       </c>
     </row>
     <row r="9">
@@ -1394,7 +1394,7 @@
         <v>0.04528001643112482</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.00593696158772055</v>
+        <v>0.7214373174347188</v>
       </c>
       <c r="K9" t="n">
         <v>1.023030153496134</v>
@@ -1421,7 +1421,7 @@
         <v>-2.872581824456137</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1172808678323042</v>
+        <v>-0.293604481811779</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1475,68 +1475,68 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2.284853062850626</v>
       </c>
       <c r="C10" t="n">
-        <v>1.013163700251244</v>
+        <v>-0.6777865780540365</v>
       </c>
       <c r="D10" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7468139844293883</v>
+        <v>0.08359037233672091</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1887891378561156</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G10" t="n">
         <v>-0.398981295740146</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2166996912529628</v>
+        <v>0.08329848985772981</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2167143944549789</v>
+        <v>-0.08329576708676574</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3696241010989402</v>
+        <v>-1.460685519632599</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.115567483805556</v>
+        <v>-0.5809180744801336</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6933589702613824</v>
+        <v>-0.5117419041327529</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3592647761527498</v>
+        <v>-0.6677516228260235</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3132631063009232</v>
+        <v>-0.3315395968549221</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1125627257327581</v>
+        <v>-0.4626984766044422</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1237787561665195</v>
+        <v>-0.0441735960655237</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4049167239112055</v>
+        <v>-0.1107752801001733</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.2543284952107916</v>
+        <v>-1.12707960495924</v>
       </c>
       <c r="S10" t="n">
-        <v>2.467028076186675</v>
+        <v>-0.6232322499309956</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6447471785188281</v>
+        <v>0.08750822233750201</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1545,40 +1545,40 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5524900958308684</v>
+        <v>-0.3958222019781681</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.131548916918645</v>
+        <v>-0.07020532458698528</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.3765391428079359</v>
+        <v>-0.6190787424256108</v>
       </c>
       <c r="AA10" t="n">
-        <v>-1.013283831305482</v>
+        <v>0.9209544445165551</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1.160219857250067</v>
+        <v>-0.7358585276797048</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.2741785699582603</v>
+        <v>0.1460881638606688</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.9365648225360037</v>
+        <v>-0.730830695945405</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.6493193849327275</v>
+        <v>-0.7131867674298671</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.3210022450247348</v>
+        <v>-0.5586607471977286</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.6351178829756178</v>
+        <v>-0.9100429854655323</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.4366727243813309</v>
+        <v>-0.6596065719069475</v>
       </c>
     </row>
     <row r="11">
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.819875174399046</v>
+        <v>2.306994867062606</v>
       </c>
       <c r="C12" t="n">
         <v>1.013163700251244</v>
@@ -1802,68 +1802,68 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.819875174399046</v>
+        <v>2.306994867062606</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.5488800545957865</v>
+        <v>0.7477679166607292</v>
       </c>
       <c r="D13" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5807331130761665</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1887891378561156</v>
+        <v>-0.5678849002445744</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01284963915427201</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.259550511304418</v>
+        <v>-0.4309841063320289</v>
       </c>
       <c r="I13" t="n">
-        <v>1.259606860766758</v>
+        <v>0.4310073669847965</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8545402871138997</v>
+        <v>-0.00593696158772055</v>
       </c>
       <c r="K13" t="n">
-        <v>2.626978381472402</v>
+        <v>0.6888742726677447</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.78306136703316</v>
+        <v>-1.238210168647272</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.873154902621778</v>
+        <v>0.7700713357442589</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.298546892729021</v>
+        <v>-0.9118181719443772</v>
       </c>
       <c r="O13" t="n">
-        <v>0.09787520567308552</v>
+        <v>1.211678810198304</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.676079378135944</v>
+        <v>-0.9994355172774767</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.1107752801001733</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.321024296014451</v>
+        <v>1.103284342175684</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1962144594129164</v>
+        <v>-1.072724661002653</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.623870137228588</v>
+        <v>-0.01956258426656824</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1872,107 +1872,107 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2045399705252551</v>
+        <v>-0.6343394208020771</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1463367184841673</v>
+        <v>-0.3379815751701792</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.4128214941249725</v>
+        <v>-0.3556690765831189</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.8362586616820753</v>
+        <v>0.3934561822041817</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.5650364329540472</v>
+        <v>-0.2911470132533752</v>
       </c>
       <c r="AC13" t="n">
-        <v>-1.087009924725866</v>
+        <v>1.673480590037023</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.3674542166242922</v>
+        <v>-0.81654030991459</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.3018583124556456</v>
+        <v>-0.6284842553397906</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.0502779134264426</v>
+        <v>-0.5060466933800721</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.459584837625255</v>
+        <v>-0.3612504523555711</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.3227106019491588</v>
+        <v>-0.4894530484796624</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.819875174399046</v>
+        <v>2.284853062850626</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7477679166607292</v>
+        <v>-0.5488800545957865</v>
       </c>
       <c r="D14" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4146522417229446</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5678849002445744</v>
+        <v>-0.1887891378561156</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8365115089431081</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4309841063320289</v>
+        <v>-1.259550511304418</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4310073669847965</v>
+        <v>1.259606860766758</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.00593696158772055</v>
+        <v>-0.8545402871138997</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6888742726677447</v>
+        <v>2.626978381472402</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.238210168647272</v>
+        <v>-1.78306136703316</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7700713357442589</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9118181719443772</v>
+        <v>-2.298546892729021</v>
       </c>
       <c r="O14" t="n">
-        <v>1.211678810198304</v>
+        <v>0.09787520567308552</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9994355172774767</v>
+        <v>-1.676079378135944</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.1107752801001733</v>
       </c>
       <c r="R14" t="n">
-        <v>1.103284342175684</v>
+        <v>-1.321024296014451</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.072724661002653</v>
+        <v>-0.1962144594129164</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.01956258426656824</v>
+        <v>-1.623870137228588</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1981,40 +1981,40 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6343394208020771</v>
+        <v>-0.2045399705252551</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.3379815751701792</v>
+        <v>0.1463367184841673</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.3556690765831189</v>
+        <v>-0.4128214941249725</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.3934561822041817</v>
+        <v>-0.8362586616820753</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.2911470132533752</v>
+        <v>-0.5650364329540472</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.673480590037023</v>
+        <v>-1.087009924725866</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.81654030991459</v>
+        <v>-0.3674542166242922</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.6284842553397906</v>
+        <v>0.3018583124556456</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.5060466933800721</v>
+        <v>-0.0502779134264426</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.3612504523555711</v>
+        <v>-0.459584837625255</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.4894530484796624</v>
+        <v>0.3227106019491588</v>
       </c>
     </row>
     <row r="15">
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.218427650214686</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C15" t="n">
         <v>0.7174369699646703</v>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.819875174399046</v>
+        <v>2.284853062850626</v>
       </c>
       <c r="C17" t="n">
         <v>0.8918399134670087</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C18" t="n">
         <v>0.543034026462332</v>
@@ -2456,68 +2456,68 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.908442391246966</v>
+        <v>2.284853062850626</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.6777865780540365</v>
+        <v>1.339221377233877</v>
       </c>
       <c r="D19" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E19" t="n">
-        <v>2.408722571281827</v>
+        <v>-0.5807331130761665</v>
       </c>
       <c r="F19" t="n">
-        <v>1.896237555280407</v>
+        <v>0.0007587433381137274</v>
       </c>
       <c r="G19" t="n">
-        <v>1.248342443837526</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H19" t="n">
-        <v>1.440433118691816</v>
+        <v>1.326148097316313</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.440484593108944</v>
+        <v>-1.326195007759708</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1271660080914603</v>
+        <v>-1.09699838012138</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2878872156736779</v>
+        <v>0.08739368717664438</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03310929425313586</v>
+        <v>4.028684749082988</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9754746155400137</v>
+        <v>-4.570413938945361</v>
       </c>
       <c r="N19" t="n">
-        <v>1.014067020183224</v>
+        <v>1.221962100234958</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5655111170221552</v>
+        <v>-3.182337607653933</v>
       </c>
       <c r="P19" t="n">
-        <v>1.229508965550414</v>
+        <v>1.468324445853402</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.808241147236616</v>
+        <v>-3.998299618032106</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.3513008407383969</v>
+        <v>-5.97569688133951</v>
       </c>
       <c r="S19" t="n">
-        <v>1.353129694999717</v>
+        <v>0.4797097537360951</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4247126779805524</v>
+        <v>0.2967193253906257</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2526,107 +2526,107 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7265752263684719</v>
+        <v>-0.9622830882963833</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.014374919398328</v>
+        <v>-0.1632019012961676</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.088197481533369</v>
+        <v>-0.1850015418680325</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.3053992537369987</v>
+        <v>-0.2675757134908732</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9870577408713016</v>
+        <v>-0.4736744678230853</v>
       </c>
       <c r="AC19" t="n">
-        <v>-1.189724430652031</v>
+        <v>-1.089275946228544</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.247815027192715</v>
+        <v>-0.09526854832020075</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.151674256428488</v>
+        <v>-0.2632227003818449</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.369587320859271</v>
+        <v>-0.1246585803421917</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.6442431494581385</v>
+        <v>-1.028780569593295</v>
       </c>
       <c r="AI19" t="n">
-        <v>-1.145611144790124</v>
+        <v>0.8246145880898825</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.284853062850626</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C20" t="n">
-        <v>1.339221377233877</v>
+        <v>-0.6777865780540365</v>
       </c>
       <c r="D20" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5807331130761665</v>
+        <v>2.408722571281827</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0007587433381137274</v>
+        <v>1.896237555280407</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8365115089431081</v>
+        <v>1.248342443837526</v>
       </c>
       <c r="H20" t="n">
-        <v>1.326148097316313</v>
+        <v>1.440433118691816</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.326195007759708</v>
+        <v>-1.440484593108944</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.09699838012138</v>
+        <v>-0.1271660080914603</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08739368717664438</v>
+        <v>0.2878872156736779</v>
       </c>
       <c r="L20" t="n">
-        <v>4.028684749082988</v>
+        <v>0.03310929425313586</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.570413938945361</v>
+        <v>0.9754746155400137</v>
       </c>
       <c r="N20" t="n">
-        <v>1.221962100234958</v>
+        <v>1.014067020183224</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.182337607653933</v>
+        <v>-0.5655111170221552</v>
       </c>
       <c r="P20" t="n">
-        <v>1.468324445853402</v>
+        <v>1.229508965550414</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.998299618032106</v>
+        <v>-2.808241147236616</v>
       </c>
       <c r="R20" t="n">
-        <v>-5.97569688133951</v>
+        <v>-0.3513008407383969</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4797097537360951</v>
+        <v>1.353129694999717</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2967193253906257</v>
+        <v>0.4247126779805524</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2635,40 +2635,40 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9622830882963833</v>
+        <v>0.7265752263684719</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.1632019012961676</v>
+        <v>1.014374919398328</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.1850015418680325</v>
+        <v>1.088197481533369</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.2675757134908732</v>
+        <v>-0.3053992537369987</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.4736744678230853</v>
+        <v>0.9870577408713016</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1.089275946228544</v>
+        <v>-1.189724430652031</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.09526854832020075</v>
+        <v>1.247815027192715</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.2632227003818449</v>
+        <v>1.151674256428488</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.1246585803421917</v>
+        <v>1.369587320859271</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>-1.028780569593295</v>
+        <v>0.6442431494581385</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.8246145880898825</v>
+        <v>-1.145611144790124</v>
       </c>
     </row>
     <row r="21">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.284853062850626</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C21" t="n">
         <v>1.286142220515774</v>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AI14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,177 +603,177 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7174369699646703</v>
+        <v>1.809351051022789</v>
       </c>
       <c r="D2" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.411137469842276</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.705172187409951</v>
+        <v>0.9484981493092606</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.810812230634564</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8166960534743479</v>
+        <v>-0.9881235855376008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8167347175384682</v>
+        <v>0.9881690955623221</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.00593696158772055</v>
+        <v>0.3577501779234991</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4883807441707113</v>
+        <v>-2.118035126290724</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2147263603817656</v>
+        <v>-1.601444300904531</v>
       </c>
       <c r="M2" t="n">
-        <v>2.207894294314541</v>
+        <v>-0.2569450632345141</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7216431713192469</v>
+        <v>-1.140274303869359</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6290738478312667</v>
+        <v>-0.3941567163259672</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3936547844899549</v>
+        <v>-0.8004226170249864</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.356963500547597</v>
+        <v>0.7619342651498524</v>
       </c>
       <c r="R2" t="n">
-        <v>2.751814216144976</v>
+        <v>1.297229033230895</v>
       </c>
       <c r="S2" t="n">
-        <v>1.214067980324422</v>
+        <v>0.6474266096172088</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1202969164078342</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.09095654158382248</v>
+        <v>0.5066312415931015</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0218193076058328</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5796855751437382</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2564937675438262</v>
+        <v>0.1338071464784746</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.431539967288882</v>
+        <v>-0.8091141310561112</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.258194315102407</v>
+        <v>-0.611512607233201</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.4171497601466182</v>
+        <v>0.3589715264233247</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.7166169625283227</v>
+        <v>-0.5168451318513012</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8777511004900883</v>
+        <v>-0.4289226605746111</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.9631492753617833</v>
+        <v>-0.2366674039729924</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.165019489194087</v>
+        <v>-0.6856194063383346</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.613923290432531</v>
+        <v>-1.04999576533202</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.182529302176419</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.1465778546102821</v>
+        <v>-0.4107143244802259</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.9715228520786635</v>
+        <v>0.1529884462045454</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2.284853062850626</v>
       </c>
       <c r="C3" t="n">
-        <v>1.339221377233877</v>
+        <v>0.8918399134670087</v>
       </c>
       <c r="D3" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5807331130761665</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007587433381137274</v>
+        <v>2.085785436474636</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8365115089431081</v>
+        <v>2.48383524852078</v>
       </c>
       <c r="H3" t="n">
-        <v>1.326148097316313</v>
+        <v>1.026149916205621</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.326195007759708</v>
+        <v>-1.026184846217963</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.73331124061016</v>
+        <v>-0.2483950545952003</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08739368717664438</v>
+        <v>-1.449723364633946</v>
       </c>
       <c r="L3" t="n">
-        <v>4.028684749082988</v>
+        <v>0.0331092942531361</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.570413938945361</v>
+        <v>-0.2569450632345141</v>
       </c>
       <c r="N3" t="n">
-        <v>1.221962100234958</v>
+        <v>-0.5485729221836555</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.182337607653933</v>
+        <v>0.5091257673439357</v>
       </c>
       <c r="P3" t="n">
-        <v>1.468324445853402</v>
+        <v>0.2742470443384608</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.998299618032106</v>
+        <v>1.436300731933963</v>
       </c>
       <c r="R3" t="n">
-        <v>-5.97569688133951</v>
+        <v>-1.030107259431635</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4797097537360951</v>
+        <v>0.9567335749858984</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2967193253906257</v>
+        <v>-0.2796738079322347</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -782,585 +782,1239 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9622830882963833</v>
+        <v>0.8596203054405587</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.1632019012961676</v>
+        <v>0.08680389657478785</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.1850015418680325</v>
+        <v>0.2881052658604176</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.2675757134908732</v>
+        <v>-1.266416027672307</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.4736744678230853</v>
+        <v>0.2946467770047251</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.089275946228544</v>
+        <v>-1.196884731770481</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.09526854832020075</v>
+        <v>0.7053456784931603</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.2632227003818449</v>
+        <v>1.122109001549577</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.1246585803421917</v>
+        <v>0.5476433360097595</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1.028780569593295</v>
+        <v>0.5558276008628101</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.8246145880898825</v>
+        <v>-0.2319556189450904</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.6777865780540365</v>
+        <v>0.543034026462332</v>
       </c>
       <c r="D4" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E4" t="n">
-        <v>2.408722571281827</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F4" t="n">
-        <v>1.896237555280407</v>
+        <v>-0.09401519725900095</v>
       </c>
       <c r="G4" t="n">
-        <v>1.248342443837526</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H4" t="n">
-        <v>1.440433118691816</v>
+        <v>-2.716684533842068</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.440484593108944</v>
+        <v>2.716799073969518</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3577501779234991</v>
+        <v>-0.00593696158772055</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2878872156736779</v>
+        <v>0.4883807441707113</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03310929425313586</v>
+        <v>-1.419827234775901</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9754746155400137</v>
+        <v>-1.078558182417533</v>
       </c>
       <c r="N4" t="n">
-        <v>1.014067020183224</v>
+        <v>-1.185965530254356</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5655111170221552</v>
+        <v>-0.3721254362364578</v>
       </c>
       <c r="P4" t="n">
-        <v>1.229508965550414</v>
+        <v>-1.556671637984449</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.808241147236616</v>
+        <v>1.555306579013512</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.3513008407383969</v>
+        <v>-0.2543284952107916</v>
       </c>
       <c r="S4" t="n">
-        <v>1.353129694999717</v>
+        <v>-1.127974769863544</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01732503138294562</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4247126779805524</v>
+        <v>0.283474171277235</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.796989639342385</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7710087222687483</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7265752263684719</v>
+        <v>-0.6939466331066687</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.014374919398328</v>
+        <v>-0.9124478815181855</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.088197481533369</v>
+        <v>-0.7595606681156428</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.3053992537369987</v>
+        <v>0.6781671955182146</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9870577408713016</v>
+        <v>-0.7048348268286899</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.189724430652031</v>
+        <v>0.7521507609031263</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.247815027192715</v>
+        <v>-0.8561541254208321</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.151674256428488</v>
+        <v>-0.9544756104763737</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.369587320859271</v>
+        <v>-1.028015426196457</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.5104973096845766</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.6442431494581385</v>
+        <v>-0.6951959540969688</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.145611144790124</v>
+        <v>-0.09781185789492947</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.284853062850626</v>
+        <v>2.240569454426666</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8918399134670087</v>
+        <v>-0.874937731578419</v>
       </c>
       <c r="D5" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.08249049901650093</v>
+        <v>-1.245056598489054</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09553268393522843</v>
+        <v>-2.273815830992639</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-1.6344741004234</v>
       </c>
       <c r="H5" t="n">
-        <v>2.054715108585138</v>
+        <v>-0.1881284359090871</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.054791114361088</v>
+        <v>0.1881419981176697</v>
       </c>
       <c r="J5" t="n">
-        <v>1.448811596457158</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.920009240278857</v>
+        <v>2.025497795981301</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.05769923881117887</v>
+        <v>-1.056593102518642</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.565049982928146</v>
+        <v>2.207894294314541</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2036041629769318</v>
+        <v>-0.4937434505216594</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9645220786432772</v>
+        <v>1.074595289641354</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2630877863432628</v>
+        <v>1.189706385499916</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.26116513520248</v>
+        <v>1.118951806388499</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.030107259431635</v>
+        <v>-0.157356149683186</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7205627706686657</v>
+        <v>-0.4203987994349035</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1832585583504674</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1760013724459726</v>
+        <v>0.4169369600566863</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.635009198774477</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1856070133563018</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.289939529538654</v>
+        <v>-0.9725917416308026</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.158682428869865</v>
+        <v>-1.168642878603107</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.599384978868622</v>
+        <v>-1.976495034282877</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.1152627424258172</v>
+        <v>0.9185819453044918</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.66540765159332</v>
+        <v>-1.098400105544104</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.04914510005192888</v>
+        <v>0.8718523632659246</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.683713197143029</v>
+        <v>-1.434702995297684</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.624501277353565</v>
+        <v>-1.631053414344164</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.906463643125794</v>
+        <v>-2.387460148101102</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1.197584004565521</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.58206944392914</v>
+        <v>-1.191253391603176</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.23827594594042</v>
+        <v>0.496557255898384</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.819875174399046</v>
+        <v>2.218427650214686</v>
       </c>
       <c r="C6" t="n">
-        <v>0.543034026462332</v>
+        <v>-1.019009728384699</v>
       </c>
       <c r="D6" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.078975727135832</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5678849002445744</v>
+        <v>-0.2835630784532303</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.810812230634564</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H6" t="n">
-        <v>2.097571991600951</v>
+        <v>-0.002415276173896646</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.097649708867051</v>
+        <v>0.04528001643112482</v>
       </c>
       <c r="J6" t="n">
         <v>0.7214373174347188</v>
       </c>
       <c r="K6" t="n">
-        <v>1.089861329661812</v>
+        <v>1.023030153496134</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.419827234775901</v>
+        <v>0.9411946248962842</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3592647761527498</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.22416521485018</v>
+        <v>0.8404403599202378</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3917087963160216</v>
+        <v>-1.405147680433473</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8004226170249864</v>
+        <v>2.304178626913861</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.142159288122931</v>
+        <v>-2.133874680452506</v>
       </c>
       <c r="R6" t="n">
-        <v>1.297229033230895</v>
+        <v>-2.872581824456137</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.54537417277618</v>
+        <v>-0.293604481811779</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0819293099328072</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.120867604656465</v>
+        <v>0.8669988787003797</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4059443523811561</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7387752832416217</v>
+        <v>0.1313977460846441</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.8598828467207934</v>
+        <v>0.6054254844804072</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.1634692743743312</v>
+        <v>-0.1213213462451937</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.003622268992228587</v>
+        <v>0.1769148237919017</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.3987828645088972</v>
+        <v>-0.3072945343970117</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1694565106070595</v>
+        <v>-0.6857903605377917</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.5410321704987857</v>
+        <v>-0.1364231951023169</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.8388314880010732</v>
+        <v>0.1654093719877117</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.5136170693458291</v>
+        <v>0.1544529646989463</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.3713400853247025</v>
+        <v>-0.1710086831307103</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.675413360647825</v>
+        <v>1.144386844857477</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4292929763521113</v>
+        <v>0.6112786565284644</v>
       </c>
       <c r="D7" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2485713703697228</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1903066245323431</v>
+        <v>-0.1887891378561156</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8365115089431081</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.145259426964558</v>
+        <v>-0.2166996912529628</v>
       </c>
       <c r="I7" t="n">
-        <v>2.145351147223337</v>
+        <v>0.2167143944549789</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.4908531476026802</v>
       </c>
       <c r="K7" t="n">
-        <v>1.290354858158845</v>
+        <v>-1.115567483805556</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.054380829933568</v>
+        <v>-0.6933589702613824</v>
       </c>
       <c r="M7" t="n">
-        <v>3.440313973089069</v>
+        <v>0.3592647761527498</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.98683770765464</v>
+        <v>-0.3132631063009232</v>
       </c>
       <c r="O7" t="n">
-        <v>2.839545616812086</v>
+        <v>0.1125627257327581</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.905023860963833</v>
+        <v>-0.1237787561665195</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.904039512581734</v>
+        <v>0.4049167239112055</v>
       </c>
       <c r="R7" t="n">
-        <v>3.624565325893424</v>
+        <v>-0.2543284952107916</v>
       </c>
       <c r="S7" t="n">
-        <v>1.555120347225045</v>
+        <v>2.467028076186675</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.04897193568787304</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.548265913694121</v>
+        <v>-0.6394910798985689</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6584985427793782</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2895347365924197</v>
+        <v>-0.5529815697875613</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2347890689512885</v>
+        <v>-1.117505938043629</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1229938381978449</v>
+        <v>-0.3667420551035191</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.717350971541407</v>
+        <v>-0.9939233860245766</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2173211118495824</v>
+        <v>-1.120213968780071</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2331742027355452</v>
+        <v>-0.3119597576373203</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1843918395121781</v>
+        <v>-0.8679688783507051</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.04641470115493537</v>
+        <v>-0.6550898572667968</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.05261108305040895</v>
+        <v>-0.315616688879101</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1459449594513093</v>
+        <v>-0.6224106386443382</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.2406012173246807</v>
+        <v>0.4182843526444291</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.819875174399046</v>
+        <v>1.908442391246966</v>
       </c>
       <c r="C8" t="n">
-        <v>1.286142220515774</v>
+        <v>-0.639872894683963</v>
       </c>
       <c r="D8" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E8" t="n">
+        <v>0.08359037233672091</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1903066245323431</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.398981295740146</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.08329848985772981</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.08329576708676574</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.73331124061016</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.5809180744801336</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.5117419041327529</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.6677516228260235</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.3315395968549221</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.4626984766044422</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.0441735960655237</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.1107752801001733</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-1.12707960495924</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.6232322499309956</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.002896673930777775</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.373612197603441</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.09300114676497309</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.6230049514231201</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.8904822888764425</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.7512218181239068</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.1464139044516828</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0.7287610982109907</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.7067296241237311</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.5452171819047679</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.9164079940508243</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0.6663694859818471</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.908442391246966</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.580132242261787</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.4157521150431646</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0007587433381137274</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.398981295740146</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.197583511233232</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.2261577487733106</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.73331124061016</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-1.115567483805556</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.5117419041327529</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.2569450632345141</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.7084922145311433</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.8715011182653473</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-1.198448417529967</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1.023153441043382</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-2.290747751290505</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-1.594089035719624</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.960182319410209</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.1389037524724569</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.2689474010220889</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.0909598337939376</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.5299878626047406</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.3064430010192576</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.604091247027272</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.02130008953425185</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.5664860998088224</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.2636994440698359</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.5254543264419433</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.8419514746605052</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.339221377233877</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.08249049901650093</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2850805651294578</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8365115089431081</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.5666975692154377</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5667262495870146</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.00593696158772055</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-2.21828189053924</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3055348934460803</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.797087734723032</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.03056337224617514</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.265508374479858</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-1.477066477883453</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.39663211624078</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.218466315743146</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.08247083545151267</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.950889523447359</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.2186230334351373</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.5735003482611793</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.2643824171751997</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.07505452411258119</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.6831705516707842</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.2796685578176172</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.601282477118947</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.4360545512506938</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.3166248481564672</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.05701702197165631</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.219600671843542</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ERWFdKZh</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.140333515168934</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E11" t="n">
         <v>-0.5807331130761665</v>
       </c>
-      <c r="F8" t="n">
-        <v>-0.4731109596474597</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.42468057404869</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.7904370596186481</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-0.7904625764351639</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="F11" t="n">
+        <v>0.1903066245323431</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01284963915427201</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3261541602806716</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.3261611359538926</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.00593696158772055</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7557054488334223</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0331092942531361</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.1538614963569951</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.274507010577705</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.7613447178177976</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.866350246358383</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-1.023153441043382</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.5452455317936075</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.6799806668287885</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.3409037872914117</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.7972447614910744</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.535207096911997</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.9121732020868</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.4744636595110804</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.53847486593972</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.9361513135142352</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.389956016169642</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.9215427708880453</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.956661808702626</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.034230394699082</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.3615377883314772</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.306994867062606</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.013163700251244</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.08359037233672091</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2850805651294578</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.248342443837526</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.08329848985772981</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.08329576708676574</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.3577501779234991</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8893678011647782</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.849279955539432</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.3592647761527498</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.079310452785065</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.6951676880997961</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.214702469337768</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-1.380170982282029</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.588146069813711</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.7982875000831346</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.229525377923294</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.5017776204546213</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.7140346938312322</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.227905381925339</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.112949556931529</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.374526804225985</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.4841113211168335</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.242614982777913</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.09301959257525098</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.384994448107078</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.515915624379784</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.782164020621224</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.986673560342574</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.033756567089463</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6RCbX36s</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.284853062850626</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.5488800545957865</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.5807331130761665</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.1887891378561156</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01284963915427201</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1.259550511304418</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.259606860766758</v>
+      </c>
+      <c r="J13" t="n">
         <v>-0.2483950545952004</v>
       </c>
-      <c r="K8" t="n">
-        <v>1.390601622407362</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-0.9657845694543271</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-0.1542434233366368</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.6896593128497492</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.1016302751374757</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.7319767149191881</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-1.102490672429748</v>
-      </c>
-      <c r="R8" t="n">
-        <v>-0.06038380415558071</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.6995240286504462</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.8896739010965521</v>
-      </c>
-      <c r="U8" t="n">
-        <v>-1.017648603844671</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-1.121299801544828</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.5682533076063216</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.8998373552523101</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-0.4499061905405299</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-0.8126509421581717</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-0.3273851470715624</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-0.8750244112519121</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.588528862258957</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-0.9382414213891003</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-0.2717120078038754</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-0.7142850039650447</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.022569292791222</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-1.079650212702884</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-1.696537076210942</v>
+      <c r="K13" t="n">
+        <v>2.626978381472402</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1.78306136703316</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.873154902621778</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-2.298546892729021</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.09787520567308552</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-1.676079378135944</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.1107752801001733</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-1.321024296014451</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.1962144594129164</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-1.531484965292775</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-1.623870137228588</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-1.542448947021387</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.1697074027330025</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.2045399705252551</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.1463367184841673</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.4128214941249725</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.8362586616820753</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.5650364329540472</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-1.087009924725866</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.3674542166242922</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.3018583124556456</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.0502779134264426</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0.9615727691070773</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.459584837625255</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.3227106019491588</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.306994867062606</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7477679166607292</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.4146522417229446</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.5678849002445744</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8365115089431081</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.4309841063320289</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.4310073669847965</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.3696241010989402</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.6888742726677447</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1.238210168647272</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.7700713357442589</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.9118181719443772</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.211678810198304</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.9994355172774767</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.1107752801001733</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.103284342175684</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-1.072724661002653</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1823621621762601</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.01956258426656824</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.3920603146181926</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.6343394208020771</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.3379815751701792</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.3556690765831189</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.3934561822041817</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.2911470132533752</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.673480590037023</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.81654030991459</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.6284842553397906</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.5060466933800721</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.3612504523555711</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0.4894530484796624</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI14"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.819875174399046</v>
+        <v>2.306994867062606</v>
       </c>
       <c r="C2" t="n">
         <v>1.809351051022789</v>
@@ -631,7 +631,7 @@
         <v>0.9881690955623221</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3577501779234991</v>
+        <v>0.7214373174347188</v>
       </c>
       <c r="K2" t="n">
         <v>-2.118035126290724</v>
@@ -664,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5066312415931015</v>
+        <v>0.4701050317758135</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -673,107 +673,107 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1338071464784746</v>
+        <v>0.1229525076272047</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.8091141310561112</v>
+        <v>-0.8096691283162128</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.611512607233201</v>
+        <v>-0.6491528019990116</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.3589715264233247</v>
+        <v>0.3419509859573793</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.5168451318513012</v>
+        <v>-0.5518342018918595</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.4289226605746111</v>
+        <v>-0.4490690079968753</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.2366674039729924</v>
+        <v>-0.261122798888482</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.6856194063383346</v>
+        <v>-0.6799947762572944</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.04999576533202</v>
+        <v>-1.037461576682892</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.4107143244802259</v>
+        <v>-0.4471793334147453</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.1529884462045454</v>
+        <v>0.1963233058739764</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.284853062850626</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8918399134670087</v>
+        <v>1.452962427344097</v>
       </c>
       <c r="D3" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E3" t="n">
-        <v>1.744399085868939</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F3" t="n">
-        <v>2.085785436474636</v>
+        <v>-0.09401519725900095</v>
       </c>
       <c r="G3" t="n">
-        <v>2.48383524852078</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H3" t="n">
-        <v>1.026149916205621</v>
+        <v>-2.716684533842068</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.026184846217963</v>
+        <v>2.716799073969518</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2483950545952003</v>
+        <v>-0.00593696158772055</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.449723364633946</v>
+        <v>0.4883807441707113</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0331092942531361</v>
+        <v>-1.419827234775901</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2569450632345141</v>
+        <v>-1.078558182417533</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5485729221836555</v>
+        <v>-1.185965530254356</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5091257673439357</v>
+        <v>-0.3721254362364578</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2742470443384608</v>
+        <v>-1.556671637984449</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.436300731933963</v>
+        <v>1.555306579013512</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.030107259431635</v>
+        <v>-0.2543284952107916</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9567335749858984</v>
+        <v>-1.127974769863544</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2796738079322347</v>
+        <v>0.3475857098672203</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -782,107 +782,107 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8596203054405587</v>
+        <v>-0.6807332188200748</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08680389657478785</v>
+        <v>-0.8701065909899082</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2881052658604176</v>
+        <v>-0.7509475345555396</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.266416027672307</v>
+        <v>0.6729028804921667</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2946467770047251</v>
+        <v>-0.6901521364372395</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.196884731770481</v>
+        <v>0.7518281675642007</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.7053456784931603</v>
+        <v>-0.8582048621317191</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.122109001549577</v>
+        <v>-0.9108574824060434</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5476433360097595</v>
+        <v>-1.000037850092813</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.5558276008628101</v>
+        <v>-0.6988965404837661</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.2319556189450904</v>
+        <v>-0.1288384201606826</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.819875174399046</v>
+        <v>2.284853062850626</v>
       </c>
       <c r="C4" t="n">
-        <v>0.543034026462332</v>
+        <v>-1.284405511975214</v>
       </c>
       <c r="D4" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4157521150431646</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.09401519725900095</v>
+        <v>2.085785436474636</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01284963915427201</v>
+        <v>2.48383524852078</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.716684533842068</v>
+        <v>1.026149916205621</v>
       </c>
       <c r="I4" t="n">
-        <v>2.716799073969518</v>
+        <v>-1.026184846217963</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.00593696158772055</v>
+        <v>0.7214373174347188</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4883807441707113</v>
+        <v>-1.449723364633946</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.419827234775901</v>
+        <v>0.0331092942531361</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.078558182417533</v>
+        <v>-0.2569450632345141</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.185965530254356</v>
+        <v>-0.5485729221836555</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3721254362364578</v>
+        <v>0.5091257673439357</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.556671637984449</v>
+        <v>0.2742470443384608</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.555306579013512</v>
+        <v>1.436300731933963</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2543284952107916</v>
+        <v>-1.030107259431635</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.127974769863544</v>
+        <v>0.9567335749858984</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.283474171277235</v>
+        <v>-0.2743799435991416</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -891,40 +891,40 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6939466331066687</v>
+        <v>0.8490002118884644</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.9124478815181855</v>
+        <v>0.1625254153321321</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.7595606681156428</v>
+        <v>0.2946796226607982</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6781671955182146</v>
+        <v>-1.262750238100831</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.7048348268286899</v>
+        <v>0.2942984507221931</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7521507609031263</v>
+        <v>-1.242859600039654</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.8561541254208321</v>
+        <v>0.7159136129061993</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.9544756104763737</v>
+        <v>1.156661699528542</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1.028015426196457</v>
+        <v>0.6180462744656475</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.6951959540969688</v>
+        <v>0.5257674529823637</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.09781185789492947</v>
+        <v>-0.2874715623842767</v>
       </c>
     </row>
     <row r="5">
@@ -958,7 +958,7 @@
         <v>0.1881419981176697</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.73331124061016</v>
+        <v>-1.09699838012138</v>
       </c>
       <c r="K5" t="n">
         <v>2.025497795981301</v>
@@ -1039,68 +1039,68 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2Fanm72d</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.218427650214686</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.019009728384699</v>
+        <v>1.816933787696803</v>
       </c>
       <c r="D6" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7468139844293883</v>
+        <v>-0.08249049901650093</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2835630784532303</v>
+        <v>0.2850805651294578</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01284963915427201</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.002415276173896646</v>
+        <v>-0.5666975692154377</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04528001643112482</v>
+        <v>0.5667262495870146</v>
       </c>
       <c r="J6" t="n">
         <v>0.7214373174347188</v>
       </c>
       <c r="K6" t="n">
-        <v>1.023030153496134</v>
+        <v>-2.21828189053924</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9411946248962842</v>
+        <v>0.3055348934460803</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.873154902621778</v>
+        <v>1.797087734723032</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8404403599202378</v>
+        <v>0.03056337224617514</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.405147680433473</v>
+        <v>2.265508374479858</v>
       </c>
       <c r="P6" t="n">
-        <v>2.304178626913861</v>
+        <v>-1.477066477883453</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.133874680452506</v>
+        <v>1.39663211624078</v>
       </c>
       <c r="R6" t="n">
-        <v>-2.872581824456137</v>
+        <v>2.218466315743146</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.293604481811779</v>
+        <v>0.08247083545151267</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8669988787003797</v>
+        <v>1.945530508210769</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1109,53 +1109,53 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1313977460846441</v>
+        <v>0.2424379538802464</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6054254844804072</v>
+        <v>0.5712281734427883</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.1213213462451937</v>
+        <v>0.2624981968318468</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1769148237919017</v>
+        <v>0.01348056250270403</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.3072945343970117</v>
+        <v>0.6800615870793432</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.6857903605377917</v>
+        <v>0.2698113642809596</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.1364231951023169</v>
+        <v>0.6014205781725875</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1654093719877117</v>
+        <v>0.4930506304477362</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1544529646989463</v>
+        <v>0.3189451801183033</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.1710086831307103</v>
+        <v>0.05189313312839831</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.144386844857477</v>
+        <v>0.187319905143335</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.819875174399046</v>
+        <v>2.306994867062606</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6112786565284644</v>
+        <v>-1.019009728384699</v>
       </c>
       <c r="D7" t="n">
         <v>-0.5056960363928432</v>
@@ -1164,52 +1164,52 @@
         <v>-0.7468139844293883</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1887891378561156</v>
+        <v>-0.2835630784532303</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.398981295740146</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2166996912529628</v>
+        <v>-0.002415276173896646</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2167143944549789</v>
+        <v>0.04528001643112482</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4908531476026802</v>
+        <v>0.3577501779234991</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.115567483805556</v>
+        <v>1.023030153496134</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6933589702613824</v>
+        <v>0.9411946248962842</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3592647761527498</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3132631063009232</v>
+        <v>0.8404403599202378</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1125627257327581</v>
+        <v>-1.405147680433473</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1237787561665195</v>
+        <v>2.304178626913861</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4049167239112055</v>
+        <v>-2.133874680452506</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.2543284952107916</v>
+        <v>-2.872581824456137</v>
       </c>
       <c r="S7" t="n">
-        <v>2.467028076186675</v>
+        <v>-0.293604481811779</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6394910798985689</v>
+        <v>0.8952897172140631</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1218,107 +1218,107 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5529815697875613</v>
+        <v>0.09661261977728121</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.117505938043629</v>
+        <v>0.5378720718932192</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.3667420551035191</v>
+        <v>-0.1247920918746</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.9939233860245766</v>
+        <v>0.07037543388906171</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.120213968780071</v>
+        <v>-0.3174538438451184</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.3119597576373203</v>
+        <v>-0.6919786449539624</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.8679688783507051</v>
+        <v>-0.1377125645074453</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.6550898572667968</v>
+        <v>0.1778820734161723</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.315616688879101</v>
+        <v>0.1466272267622667</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.6224106386443382</v>
+        <v>-0.1775147568039087</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.4182843526444291</v>
+        <v>1.198628000701595</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>lpob9cJb</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.639872894683963</v>
+        <v>0.6112786565284644</v>
       </c>
       <c r="D8" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08359037233672091</v>
+        <v>-0.7468139844293883</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1903066245323431</v>
+        <v>-0.1887891378561156</v>
       </c>
       <c r="G8" t="n">
         <v>-0.398981295740146</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08329848985772981</v>
+        <v>-0.2166996912529628</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08329576708676574</v>
+        <v>0.2167143944549789</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.73331124061016</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5809180744801336</v>
+        <v>-1.115567483805556</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5117419041327529</v>
+        <v>-0.6933589702613824</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6677516228260235</v>
+        <v>0.3592647761527498</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3315395968549221</v>
+        <v>-0.3132631063009232</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4626984766044422</v>
+        <v>0.1125627257327581</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0441735960655237</v>
+        <v>-0.1237787561665195</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1107752801001733</v>
+        <v>0.4049167239112055</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.12707960495924</v>
+        <v>-0.2543284952107916</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6232322499309956</v>
+        <v>2.467028076186675</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.002896673930777775</v>
+        <v>-0.6394910798985689</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1327,107 +1327,107 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.373612197603441</v>
+        <v>-0.5529815697875613</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.09300114676497309</v>
+        <v>-1.117505938043629</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.6230049514231201</v>
+        <v>-0.3667420551035191</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8904822888764425</v>
+        <v>-0.9939233860245766</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.7512218181239068</v>
+        <v>-1.120213968780071</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.1464139044516828</v>
+        <v>-0.3119597576373203</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.7287610982109907</v>
+        <v>-0.8679688783507051</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.7067296241237311</v>
+        <v>-0.6550898572667968</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.5452171819047679</v>
+        <v>-0.315616688879101</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.9164079940508243</v>
+        <v>-0.6224106386443382</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.6663694859818471</v>
+        <v>0.4182843526444291</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1.908442391246966</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.580132242261787</v>
+        <v>-0.639872894683963</v>
       </c>
       <c r="D9" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4157521150431646</v>
+        <v>0.08359037233672091</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0007587433381137274</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G9" t="n">
         <v>-0.398981295740146</v>
       </c>
       <c r="H9" t="n">
-        <v>0.197583511233232</v>
+        <v>0.08329848985772981</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2261577487733106</v>
+        <v>-0.08329576708676574</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.73331124061016</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.115567483805556</v>
+        <v>-0.5809180744801336</v>
       </c>
       <c r="L9" t="n">
         <v>-0.5117419041327529</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2569450632345141</v>
+        <v>-0.6677516228260235</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7084922145311433</v>
+        <v>-0.3315395968549221</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8715011182653473</v>
+        <v>-0.4626984766044422</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.198448417529967</v>
+        <v>-0.0441735960655237</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.023153441043382</v>
+        <v>-0.1107752801001733</v>
       </c>
       <c r="R9" t="n">
-        <v>-2.290747751290505</v>
+        <v>-1.12707960495924</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.594089035719624</v>
+        <v>-0.6232322499309956</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.960182319410209</v>
+        <v>-0.002896673930777775</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1436,107 +1436,107 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1389037524724569</v>
+        <v>-0.373612197603441</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.2689474010220889</v>
+        <v>-0.09300114676497309</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0909598337939376</v>
+        <v>-0.6230049514231201</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.5299878626047406</v>
+        <v>0.8904822888764425</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3064430010192576</v>
+        <v>-0.7512218181239068</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.604091247027272</v>
+        <v>0.1464139044516828</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.02130008953425185</v>
+        <v>-0.7287610982109907</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.5664860998088224</v>
+        <v>-0.7067296241237311</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.2636994440698359</v>
+        <v>-0.5452171819047679</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.5254543264419433</v>
+        <v>-0.9164079940508243</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.8419514746605052</v>
+        <v>-0.6663694859818471</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.819875174399046</v>
+        <v>2.284853062850626</v>
       </c>
       <c r="C10" t="n">
-        <v>1.339221377233877</v>
+        <v>-1.580132242261787</v>
       </c>
       <c r="D10" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.08249049901650093</v>
+        <v>0.4157521150431646</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2850805651294578</v>
+        <v>0.0007587433381137274</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8365115089431081</v>
+        <v>-0.398981295740146</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5666975692154377</v>
+        <v>0.197583511233232</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5667262495870146</v>
+        <v>-0.2261577487733106</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.00593696158772055</v>
+        <v>-1.09699838012138</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.21828189053924</v>
+        <v>-1.115567483805556</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3055348934460803</v>
+        <v>-0.5117419041327529</v>
       </c>
       <c r="M10" t="n">
-        <v>1.797087734723032</v>
+        <v>-0.2569450632345141</v>
       </c>
       <c r="N10" t="n">
-        <v>0.03056337224617514</v>
+        <v>-0.7084922145311433</v>
       </c>
       <c r="O10" t="n">
-        <v>2.265508374479858</v>
+        <v>-0.8715011182653473</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.477066477883453</v>
+        <v>-1.198448417529967</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.39663211624078</v>
+        <v>-1.023153441043382</v>
       </c>
       <c r="R10" t="n">
-        <v>2.218466315743146</v>
+        <v>-2.290747751290505</v>
       </c>
       <c r="S10" t="n">
-        <v>0.08247083545151267</v>
+        <v>-1.594089035719624</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.950889523447359</v>
+        <v>1.006813348194977</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1545,40 +1545,40 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2186230334351373</v>
+        <v>0.1815559611865851</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5735003482611793</v>
+        <v>-0.2371266325919222</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2643824171751997</v>
+        <v>0.09244121532969567</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.07505452411258119</v>
+        <v>0.5865725528055656</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.6831705516707842</v>
+        <v>0.3015154801366626</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.2796685578176172</v>
+        <v>1.577866769011878</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.601282477118947</v>
+        <v>-0.01693967663690086</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.4360545512506938</v>
+        <v>-0.58359022768378</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3166248481564672</v>
+        <v>-0.2446875955154684</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.05701702197165631</v>
+        <v>0.5195049221739381</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.219600671843542</v>
+        <v>0.9099508154151426</v>
       </c>
     </row>
     <row r="11">
@@ -1612,7 +1612,7 @@
         <v>-0.3261611359538926</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.00593696158772055</v>
+        <v>0.3577501779234991</v>
       </c>
       <c r="K11" t="n">
         <v>0.7557054488334223</v>
@@ -1688,333 +1688,6 @@
       </c>
       <c r="AI11" t="n">
         <v>0.3615377883314772</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>GdWtpsjm</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.306994867062606</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.013163700251244</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-0.5056960363928432</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.08359037233672091</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.2850805651294578</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.248342443837526</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.08329848985772981</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-0.08329576708676574</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.3577501779234991</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.8893678011647782</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.849279955539432</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.3592647761527498</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.079310452785065</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.6951676880997961</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4.214702469337768</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-1.380170982282029</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.588146069813711</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.7982875000831346</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-0.229525377923294</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-0.5017776204546213</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-0.7140346938312322</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.227905381925339</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.112949556931529</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.374526804225985</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-0.4841113211168335</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.242614982777913</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>-0.09301959257525098</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.384994448107078</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.515915624379784</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.782164020621224</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.986673560342574</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.033756567089463</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.284853062850626</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.5488800545957865</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.5056960363928432</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.5807331130761665</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-0.1887891378561156</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.01284963915427201</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-1.259550511304418</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.259606860766758</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-0.2483950545952004</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.626978381472402</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-1.78306136703316</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-0.873154902621778</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-2.298546892729021</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.09787520567308552</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-1.676079378135944</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-0.1107752801001733</v>
-      </c>
-      <c r="R13" t="n">
-        <v>-1.321024296014451</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-0.1962144594129164</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-1.531484965292775</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-1.623870137228588</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-1.542448947021387</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.1697074027330025</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.2045399705252551</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.1463367184841673</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>-0.4128214941249725</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>-0.8362586616820753</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-0.5650364329540472</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>-1.087009924725866</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-0.3674542166242922</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.3018583124556456</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>-0.0502779134264426</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>-0.9615727691070773</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>-0.459584837625255</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.3227106019491588</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.306994867062606</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.7477679166607292</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.5056960363928432</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.4146522417229446</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0.5678849002445744</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.8365115089431081</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.4309841063320289</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.4310073669847965</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.3696241010989402</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.6888742726677447</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-1.238210168647272</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.7700713357442589</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-0.9118181719443772</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.211678810198304</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-0.9994355172774767</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-0.1107752801001733</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.103284342175684</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-1.072724661002653</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.1823621621762601</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.01956258426656824</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.3920603146181926</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.6343394208020771</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>-0.3379815751701792</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>-0.3556690765831189</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.3934561822041817</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-0.2911470132533752</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.673480590037023</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-0.81654030991459</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>-0.6284842553397906</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>-0.5060466933800721</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>-0.3612504523555711</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>-0.4894530484796624</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -631,7 +631,7 @@
         <v>0.9881690955623221</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7214373174347188</v>
+        <v>0.3577501779234991</v>
       </c>
       <c r="K2" t="n">
         <v>-2.118035126290724</v>
@@ -740,7 +740,7 @@
         <v>2.716799073969518</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.00593696158772055</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K3" t="n">
         <v>0.4883807441707113</v>
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3475857098672203</v>
+        <v>0.2672594439631747</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -782,40 +782,40 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6807332188200748</v>
+        <v>-0.6511332976020074</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.8701065909899082</v>
+        <v>-0.8380628815199308</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.7509475345555396</v>
+        <v>-0.7462211998898086</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6729028804921667</v>
+        <v>0.7264370324897855</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.6901521364372395</v>
+        <v>-0.6983482706504497</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7518281675642007</v>
+        <v>0.7169792353139992</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.8582048621317191</v>
+        <v>-0.8587870763538104</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.9108574824060434</v>
+        <v>-0.8911888834361302</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1.000037850092813</v>
+        <v>-0.9548004899935344</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.6988965404837661</v>
+        <v>-0.6826447986017478</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.1288384201606826</v>
+        <v>-0.07837684174017948</v>
       </c>
     </row>
     <row r="4">
@@ -849,7 +849,7 @@
         <v>-1.026184846217963</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7214373174347188</v>
+        <v>0.3577501779234991</v>
       </c>
       <c r="K4" t="n">
         <v>-1.449723364633946</v>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2743799435991416</v>
+        <v>-0.2389150108989685</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -891,40 +891,40 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8490002118884644</v>
+        <v>0.8113154887454634</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1625254153321321</v>
+        <v>0.1597030723783048</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2946796226607982</v>
+        <v>0.2800619436210887</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.262750238100831</v>
+        <v>-1.241446198670928</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2942984507221931</v>
+        <v>0.290689395336139</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.242859600039654</v>
+        <v>-1.177236800135459</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.7159136129061993</v>
+        <v>0.697501140277962</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.156661699528542</v>
+        <v>1.130041371665526</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.6180462744656475</v>
+        <v>0.6094733697836903</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.5257674529823637</v>
+        <v>0.5250776987150024</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.2874715623842767</v>
+        <v>-0.3034301558698549</v>
       </c>
     </row>
     <row r="5">
@@ -958,7 +958,7 @@
         <v>0.1881419981176697</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.09699838012138</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K5" t="n">
         <v>2.025497795981301</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4169369600566863</v>
+        <v>0.4207044433334404</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1000,40 +1000,40 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9725917416308026</v>
+        <v>-0.9711956123770161</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.168642878603107</v>
+        <v>-1.190075516432396</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.976495034282877</v>
+        <v>-1.978765600372518</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.9185819453044918</v>
+        <v>0.8374974271968485</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.098400105544104</v>
+        <v>-1.100352901897457</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8718523632659246</v>
+        <v>0.8977699842028276</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1.434702995297684</v>
+        <v>-1.436057152851439</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.631053414344164</v>
+        <v>-1.62449927758833</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2.387460148101102</v>
+        <v>-2.368577398537371</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1.191253391603176</v>
+        <v>-1.186596345965637</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.496557255898384</v>
+        <v>0.4744285017267756</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.945530508210769</v>
+        <v>1.908435544065582</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1112,28 +1112,28 @@
         <v>0.2424379538802464</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5712281734427883</v>
+        <v>0.5867746884071927</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2624981968318468</v>
+        <v>0.2629222160887347</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01348056250270403</v>
+        <v>0.02690666352713193</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6800615870793432</v>
+        <v>0.6783278382798115</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2698113642809596</v>
+        <v>0.2461660593509097</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.6014205781725875</v>
+        <v>0.6113370010520449</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.4930506304477362</v>
+        <v>0.4936462747026125</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.3189451801183033</v>
+        <v>0.3205152098664832</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1142,7 +1142,7 @@
         <v>0.05189313312839831</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.187319905143335</v>
+        <v>0.1829482392693088</v>
       </c>
     </row>
     <row r="7">
@@ -1176,7 +1176,7 @@
         <v>0.04528001643112482</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3577501779234991</v>
+        <v>-0.00593696158772055</v>
       </c>
       <c r="K7" t="n">
         <v>1.023030153496134</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8952897172140631</v>
+        <v>0.8538069696419497</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1218,40 +1218,40 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.09661261977728121</v>
+        <v>0.05699945149273734</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5378720718932192</v>
+        <v>0.4818119088798505</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.1247920918746</v>
+        <v>-0.1292364283292563</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.07037543388906171</v>
+        <v>0.04669829382479142</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.3174538438451184</v>
+        <v>-0.3254800483515897</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.6919786449539624</v>
+        <v>-0.7064670199367209</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.1377125645074453</v>
+        <v>-0.1337248965835794</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1778820734161723</v>
+        <v>0.1669120078598607</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1466272267622667</v>
+        <v>0.1225240651350854</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.1775147568039087</v>
+        <v>-0.2011871232597601</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.198628000701595</v>
+        <v>1.275060523704955</v>
       </c>
     </row>
     <row r="8">
@@ -1318,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6394910798985689</v>
+        <v>-0.6014854437213822</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1327,40 +1327,40 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5529815697875613</v>
+        <v>-0.5463870679890579</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.117505938043629</v>
+        <v>-1.08791707451288</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.3667420551035191</v>
+        <v>-0.3654154478966917</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.9939233860245766</v>
+        <v>-0.9218074837508418</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.120213968780071</v>
+        <v>-1.123345845242083</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.3119597576373203</v>
+        <v>-0.3278219081560803</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.8679688783507051</v>
+        <v>-0.8559886119473976</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.6550898572667968</v>
+        <v>-0.676214366392401</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.315616688879101</v>
+        <v>-0.3203181539628553</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.6224106386443382</v>
+        <v>-0.6170817942473502</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.4182843526444291</v>
+        <v>0.4240184805353441</v>
       </c>
     </row>
     <row r="9">
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.002896673930777775</v>
+        <v>-0.04057885788516122</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1436,40 +1436,40 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.373612197603441</v>
+        <v>-0.4375009542270529</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.09300114676497309</v>
+        <v>-0.1105932684417849</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.6230049514231201</v>
+        <v>-0.6014326202163692</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8904822888764425</v>
+        <v>0.8503804877579645</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.7512218181239068</v>
+        <v>-0.7325433562531167</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1464139044516828</v>
+        <v>0.1185135146999321</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.7287610982109907</v>
+        <v>-0.6976001299131871</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.7067296241237311</v>
+        <v>-0.6990630287136493</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.5452171819047679</v>
+        <v>-0.5659843847949597</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.9164079940508243</v>
+        <v>-0.8841161079186479</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.6663694859818471</v>
+        <v>-0.6526268169841332</v>
       </c>
     </row>
     <row r="10">
@@ -1503,7 +1503,7 @@
         <v>-0.2261577487733106</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.09699838012138</v>
+        <v>-2.188059798655039</v>
       </c>
       <c r="K10" t="n">
         <v>-1.115567483805556</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.006813348194977</v>
+        <v>0.9647768112111327</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1545,40 +1545,40 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1815559611865851</v>
+        <v>0.1488230997717797</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.2371266325919222</v>
+        <v>-0.2415664043346972</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.09244121532969567</v>
+        <v>0.09075852484772395</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.5865725528055656</v>
+        <v>0.5155463768274725</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.3015154801366626</v>
+        <v>0.3037993236455854</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.577866769011878</v>
+        <v>1.636323042463826</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.01693967663690086</v>
+        <v>-0.02747627554428056</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.58359022768378</v>
+        <v>-0.5703888396940291</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.2446875955154684</v>
+        <v>-0.2367372465933022</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.5195049221739381</v>
+        <v>0.539004165827447</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.9099508154151426</v>
+        <v>0.9933017822906574</v>
       </c>
     </row>
     <row r="11">
@@ -1612,7 +1612,7 @@
         <v>-0.3261611359538926</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3577501779234991</v>
+        <v>0.7214373174347188</v>
       </c>
       <c r="K11" t="n">
         <v>0.7557054488334223</v>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,68 +603,68 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
+          <t>AVat9lPF</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2.306994867062606</v>
       </c>
       <c r="C2" t="n">
-        <v>1.809351051022789</v>
+        <v>0.7174369699646703</v>
       </c>
       <c r="D2" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E2" t="n">
-        <v>1.744399085868939</v>
+        <v>-0.9128948557826102</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9484981493092606</v>
+        <v>-0.5678849002445744</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.398981295740146</v>
+        <v>-1.222643165528982</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9881235855376008</v>
+        <v>-2.145259426964558</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9881690955623221</v>
+        <v>2.145351147223337</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3577501779234991</v>
+        <v>-0.00593696158772055</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.118035126290724</v>
+        <v>2.493316029141046</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.601444300904531</v>
+        <v>-5.778636821863012</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2569450632345141</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.140274303869359</v>
+        <v>-1.307047280174597</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3941567163259672</v>
+        <v>0.1811044860112334</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8004226170249864</v>
+        <v>-0.08397617611602159</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7619342651498524</v>
+        <v>0.9999459593089504</v>
       </c>
       <c r="R2" t="n">
-        <v>1.297229033230895</v>
+        <v>1.006311996648079</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6474266096172088</v>
+        <v>0.5757887566026647</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4701050317758135</v>
+        <v>-0.8040940500030912</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -673,107 +673,107 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1229525076272047</v>
+        <v>-0.6960018213942748</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.8096691283162128</v>
+        <v>-0.04742177523387121</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.6491528019990116</v>
+        <v>-0.4921937468314255</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.3419509859573793</v>
+        <v>0.1541106524460637</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.5518342018918595</v>
+        <v>-0.614423037758228</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.4490690079968753</v>
+        <v>0.5315540366788282</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.261122798888482</v>
+        <v>-0.8988791696291357</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.6799947762572944</v>
+        <v>-0.5193785194720308</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.037461576682892</v>
+        <v>-0.4520909557172059</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.4471793334147453</v>
+        <v>-0.678396788193235</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.1963233058739764</v>
+        <v>-0.1075942384098288</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>Wplk7SgS</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.819875174399046</v>
       </c>
       <c r="C3" t="n">
-        <v>1.452962427344097</v>
+        <v>-1.140333515168934</v>
       </c>
       <c r="D3" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4157521150431646</v>
+        <v>1.578318214515718</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.09401519725900095</v>
+        <v>1.13804603050349</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01284963915427201</v>
+        <v>1.660173378731944</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.716684533842068</v>
+        <v>0.9404361501739944</v>
       </c>
       <c r="I3" t="n">
-        <v>2.716799073969518</v>
+        <v>-0.9404676572060362</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.73331124061016</v>
+        <v>-0.3696241010989402</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4883807441707113</v>
+        <v>-2.318528654787757</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.419827234775901</v>
+        <v>-0.8749760363900121</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.078558182417533</v>
+        <v>-0.873154902621778</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.185965530254356</v>
+        <v>1.58520734999568</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3721254362364578</v>
+        <v>-1.742960641805958</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.556671637984449</v>
+        <v>0.2742470443384608</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.555306579013512</v>
+        <v>-1.975200217679774</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2543284952107916</v>
+        <v>-0.7391902228488183</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.127974769863544</v>
+        <v>2.467028076186675</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2672594439631747</v>
+        <v>-0.32623862891205</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -782,107 +782,107 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6511332976020074</v>
+        <v>0.5534124206403654</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.8380628815199308</v>
+        <v>0.1741647135018973</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.7462211998898086</v>
+        <v>0.5553094612112712</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7264370324897855</v>
+        <v>-0.6407477249523783</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.6983482706504497</v>
+        <v>0.6225739413630383</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7169792353139992</v>
+        <v>-0.577674383217211</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.8587870763538104</v>
+        <v>0.5842730306789069</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.8911888834361302</v>
+        <v>0.6240670609108796</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.9548004899935344</v>
+        <v>0.4714776703088335</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.6826447986017478</v>
+        <v>0.653551547523391</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.07837684174017948</v>
+        <v>-0.7831394207135323</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>tzSnG5Wr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.284853062850626</v>
+        <v>2.329136671274586</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.284405511975214</v>
+        <v>0.6112786565284644</v>
       </c>
       <c r="D4" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E4" t="n">
-        <v>1.744399085868939</v>
+        <v>-0.2485713703697228</v>
       </c>
       <c r="F4" t="n">
-        <v>2.085785436474636</v>
+        <v>0.1903066245323431</v>
       </c>
       <c r="G4" t="n">
-        <v>2.48383524852078</v>
+        <v>0.8365115089431081</v>
       </c>
       <c r="H4" t="n">
-        <v>1.026149916205621</v>
+        <v>1.069006799221434</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.026184846217963</v>
+        <v>-1.069043440723927</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3577501779234991</v>
+        <v>0.9638954104421987</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.449723364633946</v>
+        <v>-0.7145804268114895</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0331092942531361</v>
+        <v>1.849279955539432</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2569450632345141</v>
+        <v>0.6673696958463817</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5485729221836555</v>
+        <v>1.170559470551837</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5091257673439357</v>
+        <v>-1.801710722044651</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2742470443384608</v>
+        <v>1.408620575777655</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.436300731933963</v>
+        <v>-0.9041475939638333</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.030107259431635</v>
+        <v>-1.175565777723043</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9567335749858984</v>
+        <v>0.3157386679472506</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2389150108989685</v>
+        <v>-1.058061359911954</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -891,50 +891,50 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8113154887454634</v>
+        <v>2.086407385872663</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1597030723783048</v>
+        <v>1.280388572478917</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2800619436210887</v>
+        <v>2.235337962755946</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.241446198670928</v>
+        <v>0.2020061530203048</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.290689395336139</v>
+        <v>1.58262059581514</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.177236800135459</v>
+        <v>0.05639822349120148</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.697501140277962</v>
+        <v>1.739684809570255</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.130041371665526</v>
+        <v>1.541521469348164</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.6094733697836903</v>
+        <v>2.556695498984435</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.5250776987150024</v>
+        <v>2.516849658795672</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.3034301558698549</v>
+        <v>-0.3237900633474396</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>INsZAAf3</t>
+          <t>beYTapn2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.240569454426666</v>
+        <v>2.329136671274586</v>
       </c>
       <c r="C5" t="n">
         <v>-0.874937731578419</v>
@@ -943,55 +943,55 @@
         <v>-0.5056960363928432</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.245056598489054</v>
+        <v>0.08359037233672091</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.273815830992639</v>
+        <v>-0.09401519725900095</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6344741004234</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1881284359090871</v>
+        <v>0.3975822986403599</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1881419981176697</v>
+        <v>-0.3975921267971647</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.73331124061016</v>
+        <v>0.9638954104421987</v>
       </c>
       <c r="K5" t="n">
-        <v>2.025497795981301</v>
+        <v>-0.8482427791428453</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.056593102518642</v>
+        <v>1.849279955539432</v>
       </c>
       <c r="M5" t="n">
-        <v>2.207894294314541</v>
+        <v>-1.283961462213287</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4937434505216594</v>
+        <v>1.448133670840691</v>
       </c>
       <c r="O5" t="n">
-        <v>1.074595289641354</v>
+        <v>1.040324409502117</v>
       </c>
       <c r="P5" t="n">
-        <v>1.189706385499916</v>
+        <v>0.3936547844899549</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.118951806388499</v>
+        <v>-1.062822056736565</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.157356149683186</v>
+        <v>-1.514968987069662</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4203987994349035</v>
+        <v>0.5023716627942935</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4207044433334404</v>
+        <v>0.4743276760403225</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1000,107 +1000,107 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9711956123770161</v>
+        <v>-0.4177136962080822</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.190075516432396</v>
+        <v>0.08780622629409293</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.978765600372518</v>
+        <v>0.20460767663572</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.8374974271968485</v>
+        <v>0.369716282219115</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1.100352901897457</v>
+        <v>0.2048500044521767</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8977699842028276</v>
+        <v>-0.4591803421395654</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1.436057152851439</v>
+        <v>0.4501692353133167</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.62449927758833</v>
+        <v>0.02893972834318061</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2.368577398537371</v>
+        <v>0.1452602237175339</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1.186596345965637</v>
+        <v>-0.1274657492249304</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.4744285017267756</v>
+        <v>0.9104474471340056</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>2TvL16Hk</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.819875174399046</v>
+        <v>2.329136671274586</v>
       </c>
       <c r="C6" t="n">
-        <v>1.816933787696803</v>
+        <v>1.809351051022789</v>
       </c>
       <c r="D6" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.08249049901650093</v>
+        <v>-0.4146522417229446</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2850805651294578</v>
+        <v>-0.09401519725900095</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8365115089431081</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5666975692154377</v>
+        <v>-0.3309847126284649</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5667262495870146</v>
+        <v>0.3310039798042151</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7214373174347188</v>
+        <v>0.3577501779234991</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.21828189053924</v>
+        <v>-1.048736307639879</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3055348934460803</v>
+        <v>0.2147263603817656</v>
       </c>
       <c r="M6" t="n">
-        <v>1.797087734723032</v>
+        <v>-2.72178442078357</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03056337224617514</v>
+        <v>1.873062076221158</v>
       </c>
       <c r="O6" t="n">
-        <v>2.265508374479858</v>
+        <v>-1.214209919657722</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.477066477883453</v>
+        <v>0.5130625246414491</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.39663211624078</v>
+        <v>1.079283190695316</v>
       </c>
       <c r="R6" t="n">
-        <v>2.218466315743146</v>
+        <v>0.5214502690100516</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08247083545151267</v>
+        <v>1.46578373052455</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908435544065582</v>
+        <v>-0.3537412568323475</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1109,107 +1109,107 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2424379538802464</v>
+        <v>0.5879657662587784</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5867746884071927</v>
+        <v>0.6221597898185988</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2629222160887347</v>
+        <v>0.228764854825399</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02690666352713193</v>
+        <v>-0.7212179343653994</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6783278382798115</v>
+        <v>0.7786698718915479</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2461660593509097</v>
+        <v>-0.05468370171584776</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.6113370010520449</v>
+        <v>1.055322298154984</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.4936462747026125</v>
+        <v>1.496859968419069</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.3205152098664832</v>
+        <v>0.3895094074370123</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.05189313312839831</v>
+        <v>0.4832391755833244</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.1829482392693088</v>
+        <v>-1.447723566971047</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2Fanm72d</t>
+          <t>AiyHLR8L</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.306994867062606</v>
+        <v>2.240569454426666</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.019009728384699</v>
+        <v>1.816933787696803</v>
       </c>
       <c r="D7" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7468139844293883</v>
+        <v>0.9139947291028302</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2835630784532303</v>
+        <v>0.5694023869208018</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01284963915427201</v>
+        <v>1.248342443837526</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.002415276173896646</v>
+        <v>2.48328393874327</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04528001643112482</v>
+        <v>-2.483377059420723</v>
       </c>
       <c r="J7" t="n">
         <v>-0.00593696158772055</v>
       </c>
       <c r="K7" t="n">
-        <v>1.023030153496134</v>
+        <v>1.290354858158845</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9411946248962842</v>
+        <v>0.2147263603817656</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.873154902621778</v>
+        <v>-0.2569450632345141</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8404403599202378</v>
+        <v>1.749695764981668</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.405147680433473</v>
+        <v>0.3353234466378023</v>
       </c>
       <c r="P7" t="n">
-        <v>2.304178626913861</v>
+        <v>1.826547666307884</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.133874680452506</v>
+        <v>-0.9041475939638333</v>
       </c>
       <c r="R7" t="n">
-        <v>-2.872581824456137</v>
+        <v>0.7153949600652626</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.293604481811779</v>
+        <v>-0.1400279080289572</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8538069696419497</v>
+        <v>-0.5465904556840403</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1218,107 +1218,107 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.05699945149273734</v>
+        <v>0.8180988221790749</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4818119088798505</v>
+        <v>0.8424304134054785</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.1292364283292563</v>
+        <v>1.541254666826195</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.04669829382479142</v>
+        <v>-0.4094449510052436</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.3254800483515897</v>
+        <v>1.584643386674197</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.7064670199367209</v>
+        <v>0.3969036980604402</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.1337248965835794</v>
+        <v>1.467812882747153</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1669120078598607</v>
+        <v>1.100510089002417</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1225240651350854</v>
+        <v>1.603900222146725</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.2011871232597601</v>
+        <v>1.7427764514035</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.275060523704955</v>
+        <v>-0.536318837187556</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>jkLFNmv9</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.819875174399046</v>
+        <v>2.329136671274586</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6112786565284644</v>
+        <v>1.824516524370818</v>
       </c>
       <c r="D8" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7468139844293883</v>
+        <v>-1.078975727135832</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1887891378561156</v>
+        <v>-0.9469806626330332</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.398981295740146</v>
+        <v>0.01284963915427201</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2166996912529628</v>
+        <v>1.497575629379566</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2167143944549789</v>
+        <v>-1.497629385783562</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.73331124061016</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.115567483805556</v>
+        <v>-0.1130998413203891</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6933589702613824</v>
+        <v>0.2147263603817656</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3592647761527498</v>
+        <v>-0.2569450632345141</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3132631063009232</v>
+        <v>-0.3886536298361674</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1125627257327581</v>
+        <v>-1.45655400064233</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1237787561665195</v>
+        <v>1.229508965550414</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4049167239112055</v>
+        <v>-2.094206064759323</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.2543284952107916</v>
+        <v>-1.321024296014451</v>
       </c>
       <c r="S8" t="n">
-        <v>2.467028076186675</v>
+        <v>-0.8704530760204054</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6014854437213822</v>
+        <v>0.521065603334313</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1327,107 +1327,107 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5463870679890579</v>
+        <v>-0.9405165002092605</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.08791707451288</v>
+        <v>-0.08839387932176247</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.3654154478966917</v>
+        <v>-0.2712857216970603</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.9218074837508418</v>
+        <v>0.1268924262222119</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.123345845242083</v>
+        <v>-0.480100806905588</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.3278219081560803</v>
+        <v>-0.5040581898684269</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.8559886119473976</v>
+        <v>-0.3786183441619875</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.676214366392401</v>
+        <v>-0.463821920945853</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.3203181539628553</v>
+        <v>-0.3453426632135403</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.6170817942473502</v>
+        <v>-0.7866711285395339</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.4240184805353441</v>
+        <v>0.301620235481002</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>lpob9cJb</t>
+          <t>2kGeEq1e</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.908442391246966</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.639872894683963</v>
+        <v>-0.2379878509611833</v>
       </c>
       <c r="D9" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08359037233672091</v>
+        <v>-2.241541826608385</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1903066245323431</v>
+        <v>-2.747685533978212</v>
       </c>
       <c r="G9" t="n">
         <v>-0.398981295740146</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08329848985772981</v>
+        <v>1.926144459537699</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08329576708676574</v>
+        <v>-1.926215330843197</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.8545402871138997</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5809180744801336</v>
+        <v>1.490848386655879</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5117419041327529</v>
+        <v>-0.3301248380041233</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6677516228260235</v>
+        <v>0.05115985645911786</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3315395968549221</v>
+        <v>-1.039753605822368</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4626984766044422</v>
+        <v>0.228838926205172</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0441735960655237</v>
+        <v>-1.098941967403722</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1107752801001733</v>
+        <v>0.7619342651498524</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.12707960495924</v>
+        <v>1.733604588105119</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6232322499309956</v>
+        <v>-1.556490868418525</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.04057885788516122</v>
+        <v>-1.811701040277403</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1436,258 +1436,1130 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4375009542270529</v>
+        <v>-1.51365977998814</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.1105932684417849</v>
+        <v>-0.9319089498318246</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.6014326202163692</v>
+        <v>-1.025951902358735</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8503804877579645</v>
+        <v>0.08379080118722425</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.7325433562531167</v>
+        <v>-1.398547043237466</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1185135146999321</v>
+        <v>0.3053832501652823</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.6976001299131871</v>
+        <v>-1.744390434702799</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.6990630287136493</v>
+        <v>-1.245777089536098</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.5659843847949597</v>
+        <v>-1.027686684646</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.8841161079186479</v>
+        <v>-1.642186515806068</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.6526268169841332</v>
+        <v>-1.436685546775192</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.284853062850626</v>
+        <v>1.819875174399046</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.580132242261787</v>
+        <v>1.809351051022789</v>
       </c>
       <c r="D10" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4157521150431646</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0007587433381137274</v>
+        <v>0.9484981493092606</v>
       </c>
       <c r="G10" t="n">
         <v>-0.398981295740146</v>
       </c>
       <c r="H10" t="n">
-        <v>0.197583511233232</v>
+        <v>-0.9881235855376008</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2261577487733106</v>
+        <v>0.9881690955623221</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.188059798655039</v>
+        <v>0.3577501779234991</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.115567483805556</v>
+        <v>-2.118035126290724</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5117419041327529</v>
+        <v>-1.601444300904531</v>
       </c>
       <c r="M10" t="n">
         <v>-0.2569450632345141</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7084922145311433</v>
+        <v>-1.140274303869359</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8715011182653473</v>
+        <v>-0.3941567163259672</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.198448417529967</v>
+        <v>-0.8004226170249864</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.023153441043382</v>
+        <v>0.7619342651498524</v>
       </c>
       <c r="R10" t="n">
-        <v>-2.290747751290505</v>
+        <v>1.297229033230895</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.594089035719624</v>
+        <v>0.6474266096172088</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.389813307125638</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9647768112111327</v>
+        <v>0.440238122131837</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.951700556657758</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1488230997717797</v>
+        <v>0.000282688492269505</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.2415664043346972</v>
+        <v>-0.9110225122762541</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.09075852484772395</v>
+        <v>-0.6803161303133045</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.5155463768274725</v>
+        <v>0.2441885580556464</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.3037993236455854</v>
+        <v>-0.5839626451615743</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.636323042463826</v>
+        <v>-0.4646666769384636</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.02747627554428056</v>
+        <v>-0.2780639254951071</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.5703888396940291</v>
+        <v>-0.7166583427998342</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.2367372465933022</v>
+        <v>-1.110929020514369</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.539004165827447</v>
+        <v>-0.4706215315304951</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.9933017822906574</v>
+        <v>0.1949232004693471</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ERWFdKZh</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.819875174399046</v>
+        <v>2.218427650214686</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.140333515168934</v>
+        <v>-1.284405511975214</v>
       </c>
       <c r="D11" t="n">
         <v>-0.5056960363928432</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5807331130761665</v>
+        <v>1.744399085868939</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1903066245323431</v>
+        <v>2.085785436474636</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01284963915427201</v>
+        <v>2.48383524852078</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3261541602806716</v>
+        <v>1.026149916205621</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3261611359538926</v>
+        <v>-1.026184846217963</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7214373174347188</v>
+        <v>0.3577501779234991</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7557054488334223</v>
+        <v>-1.449723364633946</v>
       </c>
       <c r="L11" t="n">
         <v>0.0331092942531361</v>
       </c>
       <c r="M11" t="n">
+        <v>-0.2569450632345141</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.5485729221836555</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.5091257673439357</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.2742470443384608</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.436300731933963</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-1.030107259431635</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.9567335749858984</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.1646680233961529</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.8233609384332471</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.07807117111056669</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.2697091612539677</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-1.245784553644122</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.2811721567909154</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-1.137109336025501</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.68196477174342</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.07858125440876</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.5805525565662984</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.5182458469239922</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.2872271607057071</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.284853062850626</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.5488800545957865</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4157521150431646</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.09401519725900095</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.01284963915427201</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-2.716684533842068</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.716799073969518</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.73331124061016</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.4883807441707113</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-1.419827234775901</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-1.078558182417533</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-1.185965530254356</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.3721254362364578</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-1.556671637984449</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.555306579013512</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.2543284952107916</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-1.127974769863544</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.6281034726949558</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.2443825503880464</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.535179423768853</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.3883624280187282</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.5541054673190173</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.5911806803458056</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.7044516646301443</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.7736665238774026</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.6485907375747663</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.7740168848877085</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.8309175165010999</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.73839008997675</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.7718068116751305</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.1744813134386555</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.6240161238152263</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0.06830637874936167</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.908442391246966</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7174369699646703</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.245056598489054</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-2.273815830992639</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1.6344741004234</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.4309841063320289</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4310073669847965</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.00593696158772055</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.225991324478335</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1.419827234775901</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.591684454927278</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.4937434505216594</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.074595289641354</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.8712857450959318</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.39663211624078</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.2305332324272355</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.7626997563662814</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.04130478542983747</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.4019167787323301</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.001320755332439684</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.153655016518768</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.8840109407949988</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-1.050767103686291</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-1.947794033067518</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.768726630645673</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-1.083463391327554</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.9008801998769305</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-1.428194846139867</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-1.487838405458039</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-2.288468958651125</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.1744813134386555</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-1.17924234550203</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.428286588415913</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>SUdkBJln</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.329136671274586</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.528789794084245</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.7468139844293883</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.1887891378561156</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.398981295740146</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.02384371768180326</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.02385071917814306</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-1.717048069296657</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.8749760363900121</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.6673696958463817</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.3132631063009232</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.1125627257327581</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.2145431742627137</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1669050297521075</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.157356149683186</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.467028076186675</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1518937687990329</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.5658248361593966</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.70641588951207</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.5066249168984753</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-1.066061951076374</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.3340781372610259</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.8040066066649362</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1.054231306436361</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.4054567490135274</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.7999186251343018</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.6852737704641049</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.3316094702946379</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.5874600235234941</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.3213855493978516</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.306994867062606</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.286142220515774</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4157521150431646</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.0007587433381137274</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.398981295740146</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2690116495929202</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.2904456405322559</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-1.09699838012138</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.2133466055689058</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5779604926390248</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.565049982928146</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.7084922145311433</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.8715011182653473</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.7805213269997372</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.12232498027634</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-1.757399850888675</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-1.594089035719624</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.1832585583504674</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.10077376851825</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.08661148383299576</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-1.142222748981352</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.2022245933876207</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.2165706902104299</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.08231392630605211</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.6274933632477246</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.2904223161347999</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.597281380323901</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.05868327752663496</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.5815209574112622</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.2200086082369908</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.574547964463328</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.5138401783972256</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.8922042346124863</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.908442391246966</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.5488800545957865</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.7468139844293883</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.2835630784532303</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.01284963915427201</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.0881290422055231</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1167110072743976</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.3696241010989402</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.6220430965020671</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.7595775587676545</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.873154902621778</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.8404403599202378</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-1.405147680433473</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.985757986509876</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-2.014868833372957</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-2.484692442345715</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.09508159476213039</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.1223217715960128</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.9015060646207093</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.339165674231218</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.03331175414453413</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4140587904323121</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.1105790785687547</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.1551724439894184</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.2619828833520344</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.6227823737549354</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.1073830796367669</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.2468214452808533</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.1291299899886101</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.1577877847573656</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.380431515258615</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.284853062850626</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.6777865780540365</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.08359037233672091</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1903066245323431</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.398981295740146</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.7404373627668658</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.7404608828448729</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.73331124061016</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.848242779142845</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.7595775587676545</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-1.283961462213287</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.3315395968549221</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.4626984766044422</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.030496065297923</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.8248103625774671</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-1.902858369180083</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.6232322499309956</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.6921935736515604</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.1980192273255402</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.4178418882213444</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-1.142222748981352</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.5112128489398274</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.1573661416005957</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.6106431171092218</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.7568655079454988</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.7698632685114631</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.1299380397759477</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.7347339687809391</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.6805627027367595</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.5669403266253539</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.03447464833618678</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.8758495672515253</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.656935018613784</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.3062324810273157</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.08249049901650093</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2850805651294578</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.8365115089431081</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.8538386854213864</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8538788327769702</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.2365211314197594</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1.43635712940081</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.6207121438099308</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.180877895335768</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.03056337224617514</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.265508374479858</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-1.500948025913752</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.39663211624078</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.014824390135175</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.08247083545151267</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.4656053746830769</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.860940777749678</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.4198283901441195</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.005716133768708311</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.1952241766158424</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.6336533308373203</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.2672991073600202</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.0004517298043598279</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.6888375113743512</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.242094120391046</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.617005931268896</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.4961219062676149</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.3204063303659186</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-1.309589336647498</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.05701702197165631</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.3396241893241654</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ERWFdKZh</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.819875174399046</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.140333515168934</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.5056960363928432</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.5807331130761665</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1903066245323431</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.01284963915427201</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3261541602806716</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.3261611359538926</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.7214373174347188</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.7557054488334223</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0331092942531361</v>
+      </c>
+      <c r="M19" t="n">
         <v>0.1538614963569951</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N19" t="n">
         <v>1.274507010577705</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O19" t="n">
         <v>-0.7613447178177976</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P19" t="n">
         <v>1.866350246358383</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q19" t="n">
         <v>-1.023153441043382</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R19" t="n">
         <v>-0.5452455317936075</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S19" t="n">
         <v>-0.6799806668287885</v>
       </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.3409037872914117</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.7972447614910744</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.535207096911997</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.9121732020868</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.4744636595110804</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.53847486593972</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-0.9361513135142352</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.389956016169642</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.9215427708880453</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.956661808702626</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.034230394699082</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0.3615377883314772</v>
+      <c r="T19" t="n">
+        <v>1.017421832515082</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.451351541442278</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.178822454519457</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.8623872711604961</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.618650836518227</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.932999652472629</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.5093200654408073</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.621161383462526</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.7511666545161516</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.377332716735324</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.9917130904469338</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.961313889856289</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.080570750510676</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.3984800094151731</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR4"/>
+  <dimension ref="A1:AR11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,23 +648,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
+          <t>Of1jzRNE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.657796090425802</v>
+        <v>2.110137135281201</v>
       </c>
       <c r="C2" t="n">
-        <v>1.232831467233894</v>
+        <v>0.8048581496348093</v>
       </c>
       <c r="D2" t="n">
-        <v>0.968600002084375</v>
+        <v>1.191068017789394</v>
       </c>
       <c r="E2" t="n">
-        <v>1.887059660161394</v>
+        <v>-0.6164493509184055</v>
       </c>
       <c r="F2" t="n">
-        <v>1.389715865143474</v>
+        <v>-1.682587556542661</v>
       </c>
       <c r="G2" t="n">
         <v>-1.279685172938755</v>
@@ -673,134 +673,134 @@
         <v>-0.3132809482641702</v>
       </c>
       <c r="I2" t="n">
-        <v>2.584013175570051</v>
+        <v>-0.6294898339650484</v>
       </c>
       <c r="J2" t="n">
-        <v>1.378499138174724</v>
+        <v>-0.5394341446869493</v>
       </c>
       <c r="K2" t="n">
         <v>0.5703738274607163</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4632483075206663</v>
+        <v>-0.9520957700696422</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7597797568851032</v>
+        <v>1.468928789457125</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.01163654860575624</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.6720335887753767</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.905375120527948</v>
+        <v>2.248621059894748</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2641738093171058</v>
+        <v>-1.182327429948929</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.251825050185972</v>
+        <v>0.2551437201045104</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2449439366166656</v>
+        <v>2.366827637378504</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.338246676366624</v>
+        <v>-0.4360071316800554</v>
       </c>
       <c r="U2" t="n">
-        <v>1.132290739202736</v>
+        <v>-0.9476638637035484</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2869816459223639</v>
+        <v>1.204950990929497</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3257344836593545</v>
+        <v>-0.8267020277297294</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3254682046487311</v>
+        <v>0.5842746413465848</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6423058432822484</v>
+        <v>0.1723237381430421</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.4718315325092008</v>
+        <v>0.446314019748938</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.124107399031778</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4515378173952356</v>
+        <v>-1.871673069196926</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.01430939414740996</v>
+        <v>-0.06794463077870186</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.065504881876984</v>
+        <v>-0.2680413963941892</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.085027257179812</v>
+        <v>-0.8089333178585248</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2340837789082178</v>
+        <v>0.6093693396353648</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.7634627714836524</v>
+        <v>-0.7287394629021695</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.466409224605132</v>
+        <v>0.1938305087900518</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.3384914456384587</v>
+        <v>-0.5984833601348553</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.7693580729243445</v>
+        <v>-0.5946051463351916</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1.633433560965757</v>
+        <v>-1.03938448320567</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.7185789625858645</v>
+        <v>-0.2832487862151032</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.1857095138670624</v>
+        <v>-0.6782847719659658</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.09741365418519</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.101002916788756</v>
+        <v>-0.140825178037277</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>AFJ3CNV7</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.045516986016144</v>
+        <v>1.657796090425802</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.483868722742907</v>
+        <v>-0.01387341446778834</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.121672395477362</v>
+        <v>0.7136887340890412</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.397286566592812</v>
+        <v>0.5427316702889614</v>
       </c>
       <c r="F3" t="n">
-        <v>1.893765645263856</v>
+        <v>1.885764855103215</v>
       </c>
       <c r="G3" t="n">
         <v>-1.279685172938755</v>
@@ -809,134 +809,134 @@
         <v>-0.3132809482641702</v>
       </c>
       <c r="I3" t="n">
-        <v>2.584013175570051</v>
+        <v>0.7477257415499943</v>
       </c>
       <c r="J3" t="n">
-        <v>3.022441952056158</v>
+        <v>-1.772391255098025</v>
       </c>
       <c r="K3" t="n">
-        <v>2.083293717625351</v>
+        <v>-0.9425460627039185</v>
       </c>
       <c r="L3" t="n">
-        <v>2.958683930322165</v>
+        <v>-1.440943232618618</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6763504589354538</v>
+        <v>-0.9922355000575376</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.01163654860575624</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.01596582912758409</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9084160372265007</v>
+        <v>-0.576096342792685</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9070632489908989</v>
+        <v>2.514286848175381</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.251825050185972</v>
+        <v>1.762112490394993</v>
       </c>
       <c r="S3" t="n">
         <v>0.2449439366166656</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.338246676366624</v>
+        <v>0.4662324130065134</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9011846722131488</v>
+        <v>0.2078664712443873</v>
       </c>
       <c r="V3" t="n">
         <v>0.2869816459223639</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.828637115870479</v>
+        <v>1.17716814855177</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3254682046487311</v>
+        <v>-0.7097575421426838</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.656514865307417</v>
+        <v>0.6896989967416648</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6686773956864558</v>
+        <v>1.486400778166364</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.1547690551312663</v>
+        <v>0.6499369420233946</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.177015801175548</v>
+        <v>-0.4403468155421384</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.1021665297831843</v>
+        <v>-0.4605356554329831</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4271415023310451</v>
+        <v>-1.609529710331993</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1.263134223778247</v>
+        <v>-0.2481145339716823</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.3650540418904089</v>
+        <v>-0.7704665506796742</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.136030041336435</v>
+        <v>0.3753818145944341</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8091787873101924</v>
+        <v>-0.5931655924787342</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.191258484675006</v>
+        <v>-0.3435321615527617</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8708665010221186</v>
+        <v>-1.286851721675981</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.7904153795937542</v>
+        <v>-0.857913743634322</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.3106107951965051</v>
+        <v>1.805680453081268</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.140825178037277</v>
+        <v>7.101002916788756</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>AVat9lPF</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.110137135281201</v>
+        <v>2.045516986016144</v>
       </c>
       <c r="C4" t="n">
-        <v>1.163053208929696</v>
+        <v>-0.292986447684583</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.01860181760664507</v>
+        <v>-1.47854817067083</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6164493509184055</v>
+        <v>1.331618754166197</v>
       </c>
       <c r="F4" t="n">
-        <v>1.341711124179628</v>
+        <v>1.693745891247831</v>
       </c>
       <c r="G4" t="n">
         <v>-1.279685172938755</v>
@@ -945,111 +945,1063 @@
         <v>-0.3132809482641702</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7477257415499943</v>
+        <v>-1.088561692470063</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1284484412165907</v>
+        <v>-0.8134246136671882</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5703738274607163</v>
+        <v>-0.9425460627039185</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02559915502830965</v>
+        <v>-1.440943232618618</v>
       </c>
       <c r="M4" t="n">
-        <v>4.430668866669684</v>
+        <v>2.094648524079496</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.01163654860575624</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.01596582912758409</v>
       </c>
       <c r="P4" t="n">
-        <v>1.085502129376393</v>
+        <v>2.08246121267784</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.549952688664692</v>
+        <v>-1.664494509704273</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2471792033256505</v>
+        <v>-5.270408437627259</v>
       </c>
       <c r="S4" t="n">
         <v>-0.8159979137642533</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.142725765739762</v>
+        <v>0.01511264066322896</v>
       </c>
       <c r="U4" t="n">
+        <v>0.9011846722131488</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.204950990929497</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-2.329604659940854</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.8430810780444385</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.282113414984361</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.8704183617588024</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-1.261592241329611</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-1.206929567314803</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-1.184773491770841</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-1.025565829246761</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.1803290434281311</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.9037403401266219</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.020636615795931</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-1.237561326871378</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.9135952229610325</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-1.985321595228662</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.5261036625523962</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.07569770723387104</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.140825178037277</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.13167718503622</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.09777179881892951</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.55623285556044</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.7532971103664974</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.51772850771373</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1.279685172938755</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.3132809482641702</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.354477246317544</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.652489607154963</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.326833772543033</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.980989005224213</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.9922355000575376</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.01163654860575624</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01596582912758409</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-2.570014509395579</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5856185291540024</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.2471792033256505</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-1.876939764145172</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.2104472455084132</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.4854517297243741</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.2869816459223639</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.6762006044813952</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-1.227370415538391</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.490638828199461</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.708764154103882</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.2654207960471424</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.1409472050252899</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1807907364963402</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.9009502417092755</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-1.159681720104228</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.8484180093670577</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.7864948308121008</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.9090091855750654</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.052049582851997</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.5052371312394419</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.9285170109150007</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1.157467738430226</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.140825178037277</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2TvL16Hk</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.153217234791239</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.632729007125197</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.534039542001297</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7600781117653427</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.7144919471051028</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.279685172938755</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.3132809482641702</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.3999539047125413</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.1284484412165907</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5929211609858042</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.01163654860575624</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01596582912758409</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.9084160372265007</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.871397408501588</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.259789566964832</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-2.937881614526091</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.4662324130065134</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.9011846722131488</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-2.466926389099036</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.17716814855177</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.3254682046487311</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.016707293605304</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.663492068209806</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.4695281549316462</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.2844091591965651</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.453047591554368</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.2867421918909842</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.7966674063524436</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.6480489594596943</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.566445926180045</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.8163791379050208</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.528569405741271</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.5904644527463683</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.883959770937721</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-1.200251716222809</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.140825178037277</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>beYTapn2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.110137135281201</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.121021779561074</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.5284243535973128</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9130256076190926</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.218541727225484</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.279685172938755</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.3132809482641702</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.28865388304498</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.1284484412165907</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.5703738274607163</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.02559915502830965</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.324801116460341</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5973157515782835</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.984169108070962</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.576096342792685</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.02160507003048</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.7574666435346712</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.8159979137642533</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.3534524699206922</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.7165577967139612</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-1.089972371588336</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.576218255694542</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-1.227370415538391</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.35846905111342</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.6514621665816178</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.811902464252647</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.301405235492449</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.3380247444387757</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.3458712044194835</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.698880161419096</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.4097145819608172</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.4916086248734877</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.5557034285326682</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0.1068769735874986</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.1993887895702544</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0.1465906560971184</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.101935880688906</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.140825178037277</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.743956289445878</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.437349883873441</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.001168886970477</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.041823498864356</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6696447506857863</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.279685172938755</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.3132809482641702</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-1.31809762172257</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1.361405551627666</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.1860861176216011</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.02559915502830965</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.9922355000575376</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.01163654860575624</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.01596582912758409</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.9084160372265007</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.228507968827795</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.2471792033256505</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.305885786997584</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.4360071316800554</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.4854517297243741</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.2869816459223639</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.17716814855177</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.360693951440146</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.3579469225257533</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.7934878066965475</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.6333131871615887</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-1.62409675182772</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.8743244228253929</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.6343898122024878</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.1644052764921492</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.9396351190443213</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0.5317821840560492</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.6952436107473039</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.9603103899659037</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-1.009722153048314</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-1.392282072941827</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.5309060837446213</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.140825178037277</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.743956289445878</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9397627823562601</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.07409318893711268</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.4219836472465274</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1.378557530438304</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1.279685172938755</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.3132809482641702</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.436333529307515</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8305182002142457</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.326833772543033</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.492141542675237</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-2.076816373402982</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.01163654860575624</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01596582912758409</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.9084160372265007</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-2.307383949378067</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.7574666435346712</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2449439366166656</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.338246676366624</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.363396806192323</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.2869816459223639</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.3257344836593545</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.8430810780444385</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.6595397172674882</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.0797068695656193</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.03736550588575903</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.343083073283596</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.8983486383083963</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.898627707937143</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.2448173470602047</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2.413310246744111</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.8124322165569405</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.854857187651813</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.030223352581328</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2.068334631763675</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2.965009845050847</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.7604653294292143</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.140825178037277</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.657796090425802</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.214068895992594</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.784316059669443</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.7278786389540269</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.090529084655229</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.279685172938755</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.3132809482641702</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.1704179754600342</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.2825372622537677</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5703738274607163</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.003294080126262</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.8253769041582385</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5973157515782835</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.01596582912758409</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.2437766483588693</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.217993270438239</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.264435413825153</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2449439366166656</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.01511264066322896</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-1.178769930693136</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-1.089972371588336</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.07525071162416712</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-1.486176852236245</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.7752699682656106</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.758175828286425</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-1.422755703268377</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.686674431398808</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.610364552319731</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.25276165920107</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.9212634150228998</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.722157938283952</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0.4557982438805043</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.941118525441215</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.274280010852006</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>3.557429301389956</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>3.744821272856971</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.6272492585200362</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.140825178037277</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>2kGeEq1e</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.657796090425802</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1861575926709145</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.260589272697212</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.387967831586</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.885764855103215</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.279685172938755</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.3132809482641702</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-2.924849126490119</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-3.964315006939936</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.9425460627039185</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.4632483075206663</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1.367667340830961</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1.159721857339298</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.01596582912758409</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.417821823810209</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.067785608909347</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-1.251825050185972</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.8159979137642533</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1.451026619452445</v>
+      </c>
+      <c r="U11" t="n">
         <v>3.21224534210902</v>
       </c>
-      <c r="V4" t="n">
-        <v>-0.6309876990847695</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-2.830572204011229</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.360693951440146</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-0.08965508236872789</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.3674108863517552</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.067941711850249</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.2552287204406686</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-0.2591731906704842</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-0.768836875102835</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-0.6879166213601671</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-1.123444130195705</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.7661362946410529</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-0.8477662681641442</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.7670763181886671</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.5297059155578386</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-0.9994025323605893</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-0.7930917424617557</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-1.131350783284361</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.4161168259324937</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-0.9526564303251468</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-0.08525613633820349</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.660897564936817</v>
-      </c>
-      <c r="AR4" t="n">
+      <c r="V11" t="n">
+        <v>0.2869816459223639</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-1.327669571800104</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.913532571627268</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.3579469225257533</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.8982137837509938</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.8150894990122997</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-2.184237182206369</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-1.500006966533355</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-1.935516404421287</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0.6431344864019225</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-2.032710955949264</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.04353715800248755</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-1.993703747998268</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.806694891140075</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-1.33580173668307</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-3.08298842632459</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1.552276408803962</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
         <v>-0.140825178037277</v>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,165 +558,1641 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>KQ2pRs2b</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7452584333242087</v>
+        <v>-0.3485507806198666</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.565951156290596</v>
+        <v>0.5151213528494731</v>
       </c>
       <c r="D2" t="n">
         <v>-0.5328126607276883</v>
       </c>
       <c r="E2" t="n">
-        <v>0.170202857240616</v>
+        <v>-1.604052725628204</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.17018541146392</v>
+        <v>1.620655073718171</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09423190558561799</v>
+        <v>1.484909872403188</v>
       </c>
       <c r="H2" t="n">
-        <v>1.586626336198689</v>
+        <v>-0.7198796908421838</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5131887845823978</v>
+        <v>-0.6413623548724668</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01464091058055621</v>
+        <v>0.3326984556612403</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5095104622493165</v>
+        <v>0.9377632156009559</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.011776768369592</v>
+        <v>-0.1649071269397591</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2157232168650701</v>
+        <v>0.5490992580617047</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0812885555756799</v>
+        <v>-0.1747971267275074</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5858805675132868</v>
+        <v>0.4369015960569334</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4559779675500121</v>
+        <v>0.7583988864280905</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3153133032773076</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1125924142201598</v>
+        <v>-1.201535738270787</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5271751599819324</v>
+        <v>-0.4772095380080302</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.07062268720784</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.687032342517169</v>
+        <v>0.1086498596344201</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5894484358621253</v>
+        <v>0.08144771268982726</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.4705570758676389</v>
+        <v>0.5398350655406116</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3357744434512012</v>
+        <v>0.06659317080302765</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.2277917392755717</v>
+        <v>0.8203802689394096</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.7099580277204705</v>
+        <v>0.3931985834839791</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>SCsTyaGG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.07046369232899995</v>
+        <v>1.171658635370204</v>
       </c>
       <c r="C3" t="n">
-        <v>1.897326228323101</v>
+        <v>0.8490247778234393</v>
       </c>
       <c r="D3" t="n">
         <v>-0.5328126607276883</v>
       </c>
       <c r="E3" t="n">
-        <v>1.607294606604769</v>
+        <v>-1.322161651714467</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.607279627968067</v>
+        <v>1.322181659521156</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4871724034438584</v>
+        <v>0.08026594813162022</v>
       </c>
       <c r="H3" t="n">
-        <v>1.054355714573872</v>
+        <v>0.06078388754088072</v>
       </c>
       <c r="I3" t="n">
         <v>-0.01160718789708619</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5447368190483627</v>
+        <v>-0.7539981566977632</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8267347239912716</v>
+        <v>-0.9061028057741575</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.263130771533698</v>
+        <v>0.3223329407322</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2073906849637471</v>
+        <v>0.4367111073128512</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0558476277760523</v>
+        <v>0.1568734342911372</v>
       </c>
       <c r="O3" t="n">
-        <v>1.275181281214124</v>
+        <v>0.2706462934538846</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3003009856062991</v>
+        <v>-0.05590554138783343</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7226834177867784</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4745991499983991</v>
+        <v>0.06955509320738122</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0159351880697753</v>
+        <v>0.2225112011768085</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.484147942958663</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5179629025588799</v>
+        <v>-0.1008453065049704</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.03603078953269</v>
+        <v>-0.2057980186230849</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.4607474434267831</v>
+        <v>-0.04403740481483441</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4946518221506773</v>
+        <v>0.4780363302006604</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.2884374384020774</v>
+        <v>-0.0317680764902448</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.6566424857880431</v>
+        <v>0.1306159742218087</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.459015293270766</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.369292905108457</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.5925612251142042</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5925799803728966</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.501201200176155</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.267263963223799</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.2084056775768927</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.8865221338147148</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.8823109861435109</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.739967284451022</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.3807008998938282</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.698033540229847</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.2285876990009058</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-1.242241526161237</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.2352978295856084</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.5558774493343909</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-1.344639589551437</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.8216299893126381</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-1.059166497075543</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-1.239399910808827</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.8501343544850393</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.6686402881273761</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.7452584333242087</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.5254149017205614</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-1.110743346279163</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.110762991131603</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.599331744248506</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.089840422682193</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.2084056775768927</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.5419597933106404</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.7514559781749547</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.366418800029255</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0607121835804568</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.6757604017624607</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.8149660485698242</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1.195421986590406</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.008399315070811155</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.165714442275862</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-1.749615296583805</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-2.003329132322091</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-1.545745249313037</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-1.890182904018803</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.6911901640247324</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-1.538102820051805</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.02686678857280336</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.825729190034558</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.6091430529914825</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6257436930614537</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6966617652538246</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.0101855286757615</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2245509997186815</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.8627943641290468</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2715922659428503</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.1185033109710009</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.145047753299726</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.04656061826016639</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.4329224035552223</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.5865676389453084</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.5486129722388872</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.8356771213947564</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.184742735912209</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.01179744877268697</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1785678104941253</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.1163344025264699</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.05190900597182947</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1993629901364703</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.6173682993010375</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.6729536243834767</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.02368874992345</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.02370824532414</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.5496224041580059</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6995086334906607</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.1690459796409315</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.3034166345001277</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.4897459622378415</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3455348487165789</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.2004946620709201</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.3688457358413499</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1339139459197992</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.02117169419459044</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.111686182958408</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.2958953101525525</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.1439001137655166</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.2113541485521336</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.4916556543046042</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.2900729360903708</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0.1643816879596581</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.09008358859851752</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-1.535055690660897</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.105276243501135</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.170202857240616</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.17018541146392</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.1483970162846811</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5220850929490553</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.01160718789708619</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.1708926573831758</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1.16781282171127</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.7979720544119694</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3552218690133449</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.014352548019416</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.079804470144036</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.686566863241194</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-1.804842742802988</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0352568989672147</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.7669071677691817</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.631670171979135</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.8731737199907709</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.1290844366791561</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.048438081157489</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.276487636526369</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.6386583828127098</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.6729536243834767</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.08681547485720389</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.08683336187239861</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7818777768375397</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-1.181180896250359</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3032703955906041</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3592032510846305</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.03770138925555597</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2179243548024947</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.6753314314034097</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.14073988526866</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.5469317230858446</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.478184862440644</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.8863078284027038</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.5182185408288011</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.701692558565866</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.21636315957829</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.769687569504721</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.352110937152323</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.9721596534016069</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.789211759523845</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.709293672732546</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.825729190034558</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.4023484475225175</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.4023314002838204</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5120270734891084</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.1876090692173669</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.1690459796409312</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7567751824354855</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.6324968800217212</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.5825414706585803</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.194506642763703</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1.343713051912426</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.5269444609788179</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.3191270563820191</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-1.105763978692547</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-1.529001910532081</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.8463121424297226</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.5158412507462431</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.3884814025148892</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-1.378189345075036</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1.125615356482196</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.8616032716749626</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.102136863297488</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.415884080686219</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.288997995959909</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.289017946832598</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.2115988915426033</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1672380118658441</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.1690459796409315</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.4094358161936889</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.9179987155894809</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.92326459165435</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.5912069204962657</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1.217694514956117</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.3451512619697582</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.902334827107695</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.6506597975264349</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1559968456465304</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.8005854110260757</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-1.601128848085841</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-1.115988924134024</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-1.646338500848698</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.5943106933345859</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-1.562995641435581</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.1566407631085411</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.8490247778234393</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.223148927447813</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.223133289325612</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5539249458511016</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2763208394881699</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2507907983426556</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.01186388484283401</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8663877567090158</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-1.568622559994688</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.03796583333756062</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.6270553708099469</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.8553102549547421</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.1494641610274483</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.5322080838298913</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.6985766501519237</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.08030040967107623</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.06264309021000408</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.01212142946088254</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.6767575656272782</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5329002816601918</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.9177297264995002</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-1.683368804416026</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.5254149017205614</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.314348980772846</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.330915355563423</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5723884150275731</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.6489102746255416</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.01160718789708619</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.1206600922741171</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.6522613800331966</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.6753491025960968</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3780793196816007</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.1815991739928421</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-1.894348434657007</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.1125606093620377</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.4277374290329508</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.5333361722333323</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.1730663532554112</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.06624830954794347</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.04959474996422977</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.2474400093923298</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.522404829929011</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.0928693024821666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-1.173542475882771</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5151213528494731</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.004384578467829059</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.004366848021133896</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.3593066449543759</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.2230937773256882</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.3163902949025912</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.4094358161936889</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.5570941015106096</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2991310327478211</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0160771004131602</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1.333701125277255</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.2025982500012793</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.99843853718547</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.01488954019686391</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.7347936196010322</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.8432966498722912</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.8779624847920755</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.8617987906826045</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.43835356873302</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.2778843736375948</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.9129620638345952</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.07046369232899995</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.415884080686219</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.662567366195699</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.662552482448995</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.2705817073352503</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.575312155111537</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.05399230866284942</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.9953183412459979</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.211369141353392</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1.487415882049361</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.3690889563143902</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.187554307153694</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.7643234618182032</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.6634774388221739</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.1596800525731818</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2423262868147766</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.157114376415776</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.263128866371342</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.12314099027915</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.281886139670737</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.7643229457329574</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.9877842851430831</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>d8abY4hR</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.04077114298734669</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6548948795827613</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.3526029638906819</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.352585831250985</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.5901417507741806</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.340862082737803</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.07720668445702181</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1736696831208981</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2834881757581738</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.8377624584867496</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.5344482955373565</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.02403302742571292</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.112115749040693</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.4433760751592397</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.3777677889725736</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-1.361502508004095</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.5970904459121056</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.542860604807658</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.5018135596949796</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.721581904445312</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.2672596297255675</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.1807105844084723</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.1288320542794544</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.105276243501135</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.728894677704813</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-1.72887990782611</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6149964208194308</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2027227199741649</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.3819897914625268</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.074832727516169</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.6998450192944893</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.438342480654095</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1916937376783994</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1935746448974976</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.7359169446564769</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.5364434970209855</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2372783133368384</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.4033186618109261</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.2875229460246355</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.08198753252274742</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.07136478987308295</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.0299175043804927</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.170073741414886</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.03210807563273808</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-1.48870784261242</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6548948795827613</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.336021136013403</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.3360039749067062</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.677446421533578</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8414474659239454</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.2084056775768927</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.303416634500128</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.5570941015106096</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.8609643664711285</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.08020993489098083</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.5378437799180417</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.2526595411129963</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.7569213568405039</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.1236042731687918</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2071541914287729</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.6055374202950279</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.5681047807377911</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.614784901711979</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.2980223892022347</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.6281976758032989</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1.073850522676992</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.5895595904719509</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.369292905108457</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6676576935589769</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.6676411017922785</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.112890344791467</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.8618185232754683</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.2740051741368283</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6507560007419239</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.03367406963638408</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.02070813693527298</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.376568743722876</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.2223393426000881</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-1.242241495703749</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.04217086129714685</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.6292461152554717</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.2210785543380217</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.1780691048424884</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.06342181514269034</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.02503394831284463</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.2788973379732068</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.2682352021213069</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.1794155235471628</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.8796671926647942</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.9887983045567276</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.252167126233051</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-1.268733394272378</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.3081770380041473</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.9150455854379502</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.3163902949025912</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.06487347568961493</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.08528502851684903</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-1.696233053908772</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.4407015782007022</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.337679140532931</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.6882994997517283</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.7419832603778872</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.647174939334926</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.5169939080277138</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.100357976664532</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.113767187451858</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.490267795826404</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.361820673045963</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.155772883965003</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.614868566179955</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>C0axT3Xo</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-1.057672855761576</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9887983045567276</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.5328126607276883</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.388488963223581</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.38850908489827</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.7520104316693286</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4156309686240918</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1851913017827203</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-1.178074883472008</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.4738227328033465</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.00678922627138</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2232111741332194</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.4036537285174954</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.08004968295396216</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.5238392732854208</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.59471119151727</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.628553796593955</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.3294630097250172</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.06357237951776953</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.5183777225686274</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.9367387307718749</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.2372235420935926</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.4944128209071842</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,298 +425,6259 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:CQ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>id_team_home</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_points_against</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
+          <t>dif_mean_last_60_matches_expected_points</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
+          <t>dif_mean_last_60_matches_expected_points_against</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts</t>
+          <t>dif_mean_last_270_matches_expected_points</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
+          <t>dif_mean_last_270_matches_expected_points_against</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
+          <t>dif_mean_last_60_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_int_rep_player_sub</t>
+          <t>dif_mean_last_60_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_270_matches_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_goal_attempts</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goals</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goals_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_goals</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_goals_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_points</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_points_against</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_points</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_points_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goal_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_goal_ratio_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_goal_ratio</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_goal_ratio_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPS</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPS_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_PPS</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_PPS_against</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_attacks</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_attacks</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_red_cards_against</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_KGP</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_270_matches_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_270_matches_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>is_rival_match</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>fsjksfhd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7452584333242087</v>
+        <v>1.749583206004045</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.565951156290596</v>
+        <v>-1.652623344554931</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5328126607276883</v>
+        <v>-0.04471273827287111</v>
       </c>
       <c r="E2" t="n">
-        <v>0.170202857240616</v>
+        <v>1.852605332884634</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.17018541146392</v>
+        <v>1.351406174958697</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09423190558561799</v>
+        <v>-1.296769453625501</v>
       </c>
       <c r="H2" t="n">
-        <v>1.586626336198689</v>
+        <v>-0.3285431002619075</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5131887845823978</v>
+        <v>-1.498081294778967</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01464091058055621</v>
+        <v>0.7669198643494815</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5095104622493165</v>
+        <v>-1.987052334383452</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.011776768369592</v>
+        <v>0.8754122230352248</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2157232168650701</v>
+        <v>-0.6272769457667127</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0812885555756799</v>
+        <v>-0.1760097289348692</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5858805675132868</v>
+        <v>-0.5647795042149875</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4559779675500121</v>
+        <v>-0.0272443191353725</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3153133032773076</v>
+        <v>-0.02928599431828293</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1125924142201598</v>
+        <v>-0.2846465941987857</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5271751599819324</v>
+        <v>0.04543908546062164</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.07062268720784</v>
+        <v>0.1056316122457671</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.687032342517169</v>
+        <v>0.413031519605535</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5894484358621253</v>
+        <v>-0.2234246604938656</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.4705570758676389</v>
+        <v>-0.6643814700739715</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3357744434512012</v>
+        <v>-0.3676382957408555</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.2277917392755717</v>
+        <v>0.534390237563522</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.7099580277204705</v>
+        <v>-0.8003694331282425</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.3167073136826684</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.08186752843063301</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.181523400506362</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.6465880123286848</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.3838055733728294</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.1808524609328842</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.4537462801011026</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.2560023360919259</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.4588731126483788</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-0.1659843729900005</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-1.058079630992506</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.8867995169143797</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-0.8329047347135978</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.4955330333882174</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-1.896183835225264</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.1031363018086824</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-1.939470961843704</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.1832494286994616</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-1.28457811232646</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-1.05634830583408</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-1.702281205450547</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-1.000059322724751</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-0.5056434617546521</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.505641504314266</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-0.4707561369065507</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.4707469175026966</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-0.09668139058711669</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.3304056084331963</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.07409803903174211</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0.7138366492155004</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-0.3364124025092504</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.706718805904657</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0.008903867074986247</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.4467333776910805</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.3151899059604542</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-0.3072235327410185</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>-1.129471667422421</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-0.4582704745942268</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>-0.1763275597122005</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-0.6907765462775887</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.4683508978248732</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-0.1363585952904376</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.4758088804325755</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0.6706849515096454</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>-0.2430695344231588</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0.6902423128150545</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>-0.009115304630041668</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.4983378968535194</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.9181247127946986</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>-0.08587693317907083</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1.191585716118567</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0.8743391677296676</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>1.192196764297385</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>1.266671938602851</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.1808772931837465</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>-1.162924975532224</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>-1.177796460296628</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>-0.4199860844351208</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>-0.6037913147921538</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>-1.216285944522236</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>-1.852291618467365</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>-0.8830228058693677</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>-0.1447231216444895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>nywy5cp3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.07046369232899995</v>
+        <v>2.218445662335125</v>
       </c>
       <c r="C3" t="n">
-        <v>1.897326228323101</v>
+        <v>-1.503697585565893</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.5328126607276883</v>
+        <v>0.04764675155084097</v>
       </c>
       <c r="E3" t="n">
-        <v>1.607294606604769</v>
+        <v>0.7062172736888825</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.607279627968067</v>
+        <v>-0.6256841218893362</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4871724034438584</v>
+        <v>-1.296769453625501</v>
       </c>
       <c r="H3" t="n">
-        <v>1.054355714573872</v>
+        <v>-0.3285431002619075</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01160718789708619</v>
+        <v>1.026402187543715</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5447368190483627</v>
+        <v>0.6802008512749851</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8267347239912716</v>
+        <v>1.187182155070425</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.263130771533698</v>
+        <v>1.358511071233542</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2073906849637471</v>
+        <v>0.1467157573805001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0558476277760523</v>
+        <v>0.741719145865131</v>
       </c>
       <c r="O3" t="n">
-        <v>1.275181281214124</v>
+        <v>1.300080941335262</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3003009856062991</v>
+        <v>0.8137240808423578</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7226834177867784</v>
+        <v>-0.1504502705274864</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4745991499983991</v>
+        <v>0.1969745855145621</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0159351880697753</v>
+        <v>0.5471461125076332</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.484147942958663</v>
+        <v>0.8184570287167094</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5179629025588799</v>
+        <v>1.341097031409281</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.03603078953269</v>
+        <v>-0.01955685382513472</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.4607474434267831</v>
+        <v>1.939997436105981</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4946518221506773</v>
+        <v>-0.01044327913526669</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.2884374384020774</v>
+        <v>0.5058868428589521</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.6566424857880431</v>
+        <v>-0.2225832645332838</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.409987603048063</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-1.36107962378646</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.08537095969456776</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.7170613817744653</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.6722898869978819</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.4383151660775915</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.8511362436721769</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.5185946747466489</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.6410958323994048</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.5311925933962415</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.896875594713831</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-1.297204869038672</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.8289346011627815</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-1.604896143782874</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-0.08418501267738594</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.2327312500225262</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.5227904015442191</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.4482203266468429</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.2322415133234632</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-1.08621668170094</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-0.1637700622903406</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-1.021890740729955</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.825175604745207</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-1.842260729126596</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.761341452629481</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-1.765586683466358</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.361232587843258</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-1.139052379390918</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.349931163526493</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-1.502842014592118</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-0.1241453264326351</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.07083213154791171</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0.2552579276855584</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-0.003141976128439273</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.1811349056344844</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.5532856484209379</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>-1.416346450728139</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.03585982307183552</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>-0.7155015437144856</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.028497663010731</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>-0.1838554046893259</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1.303466082169943</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>-0.9579316071300333</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.7965815642024195</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0.3370777828041902</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0.4304686051505085</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0.4812251855487673</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0.7747740312043347</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>0.206629290927578</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>0.6537421619021788</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0.6201032977609491</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>-0.3204190789575111</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1.37983255805178</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>1.084254036590809</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>-1.358153784467579</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.6863375023894428</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.7950233484575707</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>-0.4439904351385835</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.005961061970880442</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>-0.653471468901913</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>0.8157433022467941</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>0.9561274504647636</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.218445662335125</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.07863860369263824</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.229848221294356</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.244234632581668</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4340362772212096</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.7687860665524143</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3911374743599962</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-2.805973928097947</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.211737960051495</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.9142630042370281</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2858935457989057</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-1.194554635636528</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.5118701767496575</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.4783840180937016</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1633128901582529</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-1.229852006886706</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-1.56629852518802</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1993322241244091</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.5512730048473116</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.6459616604550098</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.4421193389912318</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.9690670068082102</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.8798150313100495</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.4266217435831428</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.3584168732265877</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.146227582933227</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.5787775579755328</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.789224861367842</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.6649087614924338</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.87440692093577</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.7919897618692139</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.8402954389483074</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.4642078060500309</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.369661545675683</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.331993393416087</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0.7731362098214412</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-0.6717360556961484</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.5905728275884375</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.06214198145532367</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.3087519933789996</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-1.240087004908637</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.241399669553803</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-0.4656182053561937</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.355492342115076</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-1.402372751335244</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0.4670488890752382</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.4670471896155922</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.1009426939327022</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0.1009370550202391</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0.7810992562250011</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0.08349832614259936</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0.280170999923236</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-0.4421457592836037</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.3003888257205954</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.026035083542018</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.4476111782102929</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.8394152756761808</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.119519907916273</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-1.089504606524615</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.3471262431858011</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1.526770203960816</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>-1.195692954976354</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.161728605693174</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.0479545692223358</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-2.725651320468355</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.5497866445247606</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-1.012123038872492</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.3360594907232679</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.02729300615567134</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.9721028288452138</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-0.2567063027164455</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-1.904905509452264</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-0.3483224185304821</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-0.444706838645205</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.7031863018710367</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1.307345229342121</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>1.356343980175794</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.3250559583002846</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-0.6895824620124723</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>-0.695517562133893</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>-0.2951374047738758</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.3826429589767796</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>-1.12228167743156</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>-0.3457671490176691</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>-0.9109568284600386</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.263099229604752</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.5822194518212187</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.160578603926572</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.758611913061245</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.576386778594268</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.4882879018498933</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.027076903572971</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-3.451662107757453</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3.525414108304779</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.4388517558619603</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.3583399689613592</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-1.371333619895205</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.5200151491465359</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.4119100114434925</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1.203869813544154</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.2985574874644792</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.1991239364193079</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.2585948376208601</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.57740763174659</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-2.26265418162699</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.183838918264193</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-1.624741911307635</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.691333418937517</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-1.370162330435883</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.214154468444258</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.811215517426002</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.1112334514920255</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.113341720274942</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.4042316038177481</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.41311730946127</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.02407684498878721</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.342086083514575</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.5672085922688157</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.1399960423489256</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.4250627667115554</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.01461247434261189</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.2308544833218706</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.3463302198914402</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1.523412538018134</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.1450471809152977</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.3272635472979604</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.3744863369365055</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0.05077965164981327</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0.547188747757819</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.6703404405948004</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-1.038150856951644</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.03814534003015</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0.8640607072424489</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.864041265946578</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-0.5094106024034548</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.8868984582695525</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-0.6864054420599689</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.55071778957443</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.1817689890895461</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-3.714773584015146</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.6342641747787454</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-2.234545192032294</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-1.507958098472734</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.465946901168467</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.8190414711346014</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-1.590145294371167</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.4751907057845208</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-1.898361317091415</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.0582819494014945</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-0.02928908175082446</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>-0.06251829750423397</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.07898598365318101</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.052073847175756</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-0.06829793942888512</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0.02907730523550344</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-1.249075122668707</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>-0.04583682650914221</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0.9877636887130657</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.001176297208368</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1.236961606545256</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.163654672816213</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>1.158983894481483</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.1682752037780433</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>-1.669040030043165</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0.8321393529458919</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>-0.01267052779081091</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>-1.349119966149025</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.5014359518687763</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>-0.9544321580869878</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>-1.98423005160489</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.263099229604752</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1949868529028243</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.448576983593295</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.594762879044851</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.576386778594268</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.81312741102774</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-3.395592763226357</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.60881954512875</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-5.702920228533061</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.6482166474346867</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.7685830090209619</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.884082942904109</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-1.490139539989058</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.9123711523075951</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1.352758081466291</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.729828724214411</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-2.244189101591636</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.38994258466211</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.01955685382513472</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.249693136292926</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-1.39265423104871</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.132961526359486</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1.038706227673663</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.463066968566665</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-2.26742922577519</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.4728754367557773</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.4332756816132754</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.5811672055419297</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.13185114885539</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.5576670594901837</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.4435749974943797</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.972380431310878</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.023708615136901</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.5294049687878737</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-1.479661375801667</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.947843372463688</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-2.92256707205017</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2.625501299940084</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.5263248752299876</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3.218746916091628</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-2.216896763579322</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.2574264429568963</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-1.72008999176429</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.2782313500509419</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-2.207366534397879</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.353247032488057</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-1.353236564400357</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.850659454821445</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-1.850608341187509</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.822954835594631</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.9014041872899832</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.90566552285009</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-1.294677666444261</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.7547034053661111</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.366376944723338</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-1.541015108537811</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.6161216615212431</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-2.258666100298165</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2.196075903366491</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-1.300851408098565</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0.6298773021087953</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-1.236519286648903</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.294876841186864</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-0.1212018232459458</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1.630993752560221</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.1064847711311589</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.8419478884658316</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.6101883175307874</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-0.2866064137270202</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.447862713915584</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0.3829469807170848</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.09187196481997785</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>-0.5153331819359255</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.259997554058493</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-1.456371391828217</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.274451347737021</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>1.188010711281423</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-0.4409954603057324</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>2.760111240645497</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>1.419033808212913</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-0.2827150596766115</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>-0.9844437189246662</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>-0.7961030845189586</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>1.910481753359384</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>2.682859943864155</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.218445662335125</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.554295872010774</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.3217912077440073</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.758611913061245</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.477939953956971</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-2.002977991243504</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.067705060466932</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.6063425471565722</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.8127371260994546</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.7867136449168876</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-1.513098155795796</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.04527957729389206</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1.33451238883441</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.247513771421691</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.4011678473552409</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.8470788669786694</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.4422654277644785</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.08465787683193</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.2574026282719875</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.817900185682187</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.8265986150352145</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.1923495011086853</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.3670298066820233</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.6611408836863436</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.5223667003876972</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.885995329221815</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-1.257064357855939</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.9442544373156611</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.02115347123890876</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.9836785167734402</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.7798525641949965</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.5205027236891915</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.2866519125104305</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-1.134147927712597</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0.6294140542861101</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.2934096411827239</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.8455433218581387</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-1.261920309478089</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.06877536418927417</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.3804973451235937</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.7062431703196084</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.09944824798354616</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-0.767620672454439</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.9660574935899591</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-1.525959356317608</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.5154028281184783</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.5324967075171596</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.287591450876389</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-1.292008032256098</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.2729933351044962</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.001658942693569198</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.4789601888583894</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.3016087914925398</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-1.566312813894347</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-1.218769815512032</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-1.770883330912753</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.1381858394629209</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-0.006542094821873155</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.005688896772420239</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>-0.2092369729222592</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.7320236907195874</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-2.832961506131188</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-2.341385819779573</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-0.2470756810663719</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-0.3252075818774357</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>-0.1725727860471923</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>-0.1126615430688211</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0.1980042687650581</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1.33093370952898</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0.5540244304746252</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.9905973656207161</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.5738527344718983</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>-1.732125886747014</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.6216268555140385</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>-0.814081801773091</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0.119673348644316</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>1.079635363075681</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>1.43764665597669</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.04249065747267096</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.1848993527752873</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.8296282844669225</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.8881600157471075</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>-0.2610027493153713</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.2325808259138027</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>-0.02433594911526117</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bFdtqGNq</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.749583206004045</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.754053392319318</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7957586191229088</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.705974267535512</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.384886795878981</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-1.750529643011235</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.628647295807871</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.317935780482728</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.02755138231588295</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.633722402057398</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5229228578333426</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.4933968055345745</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.4357568140064112</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.2334214596707458</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.8158319078344024</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.1221297383649625</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.1400903164873456</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.3825030488225168</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-1.44663150050625</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.610249811993622</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.4558906968975095</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.218471710473195</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-1.082040190318285</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.2111963007732482</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.3098237448275358</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.6359441916132358</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-1.117781855257132</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.248604175584912</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.3265247341049571</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.06278270600731976</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.4734781625952982</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.2148827909444234</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.4678571641898533</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.1247823830049083</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0.1367814860260231</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.2198127490426663</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.5427925868014785</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.04710105653490988</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.1877697373769067</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.2418213329092788</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.8049276035714285</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-0.3195373995544707</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-0.1171538202428337</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0.06740344043400358</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-0.665698461992534</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.4592208552307219</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0.4592163631525883</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.6449336997035134</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.6449199534663274</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.2715086976519192</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.9106632774796457</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-0.7051041132597468</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.5166295885293183</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-1.722391546303623</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-0.1490539147249821</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0.8062732245177877</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-0.1334988014533146</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0.3688119060908421</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-0.3593756043265914</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>-1.93048567275657</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.4362757539391615</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-1.779887884613888</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-0.6728519784865091</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>2.910283309966822</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.02641979215481075</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.852037177328858</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>-0.3152974600222063</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>-0.5929307628944629</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0.1569913116958594</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>-0.7356052326804409</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.02087412562785547</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0.02301756915541781</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>-0.01430089171959508</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0.09355806706975436</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>-0.6155937300003476</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>1.534309413273953</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>1.191292460819757</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>-0.7824383952761969</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>-0.08718068981852246</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0.9554084694040516</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>-1.546239457052348</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.2656884198542392</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>-0.06077808057126485</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>-0.2925901670655452</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>-0.4610952467821457</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SQM1jbV9</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.173792095065498</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6789955696171984</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1723320628128523</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.594762879044851</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.035071727463012</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4093062251981716</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.8229287086829572</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.078406221780253</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-2.655036911697525</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2510743240969779</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.3522622942938095</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.745603450742001</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-1.702323889365396</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.4546779640527704</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.8546723255532207</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.02851940006772</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.6263069543845979</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.4191372137621385</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.813593552509966</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.798776628853797</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-2.335863846583678</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.218471710473195</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-1.537046798086815</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.755166618553564</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-1.799087495395199</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.856310795645444</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.04319748187158719</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.6339012043882851</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.2663698092706938</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.6903207726150645</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.602010310620735</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.230641401049264</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.1815023710879344</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-1.39658355139691</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.7572553971126528</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.318667941651114</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.1895043988053577</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0.4051530468760577</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.034104093059153</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.9382871653802991</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.310003370552185</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0.4156980399730319</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.6184932149964817</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.6062144968314395</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.283015101002182</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-2.337175777895498</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>2.337161577799448</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-1.34092025049248</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.340888415730765</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-1.787683449072042</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.8928396630720755</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-0.7412737750678443</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.4216169031677345</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.761285761071419</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.2916827014965887</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.5920911160112856</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-0.7881253278247964</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.368811906090842</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0.3593756043265915</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.35553457238166</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.4107172902667789</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>2.608706412027363</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1.794665892387206</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.2988306858819322</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>-1.378123982798015</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.6449556911055724</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.4737976729194857</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-1.670978850876617</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.2005282244650238</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-1.644426056495429</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.2695326413600095</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.9509406477631</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-1.517397762368586</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>2.423273310206303</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>-1.059272949257068</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.293243341934957</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>-0.312470931712383</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>-0.9882555546219572</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>2.051814217572697</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>1.772547242937578</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0.3460979113479013</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.7829025944227098</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>-0.3818395598961727</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>2.562780567555945</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>2.205777607076878</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.173792095065498</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.024342798819926</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.502308716274306</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.7062172736888825</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.035071727463012</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.6898043899006918</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.401055462512935</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-4.982845052648453</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.971569694707442</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2278835314933162</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.1886507511181108</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.626681041602185</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.512629573291314</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.103336587637319</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.003560593475357</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.873336571339331</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.117968943985692</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.2298606949074271</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.4952484027188399</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-1.012940944402023</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.837954233979091</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.7054106057909404</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.3670298066820236</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-1.108058689903983</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.172411171116567</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.8829254117409681</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-2.17909256138792</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.6115109030643815</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-1.711929663652004</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.5863451165121683</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-1.249622087650569</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0.4378359799304108</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0.9350698741793885</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.6230297265215031</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.5747988903496579</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0.6272100174886038</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.9311893426825022</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.2572431352550656</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.248600019191568</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.6703131401781601</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.445543736173607</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-0.175296438926629</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-0.3162763260218961</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.687522360761334</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.2790756311685993</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.07083243396319143</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.07083053802036102</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-1.113438605100357</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.113412682532374</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.4808425784652418</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-0.5746379231511977</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.01851861584013073</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.4851926920099373</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-0.2552514616564277</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-1.010769501470105</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0.1778400909927685</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.969790601827813</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.682550909285345</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-1.089504606524615</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.2080354391587858</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.4691366358036531</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>2.046141289879415</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>3.246653511829508</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-0.202808647970114</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.6908478012379695</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.7204273687642155</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.0009682008163203478</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-2.184974753550586</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>-0.5266151434157583</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-1.12668613273144</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-0.2034442695724802</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.5738527344718983</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>-0.5869092233954012</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-1.188532020258917</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.8743391677296676</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.187722700483684</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>-0.1694863809022796</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>1.067922344175857</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>1.07405416071991</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>1.906478348847227</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0.8721066120825035</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0.4277960680386663</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0.1706866343117326</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1.970187312832121</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>1.339594459029564</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>r3Wq3yFF</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.218445662335125</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.140691048030112</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9389158283496626</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.9655986459715891</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.477939953956971</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-2.535924504178292</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.212236748924425</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-4.08846325950278</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.053233413848179</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1.679559160157867</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.6687870498545346</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-2.737766004023332</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.3014025776852187</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.9999172069941875</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4351958141899816</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-3.346772763027575</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.2145878607240467</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.7165218993661296</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.325970670188489</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-1.17018771335688</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.8277889551153134</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-1.076051563244667</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.6874299510037766</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-1.264835497111027</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.125720520031519</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.6176307541150213</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.3817764822072234</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.56621373383053</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.3038814985586502</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.6147812122882538</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.7849747816555088</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.311610716600172</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.8779617536118713</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.003582867710245147</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.6204130170404064</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-2.252495405429303</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.782153293905279</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-1.172407311892802</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0.3742491706933343</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-2.697498783173921</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.6433823028045591</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-1.168956389918427</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0.5662856943889424</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-1.455067137658826</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.07689316371991907</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-1.035708162478263</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.035702661884664</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-2.131562380681382</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2.131509997319198</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-0.8063380929188058</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.8393688198493648</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-1.600812261299216</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2.11005702140162</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.6000599919464052</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-1.789284962598458</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.6057282529976034</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-1.20789123482873</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.3688119060908421</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-0.3593756043265914</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.07763781038345922</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-0.3560366199046967</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-0.0794254622417601</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-0.1977992974654839</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>2.028959881858519</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-1.197390427719965</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.807900813561373</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-1.539120791034469</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.077068708246602</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.3303336820730371</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-0.001099083015576437</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.964033408944316</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-1.583584996350983</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.3197206350912919</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.2713227971677894</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.5881996682510119</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.141818754360276</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>1.070148945606667</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>-0.6510787626316887</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>-2.963032197441647</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>-1.04117214892031</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.9929190613924873</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>-0.2414283443491443</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.05628298158466696</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-1.973733239558199</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>-2.248952563914428</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.173792095065498</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.312291513653587</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1723320628128523</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.860566361073494</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.035071727463012</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.933789707520854</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-3.597937127066849</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.097407541630139</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.8392948791980155</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.6772051381892638</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.6900589111909584</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.1451847433898668</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.9207551782005012</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.287717007955673</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.03902355345803453</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.7607946594884257</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.4081635101836503</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.5638795454510399</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.5292263704969619</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.8194019686738921</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.22560792707386</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.1781946300507211</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.04924741395479628</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.788138069842987</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.6196194175344206</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.5754890114240002</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8962719206583215</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.08215870541425174</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.1161520491261973</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.3784240110815479</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.1930660134594568</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2.202959474317263</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0.6718697825058264</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.2441488560875328</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.038100074588879</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0.2350198672339446</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.565200511104261</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-0.07523371291885776</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.129316708073406</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.03203783906302461</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.242864878235599</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.8504170588713572</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.798847179809038</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.273016560030912</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>3.280306875237813</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-2.039655591037729</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>2.056742126697689</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-2.241869850742052</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>2.246108623632249</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-1.606557679857678</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.174056690391515</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-1.691153411225756</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.8361147898940977</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.7124366792810846</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-0.0004822618378918681</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.319507469523228</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.095865943263151</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.119519907916273</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-1.089504606524615</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.146898366341137</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-0.5726750262706058</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>4.037747183136873</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>2.84528377815475</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.9471802418943562</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-0.4038931496510112</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.3928690571560445</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-0.6953991432393446</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-1.25295013997847</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-0.1145058693967343</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-1.033471894332499</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-0.3504165822478978</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0.02301756915541781</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0.2720032741183081</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.5859422121784057</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0.09857413608393456</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.010821665397456</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0.3330044485225365</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>-1.482394897000101</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>-0.1572413156329551</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.9224526524587642</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0.5599924648414653</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0.4225161765649143</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.3019690622259373</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0.1768641891273443</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0.1719918040158231</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>6.909745924749241</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.749583206004045</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.214197515984054</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.04471273827287111</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.9655986459715891</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.351406174958697</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.43218826890939</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.2176994482110031</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.07003133091542764</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.2738717487125032</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.1924495844480537</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.6318353290010941</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.8085886794019602</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.124769056494873</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.3848768049322506</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.1681253410423304</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.7478493851636075</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.20976218391049</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.04668987020931956</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.01955685382513472</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.7780735047557857</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.02731222293312859</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.2637048141644304</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.2974242872021792</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.5567546943429933</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.652511528991612</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.2535770232847621</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.04232464844582658</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-1.423020843362164</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-1.410063123260268</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0.7237208878593741</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.02417697973586224</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0.2596560988403661</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.04414587757631937</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-1.276775984062767</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.4306582500068922</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1.61661535086313</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.579925196902806</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-2.382111536402536</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.4469596338045949</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-2.193289997471763</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.880935560609812</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-1.498650014210637</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-0.5906228895397171</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-2.402275220755646</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.04575364853508893</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0.8720476327617561</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.8720432261371217</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-1.535059412514278</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.535022532122027</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.07850582881694076</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.308723999248712</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0.848029863667344</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.595961921189055</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0.8982958391826447</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.7195690618114086</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-0.5740683819538711</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-0.4411601500798478</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.119519907916273</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-1.089504606524615</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-0.6811522008710597</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>-1.317521681865754</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.4218305021487223</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-1.069483902092938</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.9095558426086924</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1.352145989360327</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.8729517353235018</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-0.06129861757671934</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-0.3275560912196401</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.7051932676232985</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-0.9431895198449911</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1.701924174886937</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.583717204218779</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.4628727180102434</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.9569521741066445</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-0.7103639859398152</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>1.323447054816914</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>1.188808042968559</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.04818449085793189</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.2192210806196321</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.01056136074000168</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.1521400172737519</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>-0.1454573078680419</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.3548005520010304</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>-0.3212050368748547</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.454236752189483</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.749583206004045</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.502741174025316</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.06611864951558338</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.116858181559917</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.384886795878981</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-4.224523455687463</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.813966425285185</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.449756672838218</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-2.816470745331761</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.7461297578604792</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.5928161165101641</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.9727180729922265</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.7812584258870837</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.6206203423392888</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.749803197712411</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.104506153061072</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.56764761170171</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1.479733668941579</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.5988421597366822</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.3144453446269935</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.7950109100290635</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-2.253241764543397</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.678333230144131</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.1218122387457027</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.2312072015270505</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.4746636095380844</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.2248804966444142</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.7285337966679225</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.5176400212725043</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.02099838043489477</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.01554799832925125</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.034250150945937</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.1431370843359231</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.4324178904697576</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.2792193493936055</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.404345233766398</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.4702521439514479</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.751696223241954</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.268168438302524</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.5979941216222557</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0.2783349496186641</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-0.9253494341914059</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.617424452321448</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-1.102653241414043</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.048362441086577</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-0.7225547309908585</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.7225513236333967</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.1194184838338501</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0.1194123647400122</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0.8152459176342666</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.419626488895815</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-0.5313226775329978</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.7669884873161966</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.5313853496863243</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-1.135569689895261</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.1176842194541385</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-1.20173653836196</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-2.258666100298165</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>2.196075903366491</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-0.6265093850033043</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-1.218208794453067</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-1.615350769173802</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-3.561362884374887</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.9217883112685501</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-0.2592658340160131</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0.2001226376370328</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-0.3046927941865018</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.468259929809107</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.6110082943847325</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0.6582797105263866</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.4530123931612531</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.6656585953579783</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0.5201335511778239</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.1443339121124738</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>-0.6143213705659072</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-0.2466897444325506</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>1.278235294702641</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-0.3464979693494941</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-1.349528070205824</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.9981642205438838</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.5694107946960998</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0.490069943649491</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.2932503001368833</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-1.782625358638964</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-1.150713610814322</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.218445662335125</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7860359588905695</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.9389158283496626</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.244234632581668</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.477939953956971</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-3.75328653898723</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.928954639547736</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-7.798150505911811</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.213563457439456</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-1.505628215630404</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.215777769934005</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-2.890528015868219</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.394053364119968</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.276487837471718</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.7070787382217104</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-3.561626244879003</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.471221683430433</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.8996927240642373</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3.160780930207066</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-2.035948832470534</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.940257661065157</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-2.167731580429688</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.025004931301106</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-2.012316249739038</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.082415052860235</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.2411324177658337</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.7855821285152543</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.712568673874438</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-1.743507576488337</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.09649069178985946</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0.1862351433013392</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.04476471320367</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.1868155896633746</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-1.163624392691632</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.377607520106837</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-2.620068143752682</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.062185384572044</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-1.632759870902849</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.9217003114451047</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-2.59838364205569</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.078664316384562</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-1.45011178618984</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0.7039014706051379</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-1.596786493105536</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0.1267963978095123</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-1.387456166645084</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.387448314834606</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-1.534263807735575</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.534226948020903</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-1.385346699423741</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.6334070533618879</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-1.270254723589755</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.242152759365765</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.161943428619799</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-0.8978550452759166</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.337177002146331</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>-1.028198783387885</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.3688119060908421</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0.3593756043265914</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.09477578445107397</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-0.4655728927863358</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0.09766727206759768</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0.1602093396616402</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-0.3345872401311533</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-1.545735276188341</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.8629248238265388</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>-1.198610924242676</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.8138556300179967</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0.2864405259764279</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-0.3691959321196525</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.5748631605673357</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-2.510824191300393</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>-0.2433442243899177</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-1.144103155846537</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1.154258243306613</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>1.106517826002788</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>1.127197711101078</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.07060840489759174</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>-2.688447457003509</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0.8102082727673778</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>1.10455652786089</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>-0.1480914769279695</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>-0.5961850139597599</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>-2.197175523247964</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>-1.643233418799123</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.218445662335125</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.503697585565893</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.64253191222309</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7062172736888825</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.6256841218893362</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.49763910424395</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6802008512749851</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.377699048754115</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.6031568365141198</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.1141806594106954</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.106379625918111</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.214332860868425</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.4580617489969709</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.9999172069941875</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.258612669828931</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.09399132163983966</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.278108602874682</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.08942972930554485</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.1843109528435962</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.72346957270195</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1257694589304524</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.1496912353461513</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.4303151059790198</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.035937792076248</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.8991899227729721</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.1159116069420324</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.1725060732542567</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.703744975405517</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-1.567518777652694</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.5425703562809857</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.1305513471642541</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.125078270987148</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0.353544985680689</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.7523458309456584</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.3832195582485131</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.06719253066034475</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.6297318142222581</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0.3859716902506391</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.901864349983802</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.1284365429283367</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.3246811251201</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.4456265534903659</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.149265316512007</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.2118052118714485</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.7040364358203852</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-0.1973754192140089</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.1973755223539696</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-0.3081526108129722</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.3081476174359957</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.02654351797675428</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.7740155670216075</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-0.4767222500124824</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.2060084389174198</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.311779011732704</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0.1005464621253296</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0.4839424556730271</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>-0.1860353679328391</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0.4224339062212299</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.318601326285859</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>-0.334418696546573</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.6151849996458392</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-0.1525637185122286</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0.4659446880601157</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.56306558322146</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-0.3695397421444975</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0.2658274850378017</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>-1.161488088593239</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0.05951873345066135</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>-0.08957213364144376</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>-0.5974898196770168</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1.173819125669824</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>-0.0871494639078781</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0.2147424409507275</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-0.4071968185239637</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>-1.336111134215629</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>1.293097452623145</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>1.13050318110759</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>-1.433880852297169</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0.6815514689942925</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>1.244982275935873</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0.03377889107297456</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0.8115860855614317</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0.8764564771540521</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0.9826870470002596</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>1.188147817703505</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.749583206004045</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.754053392319318</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.023723330404219</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.705974267535512</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9164463096521297</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.4321882689093895</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9114515528069759</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.6298486299391185</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-1.371091432789995</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.010572781866902</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.9331658978929454</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.9337643705313802</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.9818059948624297</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.8985079758190933</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.3234870119176034</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.5600150996843379</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.627792532817788</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.7488446982187325</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.1214907571595001</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.6015250063764556</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.7659528496255904</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.6769072110863705</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.4825870404010152</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.3335113330214683</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.119891741986541</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.4752723915321063</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9993231146081617</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.3076043224270215</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.7799100055920378</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.7404160754907902</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.5445905154176918</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.04381244097360356</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.5556481545427181</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.1837353129629786</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-0.2426062599485597</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.1716958441412573</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.4422323120286528</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.7559584075159491</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-0.6426958491362966</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.673355674582315</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.030045988774167</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-0.321826938612055</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-0.8472696747660645</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-0.6556046536574566</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0.6935797024864602</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.6253240794206093</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.6253184770456165</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.2015208716146785</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0.2015126186993559</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.1289835022045506</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.2749543636096451</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-0.1790777433248436</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.4788519341689798</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-1.659960053339912</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.128662300103993</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0.2805972024912162</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-0.5397042752022184</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-0.9449270971036613</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.3707533978714319</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>-2.270761389751232</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-0.4801777291705547</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-1.131065798701317</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-1.342822654990391</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.979256304586646</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-0.2810150884279183</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0.4871719501347765</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0.1868123826450432</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0.2269266601364809</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>-0.2093685024651344</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>-0.7145682374748092</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>-0.4963603078382037</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>-0.7114293179332227</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>-0.1097356136655628</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>0.4786082253103783</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>-0.821433211838748</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>1.505251816187432</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>1.102129686655382</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>-1.14779354643964</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>-0.5563361914314676</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-1.542566980629366</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>-1.744152144429692</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0.1520283747914746</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>-0.3648940967101887</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>-1.289406980271032</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>-0.6717052575630046</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.218445662335125</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.5822194518212187</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.143790667175045</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.758611913061245</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4340362772212096</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-2.002977991243503</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.067705060466931</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-2.084035473136612</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.387964028005056</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.2359323205799197</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.5229228578333431</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.6873673117515109</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.6690053748621013</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2011895310796594</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3885873129273997</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2481707908763015</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.9586113816865963</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.1670094252718063</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.611385599524712</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-1.339133507049907</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.1226998009101588</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.8337727082558249</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.192992848524365</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.6105471500054687</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.583560120387515</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.1437988002250432</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.1065897065008787</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.3872447400571926</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.8372807599010126</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.2558414467960876</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.3235652753839989</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.02099074929020417</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.4551387072170033</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-1.3870750143069</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.6021673663641072</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0.5015331412627921</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-0.3174865097740551</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-0.5202411866285689</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.126671913211898</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.3171228276324276</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.7569332409845552</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.8412589026410174</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.8784587086524801</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.3845291617829986</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.6932366775908522</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-1.19692599772139</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.196919419486721</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-0.3144114629842059</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.3144063069411536</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-1.113658045602195</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0.774015567021608</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0.4895792146071207</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-0.3561162300326867</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0.02569025668026994</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-1.39705579897654</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>-0.1055560195471562</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>-0.7483737786988779</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0.3688119060908421</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-0.3593756043265914</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-0.09001628375624605</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.1770399081192817</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-0.2258159860941088</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-0.6936287408780893</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-1.198456762147264</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0.8176318206818384</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-0.4744060781286346</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0.01801595794266623</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>-0.1739207927074474</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0.03827719810327909</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-0.5006382422701333</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-0.9891751210706801</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-0.5278175961610626</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>-0.01430089171959508</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0.4327689207579232</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0.4374957619050402</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>1.16087078550752</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>1.138400706942803</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0.998682358818283</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>-0.0514303933169177</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>-0.2442635944464263</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>-0.3552658171017836</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0.09001772469638385</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0.09475242288636089</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>-0.2878300322978902</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>-0.1084304270531749</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.240772445969938</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6789955696171984</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.5526899323032876</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.594762879044851</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.303956007834344</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.1404701776187684</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.3101997288237991</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.645037975954754</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1.656811800666795</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.4105110232471528</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.4226412258187734</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.8522145414834776</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-1.423598024425272</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.4085828589731822</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.139502055491222</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.128865000662225</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.7035287006743283</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.06931831876614886</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-1.066078261391286</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.50277997701853</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-1.531990012491598</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.457900225991581</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-1.355044154979403</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.718292233831674</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1.70039733705625</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.05160327754535794</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.1128282786024702</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-0.1480334960765854</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.1187519856981294</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-0.1567079060655973</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.6455328696557634</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-0.3102740448153004</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.0003400255012432272</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.04110725661280816</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.7060457871265683</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-0.1964278617794883</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-0.5958832256844681</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.016824857621643</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-0.1005129025273577</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.358921489478055</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-0.3975301115577398</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-1.143313552473479</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.08727861902367114</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-0.3326330709995274</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-0.3312974715362743</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-0.7738513149318531</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.7738475646885966</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0.2717881998299207</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.2717841515553162</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-0.4366633672271937</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>-0.3072837070376455</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.5307776929459094</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-0.8127345006721705</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2.5416794231178</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0.986033513332387</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.031251796516632</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>-0.5159422614731024</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-0.7572500966473037</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.7358178989704437</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.9730348613073686</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.512951144956309</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.851926153068831</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1.668273607796761</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>-0.4266900946790531</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-0.6327575972604765</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>0.324037687236672</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1.345327190632465</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>-0.5944483933199259</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>-1.036311289351156</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>-0.8953576877552026</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>-0.4992897769631734</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>1.693884237282075</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>-0.01430089171959508</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>2.205833220846892</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>-0.06148119630143932</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>1.367684488569435</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>-0.2410171503353926</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>-0.9406613969991312</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>2.151405794423819</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>1.012440678818948</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>-0.6334567872176493</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>0.3478297122237685</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>-0.4682851709170996</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>2.121366260920016</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>2.039131318044639</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.263099229604752</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.06467681378741591</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1.448576983593295</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.852605332884634</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.576386778594268</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9142029216627078</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-1.51668081327893</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.516967062732207</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-2.566544248636725</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.06200137605245649</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.02406786224612742</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.2759896980337854</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.5796981365374583</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.6087673153188231</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.05197035936430728</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.4670084500355613</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.3093116534708648</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.3196517791868961</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.01955685382513472</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.06156022052820463</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.4738686784317351</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.06418105123244219</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.1936939561035358</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.3104501975957001</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.2551381979416966</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.5637368736170988</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-0.7779616119176059</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.9382791067231463</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.222502308818512</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.1785720783921272</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.6767761229933986</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.01889499069825862</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.01526407800648381</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-0.3810717901836967</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.114870150368124</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-0.3556772838689746</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.8329574347223152</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.2777032489888449</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.6320952741100864</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>-0.4406351293683577</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.8063239912760033</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>-0.5187272975643472</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.099705937295884</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>-0.2156517095509128</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.213793768997814</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>-1.108988996679684</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.126081753267635</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>-0.9406860588625823</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0.9448105794466576</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-0.5049566900457244</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0.7007407077904861</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>-0.5790879811989311</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0.876711083829817</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.211888622990767</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>2.198378200891042</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0.4354483263035765</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1.288692788493947</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>-1.695635098929092</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>1.648479151717973</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.3471262431858011</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0.2646689264245929</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0.7733162443236613</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0.4422484323324777</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0.9793696385990449</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>-0.8282625235930011</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0.5744370317257553</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>-1.093566549436228</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>-0.5218288220383347</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>-0.4774136704048736</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>-0.2848941548321758</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0.01827585837959398</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0.7574644562440584</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>-0.5869092233954012</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>-0.705942630952034</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>-0.2431434114152863</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>1.094438642077302</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>1.109928144956159</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>-0.5427375165074649</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>-0.321690947386074</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>-0.08243185062581622</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>-0.8346035410321893</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>-0.1269767649993121</v>
+      </c>
+      <c r="CH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>0.2101356114997181</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>-0.2672455419118276</v>
+      </c>
+      <c r="CP20" t="n">
+        <v>-0.456643175122748</v>
+      </c>
+      <c r="CQ20" t="n">
+        <v>-0.1447231216444895</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.838890340543299</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.144388566457943</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1954219352687803</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.7188067721169481</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.7740958082790713</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.296769453625501</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.3285431002619075</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-7.051944955888869</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.842713478850824</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-5.07089344078384</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.952833767219223</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-1.091092797839949</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.784040351349899</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-1.618910754387666</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.187977041618721</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-1.708464822217576</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.634858137665729</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-2.028727134463197</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.559801693000638</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-1.266034373460453</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.218288920621718</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.8197908599147783</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.847666786945046</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.5772421559146973</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.5863173714996587</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-1.374389808508978</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.327938617611674</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-1.038701969218197</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-1.583248425312338</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-0.09906945535071324</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-1.641528862701748</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-0.09973606041110854</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-0.6386452756915764</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.2068478824598605</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>-0.3696407560741114</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>-0.4723537462478055</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.862803485157617</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-2.418255664413142</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>3.067192502459357</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-2.61228781590756</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>3.009765854604896</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>-3.423670084926147</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.887415408551008</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>-0.1432428921204424</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.608612036643894</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.03032738331227653</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.97779310057216</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>-1.604855974775966</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.604846669782834</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>-2.083174276127881</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.083123150360998</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-2.118757600996659</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0.9106632774796452</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>-2.159482768250528</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.427333334386436</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>-0.03674123628344084</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.901234895116862</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0.9797087652327843</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1.07627026014101</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.245581910654418</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>-2.18469810982165</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0.3471262431858011</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>2.14869281998879</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.386766307282945</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0.8051646227523485</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0.7629872760325344</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>-2.355513645488875</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0.1606461322003526</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>-2.222765550798083</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>-1.484108704997218</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0.260390747198701</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>-1.677063459081979</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1.050544836433055</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0.02301756915541781</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>-0.01430089171959508</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>-1.410266859699503</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0.2685319015250169</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>1.026221545716505</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>1.172970576210364</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>0.6282914621767922</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>-1.770897993998623</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>-0.7579635635545804</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>0.05442590923403538</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>2.032114842003087</v>
+      </c>
+      <c r="CH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>0.3762002520364826</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>-1.046592765388522</v>
+      </c>
+      <c r="CP21" t="n">
+        <v>-1.677879005624362</v>
+      </c>
+      <c r="CQ21" t="n">
+        <v>-0.1447231216444895</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF17"/>
+  <dimension ref="A1:AF13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,1601 +588,1201 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Gl6s8NdC</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.7106270124645843</v>
+        <v>1.803884200412066</v>
       </c>
       <c r="C2" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.079184220960354</v>
+        <v>1.619304369068277</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02672455550745966</v>
+        <v>2.084703102885732</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4665365059920998</v>
+        <v>0.6854073143231572</v>
       </c>
       <c r="G2" t="n">
-        <v>0.184612288931023</v>
+        <v>2.230355940339265</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1220492060314054</v>
+        <v>1.226822799655519</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3393969472403025</v>
+        <v>1.073035632604012</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7063009775471858</v>
+        <v>-0.3501006134154062</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5048862066541164</v>
+        <v>-0.727664194716408</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.8866365743899741</v>
+        <v>-0.340472399790393</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3964558731609966</v>
+        <v>0.2919848317339145</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2282321169322839</v>
+        <v>0.6709399548012787</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6990128578358025</v>
+        <v>1.399825941646369</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6585090648599639</v>
+        <v>0.1525932033922739</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5481275611667169</v>
+        <v>0.1858754705639074</v>
       </c>
       <c r="R2" t="n">
-        <v>1.340727737329203</v>
+        <v>0.3276337611829751</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6472585375709</v>
+        <v>1.226788531960348</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7719812759530676</v>
+        <v>0.3646766398185615</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.09775008906371702</v>
+        <v>0.9508093777743475</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1412202136263729</v>
+        <v>1.685770570285703</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1764044280706414</v>
+        <v>0.5247084043176007</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1072503225617101</v>
+        <v>-0.09021465764454691</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.2822491219036277</v>
+        <v>1.910488685302722</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.4730990126375966</v>
+        <v>0.7649154678323435</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.4375683630849758</v>
+        <v>0.2192203757734337</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00110585081648641</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.03517894821731272</v>
+        <v>0.5222010476384162</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.5911269020120136</v>
+        <v>0.2328808998895854</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.1001850409008136</v>
+        <v>-0.02096136793256776</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.2287979396963444</v>
+        <v>0.2460125892424168</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.143639517401047</v>
+        <v>-0.6650467487870619</v>
       </c>
       <c r="C3" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D3" t="n">
-        <v>0.883352935424105</v>
+        <v>-1.733363273088506</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1777416053066431</v>
+        <v>-2.728543386247825</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7512326754840287</v>
+        <v>-1.223528159342126</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2519461028279841</v>
+        <v>-2.414939536213983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.134030877442367</v>
+        <v>-2.168225655688379</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6437298881094694</v>
+        <v>-2.010457225313496</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1906268207333113</v>
+        <v>0.5379701444742412</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3824215385024105</v>
+        <v>2.580606926058192</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0291874890815672</v>
+        <v>1.751044988579344</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2420111233126476</v>
+        <v>1.976231268482565</v>
       </c>
       <c r="N3" t="n">
-        <v>0.664945474323055</v>
+        <v>-2.128482428529213</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9422461022538748</v>
+        <v>-3.324848135001084</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6857816527541832</v>
+        <v>-1.466337553304333</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1779531261680481</v>
+        <v>-1.489432435945385</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2043436726957092</v>
+        <v>-1.488237531203955</v>
       </c>
       <c r="S3" t="n">
-        <v>1.224856481308054</v>
+        <v>0.2371204925442879</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.745868127854222</v>
+        <v>-1.096014462158608</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7911958643884868</v>
+        <v>-2.337379791594754</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.11655740673839</v>
+        <v>-2.274379469026291</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.9721843535140883</v>
+        <v>-2.52892598578991</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5159296617143504</v>
+        <v>-1.950941819566827</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6140101884114006</v>
+        <v>0.3011569630274204</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.600143168937825</v>
+        <v>-1.388584004630634</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1189739372609206</v>
+        <v>0.4420059873576407</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00110585081648641</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.6348716100437214</v>
+        <v>-2.12781261836607</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.4084725229901409</v>
+        <v>-0.7814664167153837</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.8426703939919313</v>
+        <v>-1.073167985381237</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.7851093227334471</v>
+        <v>-1.255511771574057</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tWiaepD6</t>
+          <t>ShJjaSDs</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.621563145701976</v>
+        <v>-1.02209214759432</v>
       </c>
       <c r="C4" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3927186463279905</v>
+        <v>1.046897698456144</v>
       </c>
       <c r="E4" t="n">
-        <v>1.11990078950063</v>
+        <v>-1.215993413372229</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2142059548754243</v>
+        <v>1.716671305843482</v>
       </c>
       <c r="G4" t="n">
-        <v>1.10803413252056</v>
+        <v>-0.714260658906852</v>
       </c>
       <c r="H4" t="n">
-        <v>1.036768198857284</v>
+        <v>-1.801525280356029</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9644030928941815</v>
+        <v>-1.813761620868477</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2730279541355503</v>
+        <v>-1.310069404095763</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8812680354377661</v>
+        <v>0.7596862052104272</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8418067700913122</v>
+        <v>-0.04757102804281346</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8863561073777062</v>
+        <v>0.9546330758332521</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4979837384523526</v>
+        <v>-0.74975191853775</v>
       </c>
       <c r="O4" t="n">
-        <v>1.458516006962445</v>
+        <v>-1.240884115014425</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7307827593553481</v>
+        <v>-0.396686874772646</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.101765208608354</v>
+        <v>-1.392217041606692</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5998082622371856</v>
+        <v>-0.3404309232228148</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4758074698928407</v>
+        <v>0.4307452578720842</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5135291713373615</v>
+        <v>-2.281993981576692</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2652047206221269</v>
+        <v>-2.245165128645187</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5778167218905695</v>
+        <v>-2.675250182392253</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.2439260998806244</v>
+        <v>-1.797746528727649</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.006975082230273315</v>
+        <v>-1.550544440942571</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.259821471653917</v>
+        <v>-0.01224978612249866</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.5229348926704754</v>
+        <v>-1.396407400614621</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.11545083479652</v>
+        <v>-0.4231333305889944</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00110585081648641</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.07412383581217202</v>
+        <v>-1.651022741807473</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.4803490376987488</v>
+        <v>-0.6767054967648927</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.4613898436278053</v>
+        <v>-0.8923497563260847</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.2234390952641926</v>
+        <v>-1.210319279999318</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>UiYgHRZP</t>
+          <t>n9EQB5cm</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7555381358290515</v>
+        <v>1.803884200412066</v>
       </c>
       <c r="C5" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D5" t="n">
-        <v>1.074155158961483</v>
+        <v>-0.7793521554016168</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07054099706482991</v>
+        <v>0.0990387224835855</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8719125042789606</v>
+        <v>-1.596538539253733</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2931543160635756</v>
+        <v>-0.3516904948979253</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.02460589292963786</v>
+        <v>1.004058332345692</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7779922259364833</v>
+        <v>1.233413257796928</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7904616410835954</v>
+        <v>1.920642358304217</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6506555812547905</v>
+        <v>1.333625521932126</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3241290251294977</v>
+        <v>1.56655366950045</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4970683718097085</v>
+        <v>1.580370153298441</v>
       </c>
       <c r="N5" t="n">
-        <v>1.234421119754311</v>
+        <v>-3.141549629349027</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02812424955112639</v>
+        <v>-0.1486317115225139</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1075920967911095</v>
+        <v>-1.798796547983101</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6396961217273981</v>
+        <v>-1.322034455928351</v>
       </c>
       <c r="R5" t="n">
-        <v>0.09257396481797479</v>
+        <v>-2.391362011974745</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2340353686803432</v>
+        <v>-0.947040719645035</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2997139276921812</v>
+        <v>1.728995269466251</v>
       </c>
       <c r="U5" t="n">
-        <v>1.052305517330696</v>
+        <v>0.7333954923320523</v>
       </c>
       <c r="V5" t="n">
-        <v>1.758776239566756</v>
+        <v>1.058321766130438</v>
       </c>
       <c r="W5" t="n">
-        <v>1.239940959970785</v>
+        <v>0.7951239157240891</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8647983266661541</v>
+        <v>0.8267584970551792</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4141108545106014</v>
+        <v>0.839914785629471</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9930774966794832</v>
+        <v>0.9062105841742676</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.5067209613281023</v>
+        <v>1.365207316272698</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00110585081648641</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7718926086281602</v>
+        <v>0.7051391945830482</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.01459617263127</v>
+        <v>0.8396669451738435</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4422038591328142</v>
+        <v>-0.05870278947993681</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.7401507617307387</v>
+        <v>0.2980663368035887</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>n9EQB5cm</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.803884200412066</v>
+        <v>0.5884105023448029</v>
       </c>
       <c r="C6" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7793521554016168</v>
+        <v>0.3927186463279905</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0990387224835855</v>
+        <v>1.11990078950063</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.596538539253733</v>
+        <v>-0.2142059548754243</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3516904948979253</v>
+        <v>1.10803413252056</v>
       </c>
       <c r="H6" t="n">
-        <v>1.004058332345692</v>
+        <v>1.036768198857284</v>
       </c>
       <c r="I6" t="n">
-        <v>1.233413257796928</v>
+        <v>0.9644030928941815</v>
       </c>
       <c r="J6" t="n">
-        <v>1.920642358304217</v>
+        <v>-0.2730279541355503</v>
       </c>
       <c r="K6" t="n">
-        <v>1.333625521932126</v>
+        <v>-0.8812680354377661</v>
       </c>
       <c r="L6" t="n">
-        <v>1.56655366950045</v>
+        <v>-0.8418067700913122</v>
       </c>
       <c r="M6" t="n">
-        <v>1.580370153298441</v>
+        <v>-0.8863561073777062</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.141549629349027</v>
+        <v>-0.4979837384523526</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1486317115225139</v>
+        <v>1.458516006962445</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.798796547983101</v>
+        <v>0.7307827593553481</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.322034455928351</v>
+        <v>1.101765208608354</v>
       </c>
       <c r="R6" t="n">
-        <v>-2.391362011974745</v>
+        <v>0.5998082622371856</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.947040719645035</v>
+        <v>-0.4758074698928407</v>
       </c>
       <c r="T6" t="n">
-        <v>1.728995269466251</v>
+        <v>0.5135291713373615</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7235483535970076</v>
+        <v>-0.2565498264537479</v>
       </c>
       <c r="V6" t="n">
-        <v>1.019410526917757</v>
+        <v>-0.5768835013463653</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8509305988089971</v>
+        <v>-0.2127445627719131</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8376521386202413</v>
+        <v>0.0184864158399117</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8386771224175683</v>
+        <v>-1.310809373086348</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.8878180366864946</v>
+        <v>-0.5119875439493923</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.446657125736732</v>
+        <v>0.155153229905262</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00110585081648641</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.6961119580990984</v>
+        <v>-0.07008724378484328</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.8560373299686049</v>
+        <v>-0.4263532473849332</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.007099860805149909</v>
+        <v>-0.4338226543702541</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2741561930798869</v>
+        <v>-0.1842548505477969</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>Y5lic6rf</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7555381358290515</v>
+        <v>-1.143639517401047</v>
       </c>
       <c r="C7" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D7" t="n">
-        <v>1.455759606036239</v>
+        <v>0.883352935424105</v>
       </c>
       <c r="E7" t="n">
-        <v>1.86721916555256</v>
+        <v>-0.1777416053066431</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6086110596354734</v>
+        <v>0.7512326754840287</v>
       </c>
       <c r="G7" t="n">
-        <v>1.296652436543449</v>
+        <v>-0.2519461028279841</v>
       </c>
       <c r="H7" t="n">
-        <v>1.034596589462324</v>
+        <v>-0.134030877442367</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6147220183252579</v>
+        <v>-0.6437298881094694</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1852996301381928</v>
+        <v>-0.1906268207333113</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0467932473631813</v>
+        <v>0.3824215385024105</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.408800470595793</v>
+        <v>-0.0291874890815672</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.188294219775105</v>
+        <v>0.2420111233126476</v>
       </c>
       <c r="N7" t="n">
-        <v>1.444227936492142</v>
+        <v>0.664945474323055</v>
       </c>
       <c r="O7" t="n">
-        <v>1.834372442779236</v>
+        <v>-0.9422461022538748</v>
       </c>
       <c r="P7" t="n">
-        <v>1.431837595960575</v>
+        <v>-0.6857816527541832</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.724869054404841</v>
+        <v>-0.1779531261680481</v>
       </c>
       <c r="R7" t="n">
-        <v>1.054807049353063</v>
+        <v>-0.2043436726957092</v>
       </c>
       <c r="S7" t="n">
-        <v>1.050307070524537</v>
+        <v>1.224856481308054</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1526068526874382</v>
+        <v>-0.745868127854222</v>
       </c>
       <c r="U7" t="n">
-        <v>1.017304304976709</v>
+        <v>-0.7865522662767708</v>
       </c>
       <c r="V7" t="n">
-        <v>0.576509466612695</v>
+        <v>-1.09156332607623</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6015533004929872</v>
+        <v>-0.9569323075448309</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.03680313579925615</v>
+        <v>-0.5040317766765552</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1.422739842930343</v>
+        <v>0.6669955540236613</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5273812826678499</v>
+        <v>-0.5833407191566196</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.7196679693677507</v>
+        <v>0.1699036905104629</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00110585081648641</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.4368834711018252</v>
+        <v>-0.6270278546927773</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.00237160366724554</v>
+        <v>-0.3846387060725539</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.5917063063268017</v>
+        <v>-0.8223526695010606</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.8116443014519324</v>
+        <v>-0.7887112722225048</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>UiYgHRZP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.58424873295043</v>
+        <v>-1.295573729659454</v>
       </c>
       <c r="C8" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.855673044816568</v>
+        <v>1.074155158961483</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1393999075322146</v>
+        <v>0.07054099706482991</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4314296467063013</v>
+        <v>0.8719125042789606</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1210520818091885</v>
+        <v>0.2931543160635756</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.387128936300848</v>
+        <v>-0.02460589292963786</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.08431873276610968</v>
+        <v>0.7779922259364833</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4552021726644043</v>
+        <v>-0.7904616410835954</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1368226571371469</v>
+        <v>0.6506555812547905</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3426385182416739</v>
+        <v>0.3241290251294977</v>
       </c>
       <c r="M8" t="n">
-        <v>0.81448016874311</v>
+        <v>-0.4970683718097085</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.744835677922892</v>
+        <v>1.234421119754311</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.09862800446159004</v>
+        <v>0.02812424955112639</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9358486357082128</v>
+        <v>-0.1075920967911095</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.5630832387090803</v>
+        <v>0.6396961217273981</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.692333308424218</v>
+        <v>0.09257396481797479</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.362461894436495</v>
+        <v>-0.2340353686803432</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.081189718165882</v>
+        <v>-0.2997139276921812</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.497461831007993</v>
+        <v>1.048593901005892</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.530242674395607</v>
+        <v>1.756824140554</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.121011302434617</v>
+        <v>1.255080079783111</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5017696739347368</v>
+        <v>0.872664404417487</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2441862263003836</v>
+        <v>0.4080897902364807</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.374298364917666</v>
+        <v>0.9775187453669298</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.4843269881924209</v>
+        <v>-0.5905540018759665</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.1457936407637891</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.8122439696900956</v>
+        <v>0.7706874871027347</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.9177307247466148</v>
+        <v>1.028292950448884</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.4136772196771623</v>
+        <v>0.4503472344796233</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.9574943312474604</v>
+        <v>0.7299816215065771</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>Gl6s8NdC</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.58424873295043</v>
+        <v>1.454435512217728</v>
       </c>
       <c r="C9" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.588549931864239</v>
+        <v>-1.079184220960354</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06333448700789746</v>
+        <v>0.02672455550745966</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5433327606797834</v>
+        <v>-0.4665365059920998</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3968639188523488</v>
+        <v>0.184612288931023</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03507458669257953</v>
+        <v>-0.1220492060314054</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.129084889239941</v>
+        <v>-0.3393969472403025</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5118773406773776</v>
+        <v>0.7063009775471858</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4645435931383924</v>
+        <v>-0.5048862066541164</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6194458931870493</v>
+        <v>-0.8866365743899741</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.001076833084688669</v>
+        <v>-0.3964558731609966</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6418512699297225</v>
+        <v>-0.2282321169322839</v>
       </c>
       <c r="O9" t="n">
-        <v>2.761584039423209</v>
+        <v>0.6990128578358025</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1726384218369553</v>
+        <v>0.6585090648599639</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1850025017905536</v>
+        <v>0.5481275611667169</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.4119110952168498</v>
+        <v>1.340727737329203</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4509962592326731</v>
+        <v>1.6472585375709</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6954438285592356</v>
+        <v>-0.7719812759530676</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.282037787260925</v>
+        <v>-0.08970988538443372</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3481865040074222</v>
+        <v>-0.1172250460519008</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.2644683915125302</v>
+        <v>-0.1646103091774305</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.008627484039973623</v>
+        <v>-0.1033492937589512</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.1599546164248236</v>
+        <v>-0.2468817407897572</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.2401944145340327</v>
+        <v>-0.4599386239200811</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.4659657838108666</v>
+        <v>0.5104344536084043</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.709932475556775</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.02128809688704931</v>
+        <v>0.05415633915452675</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.1788151345185542</v>
+        <v>-0.5470195168850328</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.01508618884814233</v>
+        <v>-0.1191234079235238</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.2906562945205582</v>
+        <v>-0.2301580164722766</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>OE9k61RO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.6650467487870619</v>
+        <v>1.029019717894186</v>
       </c>
       <c r="C10" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D10" t="n">
-        <v>0.03837165975857418</v>
+        <v>1.455759606036239</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7229487850331426</v>
+        <v>1.86721916555256</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02715370271443903</v>
+        <v>0.6086110596354734</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3267858530301939</v>
+        <v>1.296652436543449</v>
       </c>
       <c r="H10" t="n">
-        <v>1.172789914596171</v>
+        <v>1.034596589462324</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9507290669167197</v>
+        <v>0.6147220183252579</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5565180048249678</v>
+        <v>0.1852996301381928</v>
       </c>
       <c r="K10" t="n">
-        <v>0.07195835002495148</v>
+        <v>-0.0467932473631813</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8629652811759516</v>
+        <v>-1.408800470595793</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9021745555811371</v>
+        <v>-1.188294219775105</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.198259714541165</v>
+        <v>1.444227936492142</v>
       </c>
       <c r="O10" t="n">
-        <v>1.718130058832414</v>
+        <v>1.834372442779236</v>
       </c>
       <c r="P10" t="n">
-        <v>1.966662935226419</v>
+        <v>1.431837595960575</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.725373538107392</v>
+        <v>1.724869054404841</v>
       </c>
       <c r="R10" t="n">
-        <v>1.164776544728501</v>
+        <v>1.054807049353063</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1469555263193388</v>
+        <v>1.050307070524537</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2905804240181828</v>
+        <v>-0.1526068526874382</v>
       </c>
       <c r="U10" t="n">
-        <v>1.056516504200412</v>
+        <v>1.007238353722081</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6384536708511658</v>
+        <v>0.563615694842533</v>
       </c>
       <c r="W10" t="n">
-        <v>1.560782663746029</v>
+        <v>0.6013406822535509</v>
       </c>
       <c r="X10" t="n">
-        <v>1.168068591769961</v>
+        <v>-0.02756457604006596</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.78792933771185</v>
+        <v>-1.42141112041306</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.5862271201591561</v>
+        <v>0.5134940120153506</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.06176289277219156</v>
+        <v>0.7255144971642551</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1.732308149830769</v>
+        <v>-0.2251193662171381</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.7277965334066259</v>
+        <v>0.4275568167293096</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.5971064914558086</v>
+        <v>0.003173662909574142</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.059583432783783</v>
+        <v>0.582861381580555</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.068839147798202</v>
+        <v>0.8103743833628425</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>l0Zi1FqS</t>
+          <t>fsjksfhd</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.530402618346932</v>
+        <v>-1.58424873295043</v>
       </c>
       <c r="C11" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7248372343909374</v>
+        <v>-0.855673044816568</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1304833563428706</v>
+        <v>-0.1393999075322146</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3656042855454296</v>
+        <v>-0.4314296467063013</v>
       </c>
       <c r="G11" t="n">
-        <v>0.335479498381205</v>
+        <v>0.1210520818091885</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4916476674175949</v>
+        <v>-0.387128936300848</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4337005746710698</v>
+        <v>-0.08431873276610968</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9586019266133594</v>
+        <v>0.4552021726644043</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1007559523778807</v>
+        <v>0.1368226571371469</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8755516794650637</v>
+        <v>0.3426385182416739</v>
       </c>
       <c r="M11" t="n">
-        <v>1.014178878178125</v>
+        <v>0.81448016874311</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7107877954292956</v>
+        <v>-1.744835677922892</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.358834027507755</v>
+        <v>-0.09862800446159004</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.638348946203348</v>
+        <v>-0.9358486357082128</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.047062478189535</v>
+        <v>-0.5630832387090803</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.357648755445622</v>
+        <v>-0.692333308424218</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1982136435197339</v>
+        <v>-1.362461894436495</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3436444907057282</v>
+        <v>-1.081189718165882</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.789337219249259</v>
+        <v>-1.497461831007993</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.124759314005773</v>
+        <v>-1.530242674395607</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.155647328643121</v>
+        <v>-1.121011302434617</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.227414348733031</v>
+        <v>-0.5017696739347368</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2797885563508804</v>
+        <v>0.2441862263003836</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.7318064785869887</v>
+        <v>-1.374298364917666</v>
       </c>
       <c r="AA11" t="n">
-        <v>-1.455339922198846</v>
+        <v>-0.4843269881924209</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.5953060849994349</v>
+        <v>0.4094864374096538</v>
       </c>
       <c r="AC11" t="n">
-        <v>-1.023821528900213</v>
+        <v>-0.8122439696900956</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.7172976223387262</v>
+        <v>-0.9177307247466148</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.7481969334620472</v>
+        <v>-0.4136772196771623</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.6011553154484247</v>
+        <v>-0.9574943312474604</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SQM1jbV9</t>
+          <t>ltBAlx0M</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-1.02209214759432</v>
+        <v>-1.58424873295043</v>
       </c>
       <c r="C12" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D12" t="n">
-        <v>1.466662590238375</v>
+        <v>-0.588549931864239</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8842147806900502</v>
+        <v>0.06333448700789746</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7600093903054785</v>
+        <v>-0.5433327606797834</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7588267725943056</v>
+        <v>0.3968639188523488</v>
       </c>
       <c r="H12" t="n">
-        <v>1.293092139601082</v>
+        <v>0.03507458669257953</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7323244853322696</v>
+        <v>-0.129084889239941</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3042002196557466</v>
+        <v>-0.5118773406773776</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3066146612668328</v>
+        <v>0.4645435931383924</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5933402956661054</v>
+        <v>0.6194458931870493</v>
       </c>
       <c r="M12" t="n">
-        <v>1.015825989524622</v>
+        <v>-0.001076833084688669</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.855733566770032</v>
+        <v>-0.6418512699297225</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7714700938878556</v>
+        <v>2.761584039423209</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.065941285799904</v>
+        <v>-0.1726384218369553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.8593635496657642</v>
+        <v>0.1850025017905536</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.031864125395885</v>
+        <v>-0.4119110952168498</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.882591007005207</v>
+        <v>0.4509962592326731</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.04153234724743295</v>
+        <v>-0.6954438285592356</v>
       </c>
       <c r="U12" t="n">
-        <v>2.514743284617021</v>
+        <v>-0.282037787260925</v>
       </c>
       <c r="V12" t="n">
-        <v>2.520521856073965</v>
+        <v>-0.3481865040074222</v>
       </c>
       <c r="W12" t="n">
-        <v>2.302212286213079</v>
+        <v>-0.2644683915125302</v>
       </c>
       <c r="X12" t="n">
-        <v>1.725961885903636</v>
+        <v>-0.008627484039973623</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.5709352607354989</v>
+        <v>-0.1599546164248236</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.944496093381369</v>
+        <v>-0.2401944145340327</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0380370699181336</v>
+        <v>0.4659657838108666</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.375342385290699</v>
+        <v>0.6474636137697007</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.685844579884559</v>
+        <v>0.02128809688704931</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.425100226361611</v>
+        <v>-0.1788151345185542</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.412586258468639</v>
+        <v>-0.01508618884814233</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.737935749589337</v>
+        <v>-0.2906562945205582</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bFdtqGNq</t>
+          <t>nywy5cp3</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.803884200412066</v>
+        <v>-0.6650467487870619</v>
       </c>
       <c r="C13" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6652932513813875</v>
+        <v>0.03837165975857418</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2298065108970698</v>
+        <v>0.7229487850331426</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4775073995189116</v>
+        <v>0.02715370271443903</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0692852861289992</v>
+        <v>0.3267858530301939</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.03926425634562044</v>
+        <v>1.172789914596171</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1647647532549524</v>
+        <v>0.9507290669167197</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7400895038979676</v>
+        <v>-0.5565180048249678</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3655728715653992</v>
+        <v>0.07195835002495148</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.192821283148987</v>
+        <v>-0.8629652811759516</v>
       </c>
       <c r="M13" t="n">
-        <v>0.07645344489660717</v>
+        <v>-0.9021745555811371</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1793925555869312</v>
+        <v>-0.198259714541165</v>
       </c>
       <c r="O13" t="n">
-        <v>1.143864108588226</v>
+        <v>1.718130058832414</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1742753117408891</v>
+        <v>1.966662935226419</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.01838803049369845</v>
+        <v>1.725373538107392</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.2826969381507092</v>
+        <v>1.164776544728501</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8989199018959215</v>
+        <v>-0.1469555263193388</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.01820670110503184</v>
+        <v>0.2905804240181828</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1309783252811437</v>
+        <v>1.056516504200412</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3998382323888015</v>
+        <v>0.6384536708511658</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3394069877719739</v>
+        <v>1.560782663746029</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2739640652661605</v>
+        <v>1.168068591769961</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.661174766888272</v>
+        <v>-1.78792933771185</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.2493593871419655</v>
+        <v>0.5862271201591561</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.6409870349727019</v>
+        <v>0.06176289277219156</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.983506280433042</v>
+        <v>-1.732308149830769</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.0007317372614656535</v>
+        <v>0.7277965334066259</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.8245747178991454</v>
+        <v>0.5971064914558086</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1698118434098088</v>
+        <v>1.059583432783783</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.03770120540254411</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>YXAOeg7k</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-1.02209214759432</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.5104376201607318</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.4199761068333301</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.5571527911824441</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0.2800313160362962</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.1986835160890286</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.266144441199982</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.8581580815296211</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.232633702942057</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.734308582767023</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-0.2746398256309177</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-0.6605781888926044</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-0.6958015942337363</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.850283160079188</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.3152090160068884</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.536067173352226</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-0.02426862401842819</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-0.8296154513413895</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.4844847749434492</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.188058333593335</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.2364964543395352</v>
-      </c>
-      <c r="W14" t="n">
-        <v>-0.2895635569712572</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.1096145804327217</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.7864993439976318</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>-0.1562331417637128</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>-0.01315252901123895</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.154652397383332</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>-0.115973060547638</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-0.2216785281099318</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>-0.4149056891735279</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>-0.3459800436783125</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>tbEWgXy2</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.6650467487870619</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.5104376201607318</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.8942559196262411</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.332253927405815</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1.233951990663755</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.706313062869225</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.50017175500545</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.40725758427832</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-1.499355714643892</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-1.707638264370763</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-1.073848706552221</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-0.934067413488973</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.758938161598889</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.476801022066714</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.9504947906213157</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.693860645838092</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.2238851484928</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.386984540517439</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.5881154038393526</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.349901892284524</v>
-      </c>
-      <c r="V15" t="n">
-        <v>2.257226141788724</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.982651308317453</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.908860381633587</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>-0.5623910838131801</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.323592451466549</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>-1.072428628684431</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>-1.838075783768566</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.85481448702299</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.122625585140751</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.345072561146113</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.514568102702878</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>d6dJHzU8</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>-1.143639517401047</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.5104376201607318</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-0.6430648528749183</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-1.59341392868598</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.7078961635819629</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-1.367961162722283</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.8632215347972968</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-1.011153119972134</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.8700836054228821</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.28496741679841</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-0.5041510442539069</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-0.2739415455761551</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0.5399451017999191</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-0.4433392741661477</v>
-      </c>
-      <c r="P16" t="n">
-        <v>-0.15095631348834</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-1.14833689002249</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.6671645781546417</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-1.420588512661337</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-1.261934749604291</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.7465861233925056</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.564648977169631</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.053435963489022</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.8727937065744851</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.300499920176265</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.101788130491164</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>-0.2608850131701549</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.00110585081648641</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0.7090934568270364</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.159146082430398</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0.9983829510637462</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0.6077935114123709</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>r3Wq3yFF</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1.803884200412066</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.5104376201607318</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-1.215471523487052</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-0.5377552090847162</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-1.113819224074006</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-0.8753280018680986</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.8968539192846213</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-1.523467763110023</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.4640656737802101</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.400776743446771</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.535020505069126</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.680879762425005</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-0.09635354641136146</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-0.9581361691643443</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-0.5556890026624917</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-1.499975419927287</v>
-      </c>
-      <c r="R17" t="n">
-        <v>-0.3445547792993933</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.620181107804524</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-1.275323270451581</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-1.609339536632436</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-2.18675849690906</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-2.187259969523161</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-0.9389230566985567</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>-0.5457829815237294</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>-1.065337968562046</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>-0.456914956278399</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.815700109494572</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>-0.9969799669881365</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-1.102169881384053</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-1.399731945716399</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>-0.9845875164152473</v>
+        <v>1.068839147798202</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF13"/>
+  <dimension ref="A1:AF21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,7 +588,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>EqY7Orsg</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -598,797 +598,797 @@
         <v>-0.5104376201607318</v>
       </c>
       <c r="D2" t="n">
-        <v>1.619304369068277</v>
+        <v>1.139573064174299</v>
       </c>
       <c r="E2" t="n">
-        <v>2.084703102885732</v>
+        <v>0.9937786556340964</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6854073143231572</v>
+        <v>0.4506301928493808</v>
       </c>
       <c r="G2" t="n">
-        <v>2.230355940339265</v>
+        <v>0.6647145937127257</v>
       </c>
       <c r="H2" t="n">
-        <v>1.226822799655519</v>
+        <v>0.2165590861285601</v>
       </c>
       <c r="I2" t="n">
-        <v>1.073035632604012</v>
+        <v>-0.07655926564397876</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3501006134154062</v>
+        <v>-0.02786454035568101</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.727664194716408</v>
+        <v>0.3983599783612017</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.340472399790393</v>
+        <v>0.1646039899718339</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2919848317339145</v>
+        <v>0.660903886671419</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6709399548012787</v>
+        <v>-1.415139251620586</v>
       </c>
       <c r="O2" t="n">
-        <v>1.399825941646369</v>
+        <v>0.1300828287321656</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1525932033922739</v>
+        <v>-0.05555503675443267</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1858754705639074</v>
+        <v>-0.2641399321003446</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3276337611829751</v>
+        <v>-0.3404309232228145</v>
       </c>
       <c r="S2" t="n">
-        <v>1.226788531960348</v>
+        <v>0.0454491920703558</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3646766398185615</v>
+        <v>-0.9314295492597725</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9508093777743475</v>
+        <v>0.1546303642160671</v>
       </c>
       <c r="V2" t="n">
-        <v>1.685770570285703</v>
+        <v>0.08014433657953772</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5247084043176007</v>
+        <v>-0.3199561134554467</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.09021465764454691</v>
+        <v>0.2724667629090863</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.910488685302722</v>
+        <v>-0.692596598741033</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.7649154678323435</v>
+        <v>-0.1823803221050495</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2192203757734337</v>
+        <v>-0.6731875527703894</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.2251193662171381</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5222010476384162</v>
+        <v>0.2524502112373228</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.2328808998895854</v>
+        <v>-0.4257636456022268</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.02096136793256776</v>
+        <v>-0.06473170698887788</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2460125892424168</v>
+        <v>-0.09361418455913141</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>EcDtwrdn</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.6650467487870619</v>
+        <v>0.5884105023448029</v>
       </c>
       <c r="C3" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.733363273088506</v>
+        <v>0.3054947727109035</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.728543386247825</v>
+        <v>0.9647179668811331</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.223528159342126</v>
+        <v>-0.05622508808933233</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.414939536213983</v>
+        <v>0.4955404916225415</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.168225655688379</v>
+        <v>0.5360844915897844</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.010457225313496</v>
+        <v>0.6665238211106628</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5379701444742412</v>
+        <v>0.8998197861510556</v>
       </c>
       <c r="K3" t="n">
-        <v>2.580606926058192</v>
+        <v>0.1147271467003914</v>
       </c>
       <c r="L3" t="n">
-        <v>1.751044988579344</v>
+        <v>0.8293076591302606</v>
       </c>
       <c r="M3" t="n">
-        <v>1.976231268482565</v>
+        <v>0.04076891807552932</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.128482428529213</v>
+        <v>-0.7077905551901836</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.324848135001084</v>
+        <v>-0.2633797142468563</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.466337553304333</v>
+        <v>-0.3677773969744927</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.489432435945385</v>
+        <v>0.6057534806735301</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.488237531203955</v>
+        <v>-0.6435343448513672</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2371204925442879</v>
+        <v>-0.6445257170629505</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.096014462158608</v>
+        <v>0.08298870714525068</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.337379791594754</v>
+        <v>0.3512974622661043</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.274379469026291</v>
+        <v>-0.6868818011436317</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.52892598578991</v>
+        <v>0.7390200876571147</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.950941819566827</v>
+        <v>0.2645368387370874</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3011569630274204</v>
+        <v>-2.300337836180964</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.388584004630634</v>
+        <v>-0.01602104472586586</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.4420059873576407</v>
+        <v>-1.122791445905212</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.2251193662171381</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2.12781261836607</v>
+        <v>-0.1411009010323414</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.7814664167153837</v>
+        <v>0.2457140565588609</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1.073167985381237</v>
+        <v>0.6888855361079822</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1.255511771574057</v>
+        <v>0.5543588966020235</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ShJjaSDs</t>
+          <t>EJlHkLuh</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.02209214759432</v>
+        <v>0.4516697113122358</v>
       </c>
       <c r="C4" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D4" t="n">
-        <v>1.046897698456144</v>
+        <v>-0.7411917106941414</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.215993413372229</v>
+        <v>-0.8463947153522249</v>
       </c>
       <c r="F4" t="n">
-        <v>1.716671305843482</v>
+        <v>-0.819799277555445</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.714260658906852</v>
+        <v>-0.5066763751706993</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.801525280356029</v>
+        <v>-0.6315519980504378</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.813761620868477</v>
+        <v>-0.663112283709378</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.310069404095763</v>
+        <v>0.9513393861736384</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7596862052104272</v>
+        <v>1.988562709483199</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.04757102804281346</v>
+        <v>1.036931859099038</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9546330758332521</v>
+        <v>1.125111415514157</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.74975191853775</v>
+        <v>-1.559006783097956</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.240884115014425</v>
+        <v>-0.01635589530716495</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.396686874772646</v>
+        <v>-0.7320368172312296</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.392217041606692</v>
+        <v>-0.9190502137679196</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.3404309232228148</v>
+        <v>-0.840448472508012</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4307452578720842</v>
+        <v>-0.2011881694351533</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.281993981576692</v>
+        <v>-0.9990328856938785</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.245165128645187</v>
+        <v>-0.5423885791808932</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.675250182392253</v>
+        <v>-0.2896402787829066</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.797746528727649</v>
+        <v>-0.4647757335459153</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.550544440942571</v>
+        <v>-0.1831610952694795</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.01224978612249866</v>
+        <v>1.040609494687466</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1.396407400614621</v>
+        <v>-0.1857292455462912</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.4231333305889944</v>
+        <v>-0.205623936153312</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.2251193662171381</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.651022741807473</v>
+        <v>-0.2459357802483361</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.6767054967648927</v>
+        <v>-0.0004664868133458394</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.8923497563260847</v>
+        <v>-0.3763524163183445</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1.210319279999318</v>
+        <v>-0.5692382407176584</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n9EQB5cm</t>
+          <t>zD1kyMQb</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.803884200412066</v>
+        <v>-1.58424873295043</v>
       </c>
       <c r="C5" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7793521554016168</v>
+        <v>-1.395370762822294</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0990387224835855</v>
+        <v>-0.5382531532116567</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.596538539253733</v>
+        <v>-1.346402166842419</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3516904948979253</v>
+        <v>-0.5270350142583822</v>
       </c>
       <c r="H5" t="n">
-        <v>1.004058332345692</v>
+        <v>-0.2265655666609598</v>
       </c>
       <c r="I5" t="n">
-        <v>1.233413257796928</v>
+        <v>-0.6065905582941428</v>
       </c>
       <c r="J5" t="n">
-        <v>1.920642358304217</v>
+        <v>1.667486500802778</v>
       </c>
       <c r="K5" t="n">
-        <v>1.333625521932126</v>
+        <v>0.6328891448289291</v>
       </c>
       <c r="L5" t="n">
-        <v>1.56655366950045</v>
+        <v>1.309987894613429</v>
       </c>
       <c r="M5" t="n">
-        <v>1.580370153298441</v>
+        <v>1.876839778343433</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.141549629349027</v>
+        <v>-1.379172368751244</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1486317115225139</v>
+        <v>-1.361578777086047</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.798796547983101</v>
+        <v>-1.790123704643656</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.322034455928351</v>
+        <v>-1.963810133821588</v>
       </c>
       <c r="R5" t="n">
-        <v>-2.391362011974745</v>
+        <v>-1.517791833086104</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.947040719645035</v>
+        <v>-0.2565895071653233</v>
       </c>
       <c r="T5" t="n">
-        <v>1.728995269466251</v>
+        <v>-0.9096462519643382</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7333954923320523</v>
+        <v>-1.053131157116572</v>
       </c>
       <c r="V5" t="n">
-        <v>1.058321766130438</v>
+        <v>-1.672192668063477</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7951239157240891</v>
+        <v>-1.219974379695743</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8267584970551792</v>
+        <v>-0.3984551631084463</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.839914785629471</v>
+        <v>0.1142533583306206</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9062105841742676</v>
+        <v>-0.7287330051421617</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.365207316272698</v>
+        <v>-0.6058357775292719</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.2251193662171381</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7051391945830482</v>
+        <v>-0.670343710145443</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.8396669451738435</v>
+        <v>-0.6425792484185543</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.05870278947993681</v>
+        <v>-1.157759015640385</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2980663368035887</v>
+        <v>-0.7762689736211634</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tWiaepD6</t>
+          <t>rw5cZaeB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5884105023448029</v>
+        <v>-0.6650467487870619</v>
       </c>
       <c r="C6" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3927186463279905</v>
+        <v>-0.5340350108535594</v>
       </c>
       <c r="E6" t="n">
-        <v>1.11990078950063</v>
+        <v>-0.03784874075713161</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2142059548754243</v>
+        <v>-0.4775073995189119</v>
       </c>
       <c r="G6" t="n">
-        <v>1.10803413252056</v>
+        <v>0.02172916310133817</v>
       </c>
       <c r="H6" t="n">
-        <v>1.036768198857284</v>
+        <v>-0.009253523801841301</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9644030928941815</v>
+        <v>-0.1589289935558287</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2730279541355503</v>
+        <v>0.425978725822224</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8812680354377661</v>
+        <v>0.4029280272242796</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8418067700913122</v>
+        <v>0.7876885052156318</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8863561073777062</v>
+        <v>0.7484230761535636</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4979837384523526</v>
+        <v>-0.5789092249083732</v>
       </c>
       <c r="O6" t="n">
-        <v>1.458516006962445</v>
+        <v>-1.257278293110975</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7307827593553481</v>
+        <v>-1.20615225312095</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.101765208608354</v>
+        <v>-0.8880216154577056</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5998082622371856</v>
+        <v>-0.8961205295418277</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4758074698928407</v>
+        <v>0.2834450880318979</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5135291713373615</v>
+        <v>0.3201711099994415</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2565498264537479</v>
+        <v>-0.007221255071568696</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5768835013463653</v>
+        <v>0.06472591019703769</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2127445627719131</v>
+        <v>-0.07994138520595755</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0184864158399117</v>
+        <v>-0.5093581458575859</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.310809373086348</v>
+        <v>0.4718939570523968</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.5119875439493923</v>
+        <v>-0.0414375671221744</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.155153229905262</v>
+        <v>-0.5468789300313569</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.2251193662171381</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.07008724378484328</v>
+        <v>-0.3475566304093065</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.4263532473849332</v>
+        <v>-0.09365063871314851</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.4338226543702541</v>
+        <v>-0.08455031063413118</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.1842548505477969</v>
+        <v>0.05346122150111594</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>zypxSHmo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.143639517401047</v>
+        <v>-1.02209214759432</v>
       </c>
       <c r="C7" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D7" t="n">
-        <v>0.883352935424105</v>
+        <v>0.7198081723920667</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1777416053066431</v>
+        <v>0.5666555736385971</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7512326754840287</v>
+        <v>1.365602712985499</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2519461028279841</v>
+        <v>1.068630064338467</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.134030877442367</v>
+        <v>1.366405730839369</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6437298881094694</v>
+        <v>0.9172142973641186</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1906268207333113</v>
+        <v>-0.9669316338719981</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3824215385024105</v>
+        <v>-1.058998121601242</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0291874890815672</v>
+        <v>0.05187581180721516</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2420111233126476</v>
+        <v>0.1929091287094967</v>
       </c>
       <c r="N7" t="n">
-        <v>0.664945474323055</v>
+        <v>0.6349730719319362</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9422461022538748</v>
+        <v>1.59783389842012</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6857816527541832</v>
+        <v>-0.165411052387417</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1779531261680481</v>
+        <v>0.07115995636339026</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.2043436726957092</v>
+        <v>0.3699032859679093</v>
       </c>
       <c r="S7" t="n">
-        <v>1.224856481308054</v>
+        <v>-0.1465839901438748</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.745868127854222</v>
+        <v>0.187633958858611</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7865522662767708</v>
+        <v>2.727042633142159</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.09156332607623</v>
+        <v>2.571234567510245</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9569323075448309</v>
+        <v>3.12813999921605</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5040317766765552</v>
+        <v>2.311477672591076</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6669955540236613</v>
+        <v>0.01718652810653544</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.5833407191566196</v>
+        <v>2.098264265242693</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.1699036905104629</v>
+        <v>-0.4468029097893985</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.2251193662171381</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.6270278546927773</v>
+        <v>2.302137362569602</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.3846387060725539</v>
+        <v>1.725456592933671</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.8223526695010606</v>
+        <v>1.458896307121927</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.7887112722225048</v>
+        <v>1.850179116634513</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UiYgHRZP</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.295573729659454</v>
+        <v>1.454435512217728</v>
       </c>
       <c r="C8" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D8" t="n">
-        <v>1.074155158961483</v>
+        <v>0.4036216305301263</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07054099706482991</v>
+        <v>0.2180856722167749</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8719125042789606</v>
+        <v>-0.4182645744741268</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2931543160635756</v>
+        <v>-0.1429221505514097</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.02460589292963786</v>
+        <v>0.7245993483317189</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7779922259364833</v>
+        <v>0.5812966214914635</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7904616410835954</v>
+        <v>0.6770698000332979</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6506555812547905</v>
+        <v>0.883444297156066</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3241290251294977</v>
+        <v>-0.85428498326492</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4970683718097085</v>
+        <v>-0.8922881953268644</v>
       </c>
       <c r="N8" t="n">
-        <v>1.234421119754311</v>
+        <v>-0.9895311376667</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02812424955112639</v>
+        <v>2.303150053088667</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1075920967911095</v>
+        <v>0.2089666850986735</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6396961217273981</v>
+        <v>0.6554431353698323</v>
       </c>
       <c r="R8" t="n">
-        <v>0.09257396481797479</v>
+        <v>0.3802129261593566</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2340353686803432</v>
+        <v>0.04614519973263987</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2997139276921812</v>
+        <v>-0.1530955805113741</v>
       </c>
       <c r="U8" t="n">
-        <v>1.048593901005892</v>
+        <v>0.744104798696537</v>
       </c>
       <c r="V8" t="n">
-        <v>1.756824140554</v>
+        <v>1.446095189650346</v>
       </c>
       <c r="W8" t="n">
-        <v>1.255080079783111</v>
+        <v>0.7393964478475511</v>
       </c>
       <c r="X8" t="n">
-        <v>0.872664404417487</v>
+        <v>0.8193370075428971</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4080897902364807</v>
+        <v>0.2731319352922686</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9775187453669298</v>
+        <v>0.6354369774729079</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.5905540018759665</v>
+        <v>1.063089468784237</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.2251193662171381</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.7706874871027347</v>
+        <v>0.9040204318524592</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.028292950448884</v>
+        <v>0.2704064060367168</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.4503472344796233</v>
+        <v>0.4605044281202392</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.7299816215065771</v>
+        <v>0.5337295495283203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Gl6s8NdC</t>
+          <t>viJXIvBU</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.454435512217728</v>
+        <v>-1.295573729659454</v>
       </c>
       <c r="C9" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.079184220960354</v>
+        <v>1.13412157207323</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02672455550745966</v>
+        <v>1.297500861442786</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4665365059920998</v>
+        <v>0.6283586679837349</v>
       </c>
       <c r="G9" t="n">
-        <v>0.184612288931023</v>
+        <v>0.9193191160411144</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1220492060314054</v>
+        <v>0.4823442558272417</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3393969472403025</v>
+        <v>0.9309776960603869</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7063009775471858</v>
+        <v>-0.7927492494514725</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5048862066541164</v>
+        <v>-0.9255308358609999</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8866365743899741</v>
+        <v>-0.8442976605033163</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3964558731609966</v>
+        <v>-0.4842196965617446</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2282321169322839</v>
+        <v>0.7968240448439774</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6990128578358025</v>
+        <v>1.645399702990012</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6585090648599639</v>
+        <v>0.4243422946949187</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5481275611667169</v>
+        <v>0.9888289150777131</v>
       </c>
       <c r="R9" t="n">
-        <v>1.340727737329203</v>
+        <v>0.2781474882640277</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6472585375709</v>
+        <v>-0.3705630394674693</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7719812759530676</v>
+        <v>-0.03992793772441061</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.08970988538443372</v>
+        <v>-0.07256360645818749</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1172250460519008</v>
+        <v>0.1049168659185754</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1646103091774305</v>
+        <v>-0.06226866754617507</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1033492937589512</v>
+        <v>-0.008132192753633184</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.2468817407897572</v>
+        <v>-0.3899890053469613</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.4599386239200811</v>
+        <v>-0.2382300943575919</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.5104344536084043</v>
+        <v>0.3045314995391278</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.2251193662171381</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.05415633915452675</v>
+        <v>0.1635317308394537</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.5470195168850328</v>
+        <v>-0.5262730418083605</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.1191234079235238</v>
+        <v>0.4801566203444011</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.2301580164722766</v>
+        <v>0.03696158208337203</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>rPPOK0tI</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1398,391 +1398,1191 @@
         <v>-0.5104376201607318</v>
       </c>
       <c r="D10" t="n">
-        <v>1.455759606036239</v>
+        <v>1.221345445690317</v>
       </c>
       <c r="E10" t="n">
-        <v>1.86721916555256</v>
+        <v>-0.9144690928124901</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6086110596354734</v>
+        <v>-0.3195265327328191</v>
       </c>
       <c r="G10" t="n">
-        <v>1.296652436543449</v>
+        <v>-0.9220280293280034</v>
       </c>
       <c r="H10" t="n">
-        <v>1.034596589462324</v>
+        <v>-0.7081199499934401</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6147220183252579</v>
+        <v>-1.011552096857418</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1852996301381928</v>
+        <v>0.9263543157731902</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0467932473631813</v>
+        <v>0.8686001456038628</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.408800470595793</v>
+        <v>-0.553520049051015</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.188294219775105</v>
+        <v>-0.7078182675423941</v>
       </c>
       <c r="N10" t="n">
-        <v>1.444227936492142</v>
+        <v>0.8028185253222011</v>
       </c>
       <c r="O10" t="n">
-        <v>1.834372442779236</v>
+        <v>0.09852946909290786</v>
       </c>
       <c r="P10" t="n">
-        <v>1.431837595960575</v>
+        <v>0.1525932033922739</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.724869054404841</v>
+        <v>-0.5557711925732903</v>
       </c>
       <c r="R10" t="n">
-        <v>1.054807049353063</v>
+        <v>0.5338265650119225</v>
       </c>
       <c r="S10" t="n">
-        <v>1.050307070524537</v>
+        <v>-1.678071896772522</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1526068526874382</v>
+        <v>-1.24002626094509</v>
       </c>
       <c r="U10" t="n">
-        <v>1.007238353722081</v>
+        <v>0.2192022451439633</v>
       </c>
       <c r="V10" t="n">
-        <v>0.563615694842533</v>
+        <v>0.122833541087114</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6013406822535509</v>
+        <v>0.244341699084764</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.02756457604006596</v>
+        <v>0.06835019081414516</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.42141112041306</v>
+        <v>-0.09562480114053012</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.5134940120153506</v>
+        <v>0.2873892130656674</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.7255144971642551</v>
+        <v>0.4276342340203129</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.2251193662171381</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.4275568167293096</v>
+        <v>0.1845956965226227</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.003173662909574142</v>
+        <v>-0.04740079981202564</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.582861381580555</v>
+        <v>0.865189988692348</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.8103743833628425</v>
+        <v>0.3916848382672793</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.58424873295043</v>
+        <v>-0.5662895108190968</v>
       </c>
       <c r="C11" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.855673044816568</v>
+        <v>-0.9701543789389947</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1393999075322146</v>
+        <v>0.3116859600145848</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4314296467063013</v>
+        <v>-0.45775979117065</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1210520818091885</v>
+        <v>0.3967663726677186</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.387128936300848</v>
+        <v>1.214671682308225</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08431873276610968</v>
+        <v>1.004744089072898</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4552021726644043</v>
+        <v>0.4691175689622648</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1368226571371469</v>
+        <v>-0.4839228060945257</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3426385182416739</v>
+        <v>-1.198609487371789</v>
       </c>
       <c r="M11" t="n">
-        <v>0.81448016874311</v>
+        <v>-0.6985187187647576</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.744835677922892</v>
+        <v>-0.1503038707153752</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.09862800446159004</v>
+        <v>1.86686155089011</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9358486357082128</v>
+        <v>1.574939511061436</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.5630832387090803</v>
+        <v>2.039524319543907</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.692333308424218</v>
+        <v>0.9029116838657384</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.362461894436495</v>
+        <v>0.03772609762708</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.081189718165882</v>
+        <v>0.8833444599046752</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.497461831007993</v>
+        <v>-0.2337331614603278</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.530242674395607</v>
+        <v>0.01618298482937315</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.121011302434617</v>
+        <v>-0.3358613839389847</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5017696739347368</v>
+        <v>-0.2609423007687084</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2441862263003836</v>
+        <v>0.07722434400282864</v>
       </c>
       <c r="Z11" t="n">
-        <v>-1.374298364917666</v>
+        <v>-0.3200351660196263</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.4843269881924209</v>
+        <v>-0.8496122705695535</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.4094864374096538</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.8122439696900956</v>
+        <v>-0.2385064189848742</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.9177307247466148</v>
+        <v>-0.432780942446059</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.4136772196771623</v>
+        <v>-0.3496139599609554</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.9574943312474604</v>
+        <v>-0.2403217591697301</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>KMCY9qSa</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-1.58424873295043</v>
+        <v>1.803884200412066</v>
       </c>
       <c r="C12" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.588549931864239</v>
+        <v>-0.6430648528749183</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06333448700789746</v>
+        <v>-0.4059276934267164</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5433327606797834</v>
+        <v>-1.037022969386322</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3968639188523488</v>
+        <v>-0.2821784167476653</v>
       </c>
       <c r="H12" t="n">
-        <v>0.03507458669257953</v>
+        <v>-0.2321755575979408</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.129084889239941</v>
+        <v>-0.7744317603441775</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5118773406773776</v>
+        <v>0.7747797423685382</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4645435931383924</v>
+        <v>0.1685354796392414</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6194458931870493</v>
+        <v>-0.05574053386701496</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.001076833084688669</v>
+        <v>0.1162346740387301</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6418512699297225</v>
+        <v>0.2033704774998261</v>
       </c>
       <c r="O12" t="n">
-        <v>2.761584039423209</v>
+        <v>-0.5799335276638728</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1726384218369553</v>
+        <v>-0.5954395346349531</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1850025017905536</v>
+        <v>-0.01700106301238612</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.4119110952168498</v>
+        <v>-0.3005669811492179</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4509962592326731</v>
+        <v>0.5804533365853792</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6954438285592356</v>
+        <v>-1.164001932777264</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.282037787260925</v>
+        <v>-0.4145396320746092</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3481865040074222</v>
+        <v>-0.1616660517190578</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2644683915125302</v>
+        <v>0.09576956652016193</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.008627484039973623</v>
+        <v>-0.1778704463145465</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.1599546164248236</v>
+        <v>0.5176243118849804</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.2401944145340327</v>
+        <v>-0.3417913435141088</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.4659657838108666</v>
+        <v>0.2498236725953098</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.6474636137697007</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.02128809688704931</v>
+        <v>-0.2734307350392787</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.1788151345185542</v>
+        <v>0.2150558848849017</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.01508618884814233</v>
+        <v>0.3474460998985798</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.2906562945205582</v>
+        <v>-0.400153320013915</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.6650467487870619</v>
+        <v>-0.5662895108190968</v>
       </c>
       <c r="C13" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03837165975857418</v>
+        <v>1.619304369068277</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7229487850331426</v>
+        <v>2.084703102885732</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02715370271443903</v>
+        <v>0.6854073143231572</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3267858530301939</v>
+        <v>2.230355940339265</v>
       </c>
       <c r="H13" t="n">
-        <v>1.172789914596171</v>
+        <v>1.226822799655519</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9507290669167197</v>
+        <v>1.073035632604012</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5565180048249678</v>
+        <v>-0.3501006134154062</v>
       </c>
       <c r="K13" t="n">
-        <v>0.07195835002495148</v>
+        <v>-0.727664194716408</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8629652811759516</v>
+        <v>-0.340472399790393</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9021745555811371</v>
+        <v>0.2919848317339145</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.198259714541165</v>
+        <v>0.6709399548012787</v>
       </c>
       <c r="O13" t="n">
-        <v>1.718130058832414</v>
+        <v>1.399825941646369</v>
       </c>
       <c r="P13" t="n">
-        <v>1.966662935226419</v>
+        <v>0.1525932033922739</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.725373538107392</v>
+        <v>0.1858754705639074</v>
       </c>
       <c r="R13" t="n">
-        <v>1.164776544728501</v>
+        <v>0.3276337611829751</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1469555263193388</v>
+        <v>1.226788531960348</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2905804240181828</v>
+        <v>0.3646766398185615</v>
       </c>
       <c r="U13" t="n">
-        <v>1.056516504200412</v>
+        <v>0.9289201021749095</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6384536708511658</v>
+        <v>1.661750284974017</v>
       </c>
       <c r="W13" t="n">
-        <v>1.560782663746029</v>
+        <v>0.5177923814610468</v>
       </c>
       <c r="X13" t="n">
-        <v>1.168068591769961</v>
+        <v>-0.09517792708974925</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.78792933771185</v>
+        <v>1.924977468540129</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.5862271201591561</v>
+        <v>0.7504561316569899</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.06176289277219156</v>
+        <v>0.2097444450071537</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1.732308149830769</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.7277965334066259</v>
+        <v>0.5225765870010221</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.5971064914558086</v>
+        <v>0.2246638399757624</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.059583432783783</v>
+        <v>-0.03101841151872283</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.068839147798202</v>
+        <v>0.2326267230093512</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>SSZaQ4Ct</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.6650467487870619</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.733363273088506</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-2.728543386247825</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.223528159342126</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-2.414939536213983</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-2.168225655688379</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-2.010457225313496</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5379701444742412</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.580606926058192</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.751044988579344</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.976231268482565</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-2.128482428529213</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-3.324848135001084</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1.466337553304333</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1.489432435945385</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1.488237531203955</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2371204925442879</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1.096014462158608</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-2.413497086643679</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-2.35513235012669</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-2.556332622996276</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.922667592166162</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.1433158780932554</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-1.483260898347282</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.5024791637578604</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-2.201948109163806</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.784587231222924</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-1.075248493237891</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-1.270552079696984</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ShJjaSDs</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-1.02209214759432</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.046897698456144</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.215993413372229</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.716671305843482</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.714260658906852</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-1.801525280356029</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1.813761620868477</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-1.310069404095763</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.7596862052104272</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.04757102804281346</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.9546330758332521</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.74975191853775</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1.240884115014425</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.396686874772646</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.392217041606692</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.3404309232228148</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.4307452578720842</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-2.281993981576692</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-2.245165128645187</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-2.675250182392253</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-1.797746528727649</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-1.550544440942571</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.01224978612249866</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-1.396407400614621</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.4231333305889944</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-1.651022741807473</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.6767054967648927</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.8923497563260847</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-1.210319279999318</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-1.295573729659454</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.074155158961483</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.07054099706482991</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8719125042789606</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.2931543160635756</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.02460589292963786</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7779922259364833</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.7904616410835954</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.6506555812547905</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3241290251294977</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.4970683718097085</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.234421119754311</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.02812424955112639</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.1075920967911095</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.6396961217273981</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.09257396481797479</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.2340353686803432</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.2997139276921812</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.051823396961728</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.711751327189215</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.258829522567305</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.9455393660845612</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.3785005600893765</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.9618073637533364</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.4870476811981115</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.7517493563310037</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.132663448738244</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.4785294234407245</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.7242818333041107</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-1.58424873295043</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.7793521554016168</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0990387224835855</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-1.596538539253733</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.3516904948979253</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.004058332345692</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.233413257796928</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.920642358304217</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.333625521932126</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.56655366950045</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.580370153298441</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-3.141549629349027</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.1486317115225139</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-1.798796547983101</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1.322034455928351</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-2.391362011974745</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.947040719645035</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.728995269466251</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.7409470562709264</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.059169328750295</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.7857233234695519</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.8246465755109198</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.8295749085858884</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.9006153322269251</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.279862446314827</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.7086075700457822</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8017585813846587</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.0841552302552305</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.3004928249209269</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.4516697113122358</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.883352935424105</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.1777416053066431</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.7512326754840287</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.2519461028279841</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.134030877442367</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.6437298881094694</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.1906268207333113</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.3824215385024105</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.0291874890815672</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2420111233126476</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.664945474323055</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.9422461022538748</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.6857816527541832</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.1779531261680481</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.2043436726957092</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.224856481308054</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.745868127854222</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.7924772359514176</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-1.118922338303826</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.9338871361777553</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.4937708093546779</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.6145262796348957</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.6079881279265772</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.1861693551448997</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.6390420734916064</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.3675369970112554</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.814739559718774</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.7901506126776709</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>tWiaepD6</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.5884105023448029</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.3927186463279905</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.11990078950063</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.2142059548754243</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.10803413252056</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.036768198857284</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9644030928941815</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.2730279541355503</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.8812680354377661</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.8418067700913122</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.8863561073777062</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.4979837384523526</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.458516006962445</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.7307827593553481</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.101765208608354</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.5998082622371856</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.4758074698928407</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.5135291713373615</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.2565498264537479</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.5768835013463657</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.2127445627719131</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.0184864158399117</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-1.310809373086348</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.5119875439493923</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.155153229905262</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.07008724378484328</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.4263532473849332</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-0.4338226543702541</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-0.1842548505477969</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.454435512217728</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1.079184220960354</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.02672455550745966</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.4665365059920998</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.184612288931023</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.1220492060314054</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.3393969472403025</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7063009775471858</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.5048862066541164</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.8866365743899741</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.3964558731609966</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.2282321169322839</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.6990128578358025</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.6585090648599639</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.5481275611667169</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.340727737329203</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.6472585375709</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.7719812759530676</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.08970988538443372</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.1172250460519011</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.1646103091774305</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.1033492937589512</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.2468817407897572</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.4599386239200811</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.5104344536084043</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.05415633915452675</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-0.5470195168850328</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.1191234079235238</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-0.2301580164722766</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.029019717894186</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.455759606036239</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.86721916555256</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.6086110596354734</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.296652436543449</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.034596589462324</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6147220183252579</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.1852996301381928</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.0467932473631813</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-1.408800470595793</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-1.188294219775105</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.444227936492142</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.834372442779236</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.431837595960575</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.724869054404841</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.054807049353063</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.050307070524537</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.1526068526874382</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.9877918658577072</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.5741574159381375</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.5902029015245114</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.02979940765374333</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-1.419028180689758</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.5064634787735643</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.7427385536568082</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.4081475639717783</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.01351322886216962</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.5696078518949165</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.79227227823834</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -649,40 +649,40 @@
         <v>-0.9314295492597725</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1546303642160671</v>
+        <v>0.1030718558094473</v>
       </c>
       <c r="V2" t="n">
-        <v>0.08014433657953772</v>
+        <v>0.08218466969481666</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3199561134554467</v>
+        <v>-0.3954492963433013</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2724667629090863</v>
+        <v>0.2116996295901546</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.692596598741033</v>
+        <v>-0.6870940150016284</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.1823803221050495</v>
+        <v>-0.210631833100806</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.6731875527703894</v>
+        <v>-0.7480737278539187</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.268848463154266</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2524502112373228</v>
+        <v>0.2344041004819523</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.4257636456022268</v>
+        <v>-0.4933759345496668</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.06473170698887788</v>
+        <v>-0.06867206549563315</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.09361418455913141</v>
+        <v>-0.09394163451268289</v>
       </c>
     </row>
     <row r="3">
@@ -749,40 +749,40 @@
         <v>0.08298870714525068</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3512974622661043</v>
+        <v>0.3616772142085249</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6868818011436317</v>
+        <v>-0.6859485805994278</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7390200876571147</v>
+        <v>0.6654914323009168</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2645368387370874</v>
+        <v>0.2413909990932569</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2.300337836180964</v>
+        <v>-2.335226558613785</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.01602104472586586</v>
+        <v>-0.01295353340217253</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.122791445905212</v>
+        <v>-1.088161103482283</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-1.264286369656012</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.1411009010323414</v>
+        <v>-0.13994721978398</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2457140565588609</v>
+        <v>0.2186597035588624</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.6888855361079822</v>
+        <v>0.6431706719125693</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5543588966020235</v>
+        <v>0.5723749411618101</v>
       </c>
     </row>
     <row r="4">
@@ -849,40 +849,40 @@
         <v>-0.9990328856938785</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5423885791808932</v>
+        <v>-0.5393860152779942</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2896402787829066</v>
+        <v>-0.255287586852404</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4647757335459153</v>
+        <v>-0.5032297135016039</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1831610952694795</v>
+        <v>-0.234937436733229</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.040609494687466</v>
+        <v>1.022988589919811</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.1857292455462912</v>
+        <v>-0.1681070041090948</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.205623936153312</v>
+        <v>-0.2230521571086078</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>0.1626952915547923</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.2459357802483361</v>
+        <v>-0.2366063384716449</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.0004664868133458394</v>
+        <v>-0.03592521743744009</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.3763524163183445</v>
+        <v>-0.3931363370846949</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.5692382407176584</v>
+        <v>-0.5544181316935382</v>
       </c>
     </row>
     <row r="5">
@@ -970,7 +970,7 @@
         <v>-0.6058357775292719</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>0.2704775470914114</v>
       </c>
       <c r="AC5" t="n">
         <v>-0.670343710145443</v>
@@ -1049,40 +1049,40 @@
         <v>0.3201711099994415</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.007221255071568696</v>
+        <v>0.007413302605671451</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06472591019703769</v>
+        <v>0.05000305192201759</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.07994138520595755</v>
+        <v>-0.1062176960997143</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5093581458575859</v>
+        <v>-0.5328227268423822</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4718939570523968</v>
+        <v>0.3637824029748595</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0414375671221744</v>
+        <v>-0.02072158102829051</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.5468789300313569</v>
+        <v>-0.5325300491131952</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>-0.5574060161717206</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.3475566304093065</v>
+        <v>-0.3462141151980477</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.09365063871314851</v>
+        <v>-0.116885755252961</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.08455031063413118</v>
+        <v>-0.08597242611224065</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.05346122150111594</v>
+        <v>0.0916037435630824</v>
       </c>
     </row>
     <row r="7">
@@ -1149,40 +1149,40 @@
         <v>0.187633958858611</v>
       </c>
       <c r="U7" t="n">
-        <v>2.727042633142159</v>
+        <v>2.726472064198609</v>
       </c>
       <c r="V7" t="n">
-        <v>2.571234567510245</v>
+        <v>2.560076495786066</v>
       </c>
       <c r="W7" t="n">
-        <v>3.12813999921605</v>
+        <v>3.130840381735544</v>
       </c>
       <c r="X7" t="n">
-        <v>2.311477672591076</v>
+        <v>2.297005853220077</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01718652810653544</v>
+        <v>0.09012025309364756</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.098264265242693</v>
+        <v>2.141303327182254</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.4468029097893985</v>
+        <v>-0.3333060289143925</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-1.542493021067405</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.302137362569602</v>
+        <v>2.321980892897736</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.725456592933671</v>
+        <v>1.67977502363862</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.458896307121927</v>
+        <v>1.522928845014227</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.850179116634513</v>
+        <v>1.853147756323297</v>
       </c>
     </row>
     <row r="8">
@@ -1249,40 +1249,40 @@
         <v>-0.1530955805113741</v>
       </c>
       <c r="U8" t="n">
-        <v>0.744104798696537</v>
+        <v>0.7151203308150114</v>
       </c>
       <c r="V8" t="n">
-        <v>1.446095189650346</v>
+        <v>1.388971658823447</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7393964478475511</v>
+        <v>0.6983972530623364</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8193370075428971</v>
+        <v>0.7959012134279845</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2731319352922686</v>
+        <v>0.196320358195275</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6354369774729079</v>
+        <v>0.5843884020012793</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.063089468784237</v>
+        <v>1.020591201652758</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.40326149795022</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.9040204318524592</v>
+        <v>0.8720072976127087</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.2704064060367168</v>
+        <v>0.2046789489173604</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.4605044281202392</v>
+        <v>0.4057787081570189</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.5337295495283203</v>
+        <v>0.5341001796955279</v>
       </c>
     </row>
     <row r="9">
@@ -1349,40 +1349,40 @@
         <v>-0.03992793772441061</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.07256360645818749</v>
+        <v>-0.09485651164719358</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1049168659185754</v>
+        <v>0.02296090961005158</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.06226866754617507</v>
+        <v>-0.05815665811919542</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.008132192753633184</v>
+        <v>-0.0138959794230075</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.3899890053469613</v>
+        <v>-0.6276192801161488</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.2382300943575919</v>
+        <v>-0.283975462448783</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.3045314995391278</v>
+        <v>0.2584851952568101</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-2.122766998451137</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1635317308394537</v>
+        <v>0.1289286251062631</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.5262730418083605</v>
+        <v>-0.523066619456615</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.4801566203444011</v>
+        <v>0.509089733215228</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.03696158208337203</v>
+        <v>0.05123624104750588</v>
       </c>
     </row>
     <row r="10">
@@ -1449,40 +1449,40 @@
         <v>-1.24002626094509</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2192022451439633</v>
+        <v>0.2133487367563556</v>
       </c>
       <c r="V10" t="n">
-        <v>0.122833541087114</v>
+        <v>0.1109451228500799</v>
       </c>
       <c r="W10" t="n">
-        <v>0.244341699084764</v>
+        <v>0.2353254987732341</v>
       </c>
       <c r="X10" t="n">
-        <v>0.06835019081414516</v>
+        <v>0.06638399263469827</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.09562480114053012</v>
+        <v>-0.06753605843951438</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2873892130656674</v>
+        <v>0.2690494303499357</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.4276342340203129</v>
+        <v>0.3882220561643928</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>-0.4734844351960781</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1845956965226227</v>
+        <v>0.1745564042624848</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.04740079981202564</v>
+        <v>-0.08995915988470569</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.865189988692348</v>
+        <v>0.8168690375583273</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3916848382672793</v>
+        <v>0.3706902585530792</v>
       </c>
     </row>
     <row r="11">
@@ -1549,40 +1549,40 @@
         <v>0.8833444599046752</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2337331614603278</v>
+        <v>-0.2378249835614394</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01618298482937315</v>
+        <v>0.0284249835210436</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3358613839389847</v>
+        <v>-0.3655240010016889</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2609423007687084</v>
+        <v>-0.2713123325217692</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.07722434400282864</v>
+        <v>0.04386318787659076</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.3200351660196263</v>
+        <v>-0.3267508992655108</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.8496122705695535</v>
+        <v>-0.7373589368766748</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>-0.3459966621460504</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.2385064189848742</v>
+        <v>-0.2541604808366515</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.432780942446059</v>
+        <v>-0.4596997938929374</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.3496139599609554</v>
+        <v>-0.4034836813035892</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.2403217591697301</v>
+        <v>-0.2301888023653441</v>
       </c>
     </row>
     <row r="12">
@@ -1649,40 +1649,40 @@
         <v>-1.164001932777264</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4145396320746092</v>
+        <v>-0.4104478099734976</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1616660517190578</v>
+        <v>-0.1739080504107283</v>
       </c>
       <c r="W12" t="n">
-        <v>0.09576956652016193</v>
+        <v>0.125432183582866</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1778704463145465</v>
+        <v>-0.1675004145614857</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5176243118849804</v>
+        <v>0.5509854680112182</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.3417913435141088</v>
+        <v>-0.3350756102682244</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2498236725953098</v>
+        <v>0.1375703389024312</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>0.6051565601945748</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.2734307350392787</v>
+        <v>-0.2577766731875013</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.2150558848849017</v>
+        <v>0.2419747363317801</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.3474460998985798</v>
+        <v>0.4013158212412136</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.400153320013915</v>
+        <v>-0.410286276818301</v>
       </c>
     </row>
     <row r="13">
@@ -1749,40 +1749,40 @@
         <v>0.3646766398185615</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9289201021749095</v>
+        <v>0.9108737201052344</v>
       </c>
       <c r="V13" t="n">
-        <v>1.661750284974017</v>
+        <v>1.643132245297101</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5177923814610468</v>
+        <v>0.5482733151385472</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.09517792708974925</v>
+        <v>-0.07169747963070709</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.924977468540129</v>
+        <v>1.925914078538326</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.7504561316569899</v>
+        <v>0.741817018133121</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2097444450071537</v>
+        <v>0.2365591693194326</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>-1.203469980141774</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.5225765870010221</v>
+        <v>0.5146078545828463</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.2246638399757624</v>
+        <v>0.2326194368056198</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.03101841151872283</v>
+        <v>-0.02853565319485132</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.2326267230093512</v>
+        <v>0.2183088838315639</v>
       </c>
     </row>
     <row r="14">
@@ -1849,40 +1849,40 @@
         <v>-1.096014462158608</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.413497086643679</v>
+        <v>-2.407593909960939</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.35513235012669</v>
+        <v>-2.325887575474367</v>
       </c>
       <c r="W14" t="n">
-        <v>-2.556332622996276</v>
+        <v>-2.552503474303547</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.922667592166162</v>
+        <v>-1.913851359678813</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1433158780932554</v>
+        <v>0.1351157619865931</v>
       </c>
       <c r="Z14" t="n">
-        <v>-1.483260898347282</v>
+        <v>-1.476164781773018</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.5024791637578604</v>
+        <v>0.5203466476481359</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.584018625630826</v>
       </c>
       <c r="AC14" t="n">
-        <v>-2.201948109163806</v>
+        <v>-2.199934488387146</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.784587231222924</v>
+        <v>-0.7753015586565496</v>
       </c>
       <c r="AE14" t="n">
-        <v>-1.075248493237891</v>
+        <v>-1.080077811892899</v>
       </c>
       <c r="AF14" t="n">
-        <v>-1.270552079696984</v>
+        <v>-1.257463677157985</v>
       </c>
     </row>
     <row r="15">
@@ -1949,40 +1949,40 @@
         <v>-2.281993981576692</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.245165128645187</v>
+        <v>-2.169070928635936</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.675250182392253</v>
+        <v>-2.645601591810865</v>
       </c>
       <c r="W15" t="n">
-        <v>-1.797746528727649</v>
+        <v>-1.733774306357136</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.550544440942571</v>
+        <v>-1.510306294385486</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.01224978612249866</v>
+        <v>0.01253453916140948</v>
       </c>
       <c r="Z15" t="n">
-        <v>-1.396407400614621</v>
+        <v>-1.351145063704009</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.4231333305889944</v>
+        <v>-0.3405952064269139</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0.0003631440993174694</v>
       </c>
       <c r="AC15" t="n">
-        <v>-1.651022741807473</v>
+        <v>-1.614861189952865</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.6767054967648927</v>
+        <v>-0.5896541706400976</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.8923497563260847</v>
+        <v>-0.8556427366031608</v>
       </c>
       <c r="AF15" t="n">
-        <v>-1.210319279999318</v>
+        <v>-1.210438025586871</v>
       </c>
     </row>
     <row r="16">
@@ -2049,40 +2049,40 @@
         <v>-0.2997139276921812</v>
       </c>
       <c r="U16" t="n">
-        <v>1.051823396961728</v>
+        <v>1.048564663640672</v>
       </c>
       <c r="V16" t="n">
-        <v>1.711751327189215</v>
+        <v>1.671199706523057</v>
       </c>
       <c r="W16" t="n">
-        <v>1.258829522567305</v>
+        <v>1.321955701199803</v>
       </c>
       <c r="X16" t="n">
-        <v>0.9455393660845612</v>
+        <v>1.000402594420134</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.3785005600893765</v>
+        <v>0.3762928365221972</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.9618073637533364</v>
+        <v>0.9389056640515546</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.4870476811981115</v>
+        <v>-0.4832613584346629</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>0.6474636137697007</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.7517493563310037</v>
+        <v>0.7372492798080433</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.132663448738244</v>
+        <v>1.181674137405904</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.4785294234407245</v>
+        <v>0.5120188893057094</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.7242818333041107</v>
+        <v>0.7102698539730482</v>
       </c>
     </row>
     <row r="17">
@@ -2149,40 +2149,40 @@
         <v>1.728995269466251</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7409470562709264</v>
+        <v>0.7469570328347717</v>
       </c>
       <c r="V17" t="n">
-        <v>1.059169328750295</v>
+        <v>1.110947289862291</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7857233234695519</v>
+        <v>0.8513108207060411</v>
       </c>
       <c r="X17" t="n">
-        <v>0.8246465755109198</v>
+        <v>0.844739969336776</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.8295749085858884</v>
+        <v>1.110294021894559</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.9006153322269251</v>
+        <v>0.9361970724201581</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.279862446314827</v>
+        <v>1.273410924283941</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>0.2508349865029558</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.7086075700457822</v>
+        <v>0.7400433737539514</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.8017585813846587</v>
+        <v>0.8163208394665373</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.0841552302552305</v>
+        <v>-0.06254416027563608</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.3004928249209269</v>
+        <v>0.2551137188580083</v>
       </c>
     </row>
     <row r="18">
@@ -2249,40 +2249,40 @@
         <v>-0.745868127854222</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7924772359514176</v>
+        <v>-0.7767738823176475</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.118922338303826</v>
+        <v>-1.067728525593205</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.9338871361777553</v>
+        <v>-0.8885614174741377</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4937708093546779</v>
+        <v>-0.4523377014783136</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.6145262796348957</v>
+        <v>0.6998533619195743</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.6079881279265772</v>
+        <v>-0.5796346646594235</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.1861693551448997</v>
+        <v>0.2087523069568493</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.916675221023285</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.6390420734916064</v>
+        <v>-0.6186975706129509</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.3675369970112554</v>
+        <v>-0.2864443524731112</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.814739559718774</v>
+        <v>-0.7725725128066969</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.7901506126776709</v>
+        <v>-0.7945981746841435</v>
       </c>
     </row>
     <row r="19">
@@ -2349,40 +2349,40 @@
         <v>0.5135291713373615</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2565498264537479</v>
+        <v>-0.2585390710285806</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5768835013463657</v>
+        <v>-0.557413390737786</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.2127445627719131</v>
+        <v>-0.2007385486451885</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0184864158399117</v>
+        <v>0.02296842054550781</v>
       </c>
       <c r="Y19" t="n">
-        <v>-1.310809373086348</v>
+        <v>-1.270525585919021</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.5119875439493923</v>
+        <v>-0.5000403475140556</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.155153229905262</v>
+        <v>0.1656651687717195</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>-1.177028071657326</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.07008724378484328</v>
+        <v>-0.05986854405593024</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.4263532473849332</v>
+        <v>-0.4033195921984408</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.4338226543702541</v>
+        <v>-0.4067703342470207</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.1842548505477969</v>
+        <v>-0.1825618263374072</v>
       </c>
     </row>
     <row r="20">
@@ -2449,40 +2449,40 @@
         <v>-0.7719812759530676</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.08970988538443372</v>
+        <v>-0.08913931644088387</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1172250460519011</v>
+        <v>-0.1060669743277228</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.1646103091774305</v>
+        <v>-0.1673106916969244</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1033492937589512</v>
+        <v>-0.0888774743879521</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.2468817407897572</v>
+        <v>-0.3198154657768694</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.4599386239200811</v>
+        <v>-0.5029776858596416</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.5104344536084043</v>
+        <v>0.3969375727333983</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>0.1715092610496068</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.05415633915452675</v>
+        <v>0.03431280882639231</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.5470195168850328</v>
+        <v>-0.5013379475899817</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.1191234079235238</v>
+        <v>-0.1831559458158241</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.2301580164722766</v>
+        <v>-0.2331266561610609</v>
       </c>
     </row>
     <row r="21">
@@ -2549,40 +2549,40 @@
         <v>-0.1526068526874382</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9877918658577072</v>
+        <v>0.9880480352758638</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5741574159381375</v>
+        <v>0.5803563446737927</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5902029015245114</v>
+        <v>0.5655307028477027</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.02979940765374333</v>
+        <v>-0.03288629452556707</v>
       </c>
       <c r="Y21" t="n">
-        <v>-1.419028180689758</v>
+        <v>-1.399199552354924</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.5064634787735643</v>
+        <v>0.5117429370381498</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.7427385536568082</v>
+        <v>0.7563804518486552</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>0.3301607119563049</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.4081475639717783</v>
+        <v>0.4133181987180473</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.01351322886216962</v>
+        <v>-3.872918139615303e-05</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.5696078518949165</v>
+        <v>0.5529023067962819</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.79227227823834</v>
+        <v>0.7914641485452824</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -949,40 +949,40 @@
         <v>-0.9096462519643382</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.053131157116572</v>
+        <v>-1.050105344224462</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.672192668063477</v>
+        <v>-1.678738736808328</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.219974379695743</v>
+        <v>-1.25067787400455</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3984551631084463</v>
+        <v>-0.4120058605752382</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1142533583306206</v>
+        <v>0.1205290169891718</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.7287330051421617</v>
+        <v>-0.7254505593515681</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.6058357775292719</v>
+        <v>-0.6821437921769877</v>
       </c>
       <c r="AB5" t="n">
         <v>0.2704775470914114</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.670343710145443</v>
+        <v>-0.6690422711357218</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.6425792484185543</v>
+        <v>-0.6850299772344209</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1.157759015640385</v>
+        <v>-1.198771137973755</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.7762689736211634</v>
+        <v>-0.7730980266350675</v>
       </c>
     </row>
     <row r="6">
@@ -1449,40 +1449,40 @@
         <v>-1.24002626094509</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2133487367563556</v>
+        <v>0.2058496487346553</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1109451228500799</v>
+        <v>0.1089930238373245</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2353254987732341</v>
+        <v>0.2228202534863524</v>
       </c>
       <c r="X10" t="n">
-        <v>0.06638399263469827</v>
+        <v>0.05020885862671837</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.06753605843951438</v>
+        <v>-0.1458098940030804</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2690494303499357</v>
+        <v>0.2399685883043721</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.3882220561643928</v>
+        <v>0.3128930560478214</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.4734844351960781</v>
+        <v>-0.5322862031114938</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1745564042624848</v>
+        <v>0.1633896070132009</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.08995915988470569</v>
+        <v>-0.1391515928077997</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.8168690375583273</v>
+        <v>0.8092791232031692</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3706902585530792</v>
+        <v>0.3831907304978203</v>
       </c>
     </row>
     <row r="11">
@@ -1649,40 +1649,40 @@
         <v>-1.164001932777264</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4104478099734976</v>
+        <v>-0.4134736228656074</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1739080504107283</v>
+        <v>-0.1673619816658768</v>
       </c>
       <c r="W12" t="n">
-        <v>0.125432183582866</v>
+        <v>0.1561356778916733</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1675004145614857</v>
+        <v>-0.1539497170946937</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5509854680112182</v>
+        <v>0.544709809352667</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.3350756102682244</v>
+        <v>-0.3383580560588179</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1375703389024312</v>
+        <v>0.2138783535501471</v>
       </c>
       <c r="AB12" t="n">
         <v>0.6051565601945748</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.2577766731875013</v>
+        <v>-0.2590781121972226</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.2419747363317801</v>
+        <v>0.2844254651476468</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.4013158212412136</v>
+        <v>0.4423279435745844</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.410286276818301</v>
+        <v>-0.4134572238043969</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>0.5203466476481359</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.584018625630826</v>
+        <v>1.916675221023285</v>
       </c>
       <c r="AC14" t="n">
         <v>-2.199934488387146</v>
@@ -1970,7 +1970,7 @@
         <v>-0.3405952064269139</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.0003631440993174694</v>
+        <v>-0.4763174968194114</v>
       </c>
       <c r="AC15" t="n">
         <v>-1.614861189952865</v>
@@ -2049,40 +2049,40 @@
         <v>-0.2997139276921812</v>
       </c>
       <c r="U16" t="n">
-        <v>1.048564663640672</v>
+        <v>1.056063751662373</v>
       </c>
       <c r="V16" t="n">
-        <v>1.671199706523057</v>
+        <v>1.673151805535812</v>
       </c>
       <c r="W16" t="n">
-        <v>1.321955701199803</v>
+        <v>1.334460946486685</v>
       </c>
       <c r="X16" t="n">
-        <v>1.000402594420134</v>
+        <v>1.016577728428114</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.3762928365221972</v>
+        <v>0.4545666720857633</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.9389056640515546</v>
+        <v>0.9679865060971182</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.4832613584346629</v>
+        <v>-0.4079323583180914</v>
       </c>
       <c r="AB16" t="n">
         <v>0.6474636137697007</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.7372492798080433</v>
+        <v>0.7484160770573273</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.181674137405904</v>
+        <v>1.230866570328998</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.5120188893057094</v>
+        <v>0.5196088036608676</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.7102698539730482</v>
+        <v>0.6977693820283072</v>
       </c>
     </row>
     <row r="17">
@@ -2170,7 +2170,7 @@
         <v>1.273410924283941</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.2508349865029558</v>
+        <v>-0.1061307780371146</v>
       </c>
       <c r="AC17" t="n">
         <v>0.7400433737539514</v>
@@ -2270,7 +2270,7 @@
         <v>0.2087523069568493</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.916675221023285</v>
+        <v>0.9647665155830968</v>
       </c>
       <c r="AC18" t="n">
         <v>-0.6186975706129509</v>
@@ -2370,7 +2370,7 @@
         <v>0.1656651687717195</v>
       </c>
       <c r="AB19" t="n">
-        <v>-1.177028071657326</v>
+        <v>-1.375342385290699</v>
       </c>
       <c r="AC19" t="n">
         <v>-0.05986854405593024</v>
@@ -2470,7 +2470,7 @@
         <v>0.3969375727333983</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.1715092610496068</v>
+        <v>0.277276894987404</v>
       </c>
       <c r="AC20" t="n">
         <v>0.03431280882639231</v>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF4"/>
+  <dimension ref="A1:AF21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,301 +588,2001 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KMCY9qSa</t>
+          <t>ratYowuH</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.803884200412066</v>
+        <v>1.332888142411001</v>
       </c>
       <c r="C2" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.6430648528749183</v>
+        <v>1.711979734786432</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4059276934267164</v>
+        <v>-0.07537851978270592</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.037022969386322</v>
+        <v>1.372185249101586</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2821784167476653</v>
+        <v>0.4153601761688528</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2321755575979408</v>
+        <v>0.09905950636552099</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7744317603441775</v>
+        <v>0.7157328329328775</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7747797423685382</v>
+        <v>-0.6602493996056947</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1685354796392414</v>
+        <v>-0.1662912122660022</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.05574053386701496</v>
+        <v>-0.02914882139033629</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1162346740387301</v>
+        <v>-0.4400540525813855</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2033704774998261</v>
+        <v>1.719974038490435</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5799335276638728</v>
+        <v>1.446384495339175</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5954395346349531</v>
+        <v>-0.3504317102956003</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.01700106301238612</v>
+        <v>0.6035798367066932</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.3005669811492179</v>
+        <v>0.0997907129519882</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5804533365853792</v>
+        <v>0.8792408238369648</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.164001932777264</v>
+        <v>-0.4475890035631093</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4134736228656074</v>
+        <v>0.00819040855031535</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1673619816658768</v>
+        <v>0.3697222206148678</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1561356778916733</v>
+        <v>0.05383715323714514</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1539497170946937</v>
+        <v>0.4015038055763038</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.544709809352667</v>
+        <v>1.044697871663725</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.3383580560588179</v>
+        <v>0.2099648099071864</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2138783535501471</v>
+        <v>0.06472955802316237</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.6614108562105576</v>
+        <v>1.772377949008148</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.2590781121972226</v>
+        <v>0.2019347948787991</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.2844254651476468</v>
+        <v>0.5474748084531713</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4423279435745844</v>
+        <v>-0.3391926342319489</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.4134572238043969</v>
+        <v>-0.3466882191730938</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>zil0kCo9</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.5662895108190968</v>
+        <v>0.9150690587003798</v>
       </c>
       <c r="C3" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D3" t="n">
-        <v>1.619304369068277</v>
+        <v>0.9760283011422599</v>
       </c>
       <c r="E3" t="n">
-        <v>2.084703102885732</v>
+        <v>0.08754770416957029</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6854073143231572</v>
+        <v>0.272901717715027</v>
       </c>
       <c r="G3" t="n">
-        <v>2.230355940339265</v>
+        <v>0.04543502983877517</v>
       </c>
       <c r="H3" t="n">
-        <v>1.226822799655519</v>
+        <v>-0.455368745413321</v>
       </c>
       <c r="I3" t="n">
-        <v>1.073035632604012</v>
+        <v>-0.1459200250078776</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3501006134154062</v>
+        <v>-0.3735984447580799</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.727664194716408</v>
+        <v>1.11769623869678</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.340472399790393</v>
+        <v>0.8985320629996317</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2919848317339145</v>
+        <v>1.027403060900586</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6709399548012787</v>
+        <v>0.2573208018038399</v>
       </c>
       <c r="O3" t="n">
-        <v>1.399825941646369</v>
+        <v>-0.01989200858153501</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1525932033922739</v>
+        <v>-0.7060182872128909</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1858754705639074</v>
+        <v>-0.7567654131392313</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3276337611829751</v>
+        <v>-0.8126124439911041</v>
       </c>
       <c r="S3" t="n">
-        <v>1.226788531960348</v>
+        <v>0.5291334051665519</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3646766398185615</v>
+        <v>-0.4580617426474527</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9204537126897583</v>
+        <v>-0.07452505922784827</v>
       </c>
       <c r="V3" t="n">
-        <v>1.650458896029237</v>
+        <v>0.8255151205564593</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4970127913016723</v>
+        <v>-0.5898525400132842</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.08380746893017238</v>
+        <v>-0.4077385396477543</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.90454407898764</v>
+        <v>1.6435166068372</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.7470040635201225</v>
+        <v>0.09036346752519944</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2183362255381184</v>
+        <v>-0.1748879043088322</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.7803994443905812</v>
+        <v>-0.09353939304452243</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.5193773565281674</v>
+        <v>0.0345952657828821</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2228028976389549</v>
+        <v>-0.2269918279766365</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.05054525098861335</v>
+        <v>-0.4285111872863675</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2291039372453294</v>
+        <v>-0.2026046421756244</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>drzevnw8</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.6650467487870619</v>
+        <v>-1.143639517401047</v>
       </c>
       <c r="C4" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.733363273088506</v>
+        <v>0.7307111565942029</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.728543386247825</v>
+        <v>0.4897333451600764</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.223528159342126</v>
+        <v>0.746844318073304</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.414939536213983</v>
+        <v>0.142747103626311</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.168225655688379</v>
+        <v>0.1561805892008201</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.010457225313496</v>
+        <v>-0.2826213274435228</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5379701444742412</v>
+        <v>-0.8559946295183787</v>
       </c>
       <c r="K4" t="n">
-        <v>2.580606926058192</v>
+        <v>0.1525093870192494</v>
       </c>
       <c r="L4" t="n">
-        <v>1.751044988579344</v>
+        <v>-0.9135796396663992</v>
       </c>
       <c r="M4" t="n">
-        <v>1.976231268482565</v>
+        <v>-0.5023275887638617</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.128482428529213</v>
+        <v>0.5750282671496987</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.324848135001084</v>
+        <v>-0.1906348254536885</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.466337553304333</v>
+        <v>0.3607414435389804</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.489432435945385</v>
+        <v>0.5456840999815274</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.488237531203955</v>
+        <v>0.5626935575479751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2371204925442879</v>
+        <v>0.2098837170417481</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.096014462158608</v>
+        <v>-0.4521970087602204</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.358085774532098</v>
+        <v>0.7439365840402571</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.269453816354054</v>
+        <v>0.6224556043790961</v>
       </c>
       <c r="W4" t="n">
-        <v>-2.4528119410207</v>
+        <v>0.4177632567152665</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.914646091085255</v>
+        <v>-0.11606018917357</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1269156458799326</v>
+        <v>-0.2717934960053915</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1.443096473112712</v>
+        <v>0.5375046662481453</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5422141801857108</v>
+        <v>0.1536245273991658</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.38783705133429</v>
+        <v>-0.6463011942194424</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.164326667042097</v>
+        <v>0.1236932719030375</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.7847842261730399</v>
+        <v>0.3345621574719992</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1.075022778736408</v>
+        <v>0.2651692541895276</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1.224207715941316</v>
+        <v>0.5105021929330404</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>EJ4unbdE</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.803884200412066</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.100990189364625</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.6454151068600659</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1.293741877913722</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.863213039676196</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.1103456852913798</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.2140258015236212</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2045056914978116</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.811693584074537</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.8680311543609328</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.223735949746493</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.4440334141483391</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.944609089227002</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1.065941285799904</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.6270828421431606</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1.029114888011499</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3792789471516898</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.0496249183580619</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.3608193121008489</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.03871166297723887</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.2008575776014369</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.1006156781362759</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.53195407318675</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.3881226887441319</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.1429033621411549</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.7947828181830523</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.3015849109178182</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.2816343248309269</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.3138727320884809</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.1908488290080397</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>OGMmt88e</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.287307878733479</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.297243905003071</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6161345466142356</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1.399062455771117</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6351392336943695</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.06717073038673</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5183026043816211</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.372772033266125</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.4163475580864615</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1.000783399794436</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.6629317611683064</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.1383149097589276</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.853516719196845</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.128288079079961</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.205831946211669</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.001884229703633</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2212174200692223</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.3434518886076254</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.2304650535258056</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.2606434612800098</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.1880997779143888</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.001628236473341557</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-1.054061157330731</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.6649374146850073</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.2514225808807353</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.06155727516332736</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.01311146076786729</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.5426592261925974</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.2252714211461093</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.3293277741997986</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rc1ER8g2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.803884200412066</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.384890208722356</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.962983154863942</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.06280762420541915</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.651036891578524</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.559662203947852</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.666592559712929</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.7267897838682078</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.1110811642043075</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.1302049845464171</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.8872483995162379</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1674035946304836</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.7678182772307358</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0225005533005822</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.07394757448180066</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.06576890032021188</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.7846296996278138</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.6075896159808647</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.048086207161342</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.098407333425346</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.111940633744966</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.038895482231802</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.773958114883457</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.721831935169709</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.3741086486761684</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.7103283869067901</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.150986384572229</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.268704222164149</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.5549232937661293</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.060579732486294</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>lb85TUOk</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.7106270124645843</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.06017762816284601</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.337450096763346</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.555950770706776</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5405335304605852</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.4449668371397055</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.2926328460981638</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.6894877563451811</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.8445308827436271</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.3299730209451889</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.4592442773077354</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.5879009456257088</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.205726356303696</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.2940582285892007</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.6564585039298432</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2585591719002777</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.9502336476088371</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.9084888851251122</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.1045587845214357</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.3864524105870507</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.1813159940956821</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.04890656374985777</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.5670741338041609</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.3149072450005491</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.9656722735289381</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1.038019181339079</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.006448320261841242</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0.3415983836448335</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.3584684131095881</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.03575489725372252</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>MqhPmaA4</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.6491841872481661</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.9701543789389947</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-2.162776715658261</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1.13576101112763</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1.528076638341711</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-1.799052058545101</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-1.867185118372062</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.254389983098985</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.803289708943209</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.140896196685565</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.100179578071888</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-2.278344440484806</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-2.902645406125542</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-2.362531365047098</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-2.155339316889533</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-2.085853007634854</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.03304904018589225</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.343202134887139</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-2.476508305457671</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-2.712254405710258</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-2.584586698823306</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-2.140709198256996</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.5455990045597969</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-1.534445410180776</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.09450288599607333</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.22061566252073</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-2.261127487222048</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.9910581451856318</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.9079774297274444</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-1.334951770012357</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>21YvrUwq</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.7555381358290515</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3054947727109032</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9602267061283356</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.3261090688489062</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6153131801002087</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.176509266036978</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.7922872073707768</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.350521070118121</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.3531501873447264</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.6998970066448839</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1048405229613044</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.9287026153649001</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.6516848787481174</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.1721071009060277</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.05762354154455195</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2159459924422953</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.769798281054071</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-1.028244203906146</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.4629852443381738</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-1.253811027591674</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.5257426444795058</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.5724569642693736</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.7285129904774273</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.5276457633162036</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.2647214915730864</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.52004659375654</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.5009669095707672</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.3661983627514524</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.2114564308745363</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.3666318804466266</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WIs9mjGL</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7783282676678127</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1583044859820689</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.7575017826430527</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7600093903054785</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.6515909870579915</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.5995394802454174</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.5603092396011971</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.4961904496206735</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.038992497946061</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.1360619339729076</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.5282264164825606</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-2.727930476351588</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.3672193452459774</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1569296250619967</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.7015420551803605</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.5311592667645909</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-1.01581883159542</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.5460327509559366</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-1.352407418554586</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-1.046942631981307</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.7766342265798208</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.4017861344528024</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.9236577545753657</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.5928070769879</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.579709924984434</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.130217314385792</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.6594065696602147</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.00596848567565784</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.5774193331955597</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.7062352649657826</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.9150690587003798</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.139573064174299</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9937786556340964</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4506301928493808</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6647145937127257</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2165590861285601</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.07655926564397876</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.02786454035568101</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.3983599783612017</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.1646039899718339</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.660903886671419</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-1.415139251620586</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.1300828287321656</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.05555503675443267</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.2641399321003446</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.3404309232228145</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.0454491920703558</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.9314295492597725</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.08762219796400531</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.1105754412818432</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.5242078280417116</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1661118591109078</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.5585610179276971</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.1798198891838436</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.7101683174791846</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.063734801624897</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.2541014441310807</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.5357410404222145</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.06693436754715314</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.1077323152487675</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.332888142411001</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.7411917106941414</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.8463947153522249</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.819799277555445</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.5066763751706993</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.6315519980504378</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.663112283709378</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9513393861736384</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.988562709483199</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.036931859099038</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.125111415514157</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-1.559006783097956</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.01635589530716495</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.7320368172312296</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.9190502137679196</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.840448472508012</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.2011881694351533</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.9990328856938785</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.5427823768746871</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.2469633111216679</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.4604388274590968</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.2194592201583213</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.9234015673167847</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.1752446567939273</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.2924371404290393</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.141289937067381</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.2405557185349856</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.03503505949517261</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.3617681335309732</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.5417420402224266</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.7555381358290515</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.395370762822294</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.5382531532116567</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.346402166842419</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.5270350142583822</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.2265655666609598</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.6065905582941428</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.667486500802778</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.6328891448289291</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.309987894613429</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.876839778343433</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1.379172368751244</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1.361578777086047</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1.790123704643656</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1.963810133821588</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1.517791833086104</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.2565895071653233</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.9096462519643382</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1.055685101635069</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-1.697101734845834</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-1.257079112612854</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.4271904420143252</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.09782100315534713</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.7311169592777845</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.6661076016494321</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.4857902304647879</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.6733772421100601</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.713095790439735</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-1.209839052183935</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.7702481325338301</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.803884200412066</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3054947727109035</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9647179668811331</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.05622508808933233</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.4955404916225415</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5360844915897844</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6665238211106628</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8998197861510556</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.1147271467003914</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.8293076591302606</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.04076891807552932</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.7077905551901836</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.2633797142468563</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.3677773969744927</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.6057534806735301</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.6435343448513672</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.6445257170629505</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.08298870714525068</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.2873329174753292</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.779392359438639</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.723554151900716</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.2429563551024242</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-2.256049563409102</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.08475833928533634</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-1.050223634224975</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-1.209639758788146</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.1890127298503602</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.2266695230422703</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.6346697490022981</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.4890200366396486</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-1.143639517401047</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.5340350108535594</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.03784874075713161</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.4775073995189119</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.02172916310133817</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.009253523801841301</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.1589289935558287</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.425978725822224</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.4029280272242796</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.7876885052156318</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.7484230761535636</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.5789092249083732</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-1.257278293110975</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-1.20615225312095</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.8880216154577056</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.8961205295418277</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.2834450880318979</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.3201711099994415</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.007264653184762336</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.03616124658313977</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.1063501142343066</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.54577007272684</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4310845214166923</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.03452627630307759</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.6136828920859712</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.3807488847256121</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.3489657392403308</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.1115381362788087</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.09577495169226491</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.06237793562088503</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ABRGMMB5</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.7783282676678127</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.4036216305301263</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.2180856722167749</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.4182645744741268</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.1429221505514097</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.7245993483317189</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5812966214914635</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6770698000332979</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.883444297156066</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.85428498326492</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.8922881953268644</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.9895311376667</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.303150053088667</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.2089666850986735</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.6554431353698323</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3802129261593566</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.04614519973263987</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.1530955805113741</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.71552122323402</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.382636192644472</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.7235420949295389</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.8118188128795092</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3473248272922616</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.6106715187044864</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.019907841260957</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.642812597434341</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.8865555708878744</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.230519591403841</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.4445009708173299</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.5022691655294746</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.7106270124645843</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.7198081723920667</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5666555736385971</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.365602712985499</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.068630064338467</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.366405730839369</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9172142973641186</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.9669316338719981</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1.058998121601242</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.05187581180721516</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1929091287094967</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.6349730719319362</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.59783389842012</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.165411052387417</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.07115995636339026</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3699032859679093</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.1465839901438748</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.187633958858611</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.709719552959044</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.528387572089399</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.057975626635148</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.297034471986422</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.1224213514753265</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.101294215203239</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.3870384034251287</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-1.556658329184071</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.292771684538624</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.65069373981871</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.516255015632671</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.801137188975787</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.6491841872481661</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.13412157207323</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.297500861442786</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6283586679837349</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9193191160411144</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4823442558272417</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9309776960603869</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.7927492494514725</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.9255308358609999</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.8442976605033163</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.4842196965617446</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.7968240448439774</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.645399702990012</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.4243422946949187</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.9888289150777131</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2781474882640277</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.3705630394674693</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.03992793772441061</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.1290821862543494</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.009795195895964047</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.0228937763385019</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.01678792912127159</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.7345340547515479</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.351558092881879</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.1884505977367764</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1.928544884940357</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.1019650340180378</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.4594019299716752</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.5312521542434436</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.03474499778241082</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>rPPOK0tI</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.287307878733479</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.221345445690317</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.9144690928124901</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.3195265327328191</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.9220280293280034</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.7081199499934401</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1.011552096857418</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.9263543157731902</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.8686001456038628</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.553520049051015</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.7078182675423941</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.8028185253222011</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.09852946909290786</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.1525932033922739</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.5557711925732903</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.5338265650119225</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-1.678071896772522</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-1.24002626094509</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.210615994203325</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.1067659178042966</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.2371134674439296</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.05411816993157941</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.1399799746265518</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.2573401225478666</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.3348457039812511</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.5545099976234298</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.1639018052005392</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-0.1238937488649406</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.8067882915371993</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.3868990312538447</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>v5b6XwQN</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.5662895108190968</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.9701543789389947</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.3116859600145848</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.45775979117065</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.3967663726677186</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.214671682308225</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.004744089072898</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.4691175689622648</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.4839228060945257</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-1.198609487371789</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.6985187187647576</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.1503038707153752</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.86686155089011</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.574939511061436</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.039524319543907</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.9029116838657384</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.03772609762708</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.8833444599046752</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.2291582196229235</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.03318576079002625</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.3582653155068773</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.2552936318893324</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.04837059670771343</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.3225885437641554</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.7664616530192659</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.3346644156527129</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-0.2558463028822276</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-0.4289634837934861</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-0.4190667740232556</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-0.2097469693676077</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF11"/>
+  <dimension ref="A1:AF21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,1001 +588,2001 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EqY7Orsg</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9150690587003798</v>
+        <v>1.803884200412066</v>
       </c>
       <c r="C2" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D2" t="n">
-        <v>1.139573064174299</v>
+        <v>1.292214843004201</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9937786556340964</v>
+        <v>-0.2888652243166457</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4506301928493808</v>
+        <v>1.497253435307243</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6647145937127257</v>
+        <v>-0.5235658002810345</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2165590861285601</v>
+        <v>-0.6600343133907443</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07655926564397876</v>
+        <v>-0.5747568470238625</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.02786454035568101</v>
+        <v>-1.223548419337935</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3983599783612017</v>
+        <v>0.8172433403409975</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1646039899718339</v>
+        <v>-0.6836960356200911</v>
       </c>
       <c r="M2" t="n">
-        <v>0.660903886671419</v>
+        <v>0.228399195797074</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.415139251620586</v>
+        <v>-0.5759119846692612</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1300828287321656</v>
+        <v>-0.4373016383530416</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.05555503675443267</v>
+        <v>1.0415596456855</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2641399321003446</v>
+        <v>0.07481817392292243</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.3404309232228145</v>
+        <v>0.629500025988554</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0454491920703558</v>
+        <v>-0.3968173706165243</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9314295492597725</v>
+        <v>-1.471978037702028</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04122015097756244</v>
+        <v>-1.00051809178082</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1299470130751964</v>
+        <v>-1.842858031768532</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.5365585891570749</v>
+        <v>0.03707621825696943</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1464021199004127</v>
+        <v>-0.09101619358948368</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.4727441268429418</v>
+        <v>-1.382142259556136</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.1871005334072204</v>
+        <v>-0.6889140848273373</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.7946569715497285</v>
+        <v>0.5544061169865391</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.435928345894102</v>
+        <v>0.05252067286958336</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2540981752661836</v>
+        <v>-0.8539976878224802</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.5748307223612814</v>
+        <v>0.3551165172177996</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.04896572283862338</v>
+        <v>0.07924056213346445</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.1175612113819971</v>
+        <v>-0.2168739036130558</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcDtwrdn</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.803884200412066</v>
+        <v>0.5884105023448029</v>
       </c>
       <c r="C3" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3054947727109035</v>
+        <v>-0.326878311012978</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9647179668811331</v>
+        <v>-0.211165817993358</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.05622508808933233</v>
+        <v>-0.5696629051441321</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4955404916225415</v>
+        <v>-0.0746527606159776</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5360844915897844</v>
+        <v>-0.8308796780893182</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6665238211106628</v>
+        <v>-0.8826568224664691</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8998197861510556</v>
+        <v>1.740427474222816</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1147271467003914</v>
+        <v>0.3457009730202276</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8293076591302606</v>
+        <v>0.5943451909429661</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04076891807552932</v>
+        <v>1.022901638624271</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7077905551901836</v>
+        <v>-0.08436458545491363</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2633797142468563</v>
+        <v>-1.285717440354432</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3677773969744927</v>
+        <v>-1.151224245304458</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6057534806735301</v>
+        <v>-0.9683370892965719</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.6435343448513672</v>
+        <v>-0.8701402362593801</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6445257170629505</v>
+        <v>0.5882827532177429</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08298870714525068</v>
+        <v>-1.007513590981311</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2757382414598486</v>
+        <v>-0.8266399641159833</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8103393438206598</v>
+        <v>-1.564497471555426</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6071702078608134</v>
+        <v>-0.7414101056236264</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1958415263466666</v>
+        <v>-0.8180031568039547</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2.242894015832392</v>
+        <v>-0.3164975089295154</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.1088029776086015</v>
+        <v>-0.6989349199241213</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.9556803021921434</v>
+        <v>-1.289693363226737</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8457779274030732</v>
+        <v>-0.0362485913282143</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.1961041901542708</v>
+        <v>-0.8791598133785475</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.172860627555464</v>
+        <v>-0.2649462474638949</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.6197645662474374</v>
+        <v>-0.2829620859700955</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4532839119011711</v>
+        <v>-0.6649828679328712</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zD1kyMQb</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7555381358290515</v>
+        <v>-0.5662895108190968</v>
       </c>
       <c r="C4" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.395370762822294</v>
+        <v>1.679270782180024</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5382531532116567</v>
+        <v>-0.06251147616638306</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.346402166842419</v>
+        <v>1.207621846199407</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5270350142583822</v>
+        <v>-0.173064009879371</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2265655666609598</v>
+        <v>-0.9559566463839843</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6065905582941428</v>
+        <v>-0.7856551841894686</v>
       </c>
       <c r="J4" t="n">
-        <v>1.667486500802778</v>
+        <v>-0.6066153173591967</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6328891448289291</v>
+        <v>0.9645956086678346</v>
       </c>
       <c r="L4" t="n">
-        <v>1.309987894613429</v>
+        <v>-0.2844596389050962</v>
       </c>
       <c r="M4" t="n">
-        <v>1.876839778343433</v>
+        <v>-0.277609955756804</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.379172368751244</v>
+        <v>0.9227081348866761</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.361578777086047</v>
+        <v>-0.1564690272414496</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.790123704643656</v>
+        <v>0.2566673234656274</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.963810133821588</v>
+        <v>-0.5148227101167691</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.517791833086104</v>
+        <v>0.472999687882383</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2565895071653233</v>
+        <v>0.5490707647693822</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9096462519643382</v>
+        <v>-1.258179008691285</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.066920821476473</v>
+        <v>1.221048823922384</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.716399885561175</v>
+        <v>1.384438873323028</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.274421778566053</v>
+        <v>1.189714162664414</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4312103924061914</v>
+        <v>0.9298407080073192</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1173926477945312</v>
+        <v>-0.08691815105525325</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.7426038799615441</v>
+        <v>0.9390150689743724</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.7226054766099245</v>
+        <v>0.8955649342168621</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.356602620440753</v>
+        <v>-1.290350536590683</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.6757727372588168</v>
+        <v>0.9602671059571369</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.7424738223306712</v>
+        <v>0.6522342378716393</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1.219520397918135</v>
+        <v>0.9707893100153563</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.7768616020627346</v>
+        <v>1.017634910968178</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EJlHkLuh</t>
+          <t>CzO2kX26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.332888142411001</v>
+        <v>1.029019717894186</v>
       </c>
       <c r="C5" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7411917106941414</v>
+        <v>1.592046908562937</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8463947153522249</v>
+        <v>-0.02013425777304885</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.819799277555445</v>
+        <v>1.277835564771003</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5066763751706993</v>
+        <v>0.04566807566151055</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6315519980504378</v>
+        <v>0.09444733825537195</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.663112283709378</v>
+        <v>-0.1431553106295654</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9513393861736384</v>
+        <v>-0.8224115493320451</v>
       </c>
       <c r="K5" t="n">
-        <v>1.988562709483199</v>
+        <v>0.004740584297248166</v>
       </c>
       <c r="L5" t="n">
-        <v>1.036931859099038</v>
+        <v>-1.715534005004657</v>
       </c>
       <c r="M5" t="n">
-        <v>1.125111415514157</v>
+        <v>-1.650672466359775</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.559006783097956</v>
+        <v>1.761935401838001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01635589530716495</v>
+        <v>1.946684916611004</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7320368172312296</v>
+        <v>1.236698620823038</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9190502137679196</v>
+        <v>0.7395207147102455</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.840448472508012</v>
+        <v>1.537985519658896</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2011881694351533</v>
+        <v>-1.3155290992628</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9990328856938785</v>
+        <v>-1.072912875986321</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5402087711739563</v>
+        <v>1.730431588440373</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2057457483970511</v>
+        <v>2.158130872076227</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.4257848070540205</v>
+        <v>1.711470804015739</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2270210822278549</v>
+        <v>0.8646123987907106</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8870296135744657</v>
+        <v>0.009533564269228674</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1561937917642201</v>
+        <v>1.562364671084619</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.3236124352084988</v>
+        <v>0.3979739557912443</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.7486691542092433</v>
+        <v>0.2055060005296103</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.2304835264588932</v>
+        <v>1.10441842243416</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.05367417160188161</v>
+        <v>1.134377517901654</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.3537351925435422</v>
+        <v>1.500257968429607</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.5224161958484369</v>
+        <v>1.28324809980162</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>rw5cZaeB</t>
+          <t>0zTMbytK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.143639517401047</v>
+        <v>1.454435512217728</v>
       </c>
       <c r="C6" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5340350108535594</v>
+        <v>1.286763350903133</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.03784874075713161</v>
+        <v>2.18961157161256</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4775073995189119</v>
+        <v>0.07542563423241153</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02172916310133817</v>
+        <v>1.73493494764162</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.009253523801841301</v>
+        <v>1.32289645741397</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1589289935558287</v>
+        <v>0.6747163203346317</v>
       </c>
       <c r="J6" t="n">
-        <v>0.425978725822224</v>
+        <v>-0.1542080398704883</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4029280272242796</v>
+        <v>-0.7000992338894484</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7876885052156318</v>
+        <v>-0.5654957807570251</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7484230761535636</v>
+        <v>-0.4818588257104224</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5789092249083732</v>
+        <v>0.59301170858437</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.257278293110975</v>
+        <v>-0.8654785062708179</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.20615225312095</v>
+        <v>0.2740130101445193</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.8880216154577056</v>
+        <v>0.7181907568954454</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.8961205295418277</v>
+        <v>0.5657864496054094</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2834450880318979</v>
+        <v>0.809235415584542</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3201711099994415</v>
+        <v>0.1577353155119365</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0008046717452603428</v>
+        <v>1.269033087914721</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007851624608653076</v>
+        <v>1.073090995612623</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1337497525416624</v>
+        <v>1.370777004238278</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5624575296697479</v>
+        <v>0.4113471376396533</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3863183864008493</v>
+        <v>0.403120022899113</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.02171964010620435</v>
+        <v>0.8449855622442437</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.6467879066220209</v>
+        <v>0.1392553987656764</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.1344613942704516</v>
+        <v>-1.671869501866313</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.3520406008068648</v>
+        <v>0.4395732654514796</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.113428897984777</v>
+        <v>0.714197544902202</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.1208579500190901</v>
+        <v>0.4273634326912838</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.08768513917388088</v>
+        <v>0.6849106742369443</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ABRGMMB5</t>
+          <t>6HqKvGll</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7783282676678127</v>
+        <v>-1.02209214759432</v>
       </c>
       <c r="C7" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4036216305301263</v>
+        <v>-1.098653835607025</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2180856722167749</v>
+        <v>-1.647596061246612</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4182645744741268</v>
+        <v>-1.121655576593157</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1429221505514097</v>
+        <v>-1.197078255775779</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7245993483317189</v>
+        <v>-1.66634259551974</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5812966214914635</v>
+        <v>-1.32437952876344</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6770698000332979</v>
+        <v>1.041381282400799</v>
       </c>
       <c r="K7" t="n">
-        <v>0.883444297156066</v>
+        <v>1.221790357069863</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.85428498326492</v>
+        <v>1.118021507221721</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8922881953268644</v>
+        <v>1.411706530494822</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9895311376667</v>
+        <v>-1.307238603012559</v>
       </c>
       <c r="O7" t="n">
-        <v>2.303150053088667</v>
+        <v>-1.984482099330688</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2089666850986735</v>
+        <v>-1.086384416528599</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6554431353698323</v>
+        <v>-0.7458843921038294</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3802129261593566</v>
+        <v>-0.9950930753797226</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04614519973263987</v>
+        <v>-0.1153822636328267</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1530955805113741</v>
+        <v>-1.451808317984033</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6936955653232409</v>
+        <v>-2.513851559926809</v>
       </c>
       <c r="V7" t="n">
-        <v>1.338890755084797</v>
+        <v>-2.219473383564261</v>
       </c>
       <c r="W7" t="n">
-        <v>0.673259288484905</v>
+        <v>-2.32117258387348</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7701245460106554</v>
+        <v>-1.741727095492417</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3324155252801526</v>
+        <v>-0.5761057302153428</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5841022201868284</v>
+        <v>-1.694087463783791</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.015191810902738</v>
+        <v>1.028258336517784</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6474636137697007</v>
+        <v>0.3844925381993601</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.8631524747470569</v>
+        <v>-2.04752723550168</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1330454859032117</v>
+        <v>-0.956122752819265</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.4150960849155851</v>
+        <v>-0.3687816681447963</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.4914957022225387</v>
+        <v>-1.107248110004707</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rPPOK0tI</t>
+          <t>nX2mpxRQ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.287307878733479</v>
+        <v>1.454435512217728</v>
       </c>
       <c r="C8" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D8" t="n">
-        <v>1.221345445690317</v>
+        <v>1.31947230350954</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9144690928124901</v>
+        <v>-0.1352503731410424</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3195265327328191</v>
+        <v>-0.6530416959479032</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9220280293280034</v>
+        <v>-0.6608076841678626</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7081199499934401</v>
+        <v>0.01967080973427811</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.011552096857418</v>
+        <v>-0.04950061106424083</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9263543157731902</v>
+        <v>1.967993738711475</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8686001456038628</v>
+        <v>2.007808685854255</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.553520049051015</v>
+        <v>-0.4739678036461555</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7078182675423941</v>
+        <v>-0.4425134363465161</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8028185253222011</v>
+        <v>-0.5639230237128137</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09852946909290786</v>
+        <v>0.6690479553689609</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1525932033922739</v>
+        <v>0.05863740054827443</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.5557711925732903</v>
+        <v>0.1460691722381677</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5338265650119225</v>
+        <v>0.03401520853055402</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.678071896772522</v>
+        <v>-0.863522613046371</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.24002626094509</v>
+        <v>-0.4634920518022974</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2011711066876405</v>
+        <v>-0.08150271495336972</v>
       </c>
       <c r="V8" t="n">
-        <v>0.09063002579981927</v>
+        <v>-0.01987835727626629</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2150445159664586</v>
+        <v>-0.2775424207121213</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02704856192192136</v>
+        <v>-0.1161405649548205</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.2392224054558635</v>
+        <v>0.1233985797642606</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2270260157456341</v>
+        <v>-0.1840455425379086</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.2996510502334099</v>
+        <v>1.303944478975303</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.9469834678426158</v>
+        <v>0.2065133113290168</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.1409539428417199</v>
+        <v>0.05849629366966446</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.2167448546013955</v>
+        <v>-0.7512609390704887</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.7366481160664353</v>
+        <v>0.07470272109506162</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.4189439474042063</v>
+        <v>0.03525356474324173</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>viJXIvBU</t>
+          <t>YTzyyYmD</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6491841872481661</v>
+        <v>-0.6650467487870619</v>
       </c>
       <c r="C9" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D9" t="n">
-        <v>1.13412157207323</v>
+        <v>0.01111419925323443</v>
       </c>
       <c r="E9" t="n">
-        <v>1.297500861442786</v>
+        <v>0.2727908442317001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6283586679837349</v>
+        <v>-0.4336238254116639</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9193191160411144</v>
+        <v>-0.06321641273443976</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4823442558272417</v>
+        <v>0.3232073049063131</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9309776960603869</v>
+        <v>-0.07794618529282328</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7927492494514725</v>
+        <v>0.5717194645678999</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9255308358609999</v>
+        <v>0.1418057869042686</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8442976605033163</v>
+        <v>0.5341032707342497</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4842196965617446</v>
+        <v>0.7274081400532177</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7968240448439774</v>
+        <v>0.5870172281061461</v>
       </c>
       <c r="O9" t="n">
-        <v>1.645399702990012</v>
+        <v>-0.8244946249893161</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4243422946949187</v>
+        <v>-0.9046676989402043</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9888289150777131</v>
+        <v>-0.5881170912429429</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2781474882640277</v>
+        <v>-0.6126054242770251</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3705630394674693</v>
+        <v>1.225709439390275</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.03992793772441061</v>
+        <v>-0.1799924635114394</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1442001663483254</v>
+        <v>0.4483459997349319</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.07880070451445728</v>
+        <v>-0.07809740787244848</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01374054699978162</v>
+        <v>0.04242488314225071</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03721597380375743</v>
+        <v>-0.07538383947761641</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.9808550508645523</v>
+        <v>-0.9486925325336227</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.3971854109746033</v>
+        <v>0.3431281892337876</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1914450098568898</v>
+        <v>-0.7236448593293091</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.8650135515408197</v>
+        <v>-0.3044450916704781</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.07210237365330441</v>
+        <v>0.06246902880132743</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.4472398466055593</v>
+        <v>-0.09763735880643488</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.5224058174993481</v>
+        <v>-0.2733277984495092</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.05289867927322396</v>
+        <v>0.5094037962481918</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zypxSHmo</t>
+          <t>K0RAmBXI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.7106270124645843</v>
+        <v>-0.6650467487870619</v>
       </c>
       <c r="C10" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7198081723920667</v>
+        <v>0.03837165975857418</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5666555736385971</v>
+        <v>-0.3797537072670169</v>
       </c>
       <c r="F10" t="n">
-        <v>1.365602712985499</v>
+        <v>-0.2361477419290482</v>
       </c>
       <c r="G10" t="n">
-        <v>1.068630064338467</v>
+        <v>-0.4083881725543977</v>
       </c>
       <c r="H10" t="n">
-        <v>1.366405730839369</v>
+        <v>0.200638259314316</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9172142973641186</v>
+        <v>0.04334771347407641</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9669316338719981</v>
+        <v>0.6515493516712775</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.058998121601242</v>
+        <v>1.181435116931665</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05187581180721516</v>
+        <v>-0.6663493220354233</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1929091287094967</v>
+        <v>0.05586936096831784</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6349730719319362</v>
+        <v>-0.89361945001512</v>
       </c>
       <c r="O10" t="n">
-        <v>1.59783389842012</v>
+        <v>0.2150460436412164</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.165411052387417</v>
+        <v>0.7091006510067325</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.07115995636339026</v>
+        <v>0.1579657552368742</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3699032859679093</v>
+        <v>0.5600130510981989</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1465839901438748</v>
+        <v>-0.8837263378798307</v>
       </c>
       <c r="T10" t="n">
-        <v>0.187633958858611</v>
+        <v>-0.1811159757503729</v>
       </c>
       <c r="U10" t="n">
-        <v>2.657166122846207</v>
+        <v>0.5199614815852442</v>
       </c>
       <c r="V10" t="n">
-        <v>2.454674741899072</v>
+        <v>1.02349698954921</v>
       </c>
       <c r="W10" t="n">
-        <v>3.093991361722411</v>
+        <v>0.6608999146337742</v>
       </c>
       <c r="X10" t="n">
-        <v>2.21713918704611</v>
+        <v>0.852503936474588</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2185887387646406</v>
+        <v>-0.2115565708407632</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.111697818476858</v>
+        <v>0.5834967667856207</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.286871268464238</v>
+        <v>0.03544030042928602</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.5900177033025452</v>
+        <v>-1.174006139259102</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.275669439517284</v>
+        <v>0.6482046904879131</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.574557960336869</v>
+        <v>0.5943519146841802</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.54250836056138</v>
+        <v>0.4284531980345297</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.763843877782372</v>
+        <v>0.4302040877025441</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>v5b6XwQN</t>
+          <t>0d4cBEPP</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.621563145701976</v>
+        <v>-1.02209214759432</v>
       </c>
       <c r="C11" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D11" t="n">
+        <v>-0.6570829754205215</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.288583817635904</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.33457232956959</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.416422107246789</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.4186366618973726</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.7646614004638097</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1494863745613353</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.764941201706446</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.563990229283531</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.291464414439932</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1.723854996249109</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-2.215744845850312</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1.973492392391944</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-1.64823192225393</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-1.511606048971236</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-1.061228722365096</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.3192437804398117</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.3402188257467516</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1783894674940043</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.5503780015693053</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.2911154228287079</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.1197668267100307</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.6541440268505213</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.6669873511801905</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.5594498326714614</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.1072093744880609</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.6977711197703863</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.5333037373273585</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.6267409291916859</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ratYowuH</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.029019717894186</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.711979734786432</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.07537851978270592</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.372185249101586</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4153601761688528</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.09905950636552099</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7157328329328775</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.6602493996056947</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.1662912122660022</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.02914882139033629</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.4400540525813855</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.719974038490435</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.446384495339175</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.3504317102956003</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6035798367066932</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.0997907129519882</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.8792408238369648</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.4475890035631093</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.01146919445072975</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.4214596069205943</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.09391603986150113</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.4375951719683872</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.070922951613226</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.2279525293699303</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.06153444475063887</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.727426704584584</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.2157122748792183</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.6245233445904342</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.3249243556648284</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.3284461781710096</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>zil0kCo9</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.5884105023448029</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9760283011422599</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.08754770416957029</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.272901717715027</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.04543502983877517</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.455368745413321</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.1459200250078776</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.3735984447580799</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.11769623869678</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.8985320629996317</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.027403060900586</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2573208018038399</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.01989200858153501</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.7060182872128909</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.7567654131392313</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.8126124439911041</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.5291334051665519</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.4580617426474527</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.002693432229357402</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.8836646143418929</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.7245175822916484</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.4436276569961284</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.657183467014966</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.1616263165972439</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.1092583097423657</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.3535514931416103</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.07852364063317965</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.2855444722542514</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.4502919933263021</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.1548689159799649</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>drzevnw8</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.454435512217728</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.7307111565942029</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4897333451600764</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.746844318073304</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.142747103626311</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1561805892008201</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.2826213274435228</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.8559946295183787</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.1525093870192494</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.9135796396663992</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.5023275887638617</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.5750282671496987</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.1906348254536885</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.3607414435389804</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5456840999815274</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.5626935575479751</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2098837170417481</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.4521970087602204</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.7484952646317844</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.6639114635849789</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.4581670967866903</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.09528251402839594</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.2444788901396183</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.5553337932887099</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.1801625329355045</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.4763174968194114</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.1283761109185265</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.3675833005105085</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.2548821631559298</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.4978359969275608</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>EJ4unbdE</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-1.58424873295043</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.133699141971033</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.673504262738768</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.214751444520676</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.8772363458769441</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.09375700241320968</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.1390329240119035</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6900327870783429</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.9549969933973429</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.8390610531181056</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.2037445609368442</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.4440334141483391</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.8925417371127702</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-1.044259177451289</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.5940045381955394</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-1.020867175858341</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3792789471516898</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.08613281051305575</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.3145892136992564</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.103407225507524</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.2235448592352565</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.1222248944764526</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5772124063138908</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.2919676858295587</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.3950774076284668</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.4763466917203257</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.2840961796374725</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.2972876678403027</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.3836293850017392</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.09927948856319559</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OGMmt88e</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.6650467487870619</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.297243905003071</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6161345466142356</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.399062455771117</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6351392336943695</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.06717073038673</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5183026043816211</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.372772033266125</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.4163475580864615</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1.000783399794436</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.6629317611683064</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.1383149097589276</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.853516719196845</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.128288079079961</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.205831946211669</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.001884229703633</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.2212174200692223</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.3434518886076254</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.1848303347315013</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.1637218419033916</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.2524121235942074</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.06247445058473001</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-1.073225822625457</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.5425526560513796</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.2202292881321287</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.1068862611366684</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.02261084686869689</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.4276278982852075</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.3992130745808112</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.2381851382273883</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>21YvrUwq</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.4516697113122358</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2400768674980878</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9448141498182684</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.3195265327328189</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6101494257233321</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2227205969118803</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.6795428132885346</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.7513315119286</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.4703395866526022</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.7077887863353418</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.07490160175482706</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.9287026153649001</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.562653335019688</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.2306487934472891</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.0337112024596091</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2492804957279751</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.769798281054071</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.8668864461621896</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.498389006025664</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-1.349735021969691</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.4080542579258601</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.4970009140285471</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.6609525609448234</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.5493593116445668</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.1810449958612162</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.334953234365394</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.4986663719909357</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.2796994974937367</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.1565108783026401</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.4009196688520903</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>MqhPmaA4</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-1.02209214759432</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D18" t="n">
         <v>-0.9701543789389947</v>
       </c>
-      <c r="E11" t="n">
-        <v>0.3116859600145848</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.45775979117065</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.3967663726677186</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.214671682308225</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.004744089072898</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.4691175689622648</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.4839228060945257</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-1.198609487371789</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-0.6985187187647576</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-0.1503038707153752</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.86686155089011</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.574939511061436</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.039524319543907</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.9029116838657384</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.03772609762708</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.8833444599046752</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-0.2096506170545038</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.09180283091437785</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-0.3687174316712288</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.2506753586238117</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-0.1626816169637894</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-0.3237592062489141</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-0.7685115467158237</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.5681378883163518</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-0.2693784068483752</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-0.4310762454089535</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>-0.4566620444239118</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>-0.1884970066768136</v>
+      <c r="E18" t="n">
+        <v>-2.162776715658261</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.13576101112763</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.528076638341711</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1.799052058545101</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-1.867185118372062</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.254389983098985</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.803289708943209</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.140896196685565</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.100179578071888</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-2.278344440484806</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-2.902645406125542</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-2.362531365047098</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-2.155339316889533</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-2.085853007634854</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.03304904018589225</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-1.343202134887139</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-2.459881403340371</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-2.670618858076608</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-2.447720609759295</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-2.016480454035931</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.6130922678992237</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1.477082948427729</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.1262968609656301</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.04735820502262236</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-2.231700861337217</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.863025678143175</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.9139959710060308</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-1.281832910514367</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>rc1ER8g2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-1.295573729659454</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.384890208722356</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.962983154863942</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.06280762420541915</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.651036891578524</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.559662203947852</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.666592559712929</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.7267897838682078</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.1110811642043075</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.1302049845464171</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.8872483995162379</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.1674035946304836</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.7678182772307358</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0225005533005822</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.07394757448180066</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.06576890032021188</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.7846296996278138</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.6075896159808647</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.006116505602496</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.993976798710649</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.003433416959683</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.9522981252377933</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.8058623221236154</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.634875988322218</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.2203744955462749</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0.5049628976775677</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.133361408354437</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.037533426639415</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.3938230253219264</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.9891872464595599</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>lb85TUOk</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.5662895108190968</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.06017762816284601</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.337450096763346</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.555950770706776</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5405335304605852</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.4449668371397055</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.2926328460981638</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.6894877563451811</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.8445308827436271</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.3299730209451889</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.4592442773077354</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.5879009456257088</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.205726356303696</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-0.2940582285892007</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.6564585039298432</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.2585591719002777</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.9502336476088371</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.9084888851251122</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.09539747922619775</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.4036812461826353</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.2046769985663481</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.06559695511991659</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.5649906544204181</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.2858287878034395</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.9237632524088422</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.9617153882839496</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.01873366902019095</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-0.3566696396414691</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.3366914997464936</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-0.02054696594029387</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>WIs9mjGL</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.803884200412066</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.5104376201607318</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1583044859820689</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.7575017826430527</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.7600093903054785</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.6515909870579915</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.5995394802454174</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.5603092396011971</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.4961904496206735</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.038992497946061</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.1360619339729076</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5282264164825606</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-2.727930476351588</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.3672193452459774</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.1569296250619967</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.7015420551803605</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.5311592667645909</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-1.01581883159542</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.5460327509559366</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-1.221244224316055</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.9264760321664484</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.7993234319820444</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.4004511711376257</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.8444807593706805</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.5267366392118765</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.627190817392419</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.004429378309771</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-0.6220673142012559</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.04796878620498991</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-0.6370869027805753</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-0.6217342856061951</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -588,1001 +588,1001 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ratYowuH</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1857848398600221</v>
+        <v>0.7783282676678127</v>
       </c>
       <c r="C2" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D2" t="n">
-        <v>1.711979734786432</v>
+        <v>0.6652932513813875</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.07537851978270592</v>
+        <v>-0.3282630013932666</v>
       </c>
       <c r="F2" t="n">
-        <v>1.372185249101586</v>
+        <v>0.7073491013767808</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4153601761688528</v>
+        <v>-0.5762568190230076</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09905950636552099</v>
+        <v>-0.6454922861923482</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7157328329328775</v>
+        <v>-0.5349647079360128</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.6602493996056947</v>
+        <v>-0.5250548461428289</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1662912122660022</v>
+        <v>0.8663608609743839</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.02914882139033629</v>
+        <v>-0.470841029796672</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4400540525813855</v>
+        <v>0.2246292077175239</v>
       </c>
       <c r="N2" t="n">
-        <v>1.719974038490435</v>
+        <v>-0.5759119846692612</v>
       </c>
       <c r="O2" t="n">
-        <v>1.446384495339175</v>
+        <v>-0.4255093809055674</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3504317102956003</v>
+        <v>0.2826858534839655</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6035798367066932</v>
+        <v>-0.0208726339255532</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0997907129519882</v>
+        <v>0.355675982503712</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8792408238369648</v>
+        <v>-0.3968173706165243</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4475890035631093</v>
+        <v>-1.421553738407041</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01800046958340282</v>
+        <v>-0.908961936228468</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4275110494556814</v>
+        <v>-1.745758012053236</v>
       </c>
       <c r="W2" t="n">
-        <v>0.09877569991540876</v>
+        <v>-0.06210976122228763</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4211981583017939</v>
+        <v>-0.2265136251081935</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.247770210864535</v>
+        <v>-1.268832891659239</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2789823241599825</v>
+        <v>-0.6536182283424994</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1634581678026226</v>
+        <v>0.5492813827451765</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.711309731794062</v>
+        <v>0.1771753842962733</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.235714991325834</v>
+        <v>-0.8000806501078945</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.6377747094340845</v>
+        <v>0.237442017861776</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.2361232034844174</v>
+        <v>0.003568413647108136</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.3621267448219476</v>
+        <v>-0.2269254977000457</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zil0kCo9</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9150690587003798</v>
+        <v>-0.7106270124645843</v>
       </c>
       <c r="C3" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6980022039877951</v>
+        <v>1.109200465325491</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05799937136210505</v>
+        <v>-0.08445434869738699</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009600273071539713</v>
+        <v>0.8201925776525614</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.005908922544012559</v>
+        <v>-0.1744315691344863</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.268799922393901</v>
+        <v>-0.742550567340263</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02013563233949705</v>
+        <v>-0.6282018062470268</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3866683145667162</v>
+        <v>0.3800785639951905</v>
       </c>
       <c r="K3" t="n">
-        <v>1.267919340560541</v>
+        <v>1.13849208116885</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8985320629996317</v>
+        <v>-0.2397471923326819</v>
       </c>
       <c r="M3" t="n">
-        <v>1.027403060900586</v>
+        <v>-0.2554861475450354</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2573208018038399</v>
+        <v>0.9227081348866761</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2554650285129936</v>
+        <v>-0.4045455935709295</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8476747284238446</v>
+        <v>0.06586476999781275</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.7903514980685044</v>
+        <v>-0.5195741628723496</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.8126124439911041</v>
+        <v>0.2088667061775013</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5291334051665519</v>
+        <v>0.5490707647693822</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3223040137763352</v>
+        <v>-1.24002626094509</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.01928675247335356</v>
+        <v>1.242917260886572</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8020512897307581</v>
+        <v>1.414491279833482</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.5599597105124802</v>
+        <v>1.186901957414323</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3448670358373326</v>
+        <v>0.8737865065880689</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.623612051501379</v>
+        <v>-0.1257226890984484</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1205186837991969</v>
+        <v>0.9931705057691785</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.055408385995511</v>
+        <v>0.9587156834883105</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.6693434287558944</v>
+        <v>-1.233689304124005</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.03424516781839072</v>
+        <v>0.9716491921689511</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.1202848520556815</v>
+        <v>0.6544188946841349</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.287781413695603</v>
+        <v>1.031919971795469</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.1751744114512535</v>
+        <v>1.06753334615193</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>drzevnw8</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.621563145701976</v>
+        <v>0.7783282676678127</v>
       </c>
       <c r="C4" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8288380144134257</v>
+        <v>-0.09791564276812444</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5414429275731417</v>
+        <v>-0.1482482472740131</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3650572233402474</v>
+        <v>-0.2361477419290482</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0758994536541935</v>
+        <v>0.008331172166238946</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1659528314781421</v>
+        <v>-0.7148443300303938</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2209129025195951</v>
+        <v>-0.7962118306549325</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4248740932414976</v>
+        <v>1.297338501673367</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2385223243875622</v>
+        <v>0.2488703793126086</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.9135796396663992</v>
+        <v>0.5357977171514796</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5023275887638617</v>
+        <v>0.9837769409007847</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5750282671496987</v>
+        <v>-0.08436458545491363</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3072148967728703</v>
+        <v>-1.178123256885411</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1075920967911095</v>
+        <v>-1.06883223357972</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4371002148650466</v>
+        <v>-0.93553804702183</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5626935575479751</v>
+        <v>-0.8072514310915512</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2098837170417481</v>
+        <v>0.5882827532177429</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4580617426474527</v>
+        <v>-0.8760626590261049</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7312780495429753</v>
+        <v>-0.8435038304468575</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7244490745394321</v>
+        <v>-1.618252649417393</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6605906616847567</v>
+        <v>-0.8680478513157844</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07138142392331673</v>
+        <v>-0.8588194644214232</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.2667377134641054</v>
+        <v>-0.1582449315074819</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5537168660370341</v>
+        <v>-0.6947751480085904</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4353647367351179</v>
+        <v>-1.345441322805287</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.2630194350448479</v>
+        <v>-0.0305824680815478</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1131219148657989</v>
+        <v>-0.8553933579867052</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.6455005471731087</v>
+        <v>-0.3032602317592377</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3396792660844009</v>
+        <v>-0.367545689985119</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5039639889154413</v>
+        <v>-0.7245686641050956</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EJ4unbdE</t>
+          <t>CzO2kX26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.621563145701976</v>
+        <v>-0.7106270124645843</v>
       </c>
       <c r="C5" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7193857422898694</v>
+        <v>1.755591671594976</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5715442748414014</v>
+        <v>0.07945456761507648</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.052382220323859</v>
+        <v>0.8389998236985244</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8599489942674013</v>
+        <v>-0.02649875942123526</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1539717668865676</v>
+        <v>0.1916871811630453</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2484613065034916</v>
+        <v>0.01040153379918988</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6118935581789867</v>
+        <v>-0.324594901818106</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9674017878333571</v>
+        <v>0.1016616637513949</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8390610531181056</v>
+        <v>-1.665676538624216</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2037445609368442</v>
+        <v>-1.647748999820065</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4440334141483391</v>
+        <v>1.761935401838001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8282739340240383</v>
+        <v>1.820961310286398</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.841892832864213</v>
+        <v>0.7163280204562711</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6105747788008796</v>
+        <v>0.5982937664875597</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.020867175858341</v>
+        <v>1.418806079045765</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3792789471516898</v>
+        <v>-1.3155290992628</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07604795065405834</v>
+        <v>-1.078343185141165</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3095405665310667</v>
+        <v>1.665579871614842</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1129287800454895</v>
+        <v>2.114124596476245</v>
       </c>
       <c r="W5" t="n">
-        <v>0.23029630080701</v>
+        <v>1.875730758113612</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.125609253133336</v>
+        <v>1.00831697782079</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6132718912444551</v>
+        <v>-0.08310481034830999</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.2714007527640437</v>
+        <v>1.519838053456566</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.3474390329902952</v>
+        <v>0.7321355000714502</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7796731561919507</v>
+        <v>0.1563995990584917</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.2825040143722063</v>
+        <v>1.057147595216443</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.2633666083830339</v>
+        <v>1.228186344877696</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3847411174558864</v>
+        <v>1.521549875184158</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.09087493975538857</v>
+        <v>1.267865148687005</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>MqhPmaA4</t>
+          <t>0zTMbytK</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6491841872481661</v>
+        <v>-1.143639517401047</v>
       </c>
       <c r="C6" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.397747708326861</v>
+        <v>1.428502145530899</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.010839917950736</v>
+        <v>2.22002534728812</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.010692824921973</v>
+        <v>0.1149208509289347</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.509459490454511</v>
+        <v>1.692158027632822</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.705552209595415</v>
+        <v>1.411612109420736</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.720770452753947</v>
+        <v>0.8511281369574344</v>
       </c>
       <c r="J6" t="n">
-        <v>1.252154868368715</v>
+        <v>-0.007290448248431612</v>
       </c>
       <c r="K6" t="n">
-        <v>1.820427262480837</v>
+        <v>-0.6413553978309834</v>
       </c>
       <c r="L6" t="n">
-        <v>2.140896196685565</v>
+        <v>-0.5294550227692565</v>
       </c>
       <c r="M6" t="n">
-        <v>2.100179578071888</v>
+        <v>-0.477733681029558</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.278344440484806</v>
+        <v>0.59301170858437</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.855657795680992</v>
+        <v>-0.8151255669701054</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.397222738404883</v>
+        <v>0.1959574200895044</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.168106381571071</v>
+        <v>0.6877409074085136</v>
       </c>
       <c r="R6" t="n">
-        <v>-2.085853007634854</v>
+        <v>0.4158842812217645</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03304904018589225</v>
+        <v>0.809235415584542</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.310620279958071</v>
+        <v>0.1577353155119365</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.302856509051185</v>
+        <v>1.105671265430506</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.520322047118962</v>
+        <v>0.9018833464015497</v>
       </c>
       <c r="W6" t="n">
-        <v>-2.733143799100451</v>
+        <v>1.503222780796768</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.115043306779678</v>
+        <v>0.5010323806885311</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.5444393921810751</v>
+        <v>0.2305905145011682</v>
       </c>
       <c r="Z6" t="n">
-        <v>-1.350284133412192</v>
+        <v>0.6855194905833772</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1604052622827278</v>
+        <v>0.1880276454613509</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.5205424530443407</v>
+        <v>-1.543437374941841</v>
       </c>
       <c r="AC6" t="n">
-        <v>-2.101797082564819</v>
+        <v>0.3373293882238026</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.880159744216187</v>
+        <v>0.8389724736677208</v>
       </c>
       <c r="AE6" t="n">
-        <v>-1.007613528033478</v>
+        <v>0.5177890277576769</v>
       </c>
       <c r="AF6" t="n">
-        <v>-1.213409064176414</v>
+        <v>0.6063646661480244</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>lb85TUOk</t>
+          <t>6HqKvGll</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.7106270124645843</v>
+        <v>0.6491841872481661</v>
       </c>
       <c r="C7" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.01614326125210533</v>
+        <v>-0.4250051688322006</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3619288626675704</v>
+        <v>-1.453023937651772</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5208439114209774</v>
+        <v>-0.8998868003011723</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5693449027076276</v>
+        <v>-1.152486905270444</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3364319894377956</v>
+        <v>-1.540311693133643</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1999405691641128</v>
+        <v>-1.213420679383858</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3465005314823001</v>
+        <v>1.108195630740843</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7827901016304885</v>
+        <v>1.270924659661417</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3299730209451889</v>
+        <v>1.037330119967268</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4592442773077354</v>
+        <v>1.393370405326119</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5879009456257088</v>
+        <v>-1.307238603012559</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1102090709791568</v>
+        <v>-2.073241514041097</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2882763330295703</v>
+        <v>-1.198924883671411</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.6289000779474756</v>
+        <v>-0.8071911734804359</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2585591719002777</v>
+        <v>-0.9746799878006566</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9502336476088371</v>
+        <v>-0.1153822636328267</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8892683286879642</v>
+        <v>-1.421553738407042</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07758304887758459</v>
+        <v>-2.413168302621622</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.353343368670943</v>
+        <v>-2.173001705449986</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.2004432995174944</v>
+        <v>-2.495277488534679</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0723499158107412</v>
+        <v>-1.796227629383244</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.6018067545706146</v>
+        <v>-0.8260393648928143</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.2226544503684928</v>
+        <v>-1.631721689343375</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9967343310857317</v>
+        <v>0.9345879059895342</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.4404320495905146</v>
+        <v>0.4181744930545533</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.02631839850308107</v>
+        <v>-1.977300023225709</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.308418056151214</v>
+        <v>-0.9564729897502658</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.3345679360255055</v>
+        <v>-0.5007830283658187</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.05259851681580107</v>
+        <v>-1.010493645524312</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rc1ER8g2</t>
+          <t>nX2mpxRQ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.803884200412066</v>
+        <v>0.6491841872481661</v>
       </c>
       <c r="C8" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D8" t="n">
-        <v>1.384890208722356</v>
+        <v>1.187078923912176</v>
       </c>
       <c r="E8" t="n">
-        <v>1.962983154863942</v>
+        <v>-0.1399926981595248</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.06280762420541915</v>
+        <v>-0.5778127117640497</v>
       </c>
       <c r="G8" t="n">
-        <v>1.651036891578524</v>
+        <v>-0.6376830450018508</v>
       </c>
       <c r="H8" t="n">
-        <v>1.559662203947852</v>
+        <v>0.05467939373041657</v>
       </c>
       <c r="I8" t="n">
-        <v>1.666592559712929</v>
+        <v>0.03339967870211372</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7267897838682078</v>
+        <v>1.768288155098076</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1110811642043075</v>
+        <v>1.952284705500575</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1302049845464171</v>
+        <v>-0.4739678036461555</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8872483995162379</v>
+        <v>-0.4425134363465161</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1674035946304836</v>
+        <v>-0.5639230237128137</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7678182772307358</v>
+        <v>0.7333157584576944</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0225005533005822</v>
+        <v>0.308497887232317</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.07394757448180066</v>
+        <v>0.2291898100714608</v>
       </c>
       <c r="R8" t="n">
-        <v>0.06576890032021188</v>
+        <v>0.03401520853055402</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7846296996278138</v>
+        <v>-0.863522613046371</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6075896159808647</v>
+        <v>-0.4634920518022974</v>
       </c>
       <c r="U8" t="n">
-        <v>1.841871907777894</v>
+        <v>-0.06927273943318903</v>
       </c>
       <c r="V8" t="n">
-        <v>1.888806900859483</v>
+        <v>0.01648697385412448</v>
       </c>
       <c r="W8" t="n">
-        <v>2.119024977642224</v>
+        <v>-0.283015080433679</v>
       </c>
       <c r="X8" t="n">
-        <v>0.9914057348465848</v>
+        <v>-0.1178090173886535</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.89813513212451</v>
+        <v>0.02321953893675189</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.517121114855579</v>
+        <v>-0.1884837455104197</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.3053085993536674</v>
+        <v>1.101684051394983</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.8332832613594819</v>
+        <v>0.2593971282979177</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.058471637540027</v>
+        <v>0.06125663468500667</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.03133306522302</v>
+        <v>-0.7547858968425872</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.4631239986794368</v>
+        <v>0.07772123231157055</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.8724954178201277</v>
+        <v>0.06863027063142205</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>21YvrUwq</t>
+          <t>YTzyyYmD</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4516697113122358</v>
+        <v>1.332888142411001</v>
       </c>
       <c r="C9" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2400768674980878</v>
+        <v>0.01111419925323443</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9448141498182684</v>
+        <v>0.2727908442317001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3195265327328189</v>
+        <v>-0.4336238254116639</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6101494257233321</v>
+        <v>-0.06321641273443976</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2227205969118803</v>
+        <v>0.3232073049063131</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6795428132885346</v>
+        <v>-0.07794618529282328</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7513315119286</v>
+        <v>0.5717194645678999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4703395866526022</v>
+        <v>0.1418057869042686</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7077887863353418</v>
+        <v>0.5341032707342497</v>
       </c>
       <c r="M9" t="n">
-        <v>0.07490160175482706</v>
+        <v>0.7274081400532177</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9287026153649001</v>
+        <v>0.5870172281061461</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.562653335019688</v>
+        <v>-0.8244946249893161</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2306487934472891</v>
+        <v>-0.9046676989402043</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.0337112024596091</v>
+        <v>-0.5881170912429429</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2492804957279751</v>
+        <v>-0.6126054242770251</v>
       </c>
       <c r="S9" t="n">
-        <v>1.769798281054071</v>
+        <v>1.225709439390275</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8668864461621896</v>
+        <v>-0.1799924635114394</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4878473115658875</v>
+        <v>0.4286088995054225</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.362062034541165</v>
+        <v>-0.1499057983462734</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.4253972458690844</v>
+        <v>0.03083445621772613</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5322787397503059</v>
+        <v>-0.08030794999813909</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.5867047147867688</v>
+        <v>-0.9927856782225273</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.5298318743988453</v>
+        <v>0.3216583922911376</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1424702860080868</v>
+        <v>-0.6023546703262854</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.6474636137697007</v>
+        <v>-0.3384418311504906</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.4696885181784218</v>
+        <v>0.05608280709395445</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.2977242596441153</v>
+        <v>-0.08349678403161415</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.1281640047984124</v>
+        <v>-0.2925553304567894</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.4091164128816826</v>
+        <v>0.4765629448169624</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OGMmt88e</t>
+          <t>K0RAmBXI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.6650467487870619</v>
+        <v>1.287307878733479</v>
       </c>
       <c r="C10" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8883819974229756</v>
+        <v>-0.2069454847894832</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6354098031409698</v>
+        <v>-0.4506149868701062</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9777801443415373</v>
+        <v>-0.4994491865725355</v>
       </c>
       <c r="G10" t="n">
-        <v>0.649739694877796</v>
+        <v>-0.4785047035581378</v>
       </c>
       <c r="H10" t="n">
-        <v>1.068309074021186</v>
+        <v>0.2157188801126526</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5722145347587083</v>
+        <v>0.1361960380123933</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7353351752478134</v>
+        <v>1.000567742184335</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4761768334058522</v>
+        <v>1.26280208008824</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.000783399794436</v>
+        <v>-0.6813996181921941</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6629317611683064</v>
+        <v>0.03672839443886585</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1383149097589276</v>
+        <v>-0.89361945001512</v>
       </c>
       <c r="O10" t="n">
-        <v>1.844649702387148</v>
+        <v>0.190282303001522</v>
       </c>
       <c r="P10" t="n">
-        <v>1.613967306088943</v>
+        <v>0.7221099160159018</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.257193173504193</v>
+        <v>0.174359826930213</v>
       </c>
       <c r="R10" t="n">
-        <v>1.001884229703633</v>
+        <v>0.5907357788687122</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2212174200692223</v>
+        <v>-0.8837263378798307</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3270558583852555</v>
+        <v>-0.03992793772441061</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1972002999566385</v>
+        <v>0.4956155393086976</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2136172608133803</v>
+        <v>0.9655445733942287</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.2459425192077598</v>
+        <v>0.5442903396540824</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1104243281917268</v>
+        <v>0.8570289059729262</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.145058075140203</v>
+        <v>-0.2757693098752853</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.5965193917122854</v>
+        <v>0.5412786889262738</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.4700590981354745</v>
+        <v>0.005721716279259633</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.1378610682184524</v>
+        <v>-0.603616399094544</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.01270080011264536</v>
+        <v>0.6253094087078663</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.3681353520408953</v>
+        <v>0.5191954863850199</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.4440398379036832</v>
+        <v>0.3276890624126957</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.2882166124490478</v>
+        <v>0.4177465960630634</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>WIs9mjGL</t>
+          <t>0d4cBEPP</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7783282676678127</v>
+        <v>1.287307878733479</v>
       </c>
       <c r="C11" t="n">
         <v>-0.5104376201607318</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6757738054813258</v>
+        <v>-0.6352770070162499</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9402600450283892</v>
+        <v>-1.295206719816887</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.07816687514295573</v>
+        <v>-0.4618346944806089</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8051510255790106</v>
+        <v>-1.448194293097915</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6378442570731925</v>
+        <v>-0.4147253580302178</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5601663960249844</v>
+        <v>-0.7646614004638097</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3457361842461493</v>
+        <v>0.4521551728308131</v>
       </c>
       <c r="K11" t="n">
-        <v>1.210014593824897</v>
+        <v>1.819268418915874</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1360619339729076</v>
+        <v>1.222540830317648</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5282264164825606</v>
+        <v>1.243646801850448</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.727930476351588</v>
+        <v>-1.723854996249109</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4916730161531627</v>
+        <v>-2.169633052935017</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5845984804606456</v>
+        <v>-1.74510751778653</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.8417824574958371</v>
+        <v>-1.62277033303109</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.5311592667645909</v>
+        <v>-1.241081090347657</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.01581883159542</v>
+        <v>-1.061228722365096</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5449466891249679</v>
+        <v>-0.3192437804398117</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.028173251736561</v>
+        <v>0.3465570814303626</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7907938800004367</v>
+        <v>0.1731823673560536</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.8252500179791935</v>
+        <v>0.5266429984592721</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.4201518806085281</v>
+        <v>0.2682157369455356</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.8091571822958388</v>
+        <v>0.1310682687801015</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.4190356906143187</v>
+        <v>0.665129235040813</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.658891990333461</v>
+        <v>0.9580763806252065</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.393621292318985</v>
+        <v>0.6331094348781394</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.5511691315067533</v>
+        <v>0.1254180922670381</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.05575483680798804</v>
+        <v>0.6675421648305755</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.6102596267502939</v>
+        <v>0.536125406618119</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.5369499360944968</v>
+        <v>0.6602700652322432</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_selected_nan.xlsx
@@ -425,1164 +425,2424 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF11"/>
+  <dimension ref="A1:AP18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_120_matches_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_480_matches_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_120_matches_goal_attempts</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_goal_attempts</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_goals</t>
+          <t>dif_mean_last_60_matches_expected_points</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_points</t>
+          <t>dif_mean_last_360_matches_expected_points</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goal_ratio</t>
+          <t>dif_mean_last_60_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_goal_ratio</t>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_PPS</t>
+          <t>dif_mean_last_360_matches_goal_attempts</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_PPS</t>
+          <t>dif_mean_last_60_matches_goals</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_dangerous_attacks</t>
+          <t>dif_mean_last_360_matches_goals</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_dead_balls</t>
+          <t>dif_mean_last_60_matches_goal_ratio</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_ball_possession</t>
+          <t>dif_mean_last_360_matches_attacks</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_ball_possession</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_total_passes</t>
+          <t>dif_mean_last_60_matches_dead_balls</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_KGP</t>
+          <t>dif_mean_last_360_matches_dead_balls</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_clean_sheet</t>
+          <t>dif_mean_last_60_matches_total_passes</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_value_player_start</t>
+          <t>dif_mean_last_360_matches_total_passes</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rep_player_start</t>
+          <t>dif_mean_last_60_matches_yellow_cards</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_value_player_sub</t>
+          <t>dif_mean_last_360_matches_yellow_cards</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_wage_player_sub</t>
+          <t>dif_mean_last_360_matches_red_cards</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_60_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_KGP</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CEnSxfJ0</t>
+          <t>A7iT11hT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7783282676678127</v>
+        <v>0.6894027384646061</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.5104376201607318</v>
+        <v>0.1795023569298023</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6652932513813875</v>
+        <v>-0.0681151766362503</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3282630013932666</v>
+        <v>1.319611696716479</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7073491013767808</v>
+        <v>-1.158481543367365</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5762568190230076</v>
+        <v>-0.4820187906012299</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6454922861923482</v>
+        <v>-0.1957970479676819</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5349647079360128</v>
+        <v>5.220175967230073</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.5250548461428289</v>
+        <v>0.6269284946415252</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8663608609743839</v>
+        <v>0.6607426104219161</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.470841029796672</v>
+        <v>1.593153451392299</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2246292077175239</v>
+        <v>0.08542546265382478</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5759119846692612</v>
+        <v>1.129310697742173</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4255093809055674</v>
+        <v>-0.009611125010202224</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2826858534839655</v>
+        <v>1.124462315813819</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.0208726339255532</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.355675982503712</v>
+        <v>-0.05872697770887352</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3968173706165243</v>
+        <v>2.021830385115078</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.421553738407041</v>
+        <v>-0.3364638224066921</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.908961936228468</v>
+        <v>0.607164824035659</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.745758012053236</v>
+        <v>0.6478351550971611</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.06210976122228763</v>
+        <v>-0.9218700675349086</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2265136251081935</v>
+        <v>-0.4326663634887347</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.268832891659239</v>
+        <v>0.7022342820357763</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.6536182283424994</v>
+        <v>-0.8445077446595369</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.5492813827451765</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1771753842962733</v>
+        <v>1.407589984079535</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.8000806501078945</v>
+        <v>0.3573834007217855</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.237442017861776</v>
+        <v>0.4601838972271619</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.003568413647108136</v>
+        <v>0.2052619542522571</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.2269254977000457</v>
+        <v>0.4574746543690031</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-1.496636113896387</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1.43585115520288</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.9537670179143306</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.9058597755722564</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.5490804872443256</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2128843022365209</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.2877292949206706</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.2263349733766062</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.5542776771393644</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.1024947670298163</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>KK9ggF3s</t>
+          <t>Cl3y4WHa</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.7106270124645843</v>
+        <v>1.052099735891195</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.5104376201607318</v>
+        <v>0.6694939586223988</v>
       </c>
       <c r="D3" t="n">
-        <v>1.109200465325491</v>
+        <v>0.02575743981375442</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.08445434869738699</v>
+        <v>0.4433758847256623</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8201925776525614</v>
+        <v>0.6428430194469238</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1744315691344863</v>
+        <v>-0.4820187906012299</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.742550567340263</v>
+        <v>1.800903853486129</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6282018062470268</v>
+        <v>3.201452688997454</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3800785639951905</v>
+        <v>0.5803110122558517</v>
       </c>
       <c r="K3" t="n">
-        <v>1.13849208116885</v>
+        <v>1.349684577576447</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2397471923326819</v>
+        <v>1.471309185953442</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2554861475450354</v>
+        <v>0.2868577150968587</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9227081348866761</v>
+        <v>1.104974346897268</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4045455935709295</v>
+        <v>0.1481468148516399</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06586476999781275</v>
+        <v>1.750129739647289</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.5195741628723496</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2088667061775013</v>
+        <v>2.086059031798885</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5490707647693822</v>
+        <v>1.417036113417153</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.24002626094509</v>
+        <v>1.508749233388108</v>
       </c>
       <c r="U3" t="n">
-        <v>1.242917260886572</v>
+        <v>1.103250233397017</v>
       </c>
       <c r="V3" t="n">
-        <v>1.414491279833482</v>
+        <v>0.9798955340750579</v>
       </c>
       <c r="W3" t="n">
-        <v>1.186901957414323</v>
+        <v>0.2649887423643282</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8737865065880689</v>
+        <v>0.2134746486115841</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.1257226890984484</v>
+        <v>0.8281591361341448</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.9931705057691785</v>
+        <v>-0.7945622202207518</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.9587156834883105</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.233689304124005</v>
+        <v>1.079305145374108</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.9716491921689511</v>
+        <v>-0.2544374588471485</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.6544188946841349</v>
+        <v>0.1710503550627463</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.031919971795469</v>
+        <v>-0.3801171740191338</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.06753334615193</v>
+        <v>-0.6317199665188404</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.2890216745729695</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-1.022977919022557</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.816615566059228</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>2.044069599386862</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.289855218990105</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.9167057996902652</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.015081747609168</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.092926261256315</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>2.826675482258798</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.1955228407399524</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hY71igYg</t>
+          <t>v3JHq2Wp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7783282676678127</v>
+        <v>1.036330301220474</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.5104376201607318</v>
+        <v>-0.6073110804035017</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.09791564276812444</v>
+        <v>1.757707213316341</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1482482472740131</v>
+        <v>-1.060828925858573</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2361477419290482</v>
+        <v>1.190445686542468</v>
       </c>
       <c r="G4" t="n">
-        <v>0.008331172166238946</v>
+        <v>-0.4820187906012299</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7148443300303938</v>
+        <v>-1.526930982270223</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7962118306549325</v>
+        <v>2.251341888956544</v>
       </c>
       <c r="J4" t="n">
-        <v>1.297338501673367</v>
+        <v>2.072070448597402</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2488703793126086</v>
+        <v>0.738369874326652</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5357977171514796</v>
+        <v>0.4829122339604081</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9837769409007847</v>
+        <v>0.4882899675398927</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.08436458545491363</v>
+        <v>0.2358649314343915</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.178123256885411</v>
+        <v>0.03250966359849915</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.06883223357972</v>
+        <v>0.5601029025747437</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.93553804702183</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.8072514310915512</v>
+        <v>0.8828863923189237</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5882827532177429</v>
+        <v>-0.7430740420372264</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8760626590261049</v>
+        <v>-0.4527666446289328</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8435038304468575</v>
+        <v>-0.3605326761134896</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.618252649417393</v>
+        <v>1.09058232706769</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.8680478513157844</v>
+        <v>1.014345636233852</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8588194644214232</v>
+        <v>-0.7557368695388939</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.1582449315074819</v>
+        <v>0.01537144149921882</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.6947751480085904</v>
+        <v>0.5476554799545214</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.345441322805287</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.0305824680815478</v>
+        <v>0.300331032962728</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.8553933579867052</v>
+        <v>-0.2544374588471485</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.3032602317592377</v>
+        <v>1.072976510178083</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.367545689985119</v>
+        <v>1.055741805059653</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.7245686641050956</v>
+        <v>1.788624748304793</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.6391062889583893</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.9338485507056188</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.37894114669549</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2867757029557106</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.4791272990551904</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.2768919904421744</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.4955442814030983</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.2224409096987214</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.07758060647919411</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.5381410360934383</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CzO2kX26</t>
+          <t>WveT5hmm</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.7106270124645843</v>
+        <v>1.020560866549753</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.5104376201607318</v>
+        <v>-0.3340465333057074</v>
       </c>
       <c r="D5" t="n">
-        <v>1.755591671594976</v>
+        <v>-1.692111441221332</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07945456761507648</v>
+        <v>1.319611696716479</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8389998236985244</v>
+        <v>1.637174178120411</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.02649875942123526</v>
+        <v>-0.4820187906012299</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1916871811630453</v>
+        <v>2.466470820637399</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01040153379918988</v>
+        <v>3.069617699398589</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.324594901818106</v>
+        <v>0.9066333889555656</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1016616637513949</v>
+        <v>0.2337926589458691</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.665676538624216</v>
+        <v>-0.08207438934662563</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.647748999820065</v>
+        <v>1.092586724868994</v>
       </c>
       <c r="N5" t="n">
-        <v>1.761935401838001</v>
+        <v>0.2301299424985674</v>
       </c>
       <c r="O5" t="n">
-        <v>1.820961310286398</v>
+        <v>0.3240904016996861</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7163280204562711</v>
+        <v>-0.9910323330117164</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5982937664875597</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.418806079045765</v>
+        <v>-0.686469224394071</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3155290992628</v>
+        <v>-1.328063279663557</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.078343185141165</v>
+        <v>-0.8098038031714039</v>
       </c>
       <c r="U5" t="n">
-        <v>1.665579871614842</v>
+        <v>-1.6754465794638</v>
       </c>
       <c r="V5" t="n">
-        <v>2.114124596476245</v>
+        <v>0.09440119013399963</v>
       </c>
       <c r="W5" t="n">
-        <v>1.875730758113612</v>
+        <v>0.4497968661970281</v>
       </c>
       <c r="X5" t="n">
-        <v>1.00831697782079</v>
+        <v>1.182686166762062</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.08310481034830999</v>
+        <v>1.205933698429251</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.519838053456566</v>
+        <v>0.5180884312217285</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7321355000714502</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1563995990584917</v>
+        <v>-1.077864968745645</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.057147595216443</v>
+        <v>-0.2544374588471485</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.228186344877696</v>
+        <v>-0.05221878946576001</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.521549875184158</v>
+        <v>0.599765317784333</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.267865148687005</v>
+        <v>0.2472509251187943</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.7749288398011804</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.3512171111082203</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.5130939875736725</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0.1711401377742283</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-2.390178503856492</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.564622495475526</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.1798544246647921</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.2241523490879156</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.3769670911038702</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.1348843200331923</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0zTMbytK</t>
+          <t>69B375Oi</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.143639517401047</v>
+        <v>0.6894027384646061</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.5104376201607318</v>
+        <v>-1.493065129617041</v>
       </c>
       <c r="D6" t="n">
-        <v>1.428502145530899</v>
+        <v>0.7861256330587926</v>
       </c>
       <c r="E6" t="n">
-        <v>2.22002534728812</v>
+        <v>-0.6957306708623997</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1149208509289347</v>
+        <v>1.464247020090239</v>
       </c>
       <c r="G6" t="n">
-        <v>1.692158027632822</v>
+        <v>-0.4820187906012299</v>
       </c>
       <c r="H6" t="n">
-        <v>1.411612109420736</v>
+        <v>1.800903853486129</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8511281369574344</v>
+        <v>1.697709838885401</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.007290448248431612</v>
+        <v>1.559278142354994</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6413553978309834</v>
+        <v>0.8548107701837557</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5294550227692565</v>
+        <v>0.648844697155723</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.477733681029558</v>
+        <v>-0.01529066356769206</v>
       </c>
       <c r="N6" t="n">
-        <v>0.59301170858437</v>
+        <v>0.5924571192336356</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8151255669701054</v>
+        <v>0.04140325039599105</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1959574200895044</v>
+        <v>0.9160988214529836</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6877409074085136</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4158842812217645</v>
+        <v>1.552478122116467</v>
       </c>
       <c r="S6" t="n">
-        <v>0.809235415584542</v>
+        <v>2.112578649189431</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1577353155119365</v>
+        <v>0.3375923192899511</v>
       </c>
       <c r="U6" t="n">
-        <v>1.105671265430506</v>
+        <v>0.5883425770966164</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9018833464015497</v>
+        <v>-0.01628560285863254</v>
       </c>
       <c r="W6" t="n">
-        <v>1.503222780796768</v>
+        <v>0.7395803022300484</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5010323806885311</v>
+        <v>-0.2711311104636549</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2305905145011682</v>
+        <v>-0.3051645507511747</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6855194905833772</v>
+        <v>-0.4999471053461635</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1880276454613509</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-1.543437374941841</v>
+        <v>0.2968359884780459</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.3373293882238026</v>
+        <v>-0.2544374588471485</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.8389724736677208</v>
+        <v>0.303225688623622</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.5177890277576769</v>
+        <v>-0.4443959733734467</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.6063646661480244</v>
+        <v>0.3493452825204169</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.3878610829260822</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.6446422620536756</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.08627463923856303</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0.4750479273183847</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.1117812658162</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.09371178933317759</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.5435306510090405</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-0.1291233210215858</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.1811097995836182</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.2088184788666846</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6HqKvGll</t>
+          <t>p21q2AnC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6491841872481661</v>
+        <v>0.6894027384646061</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.5104376201607318</v>
+        <v>0.06171591421523586</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4250051688322006</v>
+        <v>-1.185199312391306</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.453023937651772</v>
+        <v>-1.60117434325291</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8998868003011723</v>
+        <v>1.464247020090239</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.152486905270444</v>
+        <v>-0.4820187906012299</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.540311693133643</v>
+        <v>0.1369864356079532</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.213420679383858</v>
+        <v>2.699655759836774</v>
       </c>
       <c r="J7" t="n">
-        <v>1.108195630740843</v>
+        <v>0.5803110122558517</v>
       </c>
       <c r="K7" t="n">
-        <v>1.270924659661417</v>
+        <v>-0.3872254522920175</v>
       </c>
       <c r="L7" t="n">
-        <v>1.037330119967268</v>
+        <v>0.1048465040918673</v>
       </c>
       <c r="M7" t="n">
-        <v>1.393370405326119</v>
+        <v>-0.3677971053430013</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.307238603012559</v>
+        <v>-0.03927662191958746</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.073241514041097</v>
+        <v>1.378734386055914</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.198924883671411</v>
+        <v>0.2309035407990669</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.8071911734804359</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.9746799878006566</v>
+        <v>1.322305964998562</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1153822636328267</v>
+        <v>2.161272839668352</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.421553738407042</v>
+        <v>0.09373156301751064</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.413168302621622</v>
+        <v>0.9245457984731233</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.173001705449986</v>
+        <v>-1.123153532784955</v>
       </c>
       <c r="W7" t="n">
-        <v>-2.495277488534679</v>
+        <v>-0.7597830489463605</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.796227629383244</v>
+        <v>-0.7557368695388939</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.8260393648928143</v>
+        <v>-0.1906874106617486</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1.631721689343375</v>
+        <v>-2.241951524882328</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9345879059895342</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4181744930545533</v>
+        <v>0.7776360769200438</v>
       </c>
       <c r="AC7" t="n">
-        <v>-1.977300023225709</v>
+        <v>0.204428185829552</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.9564729897502658</v>
+        <v>0.1335411387819574</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.5007830283658187</v>
+        <v>-1.403403106814603</v>
       </c>
       <c r="AF7" t="n">
-        <v>-1.010493645524312</v>
+        <v>0.1726408219646706</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.3397861520577609</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.3226430855009102</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.02506655328671326</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.042836489414226</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.340625426091564</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.9631208352984897</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0.179854424664792</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.1204653167887104</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.1895460779802042</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.2428247339986122</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nX2mpxRQ</t>
+          <t>EubK3NNG</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6491841872481661</v>
+        <v>1.020560866549753</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.5104376201607318</v>
+        <v>-0.5790423341520057</v>
       </c>
       <c r="D8" t="n">
-        <v>1.187078923912176</v>
+        <v>-1.546608885723824</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1399926981595248</v>
+        <v>0.8960977209209177</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5778127117640497</v>
+        <v>0.7941542827233241</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6376830450018508</v>
+        <v>-0.4820187906012299</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05467939373041657</v>
+        <v>-2.192497949421493</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03339967870211372</v>
+        <v>3.113812383411845</v>
       </c>
       <c r="J8" t="n">
-        <v>1.768288155098076</v>
+        <v>-0.7715959769286783</v>
       </c>
       <c r="K8" t="n">
-        <v>1.952284705500575</v>
+        <v>-2.289093417958045</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4739678036461555</v>
+        <v>0.2155042970855186</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4425134363465161</v>
+        <v>-0.01529066356769206</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5639230237128137</v>
+        <v>0.698583146955885</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7333157584576944</v>
+        <v>2.365632628534313</v>
       </c>
       <c r="P8" t="n">
-        <v>0.308497887232317</v>
+        <v>0.6002191638953254</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2291898100714608</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03401520853055402</v>
+        <v>-0.8538671568434578</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.863522613046371</v>
+        <v>0.1669573304393636</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4634920518022974</v>
+        <v>-0.1651360090255416</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.06927273943318903</v>
+        <v>-0.7359818503377971</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01648697385412448</v>
+        <v>3.525691772905601</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.283015080433679</v>
+        <v>0.1711194997622004</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1178090173886535</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.02321953893675189</v>
+        <v>-1.541517663716978</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.1884837455104197</v>
+        <v>0.2389271822718395</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.101684051394983</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.2593971282979177</v>
+        <v>0.0855431440372859</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.06125663468500667</v>
+        <v>1.275114690075186</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.7547858968425872</v>
+        <v>0.9248881757708121</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.07772123231157055</v>
+        <v>1.168808080614269</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.06863027063142205</v>
+        <v>1.713019222518606</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.9371300134944283</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.4310047604970095</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.7683715979411188</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.987250582479161</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.918033156830658</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-1.360967471000279</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.2877292949206704</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.8006644252801841</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.1793616518576523</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.8780241809985685</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>YTzyyYmD</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.332888142411001</v>
+        <v>0.7524804771474911</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.5104376201607318</v>
+        <v>-1.540179706702868</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01111419925323443</v>
+        <v>0.673478493318787</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2727908442317001</v>
+        <v>1.692011916812576</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4336238254116639</v>
+        <v>0.6644589142006952</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.06321641273443976</v>
+        <v>-0.4820187906012299</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3232073049063131</v>
+        <v>3.398264574649178</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07794618529282328</v>
+        <v>1.581859841775398</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5717194645678999</v>
+        <v>0.9159568854327005</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1418057869042686</v>
+        <v>0.895565083733742</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5341032707342497</v>
+        <v>-0.63837909739669</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7274081400532177</v>
+        <v>0.7702951209601401</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5870172281061461</v>
+        <v>-0.5134372321996107</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8244946249893161</v>
+        <v>-0.1727975834324844</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9046676989402043</v>
+        <v>-0.5583474953966799</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.5881170912429429</v>
+        <v>0.316686939345585</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.6126054242770251</v>
+        <v>0.435096923016815</v>
       </c>
       <c r="S9" t="n">
-        <v>1.225709439390275</v>
+        <v>-0.3610862271397718</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1799924635114394</v>
+        <v>0.4651502533401508</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4286088995054225</v>
+        <v>0.0926665623940905</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1499057983462734</v>
+        <v>1.710428367826431</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03083445621772613</v>
+        <v>1.202589120381139</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.08030794999813909</v>
+        <v>-1.482645508151752</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.9927856782225273</v>
+        <v>1.020480731484381</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3216583922911376</v>
+        <v>0.5105196656270587</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.6023546703262854</v>
+        <v>-2.562402735252365</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.3384418311504906</v>
+        <v>-1.319643189548281</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.05608280709395445</v>
+        <v>0.204428185829552</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.08349678403161415</v>
+        <v>-1.113640302554279</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.2925553304567894</v>
+        <v>-0.290058723577411</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.4765629448169624</v>
+        <v>-1.264982429993584</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.554928457629129</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.7112946418816646</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.4729103435315196</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.7996053476352785</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-1.229821292286306</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.005992593778338733</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-1.06306811721511</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.6532642122031396</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-1.612454309877242</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.2426002462711455</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>K0RAmBXI</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.287307878733479</v>
+        <v>1.052099735891195</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.5104376201607318</v>
+        <v>1.211311595109405</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2069454847894832</v>
+        <v>-0.5844145671112763</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4506149868701062</v>
+        <v>1.692011916812576</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4994491865725355</v>
+        <v>-0.7477795430457068</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4785047035581378</v>
+        <v>-0.4820187906012299</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2157188801126526</v>
+        <v>-0.3289104413979358</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1361960380123933</v>
+        <v>0.2668058205267205</v>
       </c>
       <c r="J10" t="n">
-        <v>1.000567742184335</v>
+        <v>1.102426814975394</v>
       </c>
       <c r="K10" t="n">
-        <v>1.26280208008824</v>
+        <v>0.8780989493551766</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6813996181921941</v>
+        <v>-0.05715997533372812</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03672839443886585</v>
+        <v>0.9515841481588707</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.89361945001512</v>
+        <v>-0.1098962872804419</v>
       </c>
       <c r="O10" t="n">
-        <v>0.190282303001522</v>
+        <v>0.5998556599045174</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7221099160159018</v>
+        <v>-0.3434172593358135</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.174359826930213</v>
+        <v>1.082096005588654</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5907357788687122</v>
+        <v>-0.8078327254198769</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8837263378798307</v>
+        <v>-0.6027864816987824</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.03992793772441061</v>
+        <v>-0.04320563088932113</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4956155393086976</v>
+        <v>0.3209811603022875</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9655445733942287</v>
+        <v>0.6921098722942138</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5442903396540824</v>
+        <v>1.408370817337178</v>
       </c>
       <c r="X10" t="n">
-        <v>0.8570289059729262</v>
+        <v>1.182686166762062</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.2757693098752853</v>
+        <v>2.167541675180432</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.5412786889262738</v>
+        <v>1.565795722765817</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.005721716279259633</v>
+        <v>-0.8297464143993496</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.603616399094544</v>
+        <v>0.2943000896075941</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.6253094087078663</v>
+        <v>-0.5603478886316154</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.5191954863850199</v>
+        <v>-1.00673903615403</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.3276890624126957</v>
+        <v>-0.2407509392779962</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.4177465960630634</v>
+        <v>-0.1250540826380068</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.9663918663529319</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.8202079043326105</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-1.058425288338189</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.9828781606793079</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-1.113444540354396</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.03989135921844</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.3916367881618844</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.001125067701566</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.8730232791738108</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.6609120526493042</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>hY71igYg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.6894027384646061</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.04758154108948789</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.156922468036311</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.6081070896633179</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6644589142006952</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.4820187906012299</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.135336886334859</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3125468299614575</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4171498239059945</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01061427521975395</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.180972363615773</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.5890060937614096</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.5594204304521755</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.141181279747188</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.4032591425433368</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.1110388315993068</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.8059398419502586</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.8445070646409433</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.8428398934017065</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.3157747761192644</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.07020518002929352</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.240276840456079</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.169480159246283</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.4929482903942607</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.3573834007217855</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.8954481042252685</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.3272754072597839</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.1574857991589304</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-1.349184269607375</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.3991788545468081</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.1714038460649442</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-1.374001685924671</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.5426861602151002</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.3671234000104446</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0.6993918908708615</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0.6946110864433314</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.4580940948311019</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0.2998330331839612</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CzO2kX26</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.036330301220474</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.05135907079074794</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.504251148901329</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.60117434325291</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.7477795430457068</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.4820187906012299</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.597934664794558</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.327295179069098</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.797027302521928</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.29728617444075</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.1587474414827636</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.253732526823421</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.4605638666734744</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.4728818093261392</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.7107651224175279</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.409846426622551</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.3935228426076459</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.728390876375024</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.8225000538778424</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.981276935525346</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.7474532687905301</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1.287614390997606</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.4326663634887347</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.8144218793234135</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1.172086397829209</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.055873777405409</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.1406972244836636</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.6215299745885089</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.9030772020689403</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.5887786725893489</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.0825548310500024</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.7386887783391726</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.9519971801591647</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0.1591953836133188</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.731627924752598</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.5091806360925525</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.532162459140368</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.7553130145061331</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.530223383058771</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.788081494398843</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.23651638917876</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>0zTMbytK</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.020560866549753</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.914489759468697</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.04453196310375536</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.670106021512806</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.158481543367365</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.4820187906012299</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.1957970479676819</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.254209456392823</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.447396184629378</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.07465676794116088</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.91943595097182</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.6494357694943197</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.8804917791940571</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.03155766146384745</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.471689803578688</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.7540635486273389</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.8556842282958982</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.4385948894023112</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.09341892102228962</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.541436707235859</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.6146291171993715</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-1.287614390997606</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.7557368695388939</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.5112234029121419</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.717787854875678</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.471001738508735</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.508821829094847</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.2544374588471485</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.4389597772055726</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.5130485679741021</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.2302673206793452</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.1918843895399981</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.4469456041236764</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0.5426904900401006</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.238442496023627</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.005562689760128768</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.5229870533871275</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.3916367881618844</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.6920541280404783</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.793520176212959</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.8460564702162937</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6HqKvGll</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.6894027384646061</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.690946353377513</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.175953626133762</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.670106021512806</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5419688439293237</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.4820187906012299</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4697699191835883</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.2592157879727506</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.11895122352925</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.8529890357204322</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1.02251817232336</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.06564872667845048</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1.804768255940952</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.085797462607721</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1.135651780207585</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1.753631043758908</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-2.207924069667587</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.9598719608775207</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.7526091849508031</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.345161950950744</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.7914770021202771</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.6980804076868232</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.8281591361341448</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.40531595370785</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.6185287165063131</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.2544374588471485</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-1.648146634555523</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.7210787959959467</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.8234214220908881</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.9421445144418757</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.3768509127523889</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.3406706516602135</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-2.054031977140147</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.240946671806563</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.501079456741052</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.7553130145061331</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-1.635881986419588</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.6620446628604552</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.9551370174883351</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>nX2mpxRQ</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.6894027384646061</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.757840689304993</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.3497330259862644</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.6957306708623997</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5419688439293237</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.4820187906012299</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.732697607497908</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.2592157879727499</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.67116010008061</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.5347172537110152</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1.036038595250385</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.213446076334814</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.3539424777791774</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.511143270872378</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.5152437467890522</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.196757515661522</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.7589785259773967</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.5145476885850813</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.03784957225246024</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.5254448506247409</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.01985215082200349</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.5134339900012743</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-1.724681087860059</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.888410038383307</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.1264351415603432</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.9692042602907194</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.5791339705530348</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.6252391783256485</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.02347356366877566</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.110068768585566</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.2763137201231211</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.393030669502862</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.3553033812097693</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.2741244249876145</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.0805454128639988</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0.6993918908708615</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.1859829598046598</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.2731789131511548</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.7528042339529231</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
           <t>0d4cBEPP</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1.287307878733479</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.5104376201607318</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-0.6352770070162499</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-1.295206719816887</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.4618346944806089</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-1.448194293097915</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.4147253580302178</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-0.7646614004638097</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.4521551728308131</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.819268418915874</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.222540830317648</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.243646801850448</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-1.723854996249109</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-2.169633052935017</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-1.74510751778653</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-1.62277033303109</v>
-      </c>
-      <c r="R11" t="n">
-        <v>-1.241081090347657</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-1.061228722365096</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-0.3192437804398117</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.3465570814303626</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.1731823673560536</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.5266429984592721</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.2682157369455356</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.1310682687801015</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.665129235040813</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.9580763806252065</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.6331094348781394</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.1254180922670381</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.6675421648305755</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.536125406618119</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.6602700652322432</v>
+      <c r="B16" t="n">
+        <v>1.067869170561916</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7778574859198</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1524854720212608</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1.316397704355895</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.147213897034925</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.4820187906012299</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.1957970479676819</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-2.006490361659805</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.1888774471077602</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.07671639667307405</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1.224106510214339</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.1663648528999674</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.5518159514366789</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.3559701606583331</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-1.641120171584092</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1.526543056913236</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-1.178200650964143</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-1.295932134319416</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.5052904998260741</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.6741571105789728</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.5143761713254777</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.05783849151030078</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.7557368695388939</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.098855391126776</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.009472658129391</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.01161586975343213</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-1.38257800458391</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.204428185829552</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.2551907390371294</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.3187810692152863</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.1310220958219473</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.9657493951804331</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.4876320325063796</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.916967778766165</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.5700716502507719</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-1.014971904104317</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.5414223436497189</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.02796056181763574</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.6715697638440395</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.1843501944613611</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0.6740773362553896</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>K0RAmBXI</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.036330301220474</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.054899562718854</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.6125763520462777</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.6081070896633179</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.147213897034925</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.4820187906012299</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8025534027592236</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.855385841300434</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.2073711531704641</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.05730958069688996</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.278413534050073</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.116006789789209</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.3085119556094335</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.4576366188656098</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.5744583126472165</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-1.565308369753349</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.1567880812484627</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.6921283418706531</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.1757019578611415</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.311955913052955</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.5394101059342272</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.8625022781609727</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-1.557289033287329</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-1.205026239628235</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.8662583184160824</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.016495726341199</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.7492107651943727</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.2746830476015426</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.008674973729758654</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.9153568860863576</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.09307553767766345</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.13202011010487</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.6769670278288431</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.3318616372558218</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-1.06306811721511</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.5471476011476425</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.8295138246608822</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.5252557337155513</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>YTzyyYmD</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.020560866549753</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.172686005433421</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.494978946676322</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.316397704355895</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.190445686542468</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.4820187906012299</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8025534027592236</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.263250340371922</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.11895122352925</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.7171413238871446</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.06654473948307536</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.1663648528999674</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.4507373826251181</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.9621095890093645</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.1469915717933655</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1.089166447631482</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-1.586233111309522</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-1.117469319245684</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.9586213928966364</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.6934290819585942</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.1497445866303159</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.7395803022300484</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-1.078807375589053</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.8546548231804204</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.4733162634389951</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.1010079808651672</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.2493856605024195</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.7133031035238491</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.1250569112898741</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.5241508262809491</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.9897035958968443</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.6024149675454321</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.01011605168206115</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.3102555225298141</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.2899894050116215</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0.1622883947570498</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.2917285221382766</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>2.573694146227376</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.3265136747207321</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.252371335708408</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-0.07936602432869985</v>
       </c>
     </row>
   </sheetData>
